--- a/QUESTOES PROVA CRS.xlsx
+++ b/QUESTOES PROVA CRS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julião\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julião\Downloads\chobot-main (1)\chobot-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBFF6CF-EF77-4E67-BF08-48E649AC829A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93677F0-7413-4BA6-9521-4B1EE7CDC272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="495">
   <si>
     <t>ID</t>
   </si>
@@ -1362,15 +1362,6 @@
     <t>Segundo a Resolução Conjunta nº 4.220/12, de 28/06/2012 - Manual de Processos e Procedimentos Administrativos das Instituições Militares do Estado de Minas Gerais - MAPPA, marque a alternativa INCORRETA.</t>
   </si>
   <si>
-    <t>O elogio é a maior recompensa que a autoridade pode conceder ao seu subordinado sendo, preferencialmente, uma concessão individual. Apenas as assertivas I e II são verdadeiras.</t>
-  </si>
-  <si>
-    <t>O CEDMU, ao analisar a proposta de recompensa, emitirá parecer quanto ao mérito da ação ou atuação e quanto à existência dos requisitos exigidos na legislação pertinente. Apenas as assertivas I, III e IV são verdadeiras.</t>
-  </si>
-  <si>
-    <t>Havendo discordância entre o parecer do Conselho e a decisão do Comandante da Unidade quanto ao mérito da ação do militar indicado para recompensa, toda a documentação produzida será encaminhada à autoridade imediatamente superior, que decidirá sobre a concessão da recompensa. Apenas as assertivas II e III são verdadeiras.</t>
-  </si>
-  <si>
     <t>Considerando a Lei Estadual nº 5.301, de 16/10/1969, que contém o Estatuto dos Militares do Estado de Minas Gerais - EMEMG, marque a alternativa CORRETA.</t>
   </si>
   <si>
@@ -1583,6 +1574,190 @@
   </si>
   <si>
     <t>CODIGO DE PROCESSO PENAL MILITAR</t>
+  </si>
+  <si>
+    <t>O elogio é a maior recompensa que a autoridade pode conceder ao seu subordinado sendo, preferencialmente, uma concessão individual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O CEDMU, ao analisar a proposta de recompensa, emitirá parecer quanto ao mérito da ação ou atuação e quanto à existência dos requisitos exigidos na legislação pertinente. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havendo discordância entre o parecer do Conselho e a decisão do Comandante da Unidade quanto ao mérito da ação do militar indicado para recompensa, toda a documentação produzida será encaminhada à autoridade imediatamente superior, que decidirá sobre a concessão da recompensa. </t>
+  </si>
+  <si>
+    <t>Análise das Assertivas
+(F) "Um dos objetivos da Diretriz é extinguir o número de mortes e lesões graves em policiais militares em serviço, não realizando operações e ações policiais de risco, através da implementação de uma política de segurança individual e coletiva."
+• Por que é FALSA: O texto da norma não fala em "não realizar operações", mas sim em evitar mortes causadas pelo não uso ou mau uso de equipamentos.
+• Texto na Diretriz (Item 4 - Objetivos): "Extinguir o número de mortes e lesões graves em policiais militares em serviço, por não uso ou mal uso de equipamentos de proteção, através da implementação de uma política de segurança individual e coletiva, focada na prevenção".
+(V) "Em relação à criação de hábitos angulares na tropa, é fundamental que os militares interiorizem a necessidade de evitar riscos exagerados e desnecessários durante o turno operacional, não banalizando a possibilidade de envolvimento em graves acidentes para alcance de resultados desproporcionalmente inferiores à ação executada."
+• Por que é VERDADEIRA: A frase é uma cópia literal do texto da norma.
+• Texto na Diretriz (Item 5.2.3.1 - Hábitos na tropa): "Além disso, é fundamental que os militares interiorizem a necessidade de evitar riscos exagerados e desnecessários durante o turno operacional, não banalizando a possibilidade de envolvimento em graves acidentes para alcance de resultados desproporcionalmente inferiores à ação executada".
+(V) "Reconhecer o risco à vida dos policiais não significa banalizá-lo ou negar a importância de sua missão. Pelo contrário, é um passo essencial para a construção de uma polícia mais segura e profissional, capaz de servir à sociedade com o máximo de empenho e o mínimo de perdas."
+• Por que é VERDADEIRA: A frase também é uma cópia literal da conclusão da norma.
+• Texto na Diretriz (Item 6 - Conclusão): "Reconhecer o risco à vida dos policiais não significa banalizá-lo ou negar a importância de sua missão. Pelo contrário, é um passo essencial para a construção de uma polícia mais segura e profissional, capaz de servir à sociedade com o máximo de empenho e o mínimo de perdas".
+(F) "Não se deve aceitar que o risco à vida faz parte da realidade do policial militar. Essa compreensão é fundamental para a construção de uma cultura de segurança que elimine os perigos inerentes à sua função, para tomada de decisões assertivas em situações do dia-a-dia, ou de crise."
+• Por que é FALSA: A norma diz exatamente o oposto: é preciso aceitar que o risco existe para poder lidar com ele.
+• Texto na Diretriz (Item 6 - Conclusão): "É crucial reconhecer e aceitar que o risco à vida faz parte da realidade do policial militar. Essa compreensão é fundamental para a construção de uma cultura de segurança robusta..."</t>
+  </si>
+  <si>
+    <t>Análise das Assertivas
+(V) "As propostas de criação de novos serviços que não estejam contemplados no Portfólio deverão tramitar via canal de comando, contendo estudo de situação para análise do Chefe do Estado-Maior da PMMG (CHEM). Havendo parecer favorável pela implementação do serviço, deverá ser verificada a viabilidade por meio de análise experimental de projeto-piloto, que somente poderá ser implementado com autorização do Chefe do Estado-Maior da PMMG."
+• Justificativa: A assertiva é VERDADEIRA pois reproduz fielmente o fluxo de criação de novos serviços descrito na norma.
+• Fundamentação Normativa: Item 5 - CRIAÇÃO, ATIVAÇÃO E DESATIVAÇÃO DE SERVIÇOS (Pág. 25, 4º parágrafo):
+(V) "Os serviços essenciais em Unidades com responsabilidade territorial são Radiopatrulha e Tático Móvel."
+• Justificativa: A assertiva é VERDADEIRA. A norma define taxativamente quais são os serviços essenciais para unidades de área.
+• Fundamentação Normativa: Item 3 - DA CLASSIFICAÇÃO QUANTO À ESSENCIALIDADE E PRIORIZAÇÃO DE SERVIÇOS (Pág. 15, 2º parágrafo):
+(V) "Os serviços eletivos compreendem um rol não obrigatório, cuja implementação não deve ocorrer em detrimento aos essenciais."
+• Justificativa: A assertiva é VERDADEIRA. A definição de serviço eletivo e a condição de não prejudicar o essencial são pontos chaves do documento.
+• Fundamentação Normativa: Item 3 - DA CLASSIFICAÇÃO QUANTO À ESSENCIALIDADE E PRIORIZAÇÃO DE SERVIÇOS (Pág. 15, 3º parágrafo):
+(V) "Ao incorporar o conceito de equipe policial-militar multimissão ao serviço de Radiopatrulha, torna-se possível que esta, de forma versátil, execute atividades como Patrulha Escolar ou Policiamento Turístico durante o turno."
+• Justificativa: A assertiva é VERDADEIRA. O texto explica como o conceito "multimissão" permite que um serviço essencial (Rp) execute atividades que, em outro contexto, poderiam ser vistas como especializadas ou eletivas, otimizando o recurso.
+• Fundamentação Normativa: Item 3 - DA CLASSIFICAÇÃO QUANTO À ESSENCIALIDADE E PRIORIZAÇÃO DE SERVIÇOS (Pág. 16/17, último parágrafo</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA: "O Teleatendimento de emergências policiais é uma atividade prestada pela PMMG via 190 ou outros canais disponíveis. Baseia-se no recebimento de solicitações da população para posterior empenho do recurso disponível, e compreende as funções de teleatendente, despachador e coordenador, dentre outras."
+    ◦ Fundamentação: Esta assertiva é uma transcrição literal do item 4.5, alínea 'b' (Serviços Auxiliares) da Diretriz nº 3.02.008/2025.
+• INCORRETA: "O GEPMOR é um serviço de policiamento especializado..."
+    ◦ Fundamentação: O GEPMOR (Grupo Especial para Prevenção Motorizada Ostensiva Rápida) é classificado como uma Atividade Atrelada ao serviço de Tático Móvel (ver Apêndice II). O Tático Móvel, por sua vez, é um serviço de Policiamento Ostensivo Geral (POG) de Segundo Esforço, e não Policiamento Especializado.
+• INCORRETA: "O Grupo Tático Rodoviário é um serviço de policiamento ostensivo geral..."
+    ◦ Fundamentação: O Grupo Tático Rodoviário (GTR) é classificado na norma como um serviço de Policiamento Especializado (PE) (item 4.2.2.2), e não Policiamento Ostensivo Geral (POG).
+• INCORRETA: "O Grupo Especial de Policiamento Ambiental é um serviço de terceiro esforço da malha protetora..."
+    ◦ Fundamentação: O Grupo Especial de Policiamento Ambiental (GEPAM) compõe o Segundo Esforço da Malha Protetora (item 4.2.1.2), e não o terceiro. Os serviços de terceiro esforço são, via de regra, os de Policiamento de Missões Especiais (ex: GER, ROTAM, Choque).</t>
+  </si>
+  <si>
+    <t>Explicação detalhada com base na Diretriz nº 3.02.008/2025 - CG:
+1. (F) "Os serviços de apoio consistem em um conjunto de atividades desenvolvidas no interior das instalações policiais-militares..."
+    ◦ Incorreto. A definição apresentada refere-se aos Serviços Auxiliares.
+    ◦ Fonte: Item 4.5, alínea 'b' (Pág. 22): "Serviços Auxiliares - conjunto de atividades desenvolvidas no interior das instalações policiais-militares... ou atividades relacionadas ao acompanhamento, fiscalização e supervisão...".
+2. (V) "Os serviços essenciais possuem caráter imprescindível e não poderão ser desativados nem reduzidos a ponto de comprometer a capacidade de atendimento às demandas locais."
+    ◦ Correto. Transcrição literal do item 5.
+    ◦ Fonte: Item 5 - CRIAÇÃO, ATIVAÇÃO E DESATIVAÇÃO DE SERVIÇOS (Pág. 24).
+3. (V) "Os serviços Tático Móvel e GEPAR poderão, eventualmente, ser empregados com um número maior de integrantes..."
+    ◦ Correto. Transcrição literal do item 7.4.
+    ◦ Fonte: Item 7 - PRESCRIÇÕES DIVERSAS (Pág. 27).
+4. (F) "Os serviços auxiliares objetivam ampliar a capacidade operativa, decisória e de planejamento dos demais tipos de policiamento ou a garantia do poder de polícia de outros órgãos."
+    ◦ Incorreto. A definição apresentada refere-se aos Serviços de Apoio.
+    ◦ Fonte: Item 4.5, alínea 'a' (Pág. 21): "Serviços de Apoio objetivam ampliar a capacidade operativa, decisória e de planejamento dos demais tipos de policiamento ou a garantia do poder de polícia de outros órgãos."
+5. (V) "Não há previsão de emprego de patrulhas unitárias na execução de serviços policiais-militares previstos no Portfólio. Contudo, deslocamentos para serviços administrativos ou operacionais de um policial militar em viatura não caracterizam o emprego no formato patrulha unitária."
+    ◦ Correto. Transcrição literal do item 7.8.
+    ◦ Fonte: Item 7 - PRESCRIÇÕES DIVERSAS (Pág. 28).</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA: "Serviço policial-militar – conjunto de atividades policiais-militares realizadas por uma equipe de policiamento, que atua em conformidade com características específicas (diagnóstico de recursos operacionais) e com conceito operacional definido para atender às demandas de segurança pública."
+    ◦ Fundamentação: Esta definição é a transcrição literal do conceito apresentado no item 2.1 da Diretriz nº 3.02.008/2025-CG.
+• INCORRETA: "Repressão qualificada – reação no estado de flagrância..."
+    ◦ Fundamentação: A definição apresentada refere-se à Repressão Imediata. A Repressão Qualificada é definida como a reação realizada com base em planejamento prévio (item 2.2).
+• INCORRETA: "Atividade policial-militar – é a unidade elementar do procedimento operacional..."
+    ◦ Fundamentação: A definição apresentada refere-se à Ação policial-militar (item 2.1). A Atividade policial-militar é composta por um conjunto correlacionado de ações.
+• INCORRETA: "Prevenção criminal – ação da Polícia Militar por meio de ações e/ou operações..."
+    ◦ Fundamentação: A definição apresentada refere-se ao Atendimento de ocorrência. A Prevenção Criminal é definida como o conjunto de medidas que visam evitar a ocorrência de delitos (item 2.2).</t>
+  </si>
+  <si>
+    <t>A alternativa CORRETA é: Apenas as assertivas II e III são verdadeiras.
+Segue a análise detalhada de cada assertiva com base na Instrução nº 3.03.34/2025 - EMPM:
+• I - FALSA. O monitoramento indiscriminado de "alvos prioritários" definidos pela P2 sem mandado não consta como objetivo operacional. A norma é taxativa ao definir a finalidade e os objetivos operacionais focados na identificação de pessoas com restrições judiciais, foragidos da justiça e pessoas desaparecidas. Além disso, o item 4.2.b determina o descarte automático de dados de indivíduos que não apresentam correlação com o banco de dados de foragidos/desaparecidos.
+    ◦ Fundamentação: Item 2.1, alínea 'b' ("finalidade principal a identificação... de pessoas desaparecidas e captura de indivíduos com restrições judiciais") e Item 3.1 ("Objetivos operacionais").
+• II - VERDADEIRA. A Instrução prevê expressamente essas duas formas de intervenção.
+    ◦ Fundamentação: Item 3.3 Intervenção policial: "A intervenção policial com o apoio da tecnologia de reconhecimento facial pode ocorrer a partir de um alerta emitido por câmeras, ou com a utilização de aplicativo instalado em dispositivo móvel.".
+• III - VERDADEIRA. A norma restringe o acesso e exige capacitação específica.
+    ◦ Fundamentação: Item 7.2: "O acesso ao sistema é permitido apenas a policiais militares e funcionários civis devidamente autorizados e que tenham recebido formação técnica e orientação legal sobre o uso adequado da tecnologia e suas implicações jurídicas.".
+• IV - FALSA. A responsabilidade pela fiscalização das câmeras inoperantes é atribuída às Unidades de Direção Intermediária (UDI) ou Unidades de Execução Operacional (UEOp), e não à Diretoria de Tecnologia e Sistemas (DTS).
+    ◦ Fundamentação: Item 7.3: "Cabe às Unidades de Direção Intermediárias ou Unidades de Execução Operacional, além da expansão do sistema, a fiscalização das câmeras eventualmente inoperantes...".</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA: "Ao verbalizar, durante uma abordagem policial, o policial militar deve manter o equilíbrio e o autocontrole, mesmo se o abordado não obedecer, se fizer comentários ofensivos, ignorar a sua presença ou atrair a atenção de pessoas em volta. A linguagem que deve prevalecer é a do policial militar e não a do abordado."
+    ◦ Fundamentação: Esta alternativa é uma transcrição fiel do item 6.1.1 (Verbalização durante a abordagem policial) do MTP 01. O manual destaca que manter um diálogo claro, direto e sem abusos demonstra profissionalismo e domínio da situação.
+• INCORRETA: "Sobre as etapas da intervenção, a Avaliação consiste na decisão acerca das atribuições de cada policial militar..."
+    ◦ Fundamentação: A definição apresentada refere-se à etapa do Plano de Ação (Etapa 2), e não à Avaliação. Segundo o manual, o Plano de Ação "consiste na decisão, acerca das atribuições de cada policial militar, dos métodos e procedimentos para alcançar objetivos da intervenção". A Avaliação (Etapa 4) ocorre após a execução e consiste na análise das condutas e resultados alcançados.
+• INCORRETA: "...Nesse caso, a responsabilidade pelo uso da força recai sobre o policial militar que a empregou e não aos superiores que tenham dado ordens ilegais."
+    ◦ Fundamentação: O item 7.1.4 (Responsabilidade pelo uso da força) estabelece que, embora a responsabilidade do autor seja individual, "Em qualquer caso, a responsabilidade caberá também aos superiores que tenham dado ordens ilegais",.
+• INCORRETA: "...não existe possibilidade de imputar ao superior imediato responsabilidade quando os policiais militares sob suas ordens tenham recorrido ao uso excessivo de força."
+    ◦ Fundamentação: O manual prevê expressamente a responsabilidade dos superiores ("b) dos superiores") quando estes, cientes do uso excessivo de força por seus subordinados, não adotarem medidas para impedir ou comunicar o fato.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA: "Conforme o princípio da necessidade, o uso da força será empregado quando, devido as circunstâncias apresentadas no cenário de atuação, for impossível de se evitar. Guarda relação com a ação que se espera e o meio disponível."
+    ◦ Fundamentação: Esta alternativa reproduz fielmente o texto do Princípio da Necessidade descrito no item 7.1 do MTP 01. O manual estabelece que a força só deve ser usada quando outros meios não forem suficientes ou possíveis nas circunstâncias dadas.
+• INCORRETA: "O uso dissuasivo de armas de fogo faz parte do nível primário para o uso diferenciado de força."
+    ◦ Fundamentação: De acordo com o item 7.1.2 (Uso diferenciado da força), o "Uso dissuasivo de armas de fogo" pertence ao Nível Secundário (junto com controle de contato, físico e IMPO). O Nível Primário abrange apenas a "Presença policial-militar" e a "Verbalização".
+• INCORRETA: "...a exemplo do agressor, empunhando uma faca, desloca-se em direção ao policial militar e tenta atacá-lo."
+    ◦ Fundamentação: O exemplo citado na alternativa (agressor com faca tentando atacar) é classificado no manual como Resistência Ativa com Agressão Letal (põe em perigo de morte), e não "agressão não letal". A agressão não letal é exemplificada por chutes ou socos que não representam risco de morte.
+• INCORRETA: "A gravidade da ameaça consiste em aferir se o resultado da ação policial-militar está pautado na lei..."
+    ◦ Fundamentação: A alternativa inverteu os conceitos do princípio da Proporcionalidade.
+        ▪ Objetivo legal pretendido é que consiste em aferir se o resultado está pautado na lei.
+        ▪ Gravidade da ameaça é que avalia a intensidade, periculosidade, hostilidade do ambiente e meios disponíveis.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA: "A abordagem a pessoas envolve um conjunto ordenado de ações policiais para se aproximar de um ou mais indivíduos, com o intuito de resolver demandas do policiamento ostensivo. Este conceito possui um sentido amplo, ou seja, abrange a todos os cidadãos, não se restringindo às pessoas em situação de suspeição."
+    ◦ Fundamentação: Esta alternativa é uma transcrição exata do item 3 (ABORDAGEM A PESSOAS) do MTP 02, que define o conceito amplo da abordagem, aplicando-se não apenas a suspeitos, mas a orientações, assistências e fiscalizações diversas.
+• INCORRETA: "No desenvolvimento da abordagem... Contudo, o comportamento do abordado (cooperativo, resistente passivo e ativo) não será determinante para a mudança de postura tática."
+    ◦ Fundamentação: O item 3.2 (Supremacia de força na abordagem a pessoas) afirma exatamente o oposto: "O comportamento do abordado (cooperativo, resistente passivo e ativo) será determinante para a mudança de postura tática".
+• INCORRETA: "A busca pessoal é o conjunto ordenado de ações policiais para aproximar-se de uma ou mais pessoas, veículos ou edificações."
+    ◦ Fundamentação: A definição apresentada refere-se à Abordagem Policial (item 3). A Busca Pessoal (item 4.1) é definida como a técnica que visa a procura de objetos ilícitos ou perigosos no corpo ou pertences do abordado.
+• INCORRETA: "A supremacia de força... é medida apenas de forma quantitativa..."
+    ◦ Fundamentação: O item 3.2 esclarece que a supremacia de força é medida de forma qualitativa e quantitativa, relacionando-se não só ao número de policiais, mas também ao uso da força, posse de instrumentos, equipamentos e armamentos.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• INCORRETA: "Enquanto não sobrevier sentença condenatória, nos crimes comuns, os prefeitos não estarão sujeitos à prisão. O policial militar irá liberar o prefeito no local..."
+    ◦ Fundamentação: De acordo com o item 5.1.1, alínea 'f' (Pág. 93) e o Quadro 4 (Pág. 98) do MTP 02, os prefeitos não possuem prerrogativas em relação à prisão em flagrante no cometimento de delitos, recebendo o mesmo tratamento dos demais cidadãos. O manual determina expressamente que o policial militar deverá prender o prefeito, registrar o BO/REDS e encaminhá-lo à Polícia Judiciária Estadual (Polícia Civil). A imunidade à prisão citada na alternativa aplica-se aos Governadores (art. 92, § 3º da CEMG) e ao Presidente da República (art. 86, § 3º da CF/88).
+• CORRETA: "Se o delito praticado pelo vereador não tiver nenhum vínculo político com sua função..."
+    ◦ Fundamentação: Transcrição fiel do item 5.1.2, alínea 'c' (Pág. 94). Vereadores só possuem inviolabilidade por opiniões, palavras e votos no exercício do mandato e na circunscrição do Município.
+• CORRETA: "Enquanto não sobrevier sentença condenatória nas infrações comuns, o Presidente da República não estará sujeito à prisão..."
+    ◦ Fundamentação: Conforme o item 5.1.1, alínea 'a' (Pág. 92), o Presidente não está sujeito à prisão nas infrações comuns enquanto não houver sentença condenatória, devendo ser liberado no local.
+• CORRETA: "Nos casos em que Policiais Penais figurarem como autores de crimes..."
+    ◦ Fundamentação: Conforme o item 5.1.8, alínea 'b' (Pág. 97), Policiais Penais não possuem prerrogativas quanto à prisão em flagrante, devendo ser presos e encaminhados à Polícia Judiciária.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• INCORRETA: "Na execução de uma operação blitz de qualquer tipo, caso o policial se depare com irregularidades (penais ou administrativas) que não sejam o escopo primordial da operação, ele pode deixar de tomar providências..."
+    ◦ Fundamentação: O item 2.1 (Classificação por Tipos) do MTP 03 estabelece expressamente o oposto, baseando-se no princípio da universalidade. O texto afirma que: "...na execução de uma operação blitz de qualquer tipo, o policial pode se deparar com irregularidades (penais ou administrativas), ainda que não sejam o escopo primordial da operação, nem a proposta inicial da atividade, exigirá que a equipe tome as providências que o caso demandar." Portanto, o policial não pode deixar de agir.
+• CORRETA: "A Blitz Policial pode ser executada por uma equipe composta somente por policiais militares ou por policiais militares em conjunto..."
+    ◦ Fundamentação: Transcrição fiel do item 2 (Conceito e Classificação), que prevê a execução isolada ou conjunta com outros órgãos (fazendários, sanitários, etc.).
+• CORRETA: "De acordo com os objetivos, as operações blitz classificam-se em: Educativa... e Preventiva..."
+    ◦ Fundamentação: Transcrição fiel do item 2.1, que define as duas classificações por tipo (objetivos).
+• CORRETA: "As operações blitzen devem possuir caráter preventivo, ainda que objetivem reprimir alguma modalidade criminosa particular."
+    ◦ Fundamentação: Transcrição fiel do item 2.1. O manual explica que, se houver necessidade de abordar pessoas específicas envolvidas em crimes (foco puramente repressivo/investigativo), o formato deve se adequar a operações de Cerco e Bloqueio (MTP 05), e não Blitz.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• INCORRETA: "O tempo previsto para a execução da blitz policial será de no mínimo trinta minutos... Conforme avaliação feita pelo coordenador do policiamento... autorizado pelo comandante de companhia."
+    ◦ Fundamentação: O item 3 (Planejamento e Desenvolvimento) do MTP 03, especificamente na página 18 (final do preâmbulo do item 3), estabelece que: "O tempo previsto para a execução da blitz policial será o suficiente para alcançar o objetivo sem comprometer a qualidade das operações policiais." Não há fixação de tempo mínimo de 30 minutos.
+    ◦ Além disso, a norma define que a avaliação é feita pelo PM Comandante da operação (e não pelo coordenador) e a redefinição deve ser autorizada pelo coordenador do policiamento (e não pelo Cmt de Cia).
+    ◦ Texto original: "Conforme avaliação feita pelo PM Comandante da operação, no local, o tempo poderá ser redefinido, desde que autorizado pelo coordenador do policiamento."
+• CORRETA: "Se o local e horário escolhidos para a execução da operação influenciarem no desenvolvimento normal do tráfego..."
+    ◦ Fundamentação: Transcrição fiel do item 3 (Planejamento e Desenvolvimento).
+• CORRETA: "O local e o horário de instalação da blitz policial são aspectos importantes..."
+    ◦ Fundamentação: Transcrição fiel do item 3 (Planejamento e Desenvolvimento).
+• CORRETA: "Em caso de condições climáticas adversas, em especial, no caso de chuva forte..."
+    ◦ Fundamentação: Transcrição fiel do item 3 (Planejamento e Desenvolvimento)</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base no Memorando nº 30.070.2/2024 - EMPM:
+• Fundamentação para a Alternativa A (CORRETA): O documento estabelece claramente que a presunção de porte para consumo pessoal (baseada na quantidade de até 40g) é relativa. Mesmo que a quantidade encontrada seja inferior ao limite estipulado pelo STF, a presença de elementos que indiquem a comercialização configura o crime de Tráfico de Drogas.
+    ◦ Item 5.3: "Mantém-se a possibilidade de prisão em flagrante pelo crime de tráfico de drogas, mesmo para quantidades inferiores ao limite de 40 gramas... bastando a presença de elementos indicativos de traficância...".
+    ◦ Item 5.4: O memorando lista taxativamente os elementos encontrados no caso narrado como provas de tráfico: "São exemplos de condutas que podem indicar o cometimento do delito de tráfico de drogas: variedade das substâncias apreendidas, presença de instrumentos como balança de precisão, registros documentados de operações comerciais...".
+    ◦ Item 5.5: Reforça que "a presença ou não dos elementos configuradores do delito de tráfico de drogas é que definirá a natureza da ocorrência".
+• Por que as demais estão INCORRETAS:
+    ◦ Alternativa B: A lavratura de TCO e liberação aplica-se apenas quando configurado o porte para consumo pessoal. A presença da balança e anotações afasta essa hipótese, exigindo a prisão em flagrante por tráfico (crime comum), conforme o fluxo de "Elementos indicativos de tráfico de drogas" presente no fluxograma do anexo (Item 8.1).
+    ◦ Alternativa C: Separar as naturezas (maconha como administrativo e cocaína como uso) seria incorreto, pois o contexto fático (venda) contamina toda a apreensão.
+    ◦ Alternativa D: É juridicamente impossível lavrar TCO para o crime de Tráfico de Drogas, pois este possui pena máxima superior a 2 anos, não sendo infração de menor potencial ofensivo.</t>
+  </si>
+  <si>
+    <t>xplicação Detalhada:
+• INCORRETA: "O crime de maus-tratos aos animais admite ser cometido na modalidade culposa."
+    ◦ Fundamentação: O item 5.4 do POP nº 1.8.0.048 (Anexo ao Memorando nº 30.001.2/2024) estabelece taxativamente o oposto: "O crime de maus-tratos aos animais só pode ser cometido na modalidade dolosa, o que significa dizer que, para cometer o crime, o agente deve querer o resultado ou assumir o risco de produzi-lo".
+Análise das demais alternativas (que estão CORRETAS de acordo com a norma):
+• A: "Quando se tratar de maus-tratos contra cães e gatos... não é cabível a lavratura de TCO."
+    ◦ Fundamentação: Confirmado pelo item 5.2: "...exceto quando se tratar de maus-tratos contra cães e gatos, que em razão da pena, não é cabível a lavratura de TCO".
+• B: "Configura maus-tratos... provocar envenenamento em animal que resulte ou não em morte."
+    ◦ Fundamentação: Confirmado pelo item 5.3, alínea 'g': "provocar envenenamento em animal que resulte ou não em morte".
+• D: "...o REDS, também, deverá ser encaminhado à Fração PM de Polícia Ambiental responsável pela área..."
+    ◦ Fundamentação: Confirmado pelo item 6.2.2, alínea 'p': "caso a equipe policial militar responsável pelo atendimento da ocorrência não seja do CPMAmb, o REDS, também, deverá ser encaminhado à Fração de Policiamento de Meio Ambiente responsável pela área, para adoção das medidas cabíveis"</t>
   </si>
 </sst>
 </file>
@@ -1656,7 +1831,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1665,7 +1840,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2131,7 +2305,7 @@
       <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>28</v>
       </c>
       <c r="F4" t="s">
@@ -2148,6 +2322,9 @@
       </c>
       <c r="J4" t="s">
         <v>33</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>481</v>
       </c>
       <c r="L4" t="s">
         <v>21</v>
@@ -2166,7 +2343,7 @@
       <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>36</v>
       </c>
       <c r="F5" t="s">
@@ -2183,6 +2360,9 @@
       </c>
       <c r="J5" t="s">
         <v>27</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>482</v>
       </c>
       <c r="L5" t="s">
         <v>21</v>
@@ -2201,22 +2381,22 @@
       <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" t="s">
         <v>57</v>
       </c>
       <c r="L6" t="s">
@@ -2236,22 +2416,22 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>52</v>
       </c>
       <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" t="s">
         <v>56</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" t="s">
         <v>20</v>
       </c>
       <c r="L7" t="s">
@@ -2271,23 +2451,26 @@
       <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" t="s">
         <v>58</v>
       </c>
       <c r="F8" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" t="s">
         <v>27</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>483</v>
       </c>
       <c r="L8" t="s">
         <v>51</v>
@@ -2306,23 +2489,26 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" t="s">
         <v>63</v>
       </c>
       <c r="F9" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" t="s">
         <v>20</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>484</v>
       </c>
       <c r="L9" t="s">
         <v>51</v>
@@ -2341,23 +2527,26 @@
       <c r="D10" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" t="s">
         <v>27</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>485</v>
       </c>
       <c r="L10" t="s">
         <v>51</v>
@@ -2376,22 +2565,22 @@
       <c r="D11" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" t="s">
         <v>73</v>
       </c>
       <c r="F11" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" t="s">
         <v>76</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" t="s">
         <v>78</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" t="s">
         <v>33</v>
       </c>
       <c r="L11" t="s">
@@ -2411,22 +2600,22 @@
       <c r="D12" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" t="s">
         <v>80</v>
       </c>
       <c r="F12" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" t="s">
         <v>82</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" t="s">
         <v>84</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" t="s">
         <v>33</v>
       </c>
       <c r="L12" t="s">
@@ -2446,22 +2635,22 @@
       <c r="D13" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" t="s">
         <v>86</v>
       </c>
       <c r="F13" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" t="s">
         <v>89</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" t="s">
         <v>90</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" t="s">
         <v>33</v>
       </c>
       <c r="L13" t="s">
@@ -2481,23 +2670,26 @@
       <c r="D14" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" t="s">
         <v>97</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" t="s">
         <v>57</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>486</v>
       </c>
       <c r="L14" t="s">
         <v>51</v>
@@ -2516,22 +2708,22 @@
       <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" t="s">
         <v>98</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" t="s">
         <v>100</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" t="s">
         <v>101</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" t="s">
         <v>102</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" t="s">
         <v>33</v>
       </c>
       <c r="L15" t="s">
@@ -2551,22 +2743,22 @@
       <c r="D16" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" t="s">
         <v>105</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" t="s">
         <v>106</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" t="s">
         <v>57</v>
       </c>
       <c r="L16" t="s">
@@ -2586,22 +2778,22 @@
       <c r="D17" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" t="s">
         <v>114</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" t="s">
         <v>115</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" t="s">
         <v>116</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" t="s">
         <v>117</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" t="s">
         <v>20</v>
       </c>
       <c r="L17" t="s">
@@ -2621,22 +2813,22 @@
       <c r="D18" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" t="s">
         <v>118</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" t="s">
         <v>119</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" t="s">
         <v>121</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" t="s">
         <v>57</v>
       </c>
       <c r="L18" t="s">
@@ -2656,22 +2848,22 @@
       <c r="D19" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" t="s">
         <v>125</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" t="s">
         <v>126</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" t="s">
         <v>127</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" t="s">
         <v>128</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" t="s">
         <v>129</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" t="s">
         <v>33</v>
       </c>
       <c r="L19" t="s">
@@ -2694,19 +2886,19 @@
       <c r="E20" t="s">
         <v>130</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" t="s">
         <v>131</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" t="s">
         <v>132</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" t="s">
         <v>133</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" t="s">
         <v>134</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" t="s">
         <v>33</v>
       </c>
       <c r="L20" t="s">
@@ -2729,19 +2921,19 @@
       <c r="E21" t="s">
         <v>135</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" t="s">
         <v>138</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" t="s">
         <v>139</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" t="s">
         <v>140</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" t="s">
         <v>20</v>
       </c>
       <c r="L21" t="s">
@@ -2764,19 +2956,19 @@
       <c r="E22" t="s">
         <v>142</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" t="s">
         <v>143</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" t="s">
         <v>144</v>
       </c>
       <c r="H22" t="s">
         <v>145</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" t="s">
         <v>146</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" t="s">
         <v>33</v>
       </c>
       <c r="L22" t="s">
@@ -2799,19 +2991,19 @@
       <c r="E23" t="s">
         <v>147</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" t="s">
         <v>149</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" t="s">
         <v>150</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" t="s">
         <v>151</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" t="s">
         <v>57</v>
       </c>
       <c r="L23" t="s">
@@ -2834,19 +3026,19 @@
       <c r="E24" t="s">
         <v>155</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" t="s">
         <v>156</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" t="s">
         <v>157</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" t="s">
         <v>158</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" t="s">
         <v>159</v>
       </c>
-      <c r="J24" s="4" t="s">
+      <c r="J24" t="s">
         <v>27</v>
       </c>
       <c r="L24" t="s">
@@ -2869,19 +3061,19 @@
       <c r="E25" t="s">
         <v>160</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" t="s">
         <v>162</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" t="s">
         <v>163</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" t="s">
         <v>164</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" t="s">
         <v>33</v>
       </c>
       <c r="L25" t="s">
@@ -2904,19 +3096,19 @@
       <c r="E26" t="s">
         <v>165</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" t="s">
         <v>168</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" t="s">
         <v>169</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" t="s">
         <v>171</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" t="s">
         <v>170</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" t="s">
         <v>20</v>
       </c>
       <c r="L26" t="s">
@@ -2939,19 +3131,19 @@
       <c r="E27" t="s">
         <v>172</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" t="s">
         <v>173</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" t="s">
         <v>174</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" t="s">
         <v>175</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" t="s">
         <v>176</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" t="s">
         <v>57</v>
       </c>
       <c r="L27" t="s">
@@ -2974,19 +3166,19 @@
       <c r="E28" t="s">
         <v>177</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" t="s">
         <v>178</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" t="s">
         <v>179</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" t="s">
         <v>180</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" t="s">
         <v>181</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="J28" t="s">
         <v>57</v>
       </c>
       <c r="L28" t="s">
@@ -3009,19 +3201,19 @@
       <c r="E29" t="s">
         <v>187</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" t="s">
         <v>182</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" t="s">
         <v>183</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" t="s">
         <v>184</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" t="s">
         <v>185</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" t="s">
         <v>33</v>
       </c>
       <c r="L29" t="s">
@@ -3044,19 +3236,19 @@
       <c r="E30" t="s">
         <v>186</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" t="s">
         <v>188</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" t="s">
         <v>189</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" t="s">
         <v>190</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" t="s">
         <v>191</v>
       </c>
-      <c r="J30" s="4" t="s">
+      <c r="J30" t="s">
         <v>27</v>
       </c>
       <c r="L30" t="s">
@@ -3091,7 +3283,7 @@
       <c r="I31" t="s">
         <v>198</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" t="s">
         <v>20</v>
       </c>
       <c r="L31" t="s">
@@ -3111,7 +3303,7 @@
       <c r="D32" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" t="s">
         <v>201</v>
       </c>
       <c r="F32" t="s">
@@ -3126,7 +3318,7 @@
       <c r="I32" t="s">
         <v>205</v>
       </c>
-      <c r="J32" s="4" t="s">
+      <c r="J32" t="s">
         <v>27</v>
       </c>
       <c r="L32" t="s">
@@ -3161,7 +3353,7 @@
       <c r="I33" t="s">
         <v>212</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="J33" t="s">
         <v>57</v>
       </c>
       <c r="L33" t="s">
@@ -3196,7 +3388,7 @@
       <c r="I34" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="J34" t="s">
         <v>27</v>
       </c>
       <c r="L34" t="s">
@@ -3216,7 +3408,7 @@
       <c r="D35" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" t="s">
         <v>231</v>
       </c>
       <c r="F35" t="s">
@@ -3231,7 +3423,7 @@
       <c r="I35" t="s">
         <v>223</v>
       </c>
-      <c r="J35" s="4" t="s">
+      <c r="J35" t="s">
         <v>33</v>
       </c>
       <c r="L35" t="s">
@@ -3251,7 +3443,7 @@
       <c r="D36" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" t="s">
         <v>232</v>
       </c>
       <c r="F36" t="s">
@@ -3266,7 +3458,7 @@
       <c r="I36" t="s">
         <v>226</v>
       </c>
-      <c r="J36" s="4" t="s">
+      <c r="J36" t="s">
         <v>27</v>
       </c>
       <c r="L36" t="s">
@@ -3286,7 +3478,7 @@
       <c r="D37" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" t="s">
         <v>265</v>
       </c>
       <c r="F37" t="s">
@@ -3301,7 +3493,7 @@
       <c r="I37" t="s">
         <v>236</v>
       </c>
-      <c r="J37" s="4" t="s">
+      <c r="J37" t="s">
         <v>57</v>
       </c>
       <c r="L37" t="s">
@@ -3321,7 +3513,7 @@
       <c r="D38" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" t="s">
         <v>266</v>
       </c>
       <c r="F38" t="s">
@@ -3336,7 +3528,7 @@
       <c r="I38" t="s">
         <v>235</v>
       </c>
-      <c r="J38" s="4" t="s">
+      <c r="J38" t="s">
         <v>33</v>
       </c>
       <c r="L38" t="s">
@@ -3371,7 +3563,7 @@
       <c r="I39" t="s">
         <v>244</v>
       </c>
-      <c r="J39" s="4" t="s">
+      <c r="J39" t="s">
         <v>33</v>
       </c>
       <c r="L39" t="s">
@@ -3406,7 +3598,7 @@
       <c r="I40" t="s">
         <v>249</v>
       </c>
-      <c r="J40" s="4" t="s">
+      <c r="J40" t="s">
         <v>20</v>
       </c>
       <c r="L40" t="s">
@@ -3441,7 +3633,7 @@
       <c r="I41" t="s">
         <v>254</v>
       </c>
-      <c r="J41" s="4" t="s">
+      <c r="J41" t="s">
         <v>27</v>
       </c>
       <c r="L41" t="s">
@@ -3476,7 +3668,7 @@
       <c r="I42" t="s">
         <v>259</v>
       </c>
-      <c r="J42" s="4" t="s">
+      <c r="J42" t="s">
         <v>20</v>
       </c>
       <c r="L42" t="s">
@@ -3511,7 +3703,7 @@
       <c r="I43" t="s">
         <v>264</v>
       </c>
-      <c r="J43" s="4" t="s">
+      <c r="J43" t="s">
         <v>27</v>
       </c>
       <c r="L43" t="s">
@@ -3546,8 +3738,11 @@
       <c r="I44" t="s">
         <v>277</v>
       </c>
-      <c r="J44" s="4" t="s">
+      <c r="J44" t="s">
         <v>33</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>487</v>
       </c>
       <c r="L44" t="s">
         <v>103</v>
@@ -3581,8 +3776,11 @@
       <c r="I45" t="s">
         <v>282</v>
       </c>
-      <c r="J45" s="4" t="s">
+      <c r="J45" t="s">
         <v>33</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>488</v>
       </c>
       <c r="L45" t="s">
         <v>103</v>
@@ -3616,8 +3814,11 @@
       <c r="I46" t="s">
         <v>287</v>
       </c>
-      <c r="J46" s="4" t="s">
+      <c r="J46" t="s">
         <v>20</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>489</v>
       </c>
       <c r="L46" t="s">
         <v>103</v>
@@ -3651,8 +3852,11 @@
       <c r="I47" t="s">
         <v>292</v>
       </c>
-      <c r="J47" s="4" t="s">
+      <c r="J47" t="s">
         <v>57</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>490</v>
       </c>
       <c r="L47" t="s">
         <v>103</v>
@@ -3686,8 +3890,11 @@
       <c r="I48" t="s">
         <v>297</v>
       </c>
-      <c r="J48" s="4" t="s">
+      <c r="J48" t="s">
         <v>20</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>491</v>
       </c>
       <c r="L48" t="s">
         <v>103</v>
@@ -3721,8 +3928,11 @@
       <c r="I49" t="s">
         <v>302</v>
       </c>
-      <c r="J49" s="4" t="s">
+      <c r="J49" t="s">
         <v>33</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>492</v>
       </c>
       <c r="L49" t="s">
         <v>103</v>
@@ -3756,7 +3966,7 @@
       <c r="I50" t="s">
         <v>307</v>
       </c>
-      <c r="J50" s="4" t="s">
+      <c r="J50" t="s">
         <v>57</v>
       </c>
       <c r="L50" t="s">
@@ -3791,7 +4001,7 @@
       <c r="I51" t="s">
         <v>312</v>
       </c>
-      <c r="J51" s="4" t="s">
+      <c r="J51" t="s">
         <v>57</v>
       </c>
       <c r="L51" t="s">
@@ -3826,7 +4036,7 @@
       <c r="I52" t="s">
         <v>325</v>
       </c>
-      <c r="J52" s="4" t="s">
+      <c r="J52" t="s">
         <v>20</v>
       </c>
       <c r="L52" t="s">
@@ -3861,7 +4071,7 @@
       <c r="I53" t="s">
         <v>330</v>
       </c>
-      <c r="J53" s="4" t="s">
+      <c r="J53" t="s">
         <v>57</v>
       </c>
       <c r="L53" t="s">
@@ -3896,8 +4106,11 @@
       <c r="I54" t="s">
         <v>335</v>
       </c>
-      <c r="J54" s="4" t="s">
+      <c r="J54" t="s">
         <v>33</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>493</v>
       </c>
       <c r="L54" t="s">
         <v>103</v>
@@ -3931,7 +4144,7 @@
       <c r="I55" t="s">
         <v>342</v>
       </c>
-      <c r="J55" s="4" t="s">
+      <c r="J55" t="s">
         <v>20</v>
       </c>
       <c r="L55" t="s">
@@ -3966,8 +4179,11 @@
       <c r="I56" t="s">
         <v>350</v>
       </c>
-      <c r="J56" s="4" t="s">
+      <c r="J56" t="s">
         <v>57</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>494</v>
       </c>
       <c r="L56" t="s">
         <v>343</v>
@@ -3986,7 +4202,7 @@
       <c r="D57" t="s">
         <v>14</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" t="s">
         <v>375</v>
       </c>
       <c r="F57" t="s">
@@ -4001,7 +4217,7 @@
       <c r="I57" t="s">
         <v>356</v>
       </c>
-      <c r="J57" s="4" t="s">
+      <c r="J57" t="s">
         <v>33</v>
       </c>
       <c r="L57" t="s">
@@ -4034,9 +4250,9 @@
         <v>360</v>
       </c>
       <c r="I58" t="s">
-        <v>473</v>
-      </c>
-      <c r="J58" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="J58" t="s">
         <v>57</v>
       </c>
       <c r="L58" t="s">
@@ -4069,9 +4285,9 @@
         <v>364</v>
       </c>
       <c r="I59" t="s">
-        <v>472</v>
-      </c>
-      <c r="J59" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="J59" t="s">
         <v>20</v>
       </c>
       <c r="L59" t="s">
@@ -4106,7 +4322,7 @@
       <c r="I60" t="s">
         <v>369</v>
       </c>
-      <c r="J60" s="4" t="s">
+      <c r="J60" t="s">
         <v>33</v>
       </c>
       <c r="L60" t="s">
@@ -4141,7 +4357,7 @@
       <c r="I61" t="s">
         <v>374</v>
       </c>
-      <c r="J61" s="4" t="s">
+      <c r="J61" t="s">
         <v>20</v>
       </c>
       <c r="L61" t="s">
@@ -4176,7 +4392,7 @@
       <c r="I62" t="s">
         <v>381</v>
       </c>
-      <c r="J62" s="4" t="s">
+      <c r="J62" t="s">
         <v>33</v>
       </c>
       <c r="L62" t="s">
@@ -4211,7 +4427,7 @@
       <c r="I63" t="s">
         <v>389</v>
       </c>
-      <c r="J63" s="4" t="s">
+      <c r="J63" t="s">
         <v>20</v>
       </c>
       <c r="L63" t="s">
@@ -4246,7 +4462,7 @@
       <c r="I64" t="s">
         <v>394</v>
       </c>
-      <c r="J64" s="4" t="s">
+      <c r="J64" t="s">
         <v>27</v>
       </c>
       <c r="L64" t="s">
@@ -4281,7 +4497,7 @@
       <c r="I65" t="s">
         <v>399</v>
       </c>
-      <c r="J65" s="4" t="s">
+      <c r="J65" t="s">
         <v>57</v>
       </c>
       <c r="L65" t="s">
@@ -4314,9 +4530,9 @@
         <v>403</v>
       </c>
       <c r="I66" t="s">
-        <v>471</v>
-      </c>
-      <c r="J66" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="J66" t="s">
         <v>33</v>
       </c>
       <c r="L66" t="s">
@@ -4351,7 +4567,7 @@
       <c r="I67" t="s">
         <v>408</v>
       </c>
-      <c r="J67" s="4" t="s">
+      <c r="J67" t="s">
         <v>27</v>
       </c>
       <c r="L67" t="s">
@@ -4375,18 +4591,18 @@
         <v>409</v>
       </c>
       <c r="F68" t="s">
-        <v>410</v>
+        <v>478</v>
       </c>
       <c r="G68" t="s">
-        <v>411</v>
+        <v>479</v>
       </c>
       <c r="H68" t="s">
-        <v>412</v>
+        <v>480</v>
       </c>
       <c r="I68" t="s">
-        <v>470</v>
-      </c>
-      <c r="J68" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="J68" t="s">
         <v>20</v>
       </c>
       <c r="L68" t="s">
@@ -4407,21 +4623,21 @@
         <v>14</v>
       </c>
       <c r="E69" t="s">
+        <v>410</v>
+      </c>
+      <c r="F69" t="s">
+        <v>411</v>
+      </c>
+      <c r="G69" t="s">
+        <v>412</v>
+      </c>
+      <c r="H69" t="s">
         <v>413</v>
       </c>
-      <c r="F69" t="s">
+      <c r="I69" t="s">
         <v>414</v>
       </c>
-      <c r="G69" t="s">
-        <v>415</v>
-      </c>
-      <c r="H69" t="s">
-        <v>416</v>
-      </c>
-      <c r="I69" t="s">
-        <v>417</v>
-      </c>
-      <c r="J69" s="4" t="s">
+      <c r="J69" t="s">
         <v>20</v>
       </c>
       <c r="L69" t="s">
@@ -4442,21 +4658,21 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
+        <v>415</v>
+      </c>
+      <c r="F70" t="s">
+        <v>416</v>
+      </c>
+      <c r="G70" t="s">
+        <v>417</v>
+      </c>
+      <c r="H70" t="s">
         <v>418</v>
       </c>
-      <c r="F70" t="s">
+      <c r="I70" t="s">
         <v>419</v>
       </c>
-      <c r="G70" t="s">
-        <v>420</v>
-      </c>
-      <c r="H70" t="s">
-        <v>421</v>
-      </c>
-      <c r="I70" t="s">
-        <v>422</v>
-      </c>
-      <c r="J70" s="4" t="s">
+      <c r="J70" t="s">
         <v>57</v>
       </c>
       <c r="L70" t="s">
@@ -4477,21 +4693,21 @@
         <v>14</v>
       </c>
       <c r="E71" t="s">
+        <v>420</v>
+      </c>
+      <c r="F71" t="s">
+        <v>421</v>
+      </c>
+      <c r="G71" t="s">
+        <v>422</v>
+      </c>
+      <c r="H71" t="s">
         <v>423</v>
       </c>
-      <c r="F71" t="s">
+      <c r="I71" t="s">
         <v>424</v>
       </c>
-      <c r="G71" t="s">
-        <v>425</v>
-      </c>
-      <c r="H71" t="s">
-        <v>426</v>
-      </c>
-      <c r="I71" t="s">
-        <v>427</v>
-      </c>
-      <c r="J71" s="4" t="s">
+      <c r="J71" t="s">
         <v>27</v>
       </c>
       <c r="L71" t="s">
@@ -4512,21 +4728,21 @@
         <v>14</v>
       </c>
       <c r="E72" t="s">
+        <v>425</v>
+      </c>
+      <c r="F72" t="s">
+        <v>426</v>
+      </c>
+      <c r="G72" t="s">
+        <v>427</v>
+      </c>
+      <c r="H72" t="s">
         <v>428</v>
       </c>
-      <c r="F72" t="s">
-        <v>429</v>
-      </c>
-      <c r="G72" t="s">
-        <v>430</v>
-      </c>
-      <c r="H72" t="s">
-        <v>431</v>
-      </c>
       <c r="I72" t="s">
-        <v>469</v>
-      </c>
-      <c r="J72" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="J72" t="s">
         <v>20</v>
       </c>
       <c r="L72" t="s">
@@ -4541,34 +4757,34 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D73" t="s">
         <v>14</v>
       </c>
       <c r="E73" t="s">
+        <v>429</v>
+      </c>
+      <c r="F73" t="s">
+        <v>430</v>
+      </c>
+      <c r="G73" t="s">
+        <v>431</v>
+      </c>
+      <c r="H73" t="s">
         <v>432</v>
       </c>
-      <c r="F73" t="s">
+      <c r="I73" t="s">
         <v>433</v>
       </c>
-      <c r="G73" t="s">
-        <v>434</v>
-      </c>
-      <c r="H73" t="s">
-        <v>435</v>
-      </c>
-      <c r="I73" t="s">
-        <v>436</v>
-      </c>
-      <c r="J73" s="4" t="s">
+      <c r="J73" t="s">
         <v>27</v>
       </c>
       <c r="L73" t="s">
         <v>343</v>
       </c>
       <c r="M73" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.25">
@@ -4582,21 +4798,21 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
+        <v>434</v>
+      </c>
+      <c r="F74" t="s">
+        <v>435</v>
+      </c>
+      <c r="G74" t="s">
+        <v>436</v>
+      </c>
+      <c r="H74" t="s">
         <v>437</v>
       </c>
-      <c r="F74" t="s">
+      <c r="I74" t="s">
         <v>438</v>
       </c>
-      <c r="G74" t="s">
-        <v>439</v>
-      </c>
-      <c r="H74" t="s">
-        <v>440</v>
-      </c>
-      <c r="I74" t="s">
-        <v>441</v>
-      </c>
-      <c r="J74" s="4" t="s">
+      <c r="J74" t="s">
         <v>33</v>
       </c>
       <c r="L74" t="s">
@@ -4617,21 +4833,21 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
+        <v>439</v>
+      </c>
+      <c r="F75" t="s">
+        <v>440</v>
+      </c>
+      <c r="G75" t="s">
+        <v>441</v>
+      </c>
+      <c r="H75" t="s">
         <v>442</v>
       </c>
-      <c r="F75" t="s">
+      <c r="I75" t="s">
         <v>443</v>
       </c>
-      <c r="G75" t="s">
-        <v>444</v>
-      </c>
-      <c r="H75" t="s">
-        <v>445</v>
-      </c>
-      <c r="I75" t="s">
-        <v>446</v>
-      </c>
-      <c r="J75" s="4" t="s">
+      <c r="J75" t="s">
         <v>27</v>
       </c>
       <c r="L75" t="s">
@@ -4646,34 +4862,34 @@
         <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D76" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>466</v>
+      <c r="E76" t="s">
+        <v>463</v>
       </c>
       <c r="F76" t="s">
         <v>236</v>
       </c>
       <c r="G76" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H76" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="I76" t="s">
-        <v>449</v>
-      </c>
-      <c r="J76" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="J76" t="s">
         <v>33</v>
       </c>
       <c r="L76" t="s">
         <v>343</v>
       </c>
       <c r="M76" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.25">
@@ -4687,21 +4903,21 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
+        <v>447</v>
+      </c>
+      <c r="F77" t="s">
+        <v>448</v>
+      </c>
+      <c r="G77" t="s">
+        <v>449</v>
+      </c>
+      <c r="H77" t="s">
         <v>450</v>
       </c>
-      <c r="F77" t="s">
+      <c r="I77" t="s">
         <v>451</v>
       </c>
-      <c r="G77" t="s">
-        <v>452</v>
-      </c>
-      <c r="H77" t="s">
-        <v>453</v>
-      </c>
-      <c r="I77" t="s">
-        <v>454</v>
-      </c>
-      <c r="J77" s="4" t="s">
+      <c r="J77" t="s">
         <v>57</v>
       </c>
       <c r="L77" t="s">
@@ -4721,14 +4937,14 @@
       <c r="D78" t="s">
         <v>14</v>
       </c>
-      <c r="E78" s="3" t="s">
-        <v>467</v>
+      <c r="E78" t="s">
+        <v>464</v>
       </c>
       <c r="F78" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G78" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H78" t="s">
         <v>238</v>
@@ -4736,7 +4952,7 @@
       <c r="I78" t="s">
         <v>236</v>
       </c>
-      <c r="J78" s="4" t="s">
+      <c r="J78" t="s">
         <v>57</v>
       </c>
       <c r="L78" t="s">
@@ -4757,21 +4973,21 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
+        <v>452</v>
+      </c>
+      <c r="F79" t="s">
+        <v>453</v>
+      </c>
+      <c r="G79" t="s">
+        <v>454</v>
+      </c>
+      <c r="H79" t="s">
         <v>455</v>
       </c>
-      <c r="F79" t="s">
-        <v>456</v>
-      </c>
-      <c r="G79" t="s">
-        <v>457</v>
-      </c>
-      <c r="H79" t="s">
-        <v>458</v>
-      </c>
       <c r="I79" t="s">
-        <v>468</v>
-      </c>
-      <c r="J79" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="J79" t="s">
         <v>20</v>
       </c>
       <c r="L79" t="s">
@@ -4792,21 +5008,21 @@
         <v>14</v>
       </c>
       <c r="E80" t="s">
+        <v>456</v>
+      </c>
+      <c r="F80" t="s">
+        <v>457</v>
+      </c>
+      <c r="G80" t="s">
+        <v>458</v>
+      </c>
+      <c r="H80" t="s">
         <v>459</v>
       </c>
-      <c r="F80" t="s">
+      <c r="I80" t="s">
         <v>460</v>
       </c>
-      <c r="G80" t="s">
-        <v>461</v>
-      </c>
-      <c r="H80" t="s">
-        <v>462</v>
-      </c>
-      <c r="I80" t="s">
-        <v>463</v>
-      </c>
-      <c r="J80" s="4" t="s">
+      <c r="J80" t="s">
         <v>33</v>
       </c>
       <c r="L80" t="s">
@@ -4827,21 +5043,21 @@
         <v>14</v>
       </c>
       <c r="E81" t="s">
+        <v>471</v>
+      </c>
+      <c r="F81" t="s">
+        <v>472</v>
+      </c>
+      <c r="G81" t="s">
+        <v>473</v>
+      </c>
+      <c r="H81" t="s">
         <v>474</v>
       </c>
-      <c r="F81" t="s">
+      <c r="I81" t="s">
         <v>475</v>
       </c>
-      <c r="G81" t="s">
-        <v>476</v>
-      </c>
-      <c r="H81" t="s">
-        <v>477</v>
-      </c>
-      <c r="I81" t="s">
-        <v>478</v>
-      </c>
-      <c r="J81" s="4" t="s">
+      <c r="J81" t="s">
         <v>27</v>
       </c>
       <c r="L81" t="s">

--- a/QUESTOES PROVA CRS.xlsx
+++ b/QUESTOES PROVA CRS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julião\Downloads\chobot-main (1)\chobot-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93677F0-7413-4BA6-9521-4B1EE7CDC272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D52E820-FD56-49C2-9A6F-0219BA59B08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="510">
   <si>
     <t>ID</t>
   </si>
@@ -1758,6 +1758,171 @@
     ◦ Fundamentação: Confirmado pelo item 5.3, alínea 'g': "provocar envenenamento em animal que resulte ou não em morte".
 • D: "...o REDS, também, deverá ser encaminhado à Fração PM de Polícia Ambiental responsável pela área..."
     ◦ Fundamentação: Confirmado pelo item 6.2.2, alínea 'p': "caso a equipe policial militar responsável pelo atendimento da ocorrência não seja do CPMAmb, o REDS, também, deverá ser encaminhado à Fração de Policiamento de Meio Ambiente responsável pela área, para adoção das medidas cabíveis"</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA: "A Operação Cerco, Bloqueio e Interceptação é uma intervenção policial legal, coercitiva, e que expressa o poder discricionário conferido ao policial militar para que promova com eficiência o policiamento ostensivo, atendendo inclusive aos requisitos de um poder-dever de que não poderá se furtar."
+    ◦ Fundamentação: Esta alternativa é a transcrição literal do item 5.1 (Fundamentação legal) do MTP 04. A norma destaca que, embora restrinja o direito de ir e vir, a operação é legitimada pela necessidade de segurança e bem-estar coletivo.
+• INCORRETA: "Bloqueio: é uma ação tática, que consiste no posicionamento conjunto de policiais militares... a fim de controlar as rotas de fuga do veículo evasor, por meio da disposição de obstáculos na via de forma a reduzir a velocidade..."
+    ◦ Fundamentação: O conceito apresentado na alternativa refere-se, na verdade, ao Cerco. Segundo o item 5 (Operação Cerco, Bloqueio e Interceptação), o Bloqueio é a ação tática que decorre do cerco e visa interromper totalmente o fluxo da via, e não apenas reduzir a velocidade.
+• INCORRETA: "Cerco: é uma ação tática que decorre da perseguição e que consiste no posicionamento de obstáculos com a finalidade de interromper totalmente o fluxo da via."
+    ◦ Fundamentação: O conceito apresentado na alternativa refere-se ao Bloqueio. O Cerco é o posicionamento em pontos estratégicos para controlar rotas de fuga e reduzir a velocidade, preparando o terreno para o bloqueio ou interceptação.
+• INCORRETA: "A perseguição policial e a Operação Cerco, Bloqueio e Interceptação são intervenções policiais de nível II (preventiva) ou III (repressivas)..."
+    ◦ Fundamentação: O item 5 do manual classifica taxativamente a perseguição e a Operação Cerco, Bloqueio e Interceptação como intervenções policiais de nível III (repressivas), pois visam compelir o infrator a cessar resistência. A alternativa erra ao incluir o "nível II (preventiva)".</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA: "O PM Vistoriador é o policial militar que procede à abordagem e mantém contato visual e verbal com o condutor do veículo e seus passageiros. É também o responsável pela verificação de documentos e vistoria do veículo."
+    ◦ Fundamentação: Esta definição é a transcrição exata do item 2.3, alínea 'c' (Distribuição de funções) do MTP 04. O manual define o Vistoriador como aquele que mantém o contato direto (visual e verbal) e fiscaliza documentos e sinais identificadores do veículo.
+• INCORRETA: "O PM Vistoriador é o principal responsável pela segurança dos integrantes da guarnição..."
+    ◦ Fundamentação: Esta é a definição do PM Segurança ("responsável pela integridade e segurança dos componentes da equipe"), conforme a alínea 'e' do item 2.3.
+• INCORRETA: "O PM Revistador é o responsável pela busca pessoal nos passageiros e não realiza busca no interior do veículo."
+    ◦ Fundamentação: Conforme a alínea 'd' do item 2.3, o PM Revistador é responsável tanto pela busca pessoal nos passageiros quanto pela busca no veículo abordado.
+• INCORRETA: "O PM Comandante não pode acumular funções..."
+    ◦ Fundamentação: O quadro de "ATENÇÃO" ao final do item 2.3 estabelece expressamente que: "Um policial militar poderá acumular duas ou mais funções das descritas no item anterior, conforme o tipo de veículo, os objetivos a serem atingidos e o número de integrantes da equipe."</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA: "São princípios que direcionam a Diretriz de Segurança para o Emprego Operacional: proatividade dos comandantes no zelo com o subordinado; a segurança como valor fundamental; a correção de atitudes; e a não banalização do risco."
+    ◦ Fundamentação: Esta alternativa enumera corretamente os quatro princípios listados no Item 3 da Diretriz (Anexo da Resolução nº 5.383/2024):
+        ▪ A segurança como valor fundamental;
+        ▪ Proatividade dos comandantes no zelo com o subordinado;
+        ▪ Correção de atitudes;
+        ▪ Não banalização do risco.
+Análise das incorreções:
+•(Incorreta): O treinamento abrangente é um dos objetivos expressos no Item 4: "Implementar um programa abrangente de treinamento para todos os policiais militares...".
+•(Incorreta): O objetivo não é "estabilizar", mas sim "Extinguir o número de mortes e lesões graves...".
+•(Incorreta): A diretriz prevê expressamente a responsabilização, conforme o Item 4: "...promover uma cultura de segurança no trabalho... além de responsabilização por negligências</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA: "O aculturamento tem como objetivo transformar a segurança em um valor fundamental na cultura dos policiais militares e da própria Instituição. A cultura relacionada à adoção de procedimentos de segurança deve se converter em um hábito positivo, natural e indissociável da atividade policial."
+    ◦ Fundamentação: Esta alternativa é uma transcrição quase literal do Item 5.2 (ACULTURAMENTO) da Diretriz anexa à Resolução nº 5.383/2024. O texto original afirma: "O aculturamento visa transformar a segurança em um valor fundamental na cultura dos policiais militares e da própria PMMG... como um hábito natural e indissociável da atividade policial".
+Análise das Incorreções:
+• INCORRETA: "Hábitos angulares devem ser evitados..."
+    ◦ Fundamentação: O Item 5.2.3 define hábitos angulares como "ações habituais positivas" que devem ser criadas e estimuladas, e não evitadas. A norma busca a "Criação de hábitos angulares".
+• INCORRETA: "...os comandantes não devem treinar seus subordinados..."
+    ◦ Fundamentação: O Item 5.2.3.2 (Hábitos nos comandantes) determina expressamente o oposto: "Além disso, [o comandante] deve treinar seus subordinados e reforçar na consciência de seus militares quanto a necessidade do cumprimento das normas...".
+• INCORRETA: "Deve-se evitar a utilização de vivências e conhecimentos práticos, dos policiais militares..."
+    ◦ Fundamentação: O Item 5.3 (FEEDBACK) estabelece que o feedback é crucial e que, "Através de suas vivências e conhecimentos práticos, os policiais podem contribuir para o aprimoramento de protocolos de segurança, treinamento e equipamentos". Portanto, essas vivências devem ser utilizadas, e não evitadas.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base na Diretriz nº 3.01.01/2019 - CG (Item 6.1 - Teoria do Crime):
+• CORRETA: "Vincula a existência do delito a três fatores essenciais convergentes no tempo e espaço, quais sejam: ofensor motivado e disposto a cometer o delito; alvo disponível que possa ser atacado; e ausência de guardiões capazes de impedir a ocorrência do crime."
+    ◦ Fundamentação: Esta alternativa é uma transcrição literal do texto da diretriz ao definir a Teoria das Atividades Rotineiras. O documento afirma: "Esta teoria vincula a existência do delito a três fatores essenciais convergentes no tempo e espaço, quais sejam: ofensor motivado e disposto a cometer o delito; alvo disponível que possa ser atacado; e ausência de guardiões capazes de impedir a ocorrência do crime".
+Análise das Incorreções:
+•  (Incorreta): A afirmação sobre a "incapacidade de controle social informal" refere-se à Teoria da Desorganização Social, e não à das Atividades Rotineiras.
+•  (Incorreta): A teoria vincula a decisão racional à existência da oportunidade e ao contexto situacional, e não à "falta" dela.
+•  (Incorreta): A diretriz estabelece que a atuação preventiva em qualquer um (apenas um) destes fatores é suficiente para anular a possibilidade de ocorrência do crime, e não "no mínimo dois".</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• INCORRETA: "Devido à exposição corporal do abordado e por questões de segurança, recomenda-se que a busca minuciosa seja realizada em local isolado do público."
+    ◦ Fundamentação: Esta recomendação refere-se, na verdade, à Busca Completa (desnudamento), e não à Busca Minuciosa. Conforme o item 4.1.2, alínea 'c' (Pág. 83) do MTP 02: "Devido à exposição corporal do abordado e por questões de segurança, recomenda-se que a busca completa seja realizada em local isolado do público e, sempre que possível, na presença de testemunha do mesmo sexo da pessoa abordada...". A busca minuciosa é realizada sobre as vestes (podendo ocorrer em via pública), enquanto a completa exige a retirada das roupas.
+Análise das demais alternativas (CORRETAS):
+• CORRETA: "São posições de contenção para a busca minuciosa: abordado em pé sem apoio; abordado em pé, com apoio; abordado de joelhos; e abordado deitado."
+    ◦ Fundamentação: Transcrição fiel das posições listadas no item 4.1.2, alínea 'b' (Págs. 78-83),,,.
+• CORRETA: "Os movimentos rápidos de deslizamento das mãos sobre o vestuário do cidadão durante a busca ligeira, podem ser substituídos pela utilização de detector de metal."
+    ◦ Fundamentação: Conforme o item 4.1.2, alínea 'a' (Pág. 77): "Caso haja disponível detector de metal, a utilização desse aparelho poderá substituir os movimentos rápidos de deslizamento das mãos sobre o vestuário do cidadão.".
+• CORRETA: "O PM Segurança, ao receber a arma de fogo localizada durante a busca, deve colocá-la no próprio coldre. Ressalta-se que o policial militar não deve colocar essa arma no chão, entre o colete e o corpo ou na cintura."
+    ◦ Fundamentação: Conforme o item 4.1.3, alínea 'b' (Págs. 84-86): "colocar a arma recolhida no coldre, tendo em vista que a arma do próprio policial está na mão. [...] Ressalta-se que o policial militar não deve colocar essa arma no chão, entre o colete e o corpo ou na cintura...",.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base no MTP 03 (Blitz Policial):
+• CORRETA : "Durante a blitz noturna, ao proceder à parada do veículo, o policial militar deverá solicitar ao condutor que apague os faróis, acenda a luz interna do veículo e mantenha as mãos em local visível, preferencialmente sobre o volante."
+    ◦ Fundamentação: Esta alternativa é a transcrição literal do procedimento previsto no item 5.2 (Blitz noturna), alínea 'f', segundo ponto. O manual instrui essa conduta para garantir a segurança da equipe e a visualização do interior do veículo.
+Análise das Incorreções:
+•  (Incorreta): "Recomenda-se que o policial militar aponte o foco da luz diretamente para os olhos..."
+    ◦ Fundamentação: O item 5.2, alínea 'f', quarto ponto, estabelece exatamente o contrário: "utilize uma lanterna para melhor visualizar o interior do veículo, evitando apontar o foco da luz diretamente para os olhos do condutor ou dos passageiros".
+•  (Incorreta): "A blitz noturna deve ser montada, preferencialmente, em local sem iluminação artificial e que proporcione ocultação dos militares..."
+    ◦ Fundamentação: O item 5.2, alínea 'a' determina que a blitz noturna deve ser montada, preferencialmente, em local com boa iluminação artificial e que proporcione segurança no aspecto de visualização do dispositivo, e não ocultação.
+•  (Incorreta): "...o policial militar deverá afastar-se e bater no vidro, solicitando que o condutor abra a janela lentamente."
+    ◦ Fundamentação: O item 5.2, alínea 'f', terceiro ponto, orienta que, caso o veículo possua película (Insulfilm), o policial deve afastar-se e, sem bater no vidro, solicitar a abertura da janela. Bater no vidro pode ser interpretado como agressão ou provocar reações inesperadas.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base no Memorando nº 30.070.2/2024 - EMPM:
+• CORRETA : "Os procedimentos policiais previstos para a natureza “I 04.028” (uso e consumo de drogas) decorrentes do art. 28 da Lei nº 11.343/06 permanecerão em uso para as demais drogas ilícitas, uma vez que o dispositivo legal continua vigente no Brasil. Nesse caso, a PMMG continuará lavrando o Termo Circunstanciado de Ocorrência (TCO)."
+    ◦ Fundamentação: Esta alternativa é a transcrição literal do item 5.7 do Memorando. A descriminalização afetou apenas a maconha; para cocaína, crack e outras substâncias, a conduta continua sendo crime (porte para uso) sujeito a TCO.
+Análise das Incorreções:
+•  (Incorreta): Afirma que a substância só deve ser apreendida se caracterizar crime.
+    ◦ Fundamentação: O item 5.2 estabelece que, embora tenha se tornado um ilícito administrativo, "Assim, em todas as hipóteses, a substância identificada deverá ser apreendida".
+•  (Incorreta): Afirma que o autor não pode ser preso por tráfico se portar menos de 40g.
+    ◦ Fundamentação: O item 5.3 esclarece que "Mantém-se a possibilidade de prisão em flagrante pelo crime de tráfico de drogas, mesmo para quantidades inferiores ao limite de 40 gramas... bastando a presença de elementos indicativos de traficância".
+•  (Incorreta): Afirma que a pesagem e diferenciação das plantas são imprescindíveis.
+    ◦ Fundamentação: O item 5.5 afirma exatamente o oposto: "A pesagem da droga e a diferenciação entre plantas fêmeas e/ou macho... não é imprescindível para o cumprimento da decisão do STF, na medida em que a presença ou não dos elementos configuradores do delito de tráfico de drogas é que definirá a natureza da ocorrência".</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• CORRETA : "O policial militar deve diligenciar para que a narração do fato realizada pelos envolvidos no fato, durante o registro da ocorrência, não seja feita diante da criança ou do adolescente, nem em local público, preservando sua dignidade individual e sua imagem."
+    ◦ Fundamentação: Esta alternativa é uma transcrição fiel do item 5.2.3 do POP nº 1.7.0.050 (Anexo ao Memorando nº 30.079.3/2024). O objetivo é evitar a revitimização e exposição indevida da criança ou adolescente.
+• INCORRETA : "...fazendo as intervenções e interrupções que se fizerem convenientes."
+    ◦ Fundamentação: O item 5.2.4 determina expressamente o oposto: "No caso de relato espontâneo, apenas ouvir atenta e calmamente o que expressar a criança ou adolescente, sem qualquer intervenção e interrupção, devendo transcrever a fala da vítima ou testemunha da mesma forma que lhe foi dito".
+• INCORRETA : "...nos casos que envolvam violência sexual contra criança ou adolescente do sexo masculino, o atendimento policial-militar será realizado, preferencialmente, por policial militar masculino."
+    ◦ Fundamentação: O item 5.1.5 estabelece apenas que: "Nos casos que envolvam violência sexual, o atendimento policial-militar será realizado, preferencialmente, por policial militar feminina". A norma não faz a distinção de gênero do policial baseada no gênero da vítima masculina, priorizando a policial feminina para casos de violência sexual em geral neste contexto.
+• INCORRETA : "...o policial militar deve gravar as imagens da criança ou adolescente..."
+    ◦ Fundamentação: O item 5.1.3 instrui que o policial militar deve evitar a gravação de imagens da criança ou adolescente vítima ou testemunha de violência. Além disso, o item 7.4 (Ações Corretivas) reforça: "Não gravar, inclusive com a COP, nos atos que envolvam a criança ou adolescente vítima ou testemunha de violência"</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada:
+• INCORRETA (Gabarito da Questão): "Suspensão da CNH."
+    ◦ Fundamentação: Esta alternativa é a exceção porque a suspensão da CNH não gera o descredenciamento automático, mas sim a suspensão do credenciamento. O item 6.6.4, alínea "c", determina que o descredenciamento ocorre na "cassação da CNH do PM". Já o item 6.6.3, alínea "c", estabelece que o condutor poderá ser suspenso da condição de motorista credenciado quando: "o militar tiver com a CNH vencida ou suspensa".
+• CORRETA (Hipótese de Descredenciamento): "Desligamento do serviço ativo, nos casos em que não for designado para o serviço ativo após dois anos da sua passagem para a reserva."
+    ◦ Fundamentação: Transcrição fiel do item 6.6.4, alínea "a", que lista as situações de descredenciamento: "desligamento do serviço ativo, nos casos em que não for designado para o serviço ativo após dois anos da sua passagem para a reserva".
+• CORRETA (Hipótese de Descredenciamento): "Reincidência em acidente com vítima (fatal ou não) na condução de viatura, após ser submetido a treinamento de atualização."
+    ◦ Fundamentação: Transcrição fiel do item 6.6.4, alínea "d", que lista as situações de descredenciamento: "reincidência em acidente com vítima (fatal ou não) na condução de viatura, após ser submetido a treinamento de atualização".
+• CORRETA (Hipótese de Descredenciamento): "Invalidez física ou psíquica permanente."
+    ◦ Fundamentação: Transcrição fiel do item 6.6.4, alínea "b", que lista as situações de descredenciamento: "invalidez física ou psíquica permanente"</t>
+  </si>
+  <si>
+    <t>Com base na Resolução nº 5.142, de 22 de novembro de 2021 (Manual de Gerenciamento de Frota da PMMG), a sequência correta é V, V, V, V.
+Seguem as justificativas detalhadas com as citações da norma:
+• (V) Verdadeiro: O texto reproduz fielmente o Item 6.2.3: "O militar dispensado por motivo de saúde que o impeça de conduzir viaturas deverá ser avaliado pelo médico da Unidade, sendo seu afastamento comunicado pelo NAIS, ou setor de saúde responsável, ao Chefe da Seção Administrativa ou equivalente para que a administração efetive os lançamentos correspondentes no SIAD e ele não seja incluído como motorista na escala, até cessarem os impedimentos."
+• (V) Verdadeiro: A afirmativa está em conformidade com o Item 6.1.6: "Deverá ser priorizado o emprego de viaturas locadas nas frações, não sendo admitido o emprego de viaturas orgânicas no serviço se houver viaturas locadas subutilizadas na fração."
+• (V) Verdadeiro: A assertiva corresponde exatamente ao Item 6.1.12: "As viaturas, durante a execução de patrulhamento, deverão manter acionados os dispositivos luminosos e, em caso de emergência, deverão, também, manter acionados os dispositivos sonoros, conforme previsto no CTB."
+• (V) Verdadeiro: A descrição das atribuições confere com o Item 8.2.3: "O Gestor de Frota da Unidade será o Chefe da Seção Administrativa da Unidade e terá como atribuições coordenar o uso, os lançamentos necessários no SIAD e os demais sistemas de controle adotados, além da adoção de providências para manutenção, elaboração de relatórios para subsidiar instauração de procedimentos administrativos e assessoramento ao Comandante da Unidade e do Gestor de Frota da UDI/RPM."</t>
+  </si>
+  <si>
+    <t>Análise Detalhada das Assertivas:
+• (V) Verdadeiro: A primeira assertiva é uma transcrição literal do Art. 12, que define os critérios de desempate e regulação da antiguidade.
+• (V) Verdadeiro: A segunda assertiva reproduz fielmente o Art. 13-B, incluído pela Lei Complementar nº 168/2022, que trata da possibilidade de assessoramento técnico por militares de quadros operacionais/complementares.
+• (V) Verdadeiro: A terceira assertiva está correta conforme o Art. 13.
+• (F) Falso: A quarta assertiva contém um erro no prazo. O Art. 15, § 3º determina que a antecedência mínima é de sete dias, e não cinco dias</t>
+  </si>
+  <si>
+    <t>• (F) Assertiva I: Está INCORRETA. O estatuto determina expressamente que esse tempo NÃO será computado para fins de promoção (interstício e formação de turma).
+    ◦ Fundamentação (Art. 13, § 12): "O aluno do CHO reprovado, desligado ou com impedimento à promoção retornará ao seu grau hierárquico anterior, não computando esse tempo para fins do art. 183 e dos §§ 1º e 2º do art. 187 desta Lei."
+• (V) Assertiva II: Está CORRETA. Reproduz fielmente o requisito de reabilitação moral para fins de promoção previsto no Art. 186.
+    ◦ Fundamentação (Art. 186, § 2º): "O Oficial punido em decorrência de sua submissão a processo administrativo disciplinar de natureza demissionária pela prática de ato que afete a honra pessoal ou o decoro da classe será considerado possuidor do requisito de idoneidade moral dois anos após o término do cumprimento da sanção disciplinar."
+• (V) Assertiva III: Está CORRETA. A assertiva transcreve exatamente o procedimento para o Aspirante declarado não vocacionado.
+    ◦ Fundamentação (Art. 192, Parágrafo único): "O Aspirante-a-Oficial que for declarado não vocacionado para o oficialato, nos termos de regulamentação específica, não será submetido novamente ao estágio previsto no § 2º do art. 13, devendo ser exonerado ou retornar à graduação que ocupava antes do início do Curso de Formação de Oficiais, no caso de militar estável que já pertencia à IME, após submissão a processo administrativo exoneratório ou equivalente."
+• (F) Assertiva IV: Está INCORRETA. O benefício de manter a nota da última ADI (se superior a 70%) não se aplica "independentemente do motivo", mas sim especificamente para casos de acidente de serviço ou moléstia profissional. Se o afastamento for por outro problema de saúde, a nota é fixada em 70%.
+    ◦ Fundamentação (Art. 59-C, §§ 4º e 5º):
+        ▪ § 4º: "O militar que não for avaliado por estar totalmente afastado por mais de cento e vinte dias de suas atividades devido a problemas de saúde terá o resultado de sua ADI fixado em 70% (setenta por cento), enquanto perdurar essa situação."
+        ▪ § 5º: "Se o afastamento previsto no § 4º for decorrente de acidente de serviço ou moléstia profissional, o militar permanecerá com o resultado da sua última ADI, se este for superior a 70% (setenta por cento)."</t>
+  </si>
+  <si>
+    <t>Com base na Lei Estadual nº 14.310, de 19/06/2002 (Código de Ética e Disciplina dos Militares de Minas Gerais - CEDM), a alternativa CORRETA é: Apenas as assertivas II e IV são verdadeiras.
+Seguem as justificativas detalhadas para cada assertiva, com as respectivas citações da norma:
+• (F) Assertiva I: Está INCORRETA. A regra é a publicação em boletim reservado, sendo vedada a divulgação ostensiva, exceto em casos específicos definidos pelo CEDMU para fins educativos.
+    ◦ Fundamentação (Art. 25, § 2º): "As sanções disciplinares de militares serão publicadas em boletim reservado, e o transgressor notificado pessoalmente, sendo vedada a sua divulgação ostensiva, salvo quando o conhecimento for imprescindível ao caráter educativo da coletividade, assim definido pelo CEDMU."
+• (V) Assertiva II: Está CORRETA. Reproduz fielmente as medidas administrativas que podem ser aplicadas cumulativamente com as sanções.
+    ◦ Fundamentação (Art. 25): "Poderão ser aplicadas, independentemente das demais sanções ou cumulativamente com elas, as seguintes medidas: I – cancelamento de matrícula, com desligamento de curso, estágio ou exame; II – destituição de cargo, função ou comissão; III – movimentação de unidade ou fração."
+• (F) Assertiva III: Está INCORRETA. O corte do ponto (perda de vencimentos) ocorre independentemente da aplicação de sanção disciplinar. Não é condicionado à punição.
+    ◦ Fundamentação (Art. 25, § 1º): "Quando se tratar de falta ou abandono ao serviço ou expediente, o militar perderá os vencimentos correspondentes aos dias em que se verificar a transgressão, independentemente da sanção disciplinar."
+• (V) Assertiva IV: Está CORRETA. A definição de Prestação de Serviço está exata conforme o texto legal.
+    ◦ Fundamentação (Art. 30): "A prestação de serviço consiste na atribuição ao militar de tarefa, preferencialmente de natureza operacional, fora de sua jornada habitual, correspondente a um turno de serviço semanal, que não exceda a oito horas, sem remuneração extra."</t>
+  </si>
+  <si>
+    <t>Com base na Lei Estadual nº 14.310, de 19/06/2002 (Código de Ética e Disciplina dos Militares do Estado de Minas Gerais - CEDM), a alternativa que aponta a EXCEÇÃO (ou seja, o ato que NÃO está listado explicitamente no rol do Art. 64, Parágrafo único, como afetador da honra pessoal ou decoro da classe para fins de submissão a PAD)
+Análise Detalhada:
+• A) INCORRETA (Gabarito da Questão): "Apresentar-se com sinais de embriaguez alcoólica ou sob efeito de outra substância entorpecente..."
+    ◦ Explicação: Embora seja uma Transgressão Disciplinar de Natureza Grave prevista no Art. 13, inciso VI, ela NÃO consta no rol taxativo do Art. 64, Parágrafo único, como um dos atos específicos que definem "afetar a honra pessoal ou o decoro da classe" para fins automáticos de PAD (salvo se enquadrada genericamente no inciso III do mesmo artigo como "faltar publicamente com o decoro pessoal, dando causa a grave escândalo", mas a descrição literal da embriaguez não está listada ali como inciso autônomo).
+• B) CORRETA (Consta no Art. 64): "Praticar ato atentatório à dignidade da pessoa ou que ofenda os princípios da cidadania e dos direitos humanos..."
+    ◦ Fundamentação: Art. 64, Parágrafo único, inciso I.
+• C) CORRETA (Consta no Art. 64): "Fazer uso do posto ou da graduação para obter ou permitir que terceiros obtenham vantagem pecuniária indevida."
+    ◦ Fundamentação: Art. 64, Parágrafo único, inciso V.
+• D) CORRETA (Consta no Art. 64): "Exercer coação ou assediar pessoas com as quais mantenha relações funcionais."
+    ◦ Fundamentação: Art. 64, Parágrafo único, inciso IV</t>
   </si>
 </sst>
 </file>
@@ -3426,6 +3591,9 @@
       <c r="J35" t="s">
         <v>33</v>
       </c>
+      <c r="K35" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="L35" t="s">
         <v>103</v>
       </c>
@@ -3461,6 +3629,9 @@
       <c r="J36" t="s">
         <v>27</v>
       </c>
+      <c r="K36" s="3" t="s">
+        <v>506</v>
+      </c>
       <c r="L36" t="s">
         <v>103</v>
       </c>
@@ -3496,6 +3667,9 @@
       <c r="J37" t="s">
         <v>57</v>
       </c>
+      <c r="K37" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="L37" t="s">
         <v>103</v>
       </c>
@@ -3531,6 +3705,9 @@
       <c r="J38" t="s">
         <v>33</v>
       </c>
+      <c r="K38" s="3" t="s">
+        <v>508</v>
+      </c>
       <c r="L38" t="s">
         <v>103</v>
       </c>
@@ -3566,6 +3743,9 @@
       <c r="J39" t="s">
         <v>33</v>
       </c>
+      <c r="K39" s="3" t="s">
+        <v>509</v>
+      </c>
       <c r="L39" t="s">
         <v>103</v>
       </c>
@@ -3969,6 +4149,9 @@
       <c r="J50" t="s">
         <v>57</v>
       </c>
+      <c r="K50" s="3" t="s">
+        <v>495</v>
+      </c>
       <c r="L50" t="s">
         <v>103</v>
       </c>
@@ -4004,6 +4187,9 @@
       <c r="J51" t="s">
         <v>57</v>
       </c>
+      <c r="K51" s="3" t="s">
+        <v>496</v>
+      </c>
       <c r="L51" t="s">
         <v>103</v>
       </c>
@@ -4039,6 +4225,9 @@
       <c r="J52" t="s">
         <v>20</v>
       </c>
+      <c r="K52" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="L52" t="s">
         <v>103</v>
       </c>
@@ -4074,6 +4263,9 @@
       <c r="J53" t="s">
         <v>57</v>
       </c>
+      <c r="K53" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="L53" t="s">
         <v>103</v>
       </c>
@@ -4147,6 +4339,9 @@
       <c r="J55" t="s">
         <v>20</v>
       </c>
+      <c r="K55" s="3" t="s">
+        <v>499</v>
+      </c>
       <c r="L55" t="s">
         <v>343</v>
       </c>
@@ -4255,6 +4450,9 @@
       <c r="J58" t="s">
         <v>57</v>
       </c>
+      <c r="K58" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="L58" t="s">
         <v>343</v>
       </c>
@@ -4290,6 +4488,9 @@
       <c r="J59" t="s">
         <v>20</v>
       </c>
+      <c r="K59" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="L59" t="s">
         <v>343</v>
       </c>
@@ -4325,6 +4526,9 @@
       <c r="J60" t="s">
         <v>33</v>
       </c>
+      <c r="K60" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="L60" t="s">
         <v>343</v>
       </c>
@@ -4360,6 +4564,9 @@
       <c r="J61" t="s">
         <v>20</v>
       </c>
+      <c r="K61" s="3" t="s">
+        <v>503</v>
+      </c>
       <c r="L61" t="s">
         <v>343</v>
       </c>
@@ -4429,6 +4636,9 @@
       </c>
       <c r="J63" t="s">
         <v>20</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>504</v>
       </c>
       <c r="L63" t="s">
         <v>343</v>

--- a/QUESTOES PROVA CRS.xlsx
+++ b/QUESTOES PROVA CRS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julião\Downloads\chobot-main (1)\chobot-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D52E820-FD56-49C2-9A6F-0219BA59B08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C719F259-84CD-450A-9264-967D7CC3A169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="1133">
   <si>
     <t>ID</t>
   </si>
@@ -1923,6 +1923,2148 @@
     ◦ Fundamentação: Art. 64, Parágrafo único, inciso V.
 • D) CORRETA (Consta no Art. 64): "Exercer coação ou assediar pessoas com as quais mantenha relações funcionais."
     ◦ Fundamentação: Art. 64, Parágrafo único, inciso IV</t>
+  </si>
+  <si>
+    <t>De acordo com o Memorando 30.001.2/2024-EMPM, de 05/01/2024, que trata sobre a atuação policial em face do crime de abuso e maus-tratos aos animais, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>O crime de maus-tratos aos animais pode ser cometido na modalidade dolosa ou culposa, o que significa dizer que, para cometer o crime, o agente deve querer o resultado ou assumir o risco de produzi-lo, ou, ainda, quando o agente der causa ao resultado por imprudência, negligência ou imperícia.</t>
+  </si>
+  <si>
+    <t>O REDS do crime de maus-tratos deve ser registrado apenas quando o alvo da infração possua tutor/proprietário ou quando a autoria do crime seja identificada. Não sendo a autoria identificada ou não possuindo tutor, o fato deve ser registrado através de BOS com natureza “U 33.024 – ATENDIMENTO DE DENÚNCIA DE INFRAÇÕES DE MAUS-TRATOS A ANIMAIS”.</t>
+  </si>
+  <si>
+    <t>Deixar de propiciar morte rápida e indolor a animal cuja eutanásia seja necessária e recomendada por médico veterinário é um ato considerado como maus-tratos contra animais.</t>
+  </si>
+  <si>
+    <t>No caso de animal doméstico, constatado o crime de abuso ou maus-tratos, os militares devem acionar o órgão municipal competente ou o CBMMG para captura e recolhimento do animal, se for cabível. Na impossibilidade do comparecimento de órgão municipal competente ou Corpo de Bombeiros Militar, em caráter excepcional, a equipe policial militar, após prévia avaliação de risco e conveniência da ação, poderá destinar cão ou gato, que seja alvo do crime, à tutoria do autor do delito.</t>
+  </si>
+  <si>
+    <t>CHO/2025</t>
+  </si>
+  <si>
+    <t>Com base na metodologia de avaliação de riscos e no Pensamento Tático, estabelecidos pelo Manual Técnico-Profissional 3.04.01/2020-CG (MTP 01) - Intervenção Policial, Processo de Comunicação e Uso da Força, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>A identificação de direitos e garantias sob ameaça (etapa 01 da avaliação de riscos) consiste em identificar qual direito ou garantia está exposto ao risco, os bens móveis e imóveis sujeitos a algum tipo de dano, as circunstâncias e o histórico dos fatos, o comportamento das possíveis vítimas envolvidas, o tipo de delito e a possibilidade de evolução do problema.</t>
+  </si>
+  <si>
+    <t>A classificação das ameaças (etapa 02 da avaliação de riscos) consiste em avaliar as características dos fatores que ameaçam direitos e garantias, permitindo ao policial militar agir dentro de padrões de segurança, auxiliando na escolha do comportamento tático mais adequado, além de lhe propiciar melhores condições para assegurar os direitos e proteger todos os envolvidos. A classificação das ameaças está estruturada em níveis I, II e III.</t>
+  </si>
+  <si>
+    <t>Em algumas situações, a avaliação de riscos leva o policial militar à conclusão de que não possui condições suficientes (efetivo de policiais, armamento, treinamento, entre outros) para agir imediatamente.</t>
+  </si>
+  <si>
+    <t>A avaliação dos possíveis resultados (etapa 5 da avaliação de riscos) é a análise da relação custobenefício da intervenção policial-militar diante de cada situação de risco. Cabe ao policial militar estimar quais serão os resultados de suas ações e seus reflexos na defesa da vida e das pessoas, no reforço de um cenário de paz social e na imagem da PMMG.</t>
+  </si>
+  <si>
+    <t>Acerca do tema Abordagem a pessoas, considerando o Manual Técnico-Profissional 3.04.01/2020-CG (MTP 01) - Intervenção Policial, Processo de Comunicação e Uso da Força e o Manual Técnico-Profissional 3.04.02/2020-CG (MTP 02) - Abordagem a pessoas, analise as assertivas abaixo: 
+I. A abordagem policial é o conjunto ordenado de ações policiais para aproximar-se de uma ou mais pessoas, veículos ou edificações. 
+II. Abordagem a pessoa com características semelhantes às de envolvidos em delitos é um exemplo de uma intervenção de nível II. 
+III. O policial militar deve manter o equilíbrio e o autocontrole, mesmo se o abordado não obedecer, se fizer comentários ofensivos, ignorar a sua presença ou atrair a atenção de pessoas em volta. 
+IV. Ação de abordar uma pessoa é um ato administrativo, não discricionário, autoexecutório e coercitivo. 
+V. Ao realizar uma abordagem a pessoa em atitude suspeita, o policial militar deverá observar a Segurança, Surpresa, Rapidez, Ação Vigorosa e Unidade de Comando. 
+Marque a alternativa que contém a resposta CORRETA.</t>
+  </si>
+  <si>
+    <t>Apenas as alternativas I, III e V são verdadeiras.</t>
+  </si>
+  <si>
+    <t>As alternativas I, II, III, IV e V são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Apenas as alternativas I e IV são falsas.</t>
+  </si>
+  <si>
+    <t>Apenas a alternativa IV é falsa.</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe o Manual Técnico-Profissional 3.04.02/2020-CG (MTP 02) - Abordagem a pessoas, a respeito dos procedimentos policiais em ocorrências envolvendo autoridades, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Nos casos de flagrante de crime, afiançável ou não, e infrações de menor potencial ofensivo, praticados por Juízes Estaduais, o policial militar deverá realizar apenas o registro do BO/REDS que será encaminhado para o Presidente do Tribunal a que esteja vinculado para possíveis providências, sendo os Magistrados liberados no local.</t>
+  </si>
+  <si>
+    <t>Prefeitos possuem prerrogativas em relação à prisão em flagrante no cometimento de delitos. O policial militar deverá, neste caso, apenas registrar o Boletim de Ocorrência (BO/REDS), encaminhando-o à Polícia Judiciária Estadual (Polícia Civil) para possíveis providências, não devendo conduzi-lo preso.</t>
+  </si>
+  <si>
+    <t>Nos casos de ocorrências envolvendo policiais penais, o policial militar deverá prendê-los e registrar o Boletim de Ocorrência (BO/REDS). Será encaminhado à Polícia Judiciária competente, para possíveis providências. Não possuem prerrogativas em relação à prisão em flagrante no cometimento de delitos, assim não é necessário a chegada de integrantes da Instituição do conduzido, tendo o mesmo tratamento dos demais cidadãos.</t>
+  </si>
+  <si>
+    <t>Na hipótese de prisão de membros da Polícia Civil, o policial militar deverá neste caso prendê-los e registrar o Boletim de Ocorrência (BO/REDS). Após a chegada do superior hierárquico do conduzido, será encaminhado à Polícia Judiciária competente, para possíveis providências. Não possuem prerrogativas em relação à prisão em flagrante no cometimento de delitos, tendo o mesmo tratamento dos demais cidadãos.</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe o Manual Técnico-Profissional 3.04.03/2020-CG (MTP 03) - Blitz Policial e o Manual Técnico-Profissional 3.04.04/2020-CG (MTP 04) - Abordagem a Veículos, marque a alternativa que classifica a blitz quanto à categoria (MTP 03) e os níveis de abordagem a veículos (MTP 04) de forma CORRETA.</t>
+  </si>
+  <si>
+    <t>A blitz de categoria 3, considerada de grande porte, possui efetivo de 07 ou mais policiais e o mínimo de duas viaturas policiais, podendo nesta categoria ser instalados dois ou mais boxes. Já a abordagem a veículo - nível 1 - será empregada nas ações e operações policiais de caráter educativo e assistencial (risco nível I), cujo estado de prontidão coerente é o alerta (laranja).</t>
+  </si>
+  <si>
+    <t>A blitz de categoria 2, considerada de médio porte, possui efetivo de 04 a 06 policiais e o mínimo de uma viatura policial, podendo nesta categoria ser instalados dois ou mais boxes. Já a abordagem de veículo - nível 2 - será empregada nas ações e operações de verificação preventiva (risco nível II) ou em fatos que indiquem ameaça à segurança pública, cujo estado de prontidão coerente é o alerta (laranja).</t>
+  </si>
+  <si>
+    <t>A blitz de categoria 1, considerada de pequeno porte, possui efetivo de 02 ou 03 policiais e o mínimo de uma viatura policial e será instalado apenas um box. Já a abordagem a veículo - nível 3 - será empregada nas ações e operações repressivas, caracterizadas por situações onde há um elevado grau de perigo ou a certeza do cometimento de delito (risco nível III). O estado de prontidão coerente é o alerta (laranja).</t>
+  </si>
+  <si>
+    <t>A blitz de categoria 1, considerada de pequeno porte, possui efetivo de 02 ou 03 policiais e o mínimo de uma viatura policial, podendo nesta categoria ser instalados dois ou mais boxes. Já a abordagem a veículo - nível 1 - será empregada nas ações e operações policiais de caráter educativo e assistencial (risco nível I). Nesse caso, o estado de prontidão coerente é o atenção (amarelo).</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe no Manual Técnico-Profissional 3.04.03/2020-CG (MTP 03) - Blitz Policial, analise as seguintes assertivas: 
+I. A blitz policial deve ser precedida de planejamento elaborado pela Seção de Emprego Operacional (P3), por meio de ordens de serviço ou outros instrumentos, nos quais estejam presentes todos os aspectos que, direta ou indiretamente, venham a contribuir para o sucesso da operação. 
+II. Após a instalação do dispositivo_operacional, havendo condições favoráveis ao contato e interação com a população local, dentro dos princípios da polícia comunitária, o militar poderá informar aos cidadãos residentes, ou que exerçam atividades comerciais nas proximidades, sobre a importância e os benefícios da operação para a promoção da segurança pública e da prevenção da criminalidade, sendo vedado fornecer quaisquer informações sobre a duração do empenho e a finalidade da operação. 
+III. Durante a operação blitz, o emprego de arma de fogo em situação de resistência ativa (com agressão letal) na qual o abordado utiliza de agressão que põe em perigo de morte o policial ou pessoas envolvidas na intervenção, a resposta imediata será do PM Segurança, que estará com a arma em pronta resposta. A primeira reação dos policiais deve ser voltada para a preservação de suas vidas e dos cidadãos, por isso, deverão procurar abrigo e somente disparar quando presentes as condições exigidas pelas normas em vigor. 
+IV. Durante uma operação blitz, caso ocorra a parada de um veículo com número de ocupantes adultos superior ao de policiais e ainda estejam presentes outros fatores da análise de risco que indiquem falta de segurança para a guarnição seguir na intervenção, é recomendável liberar imediatamente o veículo sem abordá-lo, e recorrer a outros procedimentos técnicos e táticos, como apoio de outras guarnições ou cerco e bloqueio, para que a ação de resposta seja efetiva. 
+Marque a alternativa que contém a resposta CORRETA.</t>
+  </si>
+  <si>
+    <t>Apenas as assertivas I, III e IV estão corretas.</t>
+  </si>
+  <si>
+    <t>Apenas as assertivas I e III estão corretas.</t>
+  </si>
+  <si>
+    <t>Apenas as assertivas II e IV estão corretas.</t>
+  </si>
+  <si>
+    <t>Apenas as assertivas I e II estão corretas.</t>
+  </si>
+  <si>
+    <t>MTP 05</t>
+  </si>
+  <si>
+    <t>Conforme o Manual Técnico-Profissional 3.04.05/2020-CG (MTP 05) - Escoltas Policiais e Conduções diversas, marque a alternativa CORRETA, em relação à classificação das escoltas quanto à complexidade.</t>
+  </si>
+  <si>
+    <t>Escolta extraordinária é aquela que, pelas informações previamente obtidas, seja pela Atividade de Inteligência, por qualquer fonte confiável, ou mesmo pelo clamor público, represente um alto risco para os policiais e para o(s) escoltado(s). Essa atividade deverá, obrigatoriamente, ser executada por uma Unidade Especializada, analisando a necessidade e conveniência de apoio da Seção de Inteligência.</t>
+  </si>
+  <si>
+    <t>Escolta ordinária é aquela habitualmente realizada pelo policiamento, decorrente do turno, sem solicitação prévia e sem a necessidade de confecção de Ordem de Serviço específica.</t>
+  </si>
+  <si>
+    <t>Escolta extraordinária é aquela solicitada com antecedência pela autoridade competente e, dessa forma, exige planejamento específico no que se refere aos recursos logísticos e humanos empregados.</t>
+  </si>
+  <si>
+    <t>Escolta extraordinária (por exemplo: as escoltas de valores e de dignitários) deve ser executada, preferencialmente, por policiais pertencentes às Unidades Especializadas – Btl ROTAM, BOPE, BPChq, BPE, Cia PM Ind. PE ou Companhia de Recobrimento das Unidades (Tático Móvel).</t>
+  </si>
+  <si>
+    <t>Manual Técnico-Profissional nº 3.04.05/2020-CG (MTP 05)</t>
+  </si>
+  <si>
+    <t>PREVENÇÃO DE HOMICIDIOS</t>
+  </si>
+  <si>
+    <t>Conforme previsto na Instrução nº 3.03.10/2023-CG – Regula o emprego da Polícia Militar com vistas à prevenção e repressão aos crimes de homicídio - 2ª edição, uma das ferramentas para a prevenção ao homicídio consiste na realização de visitas preventivas por meio da classificação preditiva de ação preventiva. A coordenação do monitoramento por meio das visitas preventivas é atribuição do Coordenador de Policiamento da Unidade (CPU) ou policial empregado em função correlata. De acordo com a referida Instrução, todas as alternativas abaixo descrevem uma atividade a ser realizada pelo CPU, EXCETO:</t>
+  </si>
+  <si>
+    <t>Verificar se os registros das atividades contemplam as informações básicas e se foram registradas com as naturezas adequadas.</t>
+  </si>
+  <si>
+    <t>Certificar-se de que as equipes realizaram os devidos registros até o final do turno de serviço.</t>
+  </si>
+  <si>
+    <t>Em caso de ser identificado que o alvo da visita possui mandado de prisão em aberto, planejar operação para cumprimento e coordenar a sua execução.</t>
+  </si>
+  <si>
+    <t>Acessar via Intranet PM (Unidades – “RPM” – Classificação Preditiva de Homicídios - CPH) e selecionar os indivíduos para monitoramento preventivo a serem visitados.</t>
+  </si>
+  <si>
+    <t>Instrução nº 3.03.10/2023-CG – Regula o emprego da Polícia Militar com vistas à prevenção e repressão aos crimes de homicídio - 2ª edição</t>
+  </si>
+  <si>
+    <t>De acordo com o disposto pelo Memorando n° 30.070.2/24 – EMPM, que trata dos procedimentos policiais decorrentes da descriminalização do porte de Cannabis sativa (maconha) para consumo pessoal conforme decisão do STF, considerando os procedimentos básicos ou sequência de ações, especificamente nas ocorrências de porte de até 40 gramas ou até 6 plantas de Cannabis sativa (maconha) juntamente a outras drogas, para consumo pessoal, com autores adultos, marque a alternativa INCORRETA a respeito das condutas que devem ser adotadas pelo policial militar.</t>
+  </si>
+  <si>
+    <t>Lavrar o TCO com o registro do REDS-TC.</t>
+  </si>
+  <si>
+    <t>Lavrar o BO com a natureza I 99.000 (outros tipos de infrações referentes a substâncias entorpecentes ou que determinem dependência) até que seja criada natureza específica para essa finalidade, sendo vedada a lavratura de TCO.</t>
+  </si>
+  <si>
+    <t>Utilizar como natureza principal I 04.028 (uso e consumo de drogas) em razão do porte de substância análoga à droga (diversa da maconha) para consumo pessoal e inserir como natureza secundária I 99.000 (outros tipos de infrações referentes a substâncias entorpecentes ou que determinem dependência), descrevendo todo o material apreendido.</t>
+  </si>
+  <si>
+    <t>Apreender as substâncias, especificar em campo próprio no REDS-TC, destinar o REDS-TC ao JECrim e liberar o abordado.</t>
+  </si>
+  <si>
+    <t>Memorando n° 30.070.2/24 – EMPM, que trata dos procedimentos policiais decorrentes da descriminalização do porte de Cannabis sativa (maconha)</t>
+  </si>
+  <si>
+    <t>O Memorando nº 30.079.3/2024-EMPM estabelece o Protocolo de Atuação para o Atendimento de Criança e Adolescente Vítima ou Testemunha de Violência. Com base nesse Memorando, considerando os procedimentos previstos que devem ser adotados pelo policial militar durante o registro da ocorrência, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>A criança ou adolescente, mesmo que desacompanhados, tem assegurado o direito ao registro da ocorrência policial.</t>
+  </si>
+  <si>
+    <t>No caso de relato espontâneo da vítima ou testemunha criança ou adolescente, o policial militar ouvirá atenta e calmamente o que ela expressar, devendo realizar intervenções, exclusivamente ao final, para sanar dúvida ou para esclarecer algum ponto.</t>
+  </si>
+  <si>
+    <t>Durante a realização das diligências relativas ao registro do REDS, a condução das crianças ou adolescentes vítima ou testemunha de violência deverá ser realizada em veículo distinto da viatura que conduzirá o autor (a) da violência.</t>
+  </si>
+  <si>
+    <t>Resguardar a criança e o adolescente de qualquer contato, ainda que visual, com o suposto autor ou acusado ou com outra pessoa que represente ameaça, coação ou constrangimento.</t>
+  </si>
+  <si>
+    <t>Considerando a Diretriz Geral para Emprego Operacional nº 3.01.01/2019-CG, que regula o emprego operacional da Polícia Militar de Minas Gerais, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>Em relação à Lei Estadual nº 5.301, de 16 de outubro de 1969, que contém o Estatuto dos Militares do Estado de Minas Gerais, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe a Lei Estadual nº 5.301, de 16 de outubro de 1969 - Estatuto dos Militares do Estado de Minas Gerais, marque alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Nos termos da Resolução nº 5.380/2024, que dispõe sobre a regulamentação do uso, gerenciamento e extração de relatórios do Sistema GeoPM, e da Resolução nº 5.379/2024, que aprova o Programa de Integridade da Polícia Militar de Minas Gerais, marque a alternativa a INCORRETA.</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe a Resolução Conjunta nº 4.220, de 28 de junho de 2012 - Manual de Processos e Procedimentos Administrativos das Instituições Militares de Minas Gerais (MAPPA), marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe a Resolução n° 5.136, de 08 de outubro de 2021 - Cautela fixa de arma de fogo pertencente à Polícia Militar de Minas Gerais e o Memorando Técnico nº 01/2021-DAL, de 5 de novembro de 2021 – Autorização para Cautela Fixa de Arma de Fogo – CFAF, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe a Instrução Conjunta de Corregedorias nº 01 (ICCPM/BM nº 01/2014), que padroniza as atividades administrativas e disciplinares, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Sobre a regulamentação das Comissões de Acompanhamento e Controle da Letalidade e do Uso da Força das Unidades no âmbito da PMMG, prevista na ICCPM/BM nº 02/2014, que padroniza as atividades de Polícia Judiciária Militar, marque a alternativa que NÃO corresponde a uma análise primária no que concerne ao acompanhamento que deve ser desdobrado pela Comissão.</t>
+  </si>
+  <si>
+    <t>As atividades exercidas pelo Grupo Especial de Policiamento Ambiental (GEPAM) e pelo Grupo Tático Rodoviário (GTR), encontram-se no 2º esforço de emprego operacional.</t>
+  </si>
+  <si>
+    <t>O 5º esforço de emprego – Esforço Suplementar – considerando as características específicas da Academia de Polícia Militar e do Batalhão Metrópole, no que se refere ao efetivo disponível da atividade-meio empregado na atividade fim, estes poderão ser empregados, conforme o conceito de operação atribuído, em caráter especial ou extraordinário, preferencialmente, nas subáreas das Cias Operacionais da RMBH onde os índices criminais demonstrem esta necessidade, como força de reação do Comando-Geral, a critério do Chefe do Estado-Maior da Polícia Militar.</t>
+  </si>
+  <si>
+    <t>O 4º esforço de emprego operacional ocorre em resposta às ocorrências complexas, ou potencialmente violentas, ou que por sua dimensão ou repercussão exijam respostas estratégicas altamente qualificadas que extrapolem a capacidade de atuação do policiamento ordinário.</t>
+  </si>
+  <si>
+    <t>A força-tarefa é uma estrutura organizacional temporária, flexível, adaptável, dinâmica e integrada, com comando próprio, subordinado diretamente ao Comandante-Geral. É empregada para fazer frente a situações de grave perturbação da ordem, ou eventos de grande repercussão (nacional ou internacional) em que há necessidade da atuação simultânea de diversos esforços de defesa social e envolvimento direto do Comando-Geral. LEGISLAÇÃO INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>O somatório de percentuais de ADE e de adicionais por tempo de serviço na forma de quinquênio ou trintenário não poderá exceder a 70% (setenta por cento) da remuneração básica do militar.</t>
+  </si>
+  <si>
+    <t>O valor do ADE será determinado a cada mês, levando-se em conta o número de Avaliações de Desempenho Individual – ADIs – satisfatórias obtidas pelo militar.</t>
+  </si>
+  <si>
+    <t>Nos casos de nomeação coletiva mediante concurso, de declaração de Aspirante a Oficial e de promoção a 3º Sargento, a Cabo e a Soldado de 1ª Classe, prevalecerá, para efeito de antiguidade, a ordem de classificação obtida no concurso ou curso.</t>
+  </si>
+  <si>
+    <t>O militar da ativa que aceitar cargo público civil temporário, não eletivo, assim como em autarquia, empresa pública ou sociedade de economia mista, ficará agregado ao respectivo quadro, e, enquanto permanecer nessa situação, poderá ser promovido por antiguidade ou por merecimento, contandose lhe o tempo de serviço apenas para promoção, transferência para a reserva ou reforma.</t>
+  </si>
+  <si>
+    <t>O ADE será incorporado aos proventos do militar quando de sua transferência para a inatividade, em valor correspondente a um percentual da sua remuneração básica, estabelecido conforme o número de ADIs com desempenho satisfatório por ele obtido, respeitados os percentuais máximos. Caso o militar possua 27 (vinte e sete) ADIs com desempenho satisfatório, o ADE a ser incorporado será de até 58% (cinquenta e oito por cento).</t>
+  </si>
+  <si>
+    <t>O valor do ADE será cumulativo, devendo o percentual apurado a cada nível somar ao percentual anteriormente percebido pelo militar.</t>
+  </si>
+  <si>
+    <t>O militar, quando em tratamento de saúde em consequência de ferimentos ou doença decorrentes do serviço público, terá direito ao soldo e vantagens do posto ou graduação, até o período de 2 (dois) anos.</t>
+  </si>
+  <si>
+    <t>Os militares pertencentes ao QOS-PM/BM não poderão ser aproveitados na atividade-fim das instituições militares estaduais.</t>
+  </si>
+  <si>
+    <t>Irá perder 4 pontos; seu novo conceito será B 46 pontos positivos; a sanção disciplinar será de advertência.</t>
+  </si>
+  <si>
+    <t>Irá perder 15 pontos; seu novo conceito será B 35 pontos positivos; a sanção disciplinar será de prestação de serviço.</t>
+  </si>
+  <si>
+    <t>Irá perder 2 pontos; seu novo conceito será B 48 pontos positivos; a sanção disciplinar será de advertência.</t>
+  </si>
+  <si>
+    <t>Irá perder 12 pontos; seu novo conceito será B 38 pontos positivos; a sanção disciplinar será de prestação de serviço.</t>
+  </si>
+  <si>
+    <t>Os dados e informações existentes no GeoPM, independentemente da fonte de onde foram obtidos e de quem os produziu, são de propriedade da Polícia Militar de Minas Gerais. As informações disponibilizadas pelo GeoPM poderão ser acessadas por policiais militares ou servidores civis, sem que haja a necessidade de autorização.</t>
+  </si>
+  <si>
+    <t>A Diretoria de Operações – DOP – é a Unidade de Direção Intermediária responsável pela coordenação, controle, gestão de acesso, utilização, sigilo e controle dos dados e informações provenientes do GeoPM. No âmbito da DOP, caberá ao Centro de Gerenciamento e_Análise de Dados – CGA/DOP – o gerenciamento dos dados dos sistemas tratados na Resolução nº 5.380/2024.</t>
+  </si>
+  <si>
+    <t>Os usuários que não acessarem os sistemas tratados na Resolução nº 5.380/2024, por um período superior a 90 (noventa) dias poderão ter o acesso revogado por inatividade. Em caso de revogação por inatividade, o próprio usuário poderá solicitar a reativação do acesso através de solicitação ao CGA/DOP, via Portal de Serviços da IntranetPM.</t>
+  </si>
+  <si>
+    <t>A PMMG aderiu ao Programa Nacional de Prevenção a Corrupção, que é um projeto colaborativo que tem como principal objetivo mobilizar as instituições de controle, suas redes constituídas e gestores públicos em uma estratégia para combater a corrupção em resposta aos anseios da sociedade.</t>
+  </si>
+  <si>
+    <t>A publicação do ato de solução da SAD, decidindo a autoridade militar pelo arquivamento ou pelo enquadramento disciplinar, se dará sempre no boletim interno reservado, visando preservar informações pessoais dos envolvidos.</t>
+  </si>
+  <si>
+    <t>As tipificações contidas no TAV para as RED finais podem ser modificadas na solução do processo, pela autoridade competente, independentemente de ser para maior, igual ou menor gravidade e, ainda, que o acusado tenha, efetivamente, se defendido do(s) fato(s).</t>
+  </si>
+  <si>
+    <t>O sobrestamento de qualquer processo ou procedimento administrativo, além das situações especificadas no MAPPA, a critério da autoridade militar competente, poderá ocorrer em situação de férias, licenças, dispensas e outros motivos justificados, por prazo razoável, não superior a 30 (trinta) dias corridos e desde que não favoreça a ocorrência da prescrição administrativa.</t>
+  </si>
+  <si>
+    <t>A absolvição criminal e/ou civil por insuficiência/ausência de provas não impede a aplicação de sanção disciplinar, ressalvadas as hipóteses em que o juiz tenha reconhecido a inexistência do fato ou a negativa de autoria.</t>
+  </si>
+  <si>
+    <t>Ao militar que se envolver em ação legítima, da qual resultar em apreensão da arma de fogo institucional, poderá ser concedido nova CFAF, de imediato, a critério do Comandante e observados os demais requisitos, com isso, perdendo a validade da documentação inicial.</t>
+  </si>
+  <si>
+    <t>As armas de fogo institucionais brasonadas não necessitam ser conduzidas com Certificado de Registro de Arma de Fogo, devendo o policial militar, em todas as circunstâncias, estar portando a Carteira Especial de Identidade (CEI), a qual lhe confere o Porte.</t>
+  </si>
+  <si>
+    <t>O militar que tiver cassada a sua autorização de CFAF, somente poderá obter nova autorização após o prazo de 2 (dois) anos.</t>
+  </si>
+  <si>
+    <t>O militar que tenha contribuído dolosamente para o extravio de arma de fogo que se encontrava sob sua responsabilidade terá a CFAF cassada. A referida cassação não ocorrerá se a contribuição para o extravio for culposa.</t>
+  </si>
+  <si>
+    <t>A transgressão disciplinar que se define por descumprir norma técnica de utilização e manuseio de armamento ou equipamento, não se aplica aos casos em que o militar incorrer em inobservância de norma específica de uso de viatura.</t>
+  </si>
+  <si>
+    <t>Ocorrendo a identidade entre a transgressão disciplinar e o crime militar, seja ele próprio ou não, configura bis in idem a punição na seara administrativa pelas transgressões residuais que aflorem no mesmo fato.</t>
+  </si>
+  <si>
+    <t>A autoridade que instaurar o processo ou procedimento disciplinar poderá, ao final dos trabalhos e antes da solução, determinar ao Encarregado a realização de diligências complementares que vislumbrar necessárias, ainda que não seja competente para solucioná-lo.</t>
+  </si>
+  <si>
+    <t>A Autoridade Militar competente para solucionar o processo ou procedimento administrativo, em que aflorar a notícia do cometimento de crime comum por parte de militar, deverá encaminhar cópia dos autos ao Juizado Especial Criminal.</t>
+  </si>
+  <si>
+    <t>Obediência pelo policial militar aos princípios da legalidade, necessidade, proporcionalidade, moderação e conveniência no uso da força.</t>
+  </si>
+  <si>
+    <t>Ocorrência de uso de arma de fogo contra veículo que desrespeite bloqueio policial em via pública ou em fuga, a não ser que o ato represente um risco imediato de morte ou lesão grave aos policiais ou terceiros.</t>
+  </si>
+  <si>
+    <t>Necessidade efetiva do uso de arma de fogo pelo policial militar, decorrente de ação em legítima defesa própria ou de terceiro contra perigo iminente de morte ou lesão grave.</t>
+  </si>
+  <si>
+    <t>Verificação da instauração do procedimento de polícia judiciária militar ou administrativo-disciplinar (Auto de Prisão em Flagrante, Inquérito Policial Militar, Sindicância Regular ou Sindicância Regular Reservada, Relatório de Investigação Preliminar).</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe a Lei Estadual nº 14.310, de 19 de junho de 2002 - Código de Ética e Disciplina dos Militares do Estado de Minas Gerais, analise o caso hipotético abaixo: 
+Determinado militar cometeu a transgressão disciplinar de: referir-se de modo depreciativo a outro militar, a autoridade e a ato da administração pública. No julgamento da referida transgressão disciplinar foi verificado que esse militar possui 02 (duas) atenuantes: serviços relevantes prestados à PMMG e está classificado no conceito “A”. Além disso, não foi computada agravante à transgressão. O imputado possui 01 (um) elogio individual e 02 (duas) notas meritórias, com as respectivas pontuações previstas, dentro do prazo de validade. Caso seja sancionado, 
+marque a alternativa CORRETA, que descreva quantos pontos o militar irá perder, qual será o seu novo conceito e qual sanção disciplinar lhe será aplicada:</t>
+  </si>
+  <si>
+    <t>Resolução nº 5.380/2024, que dispõe sobre a regulamentação do uso, gerenciamento e extração de relatórios do Sistema GeoPM, e da Resolução nº 5.379/2024, que aprova o Programa de Integridade da Polícia Militar de Minas Gerais</t>
+  </si>
+  <si>
+    <t>ICCPM/BM nº 02/14</t>
+  </si>
+  <si>
+    <t>GEOPM</t>
+  </si>
+  <si>
+    <t>ICCPM 02</t>
+  </si>
+  <si>
+    <t>De acordo com a Resolução Conjunta nº 5.346/2024, que aprova o Manual de Polícia Judiciária das Instituições Militares do Estado de Minas Gerais, quanto à participação do advogado do militar conduzido na instrução do Auto de Prisão em Flagrante (APF) e da audiência de custódia, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Quanto a participação do militar conduzido nas oitivas do militar condutor, do(s) ofendido(s) e da(s) testemunha(s), temos por certo que há uma permissão doutrinária e fática para que ocorra, uma vez que o APF se trata de um Processo Administrativo e que, qualquer proibição de participação do conduzido, poderia redundar em prejuízo à investigação que se encontra em pleno curso.</t>
+  </si>
+  <si>
+    <t>O advogado poderá ter acesso aos elementos de prova já documentados no APF e aos documentos que estão sendo produzidos. A título de exemplo, o advogado poderá ter acesso à oitiva de uma testemunha que já se encontra juntada aos autos de APF (diligência finda, pretérita) e acessar uma oitiva, em andamento, de testemunha.</t>
+  </si>
+  <si>
+    <t>O advogado do conduzido não será notificado a participar das oitivas do condutor, ofendido e testemunhas a serem ouvidas em sede de APF. Além disso, há de ser ressaltado que incumbe ao próprio militar conduzido cientificar o seu advogado constituído sobre a data, hora e local em que será ouvido na investigação criminal.</t>
+  </si>
+  <si>
+    <t>A audiência de custódia consiste em uma medida de controle judicial que visa avaliar a legalidade da medida constritiva de liberdade infligida, bem como apreciar as questões relativas à pessoa do autor da prisão.</t>
+  </si>
+  <si>
+    <t>F-V-F-V.</t>
+  </si>
+  <si>
+    <t>V-F-V-F.</t>
+  </si>
+  <si>
+    <t>V-F-F-V.</t>
+  </si>
+  <si>
+    <t>F-V-V-F.</t>
+  </si>
+  <si>
+    <t>De acordo com a Resolução nº 5.142/2021, que aprova o Manual de Gerenciamento de Frota da Polícia Militar de Minas Gerais, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>Compete ao auxiliar do Gestor de Frota da Unidade fiscalizar os dados informados na Ficha de Movimentação de Viatura, anotando as irregularidades, porventura ocorridas, relatando-as ao Gestor da Frota da Unidade.</t>
+  </si>
+  <si>
+    <t>O militar dispensado por motivo de saúde que o impeça de conduzir viaturas deverá ser avaliado pelo médico da Unidade, sendo seu afastamento comunicado pelo NAIS, ou setor de saúde responsável, ao Chefe da Seção Administrativa ou equivalente para que a administração efetive os lançamentos correspondentes no SIAD e ele não seja incluído como motorista na escala, até cessarem os impedimentos.</t>
+  </si>
+  <si>
+    <t>O funcionário civil efetivo poderá conduzir viaturas administrativas e caracterizadas, desde que habilitados com a categoria correspondente. Para o funcionário civil contratado, além do requisito anterior, é necessária a previsão contratual.</t>
+  </si>
+  <si>
+    <t>Compete ao Gestor da Frota da Unidade acompanhar, quinzenalmente, a existência de notificações ou autuações de trânsito das viaturas, inclusive as locadas, via site do DETRAN e de órgãos de fiscalização de trânsito municipal, do DPRF, DNIT.</t>
+  </si>
+  <si>
+    <t>Nos termos da Resolução nº 5.332/2023, que aprova o Plano Estratégico da Polícia Militar de Minas Gerais para o quadriênio 2024-2027, e da Resolução nº 5.379/2024, que aprova o Programa de Integridade da Polícia Militar de Minas Gerais, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>O Plano de Integridade da PMMG apresenta ações a serem desenvolvidas para um período de quatro anos, dentro da área de abrangência de cada uma das perspectivas e alinhado com os objetivos estratégicos, ambos elencados no Plano Estratégico Institucional proposto para o período de 2024 a 2027. Estas ações estão divididas nos seis eixos a seguir: compromisso com a integridade; governança, gestão de riscos e controles; prevenção ao conflito de interesses; prevenção, detecção e tratamento dos riscos de integridade; promoção da cultura da integridade; e transparência e controle social.</t>
+  </si>
+  <si>
+    <t>A PMMG tem como visão de futuro estabelecer um ambiente de integridade sólido e confiável, no qual exclusivamente os comandos, em todos os níveis, estejam comprometidos com a ética, a transparência e a legalidade em suas ações. Nesse sentido, almeja ser reconhecida como uma instituição exemplar no que diz respeito à promoção da integridade, estabelecendo referências para outras organizações públicas e privadas.</t>
+  </si>
+  <si>
+    <t>No Plano Estratégico, a Identidade Organizacional conta com três núcleos, sendo eles: missão, valores e visão. A missão é a razão de ser da organização, define o porquê existimos, ela reflete nossos Valores, que traduzem a cultura organizacional e estabelece atributos relacionados ao ambiente ao qual estamos inseridos, definindo as características que se espera de cada um individualmente. Os valores são responsáveis por nos direcionar para o alcance da Visão organizacional, que define aonde queremos chegar.</t>
+  </si>
+  <si>
+    <t>Dentre as diretrizes estratégicas previstas no Plano Estratégico 2024-2027, podemos citar: aumentar a segurança e a sensação de segurança; combater as organizações criminosas; proteger e promover o uso sustentável dos ecossistemas; valorizar o público externo; aumentar a eficiência no emprego do recurso público.</t>
+  </si>
+  <si>
+    <t>Dois graduados, em preparação para a prova do CHO 2025, conversavam sobre a Resolução nº 5.332/2023, que aprova o Plano Estratégico da Polícia Militar de Minas Gerais para o quadriênio 2024-2027. O Sgt Bravo afirmou que “Cenário Prospectivo” é a identificação de futuros prováveis, por intermédio da utilização de metodologia apropriada, cuja essência está na correta avaliação de variáveis intervenientes aos cenários. Já o Sgt Charlie disse que “Gestão pelas Diretrizes” é a representação gráfica contendo as diretrizes estratégicas desdobradas em objetivos, estabelecidos em perspectivas do BSC, que permite verificar a relação de causa e efeito entre os objetivos e seu alinhamento com a missão e a visão organizacional. Considerando as afirmações, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Os dois militares estão corretos.</t>
+  </si>
+  <si>
+    <t>Nenhum dos militares está correto.</t>
+  </si>
+  <si>
+    <t>Somente o Sgt Charlie está correto.</t>
+  </si>
+  <si>
+    <t>De acordo com a Resolução nº 5.142/2021, que aprova o Manual de Gerenciamento de Frota da Polícia Militar de Minas Gerais, analise as alternativas abaixo assinalando V para a(s) verdadeira(s) e F para a(s) falsa(s): 
+( ) É vedada a circulação em via pública de viatura da PMMG que não esteja em perfeitas condições de funcionamento, segurança e cumprimento das Normas Gerais de Circulação previstas no Código de Trânsito Brasileiro. 
+( ) As viaturas da PMMG serão engarajadas e guardadas em segurança, prioritariamente em Unidades (ou frações) ou em sedes de órgãos públicos, exceto no cumprimento de diligências do serviço público. 
+( ) Caberá ao Gestor de Frota da Região fiscalizar o emprego das viaturas das Unidades subordinadas, observando sempre a alternância de utilização dos veículos disponíveis, sendo de sua responsabilidade eventual prejuízo do não cumprimento do revezamento. 
+( ) Deverá ser priorizado o emprego de viaturas orgânicas nas frações, não sendo admitido o emprego de viaturas locadas no serviço se houver viaturas orgânicas subutilizadas na fração. 
+Marque a alternativa que corresponda, na ordem de cima para baixo, a sequência CORRETA.</t>
+  </si>
+  <si>
+    <t>Somente o Sgt Bravo está correto.</t>
+  </si>
+  <si>
+    <t>De acordo com a Lei nº 13.869, de 5 de setembro de 2019, que dispõe sobre os crimes de abuso de autoridade, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Considera-se crime de abuso de autoridade o fato de o policial militar identificar-se falsamente ao preso por ocasião de sua captura. Entretanto, a referida lei não considera como crime a conduta de o policial deixar de identificar-se ao preso por ocasião de sua captura ou quando deva fazê-lo durante sua detenção ou prisão, ainda que por mero capricho.</t>
+  </si>
+  <si>
+    <t>Para os crimes de abuso de autoridade, há possibilidade de aplicação de penas restritivas de direitos substitutivas das privativas de liberdade previstas na referida lei. Além disso, os crimes previstos nela são de ação pública incondicionada, admitindo-se, todavia, ação privada se a ação penal pública não for intentada no prazo legal.</t>
+  </si>
+  <si>
+    <t>A conduta da autoridade policial de deixar de entregar ao preso, no prazo de 12 (doze) horas, a nota de culpa assinada, com o motivo da prisão e os nomes do condutor e das testemunhas, constitui crime de abuso de autoridade.</t>
+  </si>
+  <si>
+    <t>Os efeitos da condenação previstos na referida lei, de tornar certa a obrigação de indenizar o dano causado pelo crime e a inabilitação para o exercício de cargo, mandato ou função pública, pelo período de 1 (um) a 5 (cinco) anos, estão condicionados à ocorrência de reincidência em crime de abuso de autoridade e não são automáticos, devendo ser declarados motivadamente na sentença.</t>
+  </si>
+  <si>
+    <t>Abrúcio é um servidor público de carreira da secretaria de políticas urbanas de um determinado município cuja função é analisar e dar parecer sobre pedidos de licença para construções na cidade. Certa vez, um amigo de Abrúcio o procurou para solicitar uma licença para construir uma casa em área onde há restrições ambientais. Abrúcio, conhecedor das regras de concessão de licenças dessa monta, constatou que o pedido não atendia aos critérios exigidos pela lei. Entretanto, Abrúcio solicitou ao amigo a quantia de R$ 10.000,00 para facilitar a concessão da licença. De acordo com o Decreto-Lei n. 2.848/1940 – Código Penal, marque a alternativa que estabelece, de forma CORRETA, o crime praticado por Abrúcio.</t>
+  </si>
+  <si>
+    <t>Corrupção ativa.</t>
+  </si>
+  <si>
+    <t>Corrupção passiva.</t>
+  </si>
+  <si>
+    <t>Tráfico de Influência.</t>
+  </si>
+  <si>
+    <t>Concussão.</t>
+  </si>
+  <si>
+    <t>Mévio efetuou disparos de arma de fogo contra Tício, mas não o acertou. Contudo, em razão do susto provocado pelos disparos, Tício teve um colapso nervoso e morreu. De acordo com o Decreto-Lei n. 2.848/1940 – Código Penal, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Mévio não deverá responder por homicídio de Tício, pois a causa da morte de Tício é concomitante e relativamente independente à ação de Mévio.</t>
+  </si>
+  <si>
+    <t>Mévio deverá responder por homicídio de Tício, pois a causa da morte de Tício é concomitante e absolutamente independente à ação de Mévio.</t>
+  </si>
+  <si>
+    <t>Mévio não deverá responder por homicídio de Tício, pois a causa da morte de Tício é superveniente e relativamente independente à ação de Mévio.</t>
+  </si>
+  <si>
+    <t>Mévio deverá responder por homicídio de Tício, pois a causa da morte de Tício é concomitante e relativamente independente à ação de Mévio.</t>
+  </si>
+  <si>
+    <t>Tendo em vista a Constituição da República Federativa do Brasil de 1988, sobre os direitos e deveres individuais e coletivos, bem como seus reflexos no Decreto-lei nº 4.657/1942 - Lei de Introdução às normas do Direito Brasileiro e na Lei Federal nº 13.869/2019 – que dispõe sobre os crimes de abuso de autoridade, é CORRETO afirmar que:</t>
+  </si>
+  <si>
+    <t>A Constituição Federal vigente assegura a plena liberdade de associação para fins lícitos, vedada a de caráter paramilitar. Além disso, verifica-se do texto constitucional que as associações somente poderão ter suas atividades suspensas ou ser compulsoriamente dissolvidas por decisão judicial, sendo imprescindível, em ambos os casos, o trânsito em julgado da respectiva decisão, como forma de assegurar o devido processo legal.</t>
+  </si>
+  <si>
+    <t>Dentre as ações gratuitamente garantidas pela Constituição Federal vigente, está previsto o habeas data, cuja finalidade é assegurar o direito de conhecimento de informações relativas à pessoa do impetrante, constantes de registros ou bancos de dados de entidades governamentais ou de caráter público, além de possibilitá-lo a retificação de dados, quando não se prefira fazê-lo por processo sigiloso, judicial ou administrativo.</t>
+  </si>
+  <si>
+    <t>Como forma de conferir estabilidade às relações jurídicas, a Constituição Federal vigente dispõe que a lei não prejudicará o direito adquirido, o ato jurídico perfeito e a coisa julgada. E segundo a LINDB - Lei de Introdução às Normas do Direito Brasileiro (Decreto-lei nº 4.657/1942), direito adquirido é o ato já consumado segundo a lei vigente ao tempo em que se efetuou; o ato jurídico perfeito é o direito que o seu titular, ou alguém por ele, possa exercer, como aquele cujo começo do exercício tenha termo prefixo, ou condição preestabelecida inalterável, a arbítrio de outrem; já a coisa julgada é a decisão judicial de que não caiba mais recurso.</t>
+  </si>
+  <si>
+    <t>Extrai-se da Constituição Federal vigente, que a pena será cumprida em estabelecimentos distintos, considerando a natureza do delito, a idade, a periculosidade e o sexo do apenado. Nesse sentido, a Lei nº 13.869/2019 (Lei de Abuso de Autoridade) criminaliza a manutenção de presos de ambos os sexos na mesma cela ou espaço de confinamento.</t>
+  </si>
+  <si>
+    <t>De acordo com a Constituição do Estado de Minas Gerais de 1989, marque a opção CORRETA.</t>
+  </si>
+  <si>
+    <t>A segurança pública, dever do Estado e direito e responsabilidade de todos, é exercida para a preservação da ordem pública e da incolumidade das pessoas e do patrimônio, através dos seguintes órgãos: Polícia Civil; Polícia Militar; Corpo de Bombeiros Militar e Polícia Penal. Todavia, a Constituição Mineira vigente não faz menção à Polícia Federal e às Polícias Rodoviária e Ferroviária Federais. Ela prevê ainda que os municípios podem constituir guardas municipais para a proteção de seus bens, serviços e instalações.</t>
+  </si>
+  <si>
+    <t>O Conselho de Defesa Social é órgão consultivo do Governador na definição da política de defesa social do Estado e tem assegurada, em sua composição, a participação, dentre outras autoridades, do Comandante-Geral da Polícia Militar; do Chefe da Polícia Civil; de um representante do Tribunal de Contas do Estado e um representante do Ministério Público.</t>
+  </si>
+  <si>
+    <t>Administração pública indireta é a que compete a órgão de qualquer dos Poderes do Estado.</t>
+  </si>
+  <si>
+    <t>A Polícia Militar e o Corpo de Bombeiros Militar, forças públicas estaduais, são órgãos permanentes, organizados com base na hierarquia e na disciplina militares e comandados, preferencialmente, por oficial da ativa do último posto. Na referida Constituição também menciona, explicitamente, que a Polícia Civil e a Polícia Penal são organizadas com base na hierarquia e disciplina.</t>
+  </si>
+  <si>
+    <t>Somente a assertiva II é verdadeira.</t>
+  </si>
+  <si>
+    <t>As assertivas I, II, III e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Somente a assertiva III é verdadeira.</t>
+  </si>
+  <si>
+    <t>Somente as assertivas I e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Nos termos da Lei nº 14.133, de 1º de abril de 2021, Lei de Licitações e Contratos Administrativos, o dano provocado ao patrimônio da Administração, caracterizado, entre outras situações, por medição de quantidades superiores às efetivamente executadas ou fornecidas, é definido, de forma CORRETA, como:</t>
+  </si>
+  <si>
+    <t>Superfaturamento.</t>
+  </si>
+  <si>
+    <t>Sobrepreço.</t>
+  </si>
+  <si>
+    <t>Repactuação.</t>
+  </si>
+  <si>
+    <t>Reajustamento em sentido estrito.</t>
+  </si>
+  <si>
+    <t>Considerando o teor da Lei nº 14.133, de 1º de abril de 2021, Lei de Licitações e Contratos Administrativos, no que se refere à fase de habilitação, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>A habilitação jurídica visa a demonstrar a capacidade de o licitante exercer direitos e assumir obrigações, e a documentação a ser apresentada por ele limita-se à comprovação de existência jurídica da pessoa e, quando cabível, de autorização para o exercício da atividade a ser contratada.</t>
+  </si>
+  <si>
+    <t>A fase de habilitação divide-se em jurídica, técnica, fiscal, social e trabalhista, bem como econômicofinanceira.</t>
+  </si>
+  <si>
+    <t>A habilitação fiscal visa a demonstrar a aptidão econômica do licitante para cumprir as obrigações decorrentes do futuro contrato, devendo ser comprovada de forma objetiva, por coeficientes e índices econômicos previstos no edital, devidamente justificados no processo licitatório, e será restrita à apresentação, dentre outras, da certidão negativa de feitos sobre falência expedida pelo distribuidor da sede do licitante.</t>
+  </si>
+  <si>
+    <t>As condições de habilitação serão definidas no edital.</t>
+  </si>
+  <si>
+    <t>Somente as assertivas I, III e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Somente as assertivas I e III são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Somente as assertivas II e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Em relação ao Decreto-Lei nº 1.001, de 21 de outubro de 1969, Código Penal Militar, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>O crime de_desacato a superior classifica-se como propriamente militar e terá sua pena agravada se o superior for Oficial.</t>
+  </si>
+  <si>
+    <t>O crime de desacato a militar exige que o militar desacatado esteja no exercício da função de natureza militar ou em razão dela.</t>
+  </si>
+  <si>
+    <t>O crime de desobediência consiste em desobedecer a ordem legal de autoridade militar com o fim de deprimir-lhe a autoridade.</t>
+  </si>
+  <si>
+    <t>O crime de desacato a superior, por ter o superior hierárquico como sujeito passivo, trata-se de crime contra a pessoa.</t>
+  </si>
+  <si>
+    <t>Com base no Decreto-Lei nº 1002, de 21/10/1969 – Código de Processo Penal Militar e no Decreto-Lei nº 1001, de 21/10/1969 – Código Penal Militar, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>A prisão preventiva pode ser decretada durante qualquer fase do processo, de ofício, pelo Conselho de Justiça.</t>
+  </si>
+  <si>
+    <t>A decretação de prisão preventiva com fundamento na exigência de manutenção de normas ou princípios de hierarquia e disciplina, só é cabível para crimes propriamente militares.</t>
+  </si>
+  <si>
+    <t>A prisão preventiva pode ser decretada mediante representação da autoridade encarregada do inquérito policial militar.</t>
+  </si>
+  <si>
+    <t>A prisão preventiva em nenhum caso será decretada se o juiz verificar, pelas provas constantes dos autos, ter o agente praticado o fato sob coação física irresistível.</t>
+  </si>
+  <si>
+    <t>Com base no Decreto-Lei nº 3.689, de 03/10/1941 – Código de Processo Penal, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>A busca poderá ser domiciliar, pessoal ou material.</t>
+  </si>
+  <si>
+    <t>Admite-se a busca domiciliar com o objetivo de apreender cartas destinadas ao acusado ou investigado, permitida a apreensão somente daquelas que já estejam abertas.</t>
+  </si>
+  <si>
+    <t>O mandado de busca deverá indicar, o mais precisamente possível, a casa em que será realizada a diligência e o nome do respectivo proprietário ou morador; ou, no caso de busca pessoal, o nome da pessoa que terá de sofrê-la ou os sinais que a identifiquem.</t>
+  </si>
+  <si>
+    <t>O mandado de busca não precisa mencionar o motivo e os fins da diligência.</t>
+  </si>
+  <si>
+    <t>Somente as assertivas I, II e III são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Somente as assertivas I, II e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Somente as assertivas III e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Com base na Lei Federal nº 8.429, de 02/06/1992, que dispõe sobre as sanções aplicáveis em virtude da prática de atos de improbidade administrativa, marque alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>O mero exercício da função ou desempenho de competências públicas, sem comprovação de ato doloso com fim ilícito, afasta a responsabilidade por ato de improbidade administrativa.</t>
+  </si>
+  <si>
+    <t>Se houver indícios de ato de improbidade, a autoridade que conhecer dos fatos representará ao Tribunal de Contas competente, para as providências necessárias.</t>
+  </si>
+  <si>
+    <t>Não configura improbidade a ação ou omissão decorrente de divergência interpretativa da lei, baseada em jurisprudência, ainda que não pacificada, mesmo que não venha a ser posteriormente prevalecente nas decisões dos órgãos de controle ou dos tribunais do Poder Judiciário.</t>
+  </si>
+  <si>
+    <t>À luz da Lei nº 12.527, de 18 de novembro de 2011, que regula o acesso a informações, analise os itens abaixo: 
+I. O acesso à informação compreende, entre outros, os direitos de obter uma informação primária, íntegra, autêntica e atualizada dos órgãos públicos. O conceito de integridade é relacionado à qualidade da informação coletada na fonte, com o máximo de detalhamento possível, sem modificações. 
+II. Cabe aos órgãos e entidades do poder público, observadas as normas e procedimentos específicos aplicáveis, assegurar a proteção da informação, garantindo-se sua disponibilidade, autenticidade e integridade. O conceito de disponibilidade é relacionado à qualidade da informação que tenha sido produzida, expedida, recebida ou modificada por determinado indivíduo, equipamento ou sistema. 
+III. O acesso à informação compreende, entre outros, os direitos de obter informação contida em registros ou documentos, produzidos ou acumulados por seus órgãos ou entidades, recolhidos ou não a arquivos públicos. 
+IV. Cabe aos órgãos e entidades do poder público, observadas as normas e procedimentos específicos aplicáveis, assegurar a proteção da informação sigilosa e da informação pessoal, observada a sua disponibilidade, autenticidade, integridade e eventual restrição de acesso. O conceito de autenticidade é relacionado à qualidade da informação não modificada, inclusive quanto à origem, trânsito e destino. 
+Marque a alternativa que contém a resposta CORRETA.</t>
+  </si>
+  <si>
+    <t>Em relação ao Decreto-Lei nº 1.001, de 21 de outubro de 1969, Código Penal Militar, analise as assertivas a seguir: 
+I. Reunirem-se militares, assentindo em recusa conjunta de obediência, ou em resistência ou violência, em comum, contra superior, caracteriza o crime de motim. 
+II. Reunirem-se dois ou mais militares, com armamento ou material bélico de propriedade militar, praticando violência à pessoa ou à coisa pública ou particular em lugar sujeito ou não à administração militar, configura o crime de organização de grupo para a prática de violência. 
+III. Concertarem-se militares para reunirem e agirem contra a ordem recebida de superior configura o crime de conspiração. 
+IV. Reunirem-se três militares armados negando a cumprir ordem recebida de superior, configura o crime de revolta. 
+Marque a opção que contenha a resposta CORRETA.</t>
+  </si>
+  <si>
+    <t>Com base na Lei Federal nº 10.826, de 22/12/2003, que dispõe sobre registro, posse e comercialização de armas de fogo e munição, sobre o Sistema Nacional de Armas - Sinarm, analise as assertivas abaixo: 
+I. O sujeito que dispara arma de fogo, para o alto e com o fim de comemoração, em lugar habitado, em via pública, pratica o crime de disparo de arma de fogo. 
+II. O policial militar que vende arma de fogo, sem autorização ou em desacordo com determinação legal ou regulamentar, pratica o crime de comércio ilegal de arma de fogo e terá sua pena aumentada devido sua condição de policial militar. 
+III. Importar acessório ou munição, sem autorização da autoridade competente, configura crime de tráfico internacional de arma de fogo. No referido crime, a pena é aumentada se o acessório ou munição forem de uso proibido ou restrito.
+IV. Não responde pelo crime de omissão de cautela o policial militar que deixa um carregador e diversas munições em cima da mesa de jantar de sua casa, e seu filho, com 13 anos de idade, pega tais itens e passa a exibi-los nas redes sociais. 
+Marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>No que se refere a recursos de origem pública, sujeita-se às sanções previstas na Lei nº 8.429/1992 o particular, pessoa física ou jurídica, que celebra com a administração pública convênio, contrato de repasse, contrato de gestão, termo de parceria, termo de cooperação ou ajuste administrativo equivalente.</t>
+  </si>
+  <si>
+    <t>LEI DE ACESSO A INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>CODIGO PROCESSO PENAL MILITAR</t>
+  </si>
+  <si>
+    <t>Lei nº 12.527, de 18 de novembro de 2011, que regula o acesso a informações</t>
+  </si>
+  <si>
+    <t>Decreto-Lei nº 1002, de 21/10/1969 – Código de Processo Penal Militar e no Decreto-Lei nº 1001, de 21/10/1969 – Código Penal Militar</t>
+  </si>
+  <si>
+    <t>Decreto-Lei nº 3.689, de 03/10/1941 – Código de Processo Penal</t>
+  </si>
+  <si>
+    <t>Leia o fragmento de definição a seguir: “[...] é qualquer erro de sintaxe. Tal erro pode ser de concordância, de regência ou de colocação pronominal.” O fragmento de texto acima apresenta a definição de um vício de linguagem denominado:</t>
+  </si>
+  <si>
+    <t>arcaísmo.</t>
+  </si>
+  <si>
+    <t>barbarismo.</t>
+  </si>
+  <si>
+    <t>pleonasmo.</t>
+  </si>
+  <si>
+    <t>solecismo.</t>
+  </si>
+  <si>
+    <t>Apenas um par de sentenças está escrito conforme a gramática normativa.</t>
+  </si>
+  <si>
+    <t>Apenas dois pares de sentenças estão escritos conforme a gramática normativa.</t>
+  </si>
+  <si>
+    <t>Apenas três pares de sentenças estão escritos conforme a gramática normativa.</t>
+  </si>
+  <si>
+    <t>Todos os pares de sentenças estão escritos conforme a gramática normativa.</t>
+  </si>
+  <si>
+    <t>PORTUGUÊS</t>
+  </si>
+  <si>
+    <t>CHO/2024</t>
+  </si>
+  <si>
+    <t>Considerando a gramática normativa da Língua Portuguesa, analise os pares de sentenças abaixo e, ao final, marque a opção CORRETA em relação ao que se pede: 
+I. 
+a) Valente soldado, ao qual não falta a resiliência e o sentimento do dever. 
+b) Conhecimento, habilidade e qualidade fez daquele militar um profissional exemplar. 
+II. 
+a) Ontem pela manhã encontrei o candidato e a candidata estudiosa. 
+b) Todos os soldados permaneceram alertas. 
+III. 
+a) Todas as provas do concurso contém questões de múltipla escolha. 
+b) O sargento foi para a reserva com seis quinqüênios. 
+IV. 
+a) Se mantermos as posições, o inimigo não avançará. 
+b) O subtenente freiou a viatura subitamente.</t>
+  </si>
+  <si>
+    <t>Português</t>
+  </si>
+  <si>
+    <t>3, 2, 5, 4, 1.</t>
+  </si>
+  <si>
+    <t>5, 3, 2, 1, 4.</t>
+  </si>
+  <si>
+    <t>1, 5, 4, 2, 3.</t>
+  </si>
+  <si>
+    <t>Tendo por base o estabelecido na Instrução nº 3.03.10/2023-CG, que regula o emprego da Polícia Militar com vistas à prevenção e repressão aos crimes de homicídio, ENUMERE a 2ª coluna de acordo com a 1ª e, ao final, responda o que se pede: 
+(1) Intervenção indicada 
+(2) Intervenção universal 
+(3) Fase incidental 
+(4) Fase pós-incidental 
+(5) Intervenção seletiva 
+(----) Consiste no desenvolvimento de atividades de repressão imediata. Prestam a demonstração da presença do Estado na prevenção de ocorrências similares, por meio da ocupação dos locais vulneráveis, por exemplo. 
+(----) São ações e operações desencadeadas no intuito de auxiliarem na elucidação do crime, por meio da ocupação ostensiva da comunidade afetada com vistas à identificação da autoria e circunstâncias do crime que possam contribuir nas fases investigativa e processual, bem como restaurar a tranquilidade e a ordem pública. 
+(----) Conjunto de intervenções voltadas para os casos de homicídios registrados, com o fim de atuar na elucidação de autoria, prisão do(s) agente(s) e adoção de medidas no sentido de evitar o aumento destes delitos. 
+(----) Conjunto de programas ou serviços destinados à população, de forma específica, com histórico de conflitos interpessoais ou com existência de ambientes de risco.
+(----) Conjunto de programas ou serviços destinados à população em geral, com o fim de melhorar o atendimento à comunidade e inibir o surgimento de fatores de risco. As atividades neste nível de intervenção referem-se a todos esforços empregados no nível de primeiro esforço com atuação das unidades com responsabilidade territorial. 
+Assinale a alternativa que contém a sequência CORRETA de respostas, na ordem de cima para baixo:</t>
+  </si>
+  <si>
+    <t>Apenas uma assertiva está correta.</t>
+  </si>
+  <si>
+    <t>Apenas duas assertivas estão corretas.</t>
+  </si>
+  <si>
+    <t>Apenas três assertivas estão corretas.</t>
+  </si>
+  <si>
+    <t>Todas as assertivas estão corretas.</t>
+  </si>
+  <si>
+    <t>Todas assertivas estão incorretas.</t>
+  </si>
+  <si>
+    <t>Apenas uma assertiva está incorreta.</t>
+  </si>
+  <si>
+    <t>Apenas duas assertivas estão incorretas.</t>
+  </si>
+  <si>
+    <t>Apenas três assertivas estão incorretas.</t>
+  </si>
+  <si>
+    <t>Somente uma assertiva está correta.</t>
+  </si>
+  <si>
+    <t>Somente duas assertivas estão corretas.</t>
+  </si>
+  <si>
+    <t>Somente três assertivas estão corretas.</t>
+  </si>
+  <si>
+    <t>Durante uma operação policial, a equipe comandada por um Tenente executou patrulhamento em um aglomerado urbano e realizou verificações em locais com histórico de violência. O Tenente, militar mais experiente da equipe, adotou os seguintes procedimentos no desenvolvimento da operação: 
+I. Em relação à metodologia de avaliação de riscos, classificou aquela operação com risco de nível II, por considerar que havia real possibilidade de ocorrerem ameaças que comprometessem a segurança. 
+II. O Tenente conduziu a arma que portava na posição de guarda-alta. 
+III. Com intuito de se preparar mentalmente para a operação e manter o desempenho adequado, o Oficial se manteve no seguinte estado de prontidão: estado de alerta (representado pela cor vermelha). 
+IV. O Tenente considerou aquela operação uma intervenção de nível II, ou seja, uma ação repressiva em um aglomerado urbano. 
+V. Preocupado com o sucesso da operação, tão logo encerrada, o Oficial, seguindo a metodologia de divisão da intervenção em etapas, realizou, como etapa 5, a avaliação das condutas individuais e do grupo, bem como os resultados alcançados e as falhas notadas. 
+Tendo por base o Manual Técnico-Profissional Nº 3.04.01/2020-CG (MTP 01), que trata de Intervenção Policial, Processo de Comunicação e Uso da Força, assinale abaixo a opção que contém a quantidade de assertiva(s) CORRETA(S), em relação às ações adotadas pelo Tenente:</t>
+  </si>
+  <si>
+    <t>Considerando seus conhecimentos acerca do Manual Técnico-Profissional n. 3.04.02/2020 (MTP 02), que regula a abordagem a pessoas no âmbito da Polícia Militar de Minas Gerais, analise as assertivas abaixo:
+I. Deslocamento Normal é o passo com velocidade moderada, que permita ao policial militar observar todos os pontos de foco e pontos quentes antes de progredir. O policial militar deverá estar de silhueta reduzida, com a arma nas posições de guarda baixa ou guarda alta. 
+II. Numa abordagem a pessoa visivelmente portando arma imprópria, um policial militar iniciará a abordagem verbalizando e adotando uma das posturas de abordagem com mãos livres, enquanto os demais policiais militares iniciarão a abordagem com a arma na posição 2, 3 ou 4 de acordo com a avaliação de riscos. 
+III. Na postura defensiva, o policial mantém um dos braços elevados e mãos abertas, transmitindo uma mensagem gestual de contenção e defesa, não agressividade e intenção de resolução pacífica. 
+IV. Algemar uma pessoa a um ponto fixo, como um poste ou partes fixas de veículos, como as barras presentes no xadrez de algumas viaturas, é uma conduta altamente recomendável, que auxilia na segurança da guarnição e diminui os riscos do preso se ferir em qualquer situação, visto que tende a ficar imobilizado, seguro e parcialmente incapacitado. 
+Assinale abaixo a opção que contém a quantidade de assertiva(s) INCORRETA(S):</t>
+  </si>
+  <si>
+    <t>Conforme o Manual Técnico-Profissional n. 3.04.03/2020 (MTP 03), que regula a blitz policial no âmbito da Polícia Militar de Minas Gerais, durante as operações, os policiais devem ter cuidados especiais com o uso diferenciado da força, principalmente no que se refere à utilização de armas de fogo (dissuasivo e disparo), quando o emprego dos demais níveis da força não forem suficientes para solucionar a intervenção. Já o Manual Técnico-Profissional Nº 3.04.04/2020-CG (MTP 04), que regula a abordagem a veículos no âmbito da Polícia Militar de Minas Gerais, descreve ações e operações previstas para os casos em que um condutor desobedecer a ordem policial de parar o veículo ou for perseguido logo após o cometimento de delito. Com relação ao emprego de armas de fogo em blitz policial, perseguição e operação cerco, analise as assertivas abaixo: 
+I. Caso seja necessário empregar controle de contato, em relação a um abordado resistente passivo, essa reação deverá ser do policial que estiver melhor posicionado e que possua maior domínio das técnicas de defesa pessoal policial. Assim como na situação de normalidade, exclusivamente o PM Segurança manterá o seu armamento em posição de arma localizada, guarda baixa ou guarda alta, conforme avaliação de risco. Os demais deverão estar com as mãos livres para emprego de outros níveis da força e algemação, se a situação se agravar. 
+II. Se durante uma blitz policial, um condutor desobedecer à ordem policial de parada para que seja abordado, pode ser necessário iniciar uma perseguição policial. Dentre os procedimentos previstos para situação de perseguição a veículo em fuga, os policiais devem, via de regra, deslocar-se utilizando o cinto de segurança; acionar os sinais luminosos e a sirene; procurar manter as armas no coldre; evitar revidar a agressão, caso os ocupantes do veículo em fuga efetuem disparos de arma de fogo contra a viatura. 
+III. Em caso de agressão letal oferecida pelo abordado, durante uma blitz policial, a primeira reação dos policiais deve ser voltada à preservação de suas vidas e dos cidadãos, por isso, deverão procurar abrigo. A resposta imediata será do policial que estiver melhor posicionado, que estará com a arma em pronta resposta. 
+IV. Tendo progredido a perseguição policial e o PM Comandante da Operação decidido pelo cerco das rotas de fuga, simultaneamente, tomará outras providências importantes para o sucesso da intervenção. Dentre os dispositivos comuns para montagem do cerco, no afunilamento diagonal, a viatura posicionará numa inclinação de 45º em relação a guia do passeio, com a frente voltada para o sentido do fluxo da via; os policiais militares posicionarão próximos e após a viatura; os cones serão dispostos longitudinalmente na mesma faixa em que a viatura estiver posicionada. 
+Assinale abaixo a opção que contém a quantidade de assertiva(s) CORRETA(S):</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe o Manual Técnico-Profissional n. 3.04.05/2020 – MTP 05, que regula as escoltas policiais e conduções diversas no âmbito da Polícia Militar de Minas Gerais – acerca de escoltas de delegações esportivas e demais comboios, analise as assertivas abaixo: 
+I. Os procedimentos em escoltas de torcidas organizadas (grupo de pessoas que compõem agremiações particulares, destinadas a promover o incentivo de uma determinada equipe esportiva) são semelhantes aos adotados em escoltas de delegações esportivas (grupos formados por atletas, técnico, dirigentes e toda equipe de apoio, como auxiliar técnico, médico, massagista, fisioterapeuta, etc). Quanto à classificação de riscos, as escoltas de torcidas organizadas e de presos oferecem risco misto, enquanto as escoltas de VIP’s, de delegações e de valores oferecem risco externo. 
+II. As escoltas de bens e valores são regulamentadas e fiscalizadas pela Polícia Federal. A PMMG realiza esse tipo de escolta, ordinariamente, mediante convênio ou, em situações extraordinárias, mediante solicitação formal ao Comando da Instituição. Ressalta-se, no entanto, que as escoltas de bens e valores são realizadas, primordialmente, por empresas de segurança privada. 
+III. Como referencial mínimo de armamentos e equipamentos necessários à realização de escoltas serão exigidos: 1 (uma) pistola .40 com 2 (dois) carregadores municiados para cada policial militar; 1 (uma) arma portátil, com capacidade máxima de carga, mais 2 (duas) cargas reservas; 1 (uma) algema para cada policial militar; 1 (um) colete a prova de bala para cada envolvido na operação; 1 (um) bastão tonfa ou bastão de madeira para cada policial militar; e 1 (um) rádio HT com bateria reserva. 
+IV. No momento da entrega da pessoa presa pela equipe de escolta, deverá ser feita, mais uma vez, a busca pessoal e a checagem dos dados através da identificação, quando, então, serão retiradas as algemas e o escoltado será repassado à equipe responsável pelo recebimento. Fica, ainda, a cargo da escolta, conduzir a pessoa presa, ainda algemada, até o local destinado pela autoridade. 
+Assinale abaixo a opção que contém a quantidade de assertiva(s) CORRETA(S):</t>
+  </si>
+  <si>
+    <t>Todas as assertivas estão incorretas.</t>
+  </si>
+  <si>
+    <t>O Tenente “Sierra”, recém-chegado na Unidade Especializada, ficou responsável por Coordenar escolta de dignatário e se empenhou na preparação de um treinamento acerca das funções utilizadas nas atividades de escoltas, consoante preconiza o Manual Técnico-Profissional n. 3.04.05/2020 - MTP 05, que regula as escoltas policiais e conduções diversas no âmbito da Polícia Militar de Minas Gerais e alusivo à escolta de delegações esportivas e demais comboios. Analise as assertivas abaixo e responda o que se pede: 
+I. As viaturas de segurança são veículos ostensivos que têm a função de proporcionar segurança ao comboio diante de possíveis hostilidades diversas; preferencialmente, devem ser empregadas duas viaturas de 4 (quatro) rodas nessa função; nos casos em que houver emprego de duas viaturas de segurança em escolta, e considerando que tal escolta não envolva outros órgãos, o comandante da escolta deverá estar embarcado sempre na viatura de segurança à retaguarda da célula, enquanto a segunda viatura de segurança deve ficar à frente da célula (que pode ser composta por escoltado, por exemplo). 
+II. A viatura de varredura faz parte da equipe de escolta; desloca-se à frente do primeiro veículo do comboio e tem a função de se antecipar a possíveis ameaças não identificadas ou surgidas posteriormente à averiguação do avançado, o qual atua, preferencialmente, descaracterizado. 
+III. A viatura denominada regulador desloca-se a uma distância aproximada de quinhentos metros à retaguarda da viatura de varredura; é o primeiro veículo do comboio e tem a função de regular o ritmo de deslocamento do comboio. 
+IV. A critério do Comandante da Escolta, observadas as características da via e visando liberar o trânsito, os alas podem assumir a função de batedores/pontas, compondo e equipe de escolta à frente do regulador. A fluidez do comboio está ligada diretamente à atividade dos pontas, os quais deslocam na média com velocidade 50% superior à velocidade do comboio. 
+Marque a alternativa que contém a resposta CORRETA:</t>
+  </si>
+  <si>
+    <t>Acionado para auxiliar um graduado em uma ocorrência envolvendo maus-tratos a animais, o Tenente “Yankee”, com base no Memorando nº 30.001.2/2024-EMPM, de 05/01/2024 (POP nº 1.8.0.048), que trata da atuação policial em face do crime de abuso e maus-tratos aos animais, fez as seguintes orientações: 
+I. A lavratura de Termo Circunstanciado de Ocorrência (TCO) não será cabível quando se tratar de maustratos contra animais silvestres, em razão da pena. 
+II. A soltura de animais silvestres no habitat será feita exclusivamente por Policial Militar do CPMAmb, mediante registro de termo próprio, sem necessidade de acompanhamento do ato por órgão municipal competente. 
+III. Para cometer o crime de maus-tratos aos animais, o agente deve querer o resultado ou assumir o risco de produzi-lo. 
+IV. Constatado o crime de abuso ou de maus-tratos, registrar a situação encontrada no local de crime através de fotos e vídeos para a devida inserção no REDS, que será do tipo Boletim de Ocorrência Ambiental – natureza M 30.024 (praticar ato de abuso, maus-tratos, ferir ou mutilar animais silvestres, domésticos ou domesticados, nativos ou exóticos). 
+Considerando as orientações do Tenente “Yankee”, transcritas nas assertivas acima, marque a resposta CORRETA:</t>
+  </si>
+  <si>
+    <t>Quatro militares estavam conversando sobre o Plano Estratégico da PMMG para o quadriênio 2024-2027 aprovado pela Resolução nº 5.332, de 18/12/2023. Um deles, o Sargento PM Alfa, se referindo à identidade organizacional da PMMG, disse que a missão da organização é ser essencial para o povo mineiro. O Sargento PM Bravo, tratando do mesmo assunto, afirmou que os princípios presentes na identidade organizacional são hierarquia, disciplina militar e abnegação. Já o Sargento PM Charlie afirmou que a identidade organizacional está organizada em perspectivas, diretrizes e objetivos. Considerando o contido na norma tratada pelos militares, marque a alternativa CORRETA:</t>
+  </si>
+  <si>
+    <t>Apenas o Sargento PM Bravo está correto em sua afirmação.</t>
+  </si>
+  <si>
+    <t>Apenas o Sargento PM Alfa está correto em sua afirmação.</t>
+  </si>
+  <si>
+    <t>Todas as afirmações feitas pelos militares estão incorretas.</t>
+  </si>
+  <si>
+    <t>02 (dois) Sargentos estão corretos em suas afirmações.</t>
+  </si>
+  <si>
+    <t>Apenas três dos atos processuais listados acima são possíveis de serem realizados por videoconferência.</t>
+  </si>
+  <si>
+    <t>Nenhum dos atos processuais listados acima é possível de ser realizados por videoconferência.</t>
+  </si>
+  <si>
+    <t>Todos os atos processuais listados acima são possíveis de serem realizados por videoconferência.</t>
+  </si>
+  <si>
+    <t>Apenas dois dos atos processuais listados acima são possíveis de serem realizados por videoconferência.</t>
+  </si>
+  <si>
+    <t>Nos termos da Resolução Conjunta nº 5.240, de 22/11/2022, que alterou por acréscimo o Manual de processos e procedimentos administrativos das instituições militares do Estado de Minas Gerais – MAPPA, aprovado pela Resolução Conjunta nº 4.220, de 28/06/2012, considere os atos processuais abaixo: 
+I. Acareação. 
+II. Oitiva de Informante. 
+III. Reunião de CEDMU. 
+IV. Reunião de PAD. 
+Marque a alternativa CORRETA:</t>
+  </si>
+  <si>
+    <t>Nos termos da Lei Estadual n. 5.301, de 16/10/1969 que contém o Estatuto dos Militares do Estado de Minas Gerais e suas alterações (EMEMG), marque a alternativa INCORRETA:</t>
+  </si>
+  <si>
+    <t>Encerrado o curso, o Aluno do Curso de Habilitação de Oficiais CHO com impedimento à promoção não será promovido ao posto de 2º Tenente PM e permanecerá como Aluno do CHO até que seja resolvida a situação impeditiva.</t>
+  </si>
+  <si>
+    <t>Na escala hierárquica, o Aluno do Curso de Habilitação de Oficiais é classificado como Praça Especial de Polícia e possui precedência hierárquica em relação Cadetes do Curso de Formação de Oficiais dos demais anos.</t>
+  </si>
+  <si>
+    <t>A antiguidade entre dois Alunos do Curso de Habilitação de Oficiais é regulada pela ordem de classificação obtida no concurso.</t>
+  </si>
+  <si>
+    <t>O Quadro de Oficiais Especialistas da Polícia Militar será preenchido por militares pertencentes ao Quadro de Praças Especialistas da Polícia Militar mediante aprovação no Curso de Habilitação de Oficiais.</t>
+  </si>
+  <si>
+    <t>Nos termos da Lei Estadual n. 14.310, de 19/06/2002 - dispõe sobre o Código de Ética de Disciplina dos Militares do Estado de Minas Gerais (CEDM), marque a alternativa INCORRETA:</t>
+  </si>
+  <si>
+    <t>O militar que tomar conhecimento de prática de transgressão disciplinar deverá comunicar o fato à autoridade competente nos limites de sua competência.</t>
+  </si>
+  <si>
+    <t>A demissão é uma sanção disciplinar que pune militar da ativa ou da reserva remunerada pelo cometimento de determinada transgressão ou decorre da incorrigibilidade de transgressor contumaz cujo histórico e somatório de sanções indiquem sua inadaptabilidade ou incompatibilidade ao regime disciplinar da Instituição.</t>
+  </si>
+  <si>
+    <t>Em observância ao princípio da ética militar, o militar deve zelar pelo seu próprio preparo profissional e incentivar a mesma prática nos companheiros, em prol do cumprimento da missão comum.</t>
+  </si>
+  <si>
+    <t>A suspensão é uma sanção disciplinar prevista no CEDM que consiste em uma interrupção temporária do exercício de cargo, encargo ou função com a consequente perda de todas as vantagens e direitos decorrentes do exercício do cargo, encargo ou função.</t>
+  </si>
+  <si>
+    <t>Nos termos da Resolução Conjunta nº 4.220, de 28/06/2012 - Manual de processos e procedimentos administrativos das instituições militares do Estado de Minas Gerais – MAPPA e da Instrução Conjunta de Corregedorias nº 01 (ICCPM/BM nº 01/14) de 03/02/2014 que estabelece padronização sobre as atividades administrativas e disciplinares no âmbito da PMMG e CBMMG, marque a alternativa CORRETA:</t>
+  </si>
+  <si>
+    <t>Em processos disciplinares com dois acusados, caso algum dos acusados esteja realizando sua autodefesa, não poderá assistir pessoalmente o interrogatório do outro acusado. Não constituindo o acusado defensor para acompanhar a realização do ato, o encarregado e/ou a administração ficarão obrigados de nomear defensor ad hoc.</t>
+  </si>
+  <si>
+    <t>O encarregado do Processo de Comunicação Disciplinar (PCD) poderá ser militar de qualquer posto ou graduação, desde que possuidor de precedência hierárquica em relação ao comunicado.</t>
+  </si>
+  <si>
+    <t>A instauração de Processo de Comunicação Disciplinar (PCD) ou de Relatório de Investigação Preliminar (RIP) ocorrerá por intermédio de despacho da autoridade militar até o nível mínimo de Comandante de Pelotão ou equivalente, não sendo o Subcomandante de Unidade autoridade competente para instaurar PCD e RIP.</t>
+  </si>
+  <si>
+    <t>Ao final da apuração e antes de solucionar o processo ou procedimento disciplinar, caso seja vislumbrada necessidade de realização de diligências complementares, os autos devem ser encaminhados à autoridade competente para solucioná-lo para que este determine a realização de diligências complementares, independente de qual autoridade o instaurou.</t>
+  </si>
+  <si>
+    <t>Sobre o credenciamento dos condutores de viatura, conforme previsão do Manual de Gerenciamento de Frota da Polícia Militar de Minas Gerais – Aprovado pela Resolução nº 5.142, de 22/11/2021, analise as assertivas a seguir: 
+I. Cada Unidade será responsável pelo credenciamento de seu efetivo, devendo nomear uma Comissão de Credenciamento e Atualização composta por, no mínimo, três militares, sob a presidência de um Oficial PM para exercer este encargo; 
+II. Os militares designados para o serviço ativo manterão o status de credenciado independente do tempo que tenham sido transferidos para a reserva remunerada antes de sua designação; 
+III. Durante o credenciamento, o militar será submetido a instruções teóricas e práticas em que irá adquirir conhecimentos, dentre outros, sobre direção defensiva, primeiros socorros e providências em locais de acidente envolvendo viaturas; 
+IV. O militar para ser credenciado deverá ter concluído o curso de condutor de veículo de emergência (CVE), realizado dentro ou fora da Corporação. 
+Depreende-se que está CORRETO o que se afirma em:</t>
+  </si>
+  <si>
+    <t>Apenas duas afirmações estão corretas.</t>
+  </si>
+  <si>
+    <t>Apenas três afirmações estão corretas.</t>
+  </si>
+  <si>
+    <t>Apenas uma afirmação está correta.</t>
+  </si>
+  <si>
+    <t>Somente três das assertivas estão corretas.</t>
+  </si>
+  <si>
+    <t>Somente duas das assertivas estão corretas.</t>
+  </si>
+  <si>
+    <t>Somente uma das assertivas está correta.</t>
+  </si>
+  <si>
+    <t>Quanto ao lugar do crime de homicídio, em tese, deverá ser considerado o local do resultado morte (o hospital).</t>
+  </si>
+  <si>
+    <t>Quanto ao lugar do crime de homicídio, em tese, poderá ser considerado tanto o local da abordagem policial quanto o local do resultado morte (o hospital).</t>
+  </si>
+  <si>
+    <t>Quanto ao lugar do crime de homicídio, em tese, deverá ser considerado o local da captura do suspeito.</t>
+  </si>
+  <si>
+    <t>A omissão do 2º Sgt Oscar foi relevante, tendo ele, igualmente, concorrido para a consumação do mesmo delito. Portanto, responderá, em concurso com os demais.</t>
+  </si>
+  <si>
+    <t>Com base no Decreto-Lei nº 1002, de 21/10/1969 – Código de Processo Penal Militar, marque a única opção CORRETA de resposta:</t>
+  </si>
+  <si>
+    <t>Para verificar a possibilidade de haver sido a infração praticada de determinado modo, o encarregado do IPM poderá proceder à reprodução simulada dos fatos, nas hipóteses que julgar necessário, visando a completude das atividades de Polícia Judiciária Militar e da persecução penal, em quaisquer situações e circunstâncias.</t>
+  </si>
+  <si>
+    <t>Compete ao encarregado do APF ou IPM, no exercício das funções de Polícia Judiciária Militar representar a autoridades judiciárias acerca da prisão preventiva e da insanidade mental do indiciado.</t>
+  </si>
+  <si>
+    <t>Os processos da Justiça Militar Estadual, nos crimes previstos na Lei Penal Militar a que responderem os oficiais e praças das Polícias e dos Corpos de Bombeiros Militares, obedecerão às normas processuais previstas no Código de Processo Penal Militar, no que forem aplicáveis, inclusive quanto à organização de Justiça, aos recursos e à execução de sentença.</t>
+  </si>
+  <si>
+    <t>O Comandante de uma determinada Região da Polícia Militar que, em caráter de urgência, tomar conhecimento de um crime militar, pode, mediante uma mensagem transmitida via rede rádio ou por um telefonema, determinar ao comandante da Unidade da área que expeça a Portaria de IPM, formalizando, posteriormente, a ordem.</t>
+  </si>
+  <si>
+    <t>Sobre as disposições gerais nos crimes contra o patrimônio, constantes do Decreto-Lei nº 2.848/40 (Código Penal), é CORRETO afirmar que:</t>
+  </si>
+  <si>
+    <t>Quando houver emprego de grave ameaça ou violência à pessoa, não há isenção de pena e o crime se processa mediante ação pública incondicionada, mesmo que o crime seja em prejuízo de ascendente ou descendente cujo parentesco seja legítimo ou ilegítimo, civil ou natural.</t>
+  </si>
+  <si>
+    <t>Procede-se mediante representação se o crime é cometido em prejuízo de irmão, tio ou sobrinho.</t>
+  </si>
+  <si>
+    <t>Se procede mediante representação, se o crime é cometido em prejuízo do cônjuge, na constância da sociedade conjugal, ficando isento de pena o cônjuge se dissolvida a sociedade conjugal.</t>
+  </si>
+  <si>
+    <t>Não é isento de pena o estranho que participa do crime. Procede-se mediante ação penal pública incondicionada no crime contra pessoa com idade igual ou superior a 65 (sessenta e cinco) anos.</t>
+  </si>
+  <si>
+    <t>Todos os itens são verdadeiros.</t>
+  </si>
+  <si>
+    <t>Apenas quatro itens são verdadeiros.</t>
+  </si>
+  <si>
+    <t>Apenas três itens são verdadeiros.</t>
+  </si>
+  <si>
+    <t>Apenas dois itens são verdadeiros.</t>
+  </si>
+  <si>
+    <t>Somente uma das assertivas está incorreta.</t>
+  </si>
+  <si>
+    <t>Somente três das assertivas estão incorretas.</t>
+  </si>
+  <si>
+    <t>Somente duas das assertivas estão incorretas.</t>
+  </si>
+  <si>
+    <t>Apenas uma assertiva é verdadeira.</t>
+  </si>
+  <si>
+    <t>Apenas quatro assertivas são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Apenas três assertivas são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Apenas duas assertivas são verdadeiras.</t>
+  </si>
+  <si>
+    <t>De acordo com a Lei nº 13.869, de 5 de setembro de 2019, Lei de abuso de autoridade, marque a alternativa INCORRETA:</t>
+  </si>
+  <si>
+    <t>As responsabilidades civil e administrativa são independentes da criminal. A sentença penal que reconhecer ter sido o ato praticado em estado de necessidade, em legítima defesa, em estrito cumprimento do dever legal ou no exercício regular do direito faz coisa julgada em âmbito cível, assim como no administrativo disciplinar.</t>
+  </si>
+  <si>
+    <t>As penas restritivas de direitos substitutivas das privativas de liberdade previstas são: prestação de serviços à comunidade ou a entidades públicas; e suspensão do exercício do cargo, da função ou do mandato, pelo prazo de 06 (seis) meses a 1 (um) ano, com a perda dos vencimentos e das vantagens. As penas restritivas de direitos podem ser aplicadas autônoma ou cumulativamente.</t>
+  </si>
+  <si>
+    <t>Trata-se de um dos efeitos da condenação: a inabilitação para o exercício de cargo, mandato ou função pública, pelo período de 1 (um) a 5 (cinco) anos.</t>
+  </si>
+  <si>
+    <t>A conduta de “invadir ou adentrar, clandestina ou astuciosamente, ou à revelia da vontade do ocupante, imóvel alheio ou suas dependências, ou nele permanecer nas mesmas condições, sem determinação judicial, sem determinação judicial ou fora das condições estabelecidas em lei” sujeita o agente público que a praticar à pena de detenção de 1 (um) a 4 (quatro) anos, e multa. Incorre na mesma pena prevista para o crime de invasão de domicílio o agente que cumprir mandado de busca e apreensão domiciliar após as 21 horas e antes das 5 horas.</t>
+  </si>
+  <si>
+    <t>A Lei nº 14.133, de 1º de abril de 2021, Lei de Licitações e Contratos Administrativos: define as modalidades de licitação - Pregão, Concorrência, Concurso, Leilão, e Diálogo competitivo; veda a criação de outras modalidades de licitação ou, ainda, a combinação das modalidades previstas; e ainda prevê que a Administração também pode servir-se dos procedimentos auxiliares previstos no artigo 78 da aludida norma. Dentre as alternativas a seguir, marque aquela que NÃO se refere a um procedimento auxiliar das licitações e das contratações regidas pela Lei nº 14.133/2021:</t>
+  </si>
+  <si>
+    <t>Habilitação.</t>
+  </si>
+  <si>
+    <t>Credenciamento.</t>
+  </si>
+  <si>
+    <t>Sistema de registro de preço.</t>
+  </si>
+  <si>
+    <t>Registro cadastral.</t>
+  </si>
+  <si>
+    <t>No tocante ao Decreto-Lei nº 4.657, de 4 de setembro de 1942, Lei de Introdução às Normas do Direito Brasileiro, marque a alternativa INCORRETA:</t>
+  </si>
+  <si>
+    <t>Os governos estrangeiros poderão adquirir a propriedade dos prédios necessários à sede dos representantes diplomáticos ou dos agentes consulares.</t>
+  </si>
+  <si>
+    <t>Não se destinando à vigência temporária, a lei terá vigor até que outra a modifique ou revogue. Ao aplicar a lei, o juiz atenderá aos fins sociais a que ela se dirige e às exigências do bem comum.</t>
+  </si>
+  <si>
+    <t>A lei do país em que domiciliada a pessoa determina as regras sobre o começo e o fim da personalidade, o nome, a capacidade e os direitos de família.</t>
+  </si>
+  <si>
+    <t>Considerando o Plano Estratégico da PMMG para o quadriênio 2024-2027 aprovado pela Resolução nº 5.332 de 18/12/2023, avalie as afirmações abaixo. 
+I. O gerenciamento pelas diretrizes é conceituado como atividade que busca a manutenção da performance bem como a aplicação de melhorias incrementais e intervenções pontuais nos processos organizacionais como forma de atingir os resultados esperados em áreas específicas. 
+II. O planejamento por cenários prospectivos é uma abordagem estratégica que ajuda as organizações a antecipar e se preparar para possíveis futuros alternativos. 
+III. A estratégia da PMMG, conforme metodologia orientada pelo Balanced Scorecard, está organizada em perspectivas e em cada uma das perspectivas estão abarcadas as diretrizes estratégicas emanadas pelo Estado de Minas Gerais e pelo Comando da organização, mas, sobretudo, advindas de um amplo processo de participação da sociedade e do público interno, sustentadas por critérios técnicocientíficos. 
+IV. As diretrizes estratégicas foram desdobradas em iniciativas estratégicas que por sua vez serão implementadas por meio do alcance de objetivos estratégicos. 
+Assim, marque a alternativa CORRETA:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todas as afirmações estão corretas. </t>
+  </si>
+  <si>
+    <t>Tendo em vista a Constituição da República Federativa do Brasil de 1988, sobre os princípios fundamentais, analise as assertivas abaixo: 
+I. O cidadão brasileiro que viaja para outro país, lá deve ser reconhecido como tal, pois o princípio da cidadania rege a República Federativa do Brasil nas suas relações internacionais. 
+II. Pode-se dizer que a erradicação da pobreza constitui um dos fundamentos da República Federativa do Brasil. 
+III. O Ministério Público, órgão responsável pela defesa da ordem jurídica, portanto, essencial à função jurisdicional do Estado, não se subordina a nenhum dos poderes da União. 
+IV. De acordo com as regras sobre as relações internacionais, em caso de guerra, se o Brasil tiver aliança militar com outro país, poderá atuar em favor deste, e, inclusive, atacar e invadir o território inimigo, pelo princípio da intervenção. 
+Marque a opção que contém a resposta CORRETA:</t>
+  </si>
+  <si>
+    <t>Analise as assertivas abaixo, à luz da Constituição do Estado de Minas Gerais de 1989, mormente sobre os princípios da administração pública: 
+I. A Constituição prevê, além dos princípios da legalidade, impessoalidade, moralidade e publicidade, os princípios da razoabilidade e sustentabilidade. 
+II. A Constituição determina, especificamente, que a publicidade e a legalidade dos atos do Poder Público serão apuradas, para efeito de controle e invalidação, em face dos dados objetivos de cada caso. 
+III. A motivação do ato administrativo está sujeita ao princípio da discricionariedade, cabendo ao agente público a escolha dos casos em que deverá fundamentar sua decisão, sendo certo que isso se aplica às atividades de polícia ostensiva, vez que as abordagens policiais aceitam certo grau de subjetividade. 
+IV. Pelo princípio da legalidade, a instituição de autarquia, fundação pública e órgão autônomo dependem de lei específica, enquanto a extinção de qualquer deles poderá ser procedida mediante Resolução aprovada pelo Tribunal de Contas do Estado. 
+Marque a opção que contém a resposta CORRETA:</t>
+  </si>
+  <si>
+    <t>Considere e interprete o caso hipotético. 
+Durante uma abordagem policial a um ponto de tráfico de drogas, um dos suspeitos, ao perceber a aproximação da guarnição TM, resolveu dispensar um pacote contendo centenas de pinos de cocaína e uma arma de fogo, e fugiu, em desabalada carreira. Os soldados Quebec e Romeo, ambos nota 10 no Treinamento Policial Básico, com notável desempenho físico, perseguiram o suspeito, enquanto o Cmt da GuTM, 2º Sgt Oscar, permaneceu no local da abordagem, de modo a guardar a viatura e os materiais arrecadados. Após longa perseguição, em terrenos baldios e acidentados, fora das vistas do Cmt da GuTM, os policiais militares lograram alcançar o suspeito que, para não ser preso, saltou de uma altura de 6m e contundiu o abdômen em uma pedra. Aparentemente, o suspeito não sofreu qualquer lesão visível, apenas queixou dor abdominal, e disse não precisar de assistência médica. Contentes com o resultado da operação, os soldados Quebec e Romeo anunciaram ao 2º Sgt Oscar que a captura do suspeito ocorreu sem alteração e sem resistência, portanto, sem uso de força física, mas tão somente aplicação de técnicas de algemação. Ocorre que, após 8 horas de espera pela lavratura do APFD, o suspeito queixou-se de que a dor aumentou, o que levou seu advogado a requerer à GuTM sua imediata assistência médica, o que, presto, foi atendido pelo Sgt Oscar, que ficou surpreso com a notícia. O suspeito precisou ficar internado, e, ao cabo de 2 dias, veio a óbito, sendo certo que os relatórios médicos atestaram hemorragia interna provocada pela contusão abdominal, e que o retardo no socorro agravou o sangramento provocou a morte do suspeito. O fato resultou no indiciamento dos militares responsáveis pelo crime de homicídio, na modalidade culposa, tendo-se a omissão como relação de causalidade. 
+Agora, com fundamento no Decreto-Lei nº 1001, de 21/10/1969 – Código Penal Militar, marque a opção CORRETA de resposta:</t>
+  </si>
+  <si>
+    <t>Em relação ao Decreto-Lei nº 1.001, de 21 de outubro de 1969, Código Penal Militar (CPM), analise as assertivas a seguir: 
+I. Tanto o delito de Desrespeito a superior quanto o de Organização de grupo para a prática de violência são crimes contra a autoridade ou disciplina militar. 
+II. A pena cumprida no estrangeiro atenua a pena imposta no Brasil pelo mesmo crime, quando idênticas, ou nela é computada, quando diversas. 
+III. A pena de impedimento trata-se de espécie de pena acessória prevista no CPM. 
+IV. Fica sujeito à declaração de indignidade para o oficialato o militar condenado, qualquer que seja a pena, no crime de chantagem. 
+V. No caso do furto simples, previsto no CPM, “subtrair, para si ou para outrem, coisa alheia móvel”, se o agente é primário e é de pequeno valor a coisa furtada, o juiz pode substituir a pena de reclusão pela de detenção, diminuí-la de um a dois terços, ou aplicar multa. 
+Marque a opção que contém a resposta CORRETA:</t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe o Decreto-Lei nº 3.689, de 03/10/1941 – Código de Processo Penal, analise as assertivas abaixo: 
+I. Considera-se cadeia de custódia o conjunto de todos os procedimentos utilizados para manter e documentar a história cronológica do indício coletado em locais ou em vítimas de crimes, para rastrear sua posse e manuseio a partir de seu reconhecimento até o descarte. 
+II. A coleta dos indícios deverá ser realizada exclusivamente por perito oficial, que dará o encaminhamento necessário para a central de custódia, mesmo quando for necessária a realização de exames complementares. 
+III. Todas as pessoas que tiverem acesso ao vestígio armazenado deverão ser identificadas e deverão ser registradas a data e a hora do acesso. 
+IV. O compromisso de bem e fielmente desempenhar o encargo será prestado pelos peritos não oficiais. 
+Marque a opção que contém a resposta CORRETA:</t>
+  </si>
+  <si>
+    <t>No tocante à Lei n. 8.429, de 02 de junho de 1992, a qual dispõe sobre as sanções aplicáveis em virtude da prática de atos de improbidade administrativa, analise os itens a seguir: 
+I. Revelar ou permitir que chegue ao conhecimento de terceiro, antes da respectiva divulgação oficial, teor de medida política ou econômica capaz de afetar o preço de mercadoria, bem ou serviço constitui ato de improbidade administrativa que atenta contra os princípios da administração pública. 
+II. Permitir, facilitar ou concorrer para que terceiro se enriqueça ilicitamente constitui ato de improbidade administrativa que causa lesão ao erário. 
+III. Perceber vantagem econômica para intermediar a liberação ou aplicação de verba pública de qualquer natureza constitui ato de improbidade administrativa importando em enriquecimento ilícito. 
+IV. Receber vantagem econômica de qualquer natureza, direta ou indiretamente, para omitir ato de ofício, providência ou declaração a que esteja obrigado constitui ato de improbidade administrativa importando em enriquecimento ilícito. 
+V. Ordenar ou permitir a realização de despesas não autorizadas em lei ou regulamento constitui ato de improbidade administrativa que causa lesão ao erário. 
+Marque a opção que indique CORRETAMENTE a quantidade de itens verdadeiros:</t>
+  </si>
+  <si>
+    <t>Analise as assertivas abaixo, tendo por diretriz a Lei Federal nº 10.826 de 22/12/2003, que dispõe sobre registro, posse e comercialização de armas de fogo e munição, sobre o Sistema Nacional de Armas – SINARM, define crimes e dá outras providências:
+I. Em razão do princípio da presunção da inocência, o Estatuto autoriza a aquisição de arma de fogo por cidadão que esteja respondendo a inquérito policial, desde que os demais requisitos de idoneidade estejam presentes. 
+II. Não há vinculação legal da aquisição de munição ao registro da arma registrada, mas a quantidade de munições deve obedecer ao limite estabelecido no regulamento da referida Lei. 
+III. O funcionário da empresa privada Alpha, que sofre ameaças de morte, e que obteve o Certificado de Registro de Arma de Fogo para sua defesa, está autorizado pela Lei a possuir a arma em qualquer lugar do país, mantendo-a, exclusivamente, no interior de sua residência ou domicílio, ou dependência desses, ou, ainda, no seu local de trabalho, desde que comprovado o vínculo formal de trabalho em ocupação lícita. 
+IV. É permitido o porte de arma de fogo aos integrantes das guardas municipais das capitais dos Estados e dos Municípios com mais de 550.000 (quinhentos e cinquenta mil) habitantes, nas condições estabelecidas em regulamento. 
+Assinale abaixo a opção que contém a quantidade de assertiva(s) INCORRETA(S):</t>
+  </si>
+  <si>
+    <t>À luz da Lei nº 12.527, de 18 de novembro de 2011, Lei de Acesso à Informação, analise os itens abaixo: 
+I. Cabe aos órgãos e entidades do poder público, observadas as normas e procedimentos específicos aplicáveis, assegurar a: gestão transparente da informação, propiciando amplo acesso a ela e sua divulgação; proteção da informação, garantindo-se sua disponibilidade, autenticidade e integridade; e proteção da informação sigilosa e da informação pessoal, observada a sua disponibilidade, autenticidade, integridade e eventual restrição de acesso. 
+II. A informação em poder dos órgãos e entidades públicas, observado o seu teor e em razão de sua imprescindibilidade à segurança da sociedade ou do Estado, poderá ser classificada como ultrassecreta, secreta ou sigilosa.
+III. No caso de indeferimento de acesso a informações ou às razões da negativa do acesso, poderá o interessado interpor recurso contra a decisão no prazo de 05 (cinco) dias a contar da sua ciência. 
+IV. A pessoa física ou entidade privada que detiver informações em virtude de vínculo de qualquer natureza com o poder público e deixar de observar o disposto nesta Lei estará sujeita às seguintes sanções: rescisão do vínculo com o poder público; multa; suspensão temporária de participar em licitação e impedimento de contratar com a administração pública por prazo não superior a 2 (dois) anos; advertência; e declaração de inidoneidade para licitar ou contratar com a administração pública, até que seja promovida a reabilitação perante a própria autoridade que aplicou a penalidade. 
+V. Para os fins da Lei 12.527/2011, a sanção de multa só poderá ser aplicada de forma cumulativa com outra sanção. 
+Marque a opção que indica CORRETAMENTE a quantidade de assertiva(s) VERDADEIRA(S):</t>
+  </si>
+  <si>
+    <t>CODIGO DE PROCESSO PENAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A homologação pelo Superior Tribunal de Justiça trata-se de um requisito para que a sentença proferida no estrangeiro seja executada no Brasil. </t>
+  </si>
+  <si>
+    <t>Considerando as disposições da Lei Federal nº 13.869, de 05/09/2019, em especial, quanto às condutas que podem ser praticadas por policiais militares, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>É permitido ao policial militar invadir domicílio sem mandado judicial sempre que houver denúncia anônima de crime em andamento, bastando justificar a conduta no tirocínio policial de que a entrada é necessária.</t>
+  </si>
+  <si>
+    <t>É lícita a conduta do policial militar que, sendo o primeiro a chegar ao local de crime, solicita que a vítima relate o ocorrido e a orienta sobre a necessidade de colaborar com a apuração, preocupandose em não deixá-la reviver o evento desnecessariamente.</t>
+  </si>
+  <si>
+    <t>É regular a atuação do policial militar que, para obter a versão dos fatos de uma testemunha que não quis prestar esclarecimentos, a conduz à força até a sede da companhia para ser ouvida informalmente, e a mantém no local até que preste as informações necessárias.</t>
+  </si>
+  <si>
+    <t>É lícito ao policial militar constranger o conduzido a se identificar para foto ao lado de drogas ou armas apreendidas, desde que o fato seja de relevante interesse público.</t>
+  </si>
+  <si>
+    <t>Segundo as disposições da Lei Federal nº 13.869, de 05/09/2019, Lei de Abuso de Autoridade, marque a alternativa que prevê conduta que NÃO constituirá crime de abuso de autoridade.</t>
+  </si>
+  <si>
+    <t>Inovar artificiosamente, no curso de diligência, de investigação ou de processo, o estado de lugar, de coisa ou de pessoa, com o fim de eximir-se de responsabilidade ou de responsabilizar criminalmente alguém ou agravar-lhe a responsabilidade.</t>
+  </si>
+  <si>
+    <t>Constranger o preso ou o detento, mediante violência, grave ameaça ou redução de sua capacidade de resistência, a exibir-se ou ter seu corpo ou parte dele exibido à curiosidade pública, ou submeterse a situação vexatória ou a constrangimento não autorizado em lei ou produzir prova contra si mesmo ou contra terceiro.</t>
+  </si>
+  <si>
+    <t>Manter presos de ambos os sexos na mesma cela ou espaço de confinamento.</t>
+  </si>
+  <si>
+    <t>Invadir imóvel alheio ou suas dependências, à revelia da vontade do ocupante, sem determinação judicial, quando houver fundados indícios que indiquem a necessidade de ingresso em razão de situação de flagrante delito.</t>
+  </si>
+  <si>
+    <t>São princípios expressamente previstos na Lei Federal n° 14.133, de 01/04/2021, Lei de Licitações e Contratos Administrativos, EXCETO:</t>
+  </si>
+  <si>
+    <t>Interesse público.</t>
+  </si>
+  <si>
+    <t>Vinculação ao edital.</t>
+  </si>
+  <si>
+    <t>Julgamento subjetivo.</t>
+  </si>
+  <si>
+    <t>Segundo o Decreto-lei nº 4.657, de 04/09/1942, Lei de Introdução às Normas do Direito Brasileiro, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>Salvo o conscrito ou, nos casos expressamente previstos em lei específica, o analfabeto, ninguém se escusa de cumprir a lei, alegando que não a conhece.</t>
+  </si>
+  <si>
+    <t>Quando a lei for omissa, o juiz decidirá o caso de acordo com a analogia, os costumes e os princípios gerais de direito.</t>
+  </si>
+  <si>
+    <t>Conforme o Decreto-Lei nº 3.689, de 03/10/1941, Código de Processo Penal, a respeito da cadeia de custódia, são etapas do rastreamento do vestígio, EXCETO.</t>
+  </si>
+  <si>
+    <t>Isolamento.</t>
+  </si>
+  <si>
+    <t>Declaração.</t>
+  </si>
+  <si>
+    <t>Coleta.</t>
+  </si>
+  <si>
+    <t>Armazenamento.</t>
+  </si>
+  <si>
+    <t>Alfa e Bravo combinam de subtrair bens de uma casa. Ao adentrarem na residência, encontram um casal em um quarto e a filha, de 14 anos, em outro quarto. A família percebeu a presença de Alfa e Bravo na casa, mas os citados autores trancaram as portas, prendendo o casal e a filha em seus quartos e, em ato contínuo, levaram os bens subtraídos para fora da casa. Na sequência, Bravo, sem dar conhecimento a Alfa, vai ao quarto da adolescente de 14 anos e a obriga, de forma violenta, à prática da conjunção carnal. Em seguida, Bravo tranca a adolescente novamente no quarto e sai da casa. Alfa e Bravo fogem e são localizados e presos por uma guarnição policial. De acordo com o Decreto-Lei nº 2.848, de 07/12/1940, Código Penal, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Alfa e Bravo deverão ser responsabilizados pela prática de furto e estupro de vulnerável.</t>
+  </si>
+  <si>
+    <t>Alfa e Bravo deverão ser responsabilizados pela prática de furto e somente Bravo responderá pelo crime de estupro.</t>
+  </si>
+  <si>
+    <t>Alfa e Bravo deverão ser responsabilizados pela prática de roubo e somente Bravo responderá pelo crime de estupro.</t>
+  </si>
+  <si>
+    <t>Conforme o Decreto-Lei nº 2.848, de 07/12/1940, Código Penal, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Se não houver violência ou grave ameaça, não configura crime praticar contra alguém e sem a sua anuência ato libidinoso com o objetivo de satisfazer a própria lascívia ou a de terceiro.</t>
+  </si>
+  <si>
+    <t>Ter conjunção carnal ou praticar outro ato libidinoso com uma adolescente de 15 (quinze) anos configura estupro, mesmo que não tenha ocorrido violência, grave ameaça, ainda que a adolescente possua o necessário discernimento para a prática do ato e tenha condições oferecer resistência.</t>
+  </si>
+  <si>
+    <t>Configura importunação sexual constranger alguém com o intuito de obter vantagem ou favorecimento sexual, prevalecendo-se o agente da sua condição de superior hierárquico ou ascendência inerentes ao exercício de emprego, cargo ou função.</t>
+  </si>
+  <si>
+    <t>É crime realizar montagem em fotografia, vídeo, áudio ou qualquer outro registro com o fim de incluir pessoa em cena de nudez ou ato sexual ou libidinoso de caráter íntimo, uma vez que, é definido pelo Código Penal que quem pratica a referida conduta incorre na mesma pena prevista para o crime de registro não autorizado da intimidade sexual.</t>
+  </si>
+  <si>
+    <t>Charlie, funcionário de uma empresa de fornecimento de energia elétrica, desloca até a residência de Oscar, com vistas a realizar verificação de denúncia de desvio de energia elétrica. Após realização de testes técnicos, constata-se que o medidor de energia elétrica funciona, mas indica um consumo menor do que o efetivamente realizado. Oscar, então, confessa a Charlie que, de fato, adulterou o seu medidor de energia para economizar, após aprender como fazê-lo na internet. Charlie, então, solicita a presença da guarnição policial para adoção das medidas cabíveis. De acordo com o Decreto-Lei nº 2.848, de 07/12/1940, Código Penal, marque a alternativa CORRETA, em relação ao crime cometido por Oscar.</t>
+  </si>
+  <si>
+    <t>Receptação.</t>
+  </si>
+  <si>
+    <t>Furto.</t>
+  </si>
+  <si>
+    <t>Dano.</t>
+  </si>
+  <si>
+    <t>Durante a madrugada, Lima Bravo, vigilante noturno de um condomínio, deparou-se com um homem escalando o muro de uma casa com alguns pertences em sua posse. Embora tenha recebido do vigilante uma ordem de parada, o suspeito tentou fugir correndo. Lima Bravo perseguiu-o até alcançá-lo, quando, então, utilizando-se de força moderada e necessária, quebrou a resistência do suspeito e o manteve detido até a chegada da polícia. A guarnição policial constatou que o suspeito tinha, em sua posse, de fato, pertences de pessoas do condomínio sob a vigilância de Lima Bravo. A ação do vigilante causou lesões leves no suspeito. Considerando a situação descrita e o que prevê o Decreto-Lei nº 3.689, de 03/10/1941, Código de Processo Penal, e o Decreto-Lei nº 2.848, de 07/12/1940, Código Penal, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>A conduta de Lima Bravo configura estado de necessidade, o que afasta a ilicitude do fato.</t>
+  </si>
+  <si>
+    <t>Lima Bravo deve ser punido por lesão corporal, pois a vítima estava em fuga e não representava mais ameaça.</t>
+  </si>
+  <si>
+    <t>A ação de Lima Bravo é lícita, pois qualquer do povo pode prender quem for encontrado em flagrante delito.</t>
+  </si>
+  <si>
+    <t>Compareceu ao Quartel da PMMG a Senhora November, afirmando ter sido vítima de um crime. Segundo ela, havia recebido uma mensagem em seu telefone afirmando ter sido ganhadora de um prêmio em razão de seu aniversário. A mensagem dizia que a empresa havia tentado realizar a entrega por três vezes em sua residência, sem sucesso. Informava que em razão das tentativas frustradas de entrega, para receber o prêmio, deveria pagar uma taxa de conveniência no valor de R$ 50,00, via PIX. A vítima concordou e realizou o pagamento, contudo, o prêmio nunca foi entregue e não houve comunicação posterior. Com base no Decreto-Lei nº 2.848, de 07/12/1940, Código Penal, marque a alternativa CORRETA que apresenta o crime do qual November foi vítima.</t>
+  </si>
+  <si>
+    <t>Furto qualificado com abuso de confiança.</t>
+  </si>
+  <si>
+    <t>O Cb Bravo está escalado como sentinela no 99º BPM, no turno das 19h às 07h. O serviço de sentinela no quartel é prestado de forma ininterrupta, de modo que o Cb Charlie renderá o Cb Bravo no turno seguinte. Percebendo que já eram 8 horas da manhã e que seu rendimento não havia chegado, por já haver terminado seu turno, o Cb Bravo decide ir embora. Ao passar pela sentinela às 08h10min, o 1º Sgt Delta verificou que não havia ninguém no posto e constatou que o Cb Charlie era quem estava escalado. Em contato telefônico com o Cb Charlie, este informou ao Sgt Delta que perdera a hora e ainda não havia chegado ao quartel. Em contato telefônico com o Cb Bravo, este informou ao Sgt Delta que, como havia terminado o seu turno de serviço, já estava em casa. De acordo com o Decreto-Lei nº 1.001/1969, Código Penal Militar, marque a alternativa CORRETA em relação à possível responsabilização do Cb Bravo.</t>
+  </si>
+  <si>
+    <t>Deve ser responsabilizado pelo crime de descumprimento de missão.</t>
+  </si>
+  <si>
+    <t>Deve ser responsabilizado pelo crime de abandono de posto.</t>
+  </si>
+  <si>
+    <t>Deve ser responsabilizado pelo crime de prevaricação.</t>
+  </si>
+  <si>
+    <t>Cb Bravo não cometeu qualquer crime por não existir adequação típica para o caso concreto, uma vez que seu turno de serviço já havia se findado.</t>
+  </si>
+  <si>
+    <t>O Sgt Bravo e o Cb Charlie trabalham na administração do 99º BPM, sob a chefia do Cap Alfa. Certo dia, Sgt Bravo e o Cb Charlie, ambos desarmados, combinam entre si que não vão mais executar as ordens emanadas pelo Cap Alfa. Assim, quando o oficial lhes repassa a confecção de uma ordem de serviço, ambos ficam inertes, sem cumprir a ordem dada. Ato contínuo, o Cap Alfa lhes repassa um documento cuja revisão e entrega deve ocorrer no mesmo dia, mas ambos respondem, em uníssono, que não fariam o trabalho. De acordo com o Decreto-Lei nº 1.001/1969, Código Penal Militar, marque a alternativa CORRETA, que contém o crime pelo qual o Sgt Bravo e o Cabo Charlie devem responder.</t>
+  </si>
+  <si>
+    <t>Motim.</t>
+  </si>
+  <si>
+    <t>Recusa de obediência.</t>
+  </si>
+  <si>
+    <t>Desobediência.</t>
+  </si>
+  <si>
+    <t>Segundo o que está estritamente previsto na Lei Federal nº 8.429, de 02/06/1992, Lei de Improbidade Administrativa, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>A posse e o exercício de agente público ficam condicionados à apresentação de declaração de imposto de renda e proventos de qualquer natureza, que tenha sido apresentada à Secretaria Especial da Receita Federal do Brasil, a fim de ser arquivada no serviço de pessoal competente.</t>
+  </si>
+  <si>
+    <t>As penas e sanções previstas na Lei de Improbidade Administrativa poderão ser executadas provisoriamente após a condenação no juízo de primeira instância, ainda que recorrível.</t>
+  </si>
+  <si>
+    <t>Conforme a Resolução nº 5.332, de 18/12/2023, que aprovou o Plano Estratégico da Polícia Militar de Minas Gerais para o quadriênio 2024-2027, marque a alternativa CORRETA que contenha os objetivos estratégicos para a diretriz estratégica de combate às organizações criminosas.</t>
+  </si>
+  <si>
+    <t>Melhorar a agilidade e a qualidade do atendimento à população; totalizar a digitalização e a integração da rede de rádio; aprimorar o atendimento de minorias e pessoas em situação de vulnerabilidade.</t>
+  </si>
+  <si>
+    <t>Manter a PMMG aprestada para atuação em Defesa Civil; expandir as iniciativas para preservação do meio ambiente e desenvolvimento sustentável.</t>
+  </si>
+  <si>
+    <t>Aumentar o custo do crime; enfrentar a violência contra a mulher; assegurar efetivo policial sustentável para atendimento à população.</t>
+  </si>
+  <si>
+    <t>Otimizar as operações de inteligência policial militar; potencializar a capacidade de primeira resposta.</t>
+  </si>
+  <si>
+    <t>4, 3, 1, 2.</t>
+  </si>
+  <si>
+    <t>2, 3, 4, 1.</t>
+  </si>
+  <si>
+    <t>2, 4, 3, 1.</t>
+  </si>
+  <si>
+    <t>1, 3, 4, 2.</t>
+  </si>
+  <si>
+    <t>EAP 1º SGT/2025</t>
+  </si>
+  <si>
+    <t>Conforme a Lei Federal nº 14.133, de 01/04/2021, Lei de Licitações e Contratos Administrativos, avalie: 
+I. O pregão é a modalidade de licitação obrigatória para aquisição de bens e serviços comuns, cujo critério de julgamento poderá ser o de menor preço ou o de maior desconto. 
+II. O sistema de registro de preços, assim como o pregão, é uma modalidade de licitação.
+III. Em licitação na modalidade pregão, o agente responsável pela condução do certame será designado pregoeiro. 
+Conforme previsto na legislação referenciada, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>A Resolução nº 5.332, de 18/12/2023, que aprovou o Plano Estratégico da Polícia Militar de Minas Gerais para o quadriênio 2024-2027, descreve a Identidade Organizacional em quatro núcleos, sendo eles princípios, missão, valores e visão. Isto posto, analise as assertivas abaixo assinalando V (para as VERDADEIRAS) ou F (para as FALSAS). 
+(----) Os princípios Institucionais são proteger e cuidar de Minas Gerais.
+(----) A missão Institucional traduz-se em hierarquia, disciplina militar e patriotismo. 
+(----) Os valores são a honra, o profissionalismo e a abnegação. 
+(----) A visão organizacional busca que a Instituição seja essencial para o povo mineiro.
+Marque a alternativa que corresponda, de cima para baixo, à sequência CORRETA.</t>
+  </si>
+  <si>
+    <t>Com base na Resolução nº 5.142, de 22/11/2021, que aprovou o Manual de Gerenciamento de Frota da Polícia Militar (MAGEF), analise as assertivas abaixo e, ao final, responda o que se pede. 
+I. Na apuração dos danos ocorridos na viatura policial, caso a autoridade militar detentora da carga patrimonial da viatura vislumbre de imediato, devidamente demonstrado pela documentação produzida, que a responsabilidade deve recair sobre o Estado, formalizará o seu arquivamento prévio, sem necessidade da instauração de processo administrativo. 
+II. A aplicação do arquivamento prévio será possível quando o acidente de viatura ocasionar danos em patrimônio de terceiros. 
+III. Se o laudo pericial for absolutamente necessário para determinar a correta imputação da responsabilidade pelos danos do acidente, o Procedimento Administrativo de Viaturas (PAV) será sobrestado até que ele possa ser juntado aos autos. 
+IV. O Procedimento Administrativo de Viaturas (PAV) tramitará totalmente em meio eletrônico (SICOR), sem a necessidade de impressão de documentos. Os documentos que tiverem de ser produzidos ou preexistirem em meio físico serão digitalizados e oportunamente anexados ao PAV. 
+Marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas as assertivas I, III e IV são verdadeiras. </t>
+  </si>
+  <si>
+    <t>Com base na Resolução nº 5.142, de 22/11/2021, que aprovou o Manual de Gerenciamento de Frota da Polícia Militar (MAGEF), é possível afirmar que dos desdobramentos dos fatos envolvendo as viaturas policiais podem derivar apurações com instrumentos específicos. Neste sentido, ENUMERE a segunda coluna de acordo com a primeira e, ao final, responda o que se pede. 
+( 1 ) Procedimento Administrativo de Viaturas (PAV)
+( 2 ) Relatório Investigativo Preliminar (RIP)
+( 3 ) Processo de Comunicação Disciplinar (PCD)
+( 4 ) Inquérito Policial Militar (IPM) 
+(---) Será instaurado quando da ausência de elementos que  justifiquem a instauração de processo acusatório ou o arquivamento prévio dos autos. 
+(---) Será instaurado quando houver indícios da prática de  transgressão disciplinar. 
+(---) Será instaurado quando do acidente resultar vítima (militar ou civil). 
+(---) Será instaurado para quantificar o prejuízo ocorrido, identificar o responsável e determinar a forma de pagamento. 
+Marque a alternativa que contém a sequência CORRETA de respostas, na ordem de cima para baixo.</t>
+  </si>
+  <si>
+    <t>Apenas a assertiva III é verdadeira.</t>
+  </si>
+  <si>
+    <t>Sobre a Resolução Conjunta nº 4.220, de 28/06/2012, que criou o Manual de Processos e Procedimentos Administrativos das Instituições Militares do Estado de Minas Gerais (MAPPA), é CORRETO afirmar que:</t>
+  </si>
+  <si>
+    <t>Não há discordância se o CEDMU propõe um tipo de recompensa e o Comandante, motivadamente, conceda outra.</t>
+  </si>
+  <si>
+    <t>Na hipótese de discordância entre o parecer do CEDMU e a decisão do Comandante da Unidade, a decisão que caberá ao escalão imediatamente superior depende de nova manifestação do CEDMU.</t>
+  </si>
+  <si>
+    <t>Ao receber o recurso disciplinar, autoridade que aplicou a sanção poderá, desde que ouvido o CEDMU, reconsiderar a sua decisão, devendo enviar a documentação ao escalão imediatamente superior, caso entenda procedente o pedido do requerente.</t>
+  </si>
+  <si>
+    <t>Considerando os atos probatórios em processos administrativos previstos na Resolução Conjunta nº 4.220, de 28/06/2012, que criou o Manual de Processos e Procedimentos Administrativos das Instituições Militares do Estado de Minas Gerais (MAPPA), é CORRETO afirmar que:</t>
+  </si>
+  <si>
+    <t>A perícia psicopatológica, caso necessário, conforme o interesse da IME, independentemente de acordo entre os profissionais de saúde da IME e os particulares que acompanham o acusado, poderá ser realizada no local onde o acusado se encontra internado ou em tratamento.</t>
+  </si>
+  <si>
+    <t>Durante a inquirição da testemunha, é vedada recusa às perguntas apresentadas pela defesa, por qualquer que seja o motivo.</t>
+  </si>
+  <si>
+    <t>Poderá o sindicado/acusado/defensor contraditar a testemunha no todo ou em parte, bem como requerer ao responsável pelo ato que a testemunha inquirida esclareça ou torne mais precisa qualquer informação, não podendo reperguntá-lo desnecessariamente, procrastinando o procedimento.</t>
+  </si>
+  <si>
+    <t>A solução de processo que redunde em sanção de advertência, repreensão, prestação de serviço e suspensão, envolvendo militares agregados, aguardando passagem para a reserva remunerada, terá seu curso normal até que se concretize ou não a mudança de quadro.</t>
+  </si>
+  <si>
+    <t>O Manual de Polícia Judiciária das Instituições Militares do Estado de Minas Gerais - Aprovado pela Resolução Conjunta nº 5.346, de 15/02/2024, trata da Instrução Provisória de Deserção. Acerca do tema, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Há previsão legal para a realização compulsória de diligências necessárias para localização e retorno do ausente à sua Unidade.</t>
+  </si>
+  <si>
+    <t>Poderá ser encarregado da Instrução Provisória de Deserção, Oficial, Praça Especial ou Graduada.</t>
+  </si>
+  <si>
+    <t>Será consumado o crime de deserção ou por casos assimilados no oitavo dia de ausência do militar.</t>
+  </si>
+  <si>
+    <t>A parte de ausência será produzida pelo encarregado da Instrução Provisória de Deserção.</t>
+  </si>
+  <si>
+    <t>Tendo por base as prescrições contidas na Instrução Conjunta de Corregedorias nº 01, de 03/02/2014 - ICCPM/BM nº 01/14, que estabelece padronização sobre as atividades administrativas e disciplinares no âmbito da PMMG e do CBMMG, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>A movimentação por conveniência da disciplina, prevista no art. 25, III, do CEDM, configura medida administrativa a ser aplicada quando a presença do militar em determinada localidade seja perniciosa, nociva ou prejudicial à imagem institucional e à própria hierarquia e disciplina.</t>
+  </si>
+  <si>
+    <t>Para se configurar a transgressão disciplinar grave, prevista no inciso IX do artigo 13 (utilizar-se de recursos humanos ou logísticos do Estado ou sob sua responsabilidade para satisfazer a interesses pessoais ou de terceiros), há a necessidade da ocorrência de vantagem pessoal ou de terceiro.</t>
+  </si>
+  <si>
+    <t>Os institutos da simultaneidade e conexão são respectivamente a prática de transgressões que estão intimamente ligadas entre si e a prática de transgressões praticadas pelo mesmo militar, ao mesmo tempo e lugar.</t>
+  </si>
+  <si>
+    <t>Analise as assertivas abaixo sobre a Lei Estadual nº 5.301, de 16/10/1969, que contém o Estatuto dos Militares do Estado de Minas Gerais - EMEMG, e marque V (Verdadeiro) ou F (Falso). 
+(----) A qualquer hora do dia ou da noite, na sede da Unidade ou onde o serviço o exigir, o policial-militar deve estar pronto para cumprir a missão que lhe for confiada pelos seus superiores hierárquicos ou impostos pelas leis e regulamentos. 
+(----) A carga horária semanal de trabalho dos militares estaduais que desempenham atividades administrativas, especializadas, de ensino e operacionais será de quarenta horas, salvo exceções previstas em leis e regulamentos. 
+(----) Os militares terão livre acesso à respectiva escala de trabalho, sendo vedado o acesso ao respectivo banco de horas. 
+(----) O cômputo do cumprimento da carga horária semanal de trabalho será apurado ao final de noventa dias, e o somatório da carga horária não poderá exceder cento e sessenta horas por mês. 
+Assinale a alternativa que corresponda, de cima para baixo, à sequência CORRETA.</t>
+  </si>
+  <si>
+    <t>Com base na Lei Estadual nº 5.301, de 16/10/1969, que contém o Estatuto dos Militares do Estado de Minas Gerais - EMEMG, analise as assertivas abaixo e, ao final, responda o que se pede: 
+I. São requisitos para a obtenção do ADE a avaliação anual de desempenho e produtividade, o conceito disciplinar e o treinamento profissional básico. 
+II. O militar que fizer jus à percepção do ADE continuará percebendo o adicional no percentual adquirido, até atingir o número necessário de ADIs com desempenho satisfatório para alcançar o nível subsequente definido na lei. 
+III. O ingresso nas instituições militares estaduais dar-se-á por meio de concurso público, de provas ou de provas e títulos, no posto ou graduação inicial do QO-PM/BM, do QOS-PM/BM, do QP-PM/BM, do QPEPM/BM e do QOCPL-PM/BM, observados, entre outros, o requisito de possuir Carteira Nacional de Habilitação válida, no mínimo na categoria “B”. 
+IV. O desertor comete ato atentatório à honra pessoal e ao decoro da classe, contudo não configura causa para submissão do militar desertor à processo administrativo-disciplinar. 
+Marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Considerando a Lei Estadual nº 14.310, de 19/06/2002, que contém o Código de Ética e Disciplina dos Militares do Estado de Minas Gerais – CEDM, analise as assertivas abaixo e, ao final, responda o que se pede. 
+I. A sanção disciplinar de suspensão é a interrupção temporária do exercício de cargo, encargo ou função, por um período máximo de dez dias, observando-se a perda da remuneração, contudo, mantem-se as vantagens e direitos vinculados ao exercício do cargo, encargo ou função durante os dias de suspensão. 
+II. A sanção disciplinar de demissão pune determinada transgressão ou decorre da incorrigibilidade do transgressor contumaz, cujo histórico e somatório de sanções indiquem sua inadaptabilidade ou incompatibilidade ao regime disciplinar da Instituição. 
+III. Faltar com a verdade, na condição de testemunha, ou omitir fato do qual tenha conhecimento, assegurado o exercício constitucional da ampla defesa, é transgressão disciplinar. 
+Marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Considerando o Manual de Polícia Judiciária das Instituições Militares do Estado de Minas Gerais - Aprovado pela Resolução Conjunta nº 5.346, de 15/02/2024, no que diz respeito às definições relativas à prisão em flagrante, constantes do referido manual, analise as assertivas abaixo e, ao final, responda o que se pede. 
+I. Captura: no primeiro momento, o agente encontrado em situação de flagrância é capturado, de forma a evitar que continue a praticar o ato delituoso; 
+II. Condução coercitiva: após a captura, o agente será conduzido coercitivamente à presença da autoridade policial para que sejam adotadas as providências legais. No âmbito militar, a autoridade policial é, em regra, o Presidente do Auto de Prisão em Flagrante, bem como o oficial de dia, de quarto, de serviço, ou equivalente; 
+III. Lavratura do auto de prisão em flagrante: a lavratura é a elaboração do auto de prisão em flagrante, no qual são documentados os elementos sensíveis existentes no momento da infração; 
+IV. Recolhimento à prisão (detenção): é manutenção do agente no cárcere, com a consequente expedição de nota de culpa e certidão de direitos constitucionais. 
+Marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No curso de processos e procedimentos administrativos de natureza disciplinar, poderá ser requisitada, judicialmente, a interceptação de escuta telefônica, independentemente da existência de IPM ou APF, conforme a situação. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O grave escândalo deve ser compreendido como algo marcantemente negativo, um fato repreensível, uma situação vergonhosa, perniciosa, cometida pelo transgressor. É necessário que tal conduta saia da normalidade e que tenha repercussão, mesmo que restrita apenas ao público interno, carecendo necessariamente de divulgação pela mídia. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">V, V, F, F. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitui ato de improbidade administrativa que atenta contra os princípios da administração pública a ação ou omissão dolosa que viole os deveres de honestidade, de imparcialidade e de legalidade, caracterizada pela revelação de fato ou circunstância de que tenha ciência em razão das atribuições e que deva permanecer em segredo, propiciando beneficiamento por informação privilegiada ou colocando em risco a segurança da sociedade e do Estado. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A atuação de Lima Bravo é ilícita, pois só o policial poderia agir diante da tentativa de fuga do suspeito. </t>
+  </si>
+  <si>
+    <t>Alfa e Bravo deverão ser responsabilizados pela prática de roubo e somente Bravo responderá pelo crime de estupro de vulnerável.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segurança jurídica. </t>
+  </si>
+  <si>
+    <t>De acordo com o Manual Técnico-Profissional n. 3.04.01/2020-CG (MTP 01), que regula a intervenção policial, o processo de comunicação e o uso da força no âmbito da Polícia Militar de Minas Gerais, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>O policial militar que disparou sua arma de fogo deverá confeccionar o Boletim de Ocorrência (BO) e o respectivo Auto de Resistência (AR), detalhando todos os motivos de sua intervenção e suas consequências, assim como as medidas decorrentes adotadas e, por fim, após encerradas todos os procedimentos supracitados, comunicar o fato verbalmente aos seus superiores.</t>
+  </si>
+  <si>
+    <t>Os disparos com munições de menor potencial ofensivo são realizados para obter uma vantagem tática, para dar mais segurança ao reposicionamento da equipe de policiais militares no terreno.</t>
+  </si>
+  <si>
+    <t>Quando um policial militar dispara sua arma de fogo no exercício das suas atividades, como último recurso na escala de uso diferenciado da força, não o faz para advertir, assustar, intimidar ou ferir um agressor. Contudo, se o disparo de sua arma de fogo for o meio necessário empreendido contra uma agressão injusta atual ou iminente, que atente contra a sua própria vida ou a de terceiros, a intenção do policial militar será de matar o agressor.</t>
+  </si>
+  <si>
+    <t>F, V, V, V.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional n. 3.04.01/2020-CG (MTP 01), que regula a intervenção policial, o processo de comunicação e o uso da força no âmbito da Polícia Militar de Minas Gerais, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Em deslocamento à paisana, em ambientes não controlados, o policial militar deve estar no estado relaxado (branco).</t>
+  </si>
+  <si>
+    <t>Os pontos de foco são partes, em regra, fora da área de risco, que requerem monitoramento específico e demandam imediata atenção do policial militar, uma vez que deles podem surgir ameaças que representem risco à segurança dos envolvidos.</t>
+  </si>
+  <si>
+    <t>Caso a ocorrência tenha exigido atuação no estado de alarme (vermelho), quando cessada a situação de ameaça, é importante incentivar o policial militar a retornar ao estado de alarme (laranja), se as condições de segurança do ambiente assim permitirem. Essa medida favorece o retorno do organismo às condições de funcionamento normal, sem muito desgaste.</t>
+  </si>
+  <si>
+    <t>Área de segurança é a área na qual a Polícia Militar tem o domínio da situação, não havendo, presumidamente, riscos à integridade física e à segurança dos envolvidos.</t>
+  </si>
+  <si>
+    <t>Na busca completa, o policial militar deve utilizar o tato diretamente no corpo despido do abordado para verificar cavidades corporais, sendo essa uma técnica obrigatória para garantir a eficiência do procedimento.</t>
+  </si>
+  <si>
+    <t>A busca ligeira é realizada com movimentos rápidos de deslizamento das mãos sobre o vestuário do abordado e pode ser substituída pelo uso de detector de metal, sendo comum em entradas de eventos esportivos, shows ou estádios.</t>
+  </si>
+  <si>
+    <t>A busca pessoal independe de mandado judicial, desde que haja fundada suspeita ou quando a medida for determinada no curso de busca domiciliar, conforme previsto no art. 244 do Código de Processo Penal (CPP), ou no caso de prisão.</t>
+  </si>
+  <si>
+    <t>Caso uma arma de fogo seja localizada durante a busca pessoal, o PM Revistador deve informar a equipe, determinar que o suspeito assuma a posição de contenção 3 ou 4 (ajoelhado ou deitado), e entregar a arma ao PM Segurança, que a receberá com a mão fraca, mantendo o controle do cano e o dedo fora do gatilho.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.02/2020-CG (MTP 02), Abordagem a Pessoas, marque a alternativa INCORRETA quanto aos procedimentos no local de crime.</t>
+  </si>
+  <si>
+    <t>O policial militar, ao chegar, deve dar atenção apenas aos vestígios presentes no local de crime, valorando o que julgar mais importante para a elucidação do fato. A preservação deverá ser realizada por meio do isolamento e proteção de forma efetiva para que poucas pessoas tenham acesso a ele, evitando-se que vestígios sejam modificados ou destruídos, antes de seu reconhecimento. Em princípio, apenas os vestígios presentes no local são importantes.</t>
+  </si>
+  <si>
+    <t>A conscientização dos policiais militares e da sociedade é fundamental para a conservação do local de crime. Qualquer alteração nesse ambiente prejudicará os trabalhos periciais, a investigação policial e, consequentemente, a elucidação do fato.</t>
+  </si>
+  <si>
+    <t>A preocupação inicial da guarnição será com o socorro à vítima e com a segurança dos envolvidos. Também deve se atentar ao fato de que o autor do delito poderá permanecer nas imediações. Além disso, em decorrência do crime, o local poderá ser alvo de manifestações e da comoção social.</t>
+  </si>
+  <si>
+    <t>O comportamento do abordado (cooperativo, resistente passivo ou ativo) não deve influenciar a postura tática do policial militar durante a abordagem, sendo as mudanças no nível de força determinadas apenas pelo ambiente e pelos fatos motivadores.</t>
+  </si>
+  <si>
+    <t>A abordagem policial é um ato administrativo que exige mandado judicial para ser executado, sendo caracterizada como um procedimento coercitivo e autoexecutório, no qual o policial militar age como representante do Estado.</t>
+  </si>
+  <si>
+    <t>A supremacia de força na abordagem a pessoas é uma vantagem tática do policial militar, medida exclusivamente de forma quantitativa, ou seja, relacionada ao número de policiais em relação ao número de abordados, sem considerar outros recursos ou equipamentos.</t>
+  </si>
+  <si>
+    <t>Na abordagem a pessoas visivelmente portando arma de fogo, todos os policiais militares devem, sempre que possível, estar abrigados e com a arma na posição 3 ou 4 (guarda-alta ou pronta resposta), determinando que o abordado solte a arma e se posicione em uma das posições de contenção.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.03/2020-CG (MTP 03), Blitz Policial, marque a alternativa INCORRETA quanto aos procedimentos na Blitz Noturna.</t>
+  </si>
+  <si>
+    <t>A sinalização da via poderá sofrer algumas alterações para aumentar a segurança dos envolvidos, pois desta forma é possível dar maior visibilidade à blitz e evitar acidentes que envolvam a equipe policial e os pedestres. Cones com dispositivo luminoso e balizadores manuais luminosos poderão ser utilizados como meios de sinalização.</t>
+  </si>
+  <si>
+    <t>A Blitz noturna deve ser montada preferencialmente em local com boa iluminação artificial e que proporcione segurança tanto no aspecto de visualização do dispositivo montado, quanto nas condições de controle de perímetro. Preferencialmente, deve ser montada próximos a desfiladeiros, pontes, aglomerados urbanos, rios, locais de grande concentração de pessoas, para dificultar a fuga do abordado.</t>
+  </si>
+  <si>
+    <t>A utilização de lanternas e dispositivos de iluminação manuais para esta operação é imprescindível, seja para a correta iluminação dos abordados e monitoramento dos pontos de foco e pontos quentes durante a abordagem, seja para efetuar a busca no interior dos compartimentos do veículo.</t>
+  </si>
+  <si>
+    <t>Durante a abordagem noturna, o policial deve ter atenção redobrada, pois a baixa luminosidade interfere diretamente na segurança do trânsito e na identificação de possíveis ameaças. Cabe ao policial militar se manter no estado de prontidão adequado para esta situação, o que é uma medida de prevenção decisiva para a segurança da equipe.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.03/2020-CG (MTP 03), Blitz Policial, marque a alternativa CORRETA quanto à classificação da Blitz Policial.</t>
+  </si>
+  <si>
+    <t>A Blitz de Categoria 3 é considerada de grande porte e o efetivo necessário é de 7 policiais ou mais, além de, no mínimo, uma viatura.</t>
+  </si>
+  <si>
+    <t>A Blitz Policial classifica-se em 4 (quatro) categorias que se diferem basicamente quanto à estrutura de pessoal e logística necessária para a sua execução, além do caráter repressivo ou preventivo.</t>
+  </si>
+  <si>
+    <t>A Blitz de Categoria 1 é considerada de médio porte e o efetivo necessário é de 5 policiais, além de pelo menos uma viatura.</t>
+  </si>
+  <si>
+    <t>Apenas as assertivas II, III e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Apenas as assertivas II, III e IV são verdadeiras</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.04/2020-CG (MTP 04), Abordagem a veículos, marque a alternativa CORRETA quanto à distribuição de funções em uma abordagem a veículos.</t>
+  </si>
+  <si>
+    <t>PM Comandante não pode acumular funções, pois sua atuação é limitada à supervisão estratégica.</t>
+  </si>
+  <si>
+    <t>O disparo de advertência não é previsto como procedimento policial-militar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O local a ser isolado deverá abranger todos os vestígios visualizados numa primeira observação, além de áreas adjacentes que possam ter relação com o crime. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Blitz de Categoria 2 é considerada de médio porte e o efetivo necessário é de 2 ou 3 policiais. </t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional n. 3.04.01/2020-CG (MTP 01), que regula a intervenção policial, o processo de comunicação e o uso da força no âmbito da Polícia Militar de Minas Gerais, marque V para a(s) assertiva(s) verdadeira(s) e F para a(s) assertiva(s) falsas. 
+( ) Em situações em que há mais de um policial militar, é possível dividir os pontos de foco de uma área de risco. 
+( ) Numa abordagem policial, a posição em que o policial militar sustenta sua arma durante a abordagem dependerá exclusivamente do tipo de delito envolvido. O policial militar deve manter-se sempre atento ao comportamento do abordado e não descuidar da sua segurança. 
+( ) Sobre as etapas da intervenção, a Avaliação consiste na decisão acerca das atribuições de cada policial militar, dos métodos e procedimentos para alcançar objetivos da intervenção. Os policiais militares, trabalhando em equipe, devem ter atitudes coerentes entre si, fruto de uma mesma avaliação de risco e um consequente escalonamento da força. 
+( ) Os verbos “usar” ou “empregar” arma de fogo devem ser entendidos como sinônimos. 
+Marque a alternativa que contém a sequência CORRETA de respostas, na ordem de cima para baixo.</t>
+  </si>
+  <si>
+    <t>Considerando o disposto no Manual Técnico-Profissional n. 3.04.01/2020-CG (MTP 01), que regula a intervenção policial, o processo de comunicação e o uso da força no âmbito da Polícia Militar de Minas Gerais, analise as assertivas abaixo e, ao final, responda o que se pede. 
+I. Quando o policial militar atira contra um agressor está fazendo uso da força letal, reafirmando sua intenção de controlar a ameaça. 
+II. O fato de o policial militar somente portar a arma no coldre, como parte do seu equipamento profissional, não será considerado “uso” ou “emprego” de arma de fogo. 
+III. Na intervenção policial-militar, durante o confronto armado, o direcionamento do disparo é uma variável parcialmente controlada pelo policial militar. 
+IV. O Estado de Atenção é o adequado para quando o policial militar detectar um problema que o faça crer que o confronto é provável. 
+Marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.03/2020-CG (MTP 03), Blitz Policial, analise as assertivas abaixo quanto à montagem do dispositivo e procedimento operacional da Blitz Policial e, em seguida, responda o que se pede. 
+I. O dispositivo de uma blitz policial é montado em via pública e constitui-se no espaço sinalizado e demarcado pelos meios logísticos (viatura, cones, cavaletes, etc.), denominado Box. 
+II. No caso do PM Revistador/Vistoriador detectar alguma irregularidade que exija a adoção de providências imediatas, deverá encaminhar o condutor do veículo ao local onde o PM Relator irá registrar o BO/REDS, e o veículo permanecerá parado no local da abordagem. 
+III. Nas operações blitz categoria 1 e 2, será instalado 1 (um) Box. Nas operações de blitz categoria 3 poderão ser instalados 2 (dois) ou mais Boxes, que permitirão abordagens simultâneas, analisando as condições de segurança, de acordo com a avaliação de riscos, o número de policiais disponíveis e os objetivos a serem atingidos. 
+IV. Após a constatação da irregularidade, jamais poderá haver movimentação do veículo do infrator, devido a aspectos legais. 
+Marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.04/2020-CG (MTP 04), Abordagem a veículos, marque a alternativa CORRETA quanto aos níveis de abordagem. 
+I. A abordagem a veículo nível 1 será empregada nas ações e operações policiais de caráter educativo e assistencial (risco nível I). 
+II. A abordagem a veículo nível 3 será empregada nas ações e operações repressivas, caracterizadas por situações onde há um elevado grau de perigo ou a certeza do cometimento de delito (risco nível III). 
+III. A abordagem a veículo nível 2 será empregada nas ações e operações de verificação preventiva (risco nível II) ou em fatos que indiquem ameaça à segurança pública. É o caso das abordagens baseadas em histórico de infrações ou situações em que a infração não foi consumada, mas há indício de preparação para o seu cometimento. Exemplo: veículo produto de furto ou roubo. 
+IV. São exemplos de abordagens a veículo nível 3: ações e operações de fiscalização de documentos e equipamentos obrigatórios; abordagens de iniciativa, decididas com base na avaliação de riscos; denúncia de veículos em locais ermos ou parados em frente a estabelecimentos comerciais, causando suspeição de comerciantes; operações com parada de veículos para fiscalização de porte de armas, busca e apreensão de drogas.</t>
+  </si>
+  <si>
+    <t>De acordo com a Resolução nº 5.383, de 29/08/2024, Diretriz de Segurança para o Emprego Operacional, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Para realizar a comunicação relacionada à Diretriz de Segurança para o Emprego Operacional as possibilidades de convencimento devem ser adotadas de forma restrita, se limitando às campanhas com pílulas de segurança e o treinamento contínuo.</t>
+  </si>
+  <si>
+    <t>Os hábitos angulares são ações habituais positivas que têm a capacidade de influenciar outros hábitos e aspectos na vida de uma pessoa, com potencial de gerar mudanças organizacionais.</t>
+  </si>
+  <si>
+    <t>Para consolidar a cultura de segurança, a Academia de Polícia Militar abordará o tema “Segurança para o Emprego Operacional” no treinamento policial básico. O referido tema não integrará os cursos de formação e habilitação, tendo em vista que trata-se de assunto de relevância apenas para os militares que atuam em Unidade de Execução Operacional.</t>
+  </si>
+  <si>
+    <t>Excetuando-se os comandantes de guarnição e de equipe, os comandantes deverão realizar a fiscalização do fiel cumprimento do uso correto dos equipamentos de proteção individual e coletiva por seus comandados.</t>
+  </si>
+  <si>
+    <t>A Resolução nº 5.383, de 29/08/2024, instituiu, na Polícia Militar de Minas Gerais, a Diretriz de Segurança para o Emprego Operacional. Esta Diretriz Estratégica estabeleceu os princípios e objetivos para a implementação de uma cultura de segurança pessoal e coletiva entre os membros da PMMG. De acordo com a mencionada norma, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>A Polícia Militar de Minas Gerais publicou o Procedimento Operacional Padrão decorrente da descriminalização do porte de Cannabis sativa (maconha) para consumo pessoal através do Memorando nº 30.070.2 - EMPM, de 12/07/2024. De acordo com a mencionada norma, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>O abordado com 40 gramas ou 6 plantas fêmeas de Cannabis sativa (maconha) deverá ser verbalmente notificado a comparecer em juízo, não sendo necessário constar a medida de forma expressa no histórico do Boletim de Ocorrência ou Termo Circunstanciado de Ocorrência.</t>
+  </si>
+  <si>
+    <t>Para quantidades inferiores ao limite de 40 gramas ou 6 plantas fêmeas de Cannabis sativa (maconha) não há que se falar em possibilidade de prisão em flagrante pelo crime de tráfico de drogas, mesmo que existam elementos que indiquem a traficância.</t>
+  </si>
+  <si>
+    <t>O porte para consumo pessoal passou a ser presumido quando a quantidade de maconha encontrada não superar 40 gramas ou 6 plantas fêmeas de Cannabis sativa (maconha). Tal conduta deixou de ser considerada crime e passou a constituir um ilícito administrativo.</t>
+  </si>
+  <si>
+    <t>O porte de substância análoga a drogas para consumo pessoal envolvendo crianças deverá ser lavrado em Termo Circunstanciado de Ocorrência e destinado ao Ministério Público com atribuições para oficiar perante a Vara da Infância e Juventude.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O treinamento abrangente para todos os policiais militares, focado nos procedimentos de segurança e no uso correto dos equipamentos de proteção, não é um dos objetivos da Diretriz de Segurança para o Emprego Operacional. </t>
+  </si>
+  <si>
+    <t>O Cb PM Charlie se encontra processado criminalmente pelo delito militar de deserção. Nesse contexto, suponha que, no decorrer do processo criminal, entre em vigor lei posterior, a qual deixa de considerar como crime a conduta da deserção. Utilizando como base o Decreto-Lei nº 1.001, de 21/10/1969, Código Penal Militar, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Charlie não poderá ser punido por fato que lei posterior deixou de considerar crime.</t>
+  </si>
+  <si>
+    <t>Charlie deve ser condenado, pois o crime foi cometido sob a vigência de norma anterior.</t>
+  </si>
+  <si>
+    <t>Charlie somente será beneficiado com a aplicação da nova lei se não houver sentença condenatória irrecorrível, pois, após o trânsito em julgado, não é possível rever a condenação com base em lei posterior mais benéfica.</t>
+  </si>
+  <si>
+    <t>Charlie continua respondendo ao processo, pois a lei vigente no momento da prática do fato continua aplicável, ainda que tenha sido posteriormente revogada.</t>
+  </si>
+  <si>
+    <t>O Sgt Bravo e o Cb Charlie trabalham na administração do 99º BPM, sob a chefia do Cap Alfa. Certo dia, o Sgt Bravo e o Cb Charlie, ambos desarmados, combinam entre si que não vão mais executar as ordens emanadas pelo Cap Alfa. Assim, quando o oficial lhes repassa a confecção de uma ordem de serviço, ambos ficam inertes, sem cumprir a ordem dada. Ato contínuo, o Cap Alfa lhes repassa um documento cuja revisão e entrega deve ocorrer no mesmo dia, mas ambos respondem, em uníssono, que não fariam o trabalho. De acordo com o Decreto-Lei nº 1.001, de 21/10/1969, Código Penal Militar, marque a alternativa CORRETA, que contém o crime pelo qual o Sgt Bravo e o Cb Charlie devem responder.</t>
+  </si>
+  <si>
+    <t>Revolta.</t>
+  </si>
+  <si>
+    <t>Avalie o caso abaixo: O Sgt Alfa, lotado em um Batalhão da Polícia Militar, tinha constantes desavenças com o Sd Golf. Durante uma discussão acalorada dentro do quartel, o Sgt Alfa ameaçou o Sd Golf e, mais tarde, procurou o Cb Delta, seu amigo próximo, para convencê-lo a ajudá-lo a se vingar. Após conversas ao longo dos dias seguintes, o Cb Delta concordou em auxiliar o Sgt Alfa a executar o plano e o emprestou uma arma de fogo. Certa noite, dentro do alojamento do quartel, o Sgt Alfa, com a arma emprestada, e o Cb Delta, surpreenderam o Sd Golf e o alvejaram com diversos disparos, causando sua morte. A investigação concluiu que ambos participaram do crime: o Sgt Alfa foi o mentor e executor principal, enquanto o Cb Delta ajudou na execução. Diante dos fatos, ambos foram denunciados pelo crime de homicídio qualificado. Com base no Decreto-Lei nº 1.001, de 21/10/1969, Código Penal Militar, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Somente o Sgt Alfa responderá pelo homicídio, pois o Cb Delta não efetuou os disparos.</t>
+  </si>
+  <si>
+    <t>A pena do Cb Delta deverá ser a mesma do Sgt Alfa.</t>
+  </si>
+  <si>
+    <t>O Sgt Alfa terá sua pena agravada, pois foi ele quem instigou e organizou a execução do crime.</t>
+  </si>
+  <si>
+    <t>Se o Cb Delta não estivesse presente quando da execução do crime, não poderia ser responsabilizado pelo homicídio.</t>
+  </si>
+  <si>
+    <t>A senhora Sierra compareceu à Base de Segurança Comunitária relatando ter sido vítima de crime. Segundo seu relato, enquanto aguardava um carro de aplicativo na rua X, um indivíduo que passava puxou o aparelho celular que estava em seu bolso traseiro e fugiu rapidamente. Tendo por referência o Decreto-Lei nº 2.848, de 07/12/1940, Código Penal, marque a alternativa que apresenta de forma CORRETA o crime do qual Sierra foi vítima.</t>
+  </si>
+  <si>
+    <t>Roubo.</t>
+  </si>
+  <si>
+    <t>Compareceu ao Quartel da PMMG a Senhora November, afirmando ter sido vítima de um crime. Segundo ela, havia recebido uma mensagem em seu telefone afirmando ter sido ganhadora de um prêmio em razão de seu aniversário. A mensagem dizia que a empresa havia tentado realizar a entrega por três vezes em sua residência, sem sucesso. Informava que em razão das tentativas frustradas de entrega, para receber o prêmio, November deveria pagar uma taxa de conveniência no valor de R$ 50,00, via PIX. A vítima concordou e realizou o pagamento, contudo, o prêmio nunca foi entregue e não houve comunicação posterior. Com base no Decreto-Lei nº 2.848, de 07/12/1940, Código Penal, marque a alternativa CORRETA que apresenta o crime do qual November foi vítima.</t>
+  </si>
+  <si>
+    <t>A guarnição policial foi acionada para atender a um chamado na Pizzaria da Praça, onde um indivíduo estaria provocando tumulto e constrangendo os clientes. Ao chegar ao local, foi informada de que o indivíduo havia evadido pela avenida. Durante o rastreamento, a equipe localizou Charlie Alfa, que ao ser abordado, passou a proferir palavras ofensivas contra os policiais, desrespeitando a guarnição e tentando menosprezar a autoridade policial diante de transeuntes. De acordo com o Decreto-Lei nº 2.848, de 07/12/1940, Código Penal, qual alternativa define, de forma CORRETA, o crime cometido por Charlie Alfa contra os policias.</t>
+  </si>
+  <si>
+    <t>Resistência.</t>
+  </si>
+  <si>
+    <t>Desacato.</t>
+  </si>
+  <si>
+    <t>Charlie Alfa não cometeu crime.</t>
+  </si>
+  <si>
+    <t>Tomando por base o Decreto-Lei nº 3.689, de 03/10/1941, Código de Processo Penal, notadamente os dispositivos que tratam sobre o Exame de Corpo de Delito, a Cadeia de Custódia e das Perícias em Geral, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Em qualquer circunstância é permitida a entrada de policiais militares em locais isolados bem como a remoção de vestígios de locais de crime antes da liberação por parte do perito responsável.</t>
+  </si>
+  <si>
+    <t>Quando a infração deixar vestígios será indispensável o exame de corpo de delito, direto ou indireto, salvo se houver confissão do acusado.</t>
+  </si>
+  <si>
+    <t>O agente público que reconhecer um elemento como de potencial interesse para a produção de prova pericial fica responsável por sua preservação.</t>
+  </si>
+  <si>
+    <t>Vestígio é todo objeto ou material bruto, visível ou latente, constatado ou recolhido, mesmo os que não tenham relação com a infração penal.</t>
+  </si>
+  <si>
+    <t>De acordo com o Decreto-Lei nº 3.689, de 03/10/1941, Código de Processo Penal, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>O emprego de força na prisão é sempre permitido, desde que os policiais considerem necessário para garantir a condução do preso até a delegacia, independentemente de resistência ou tentativa de fuga.</t>
+  </si>
+  <si>
+    <t>Quem, logo depois de cometer a infração penal, é encontrado com instrumentos, armas, objetos ou papéis que façam presumir ser ele o autor da infração, não está em flagrante delito.</t>
+  </si>
+  <si>
+    <t>A falta de testemunhas da infração impedirá o auto de prisão em flagrante.</t>
+  </si>
+  <si>
+    <t>Ninguém poderá ser preso senão em flagrante delito ou por ordem escrita e fundamentada da autoridade judiciária competente, em decorrência de prisão cautelar ou em virtude de condenação criminal transitada em julgado. EXAME DE APTIDÃO PROFISSIONAL – EAP 2025 – 3º SARGENTO QPPM E QPE</t>
+  </si>
+  <si>
+    <t>Apenas o item I configura improbidade administrativa.</t>
+  </si>
+  <si>
+    <t>Apenas os itens I e II configuram improbidade administrativa.</t>
+  </si>
+  <si>
+    <t>Todos os itens configuram improbidade administrativa.</t>
+  </si>
+  <si>
+    <t>Apenas o item III configura improbidade administrativa.</t>
+  </si>
+  <si>
+    <t>Considerando as disposições da Lei Federal nº 13.869, de 05/09/2019, Lei de Abuso de Autoridade, em especial, quanto às condutas que podem ser praticadas por policiais militares, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>A Lei Federal nº 14.133, de 01/04/2021, Lei de Licitações e Contratos Administrativos, diferencia modalidades de licitação e critérios de julgamento. Escolha a alternativa que NÃO corresponda a um critério de julgamento.</t>
+  </si>
+  <si>
+    <t>Maior desconto.</t>
+  </si>
+  <si>
+    <t>Diálogo competitivo.</t>
+  </si>
+  <si>
+    <t>Menor preço.</t>
+  </si>
+  <si>
+    <t>Salvo o conscrito ou, nos casos expressamente previstos em lei específica, o analfabeto, ninguém se escusa de cumprir a lei, alegando que não a conhece. EXAME DE APTIDÃO PROFISSIONAL – EAP 2025 – 3º SARGENTO QPPM E QPE LEGISLAÇÃO INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>Considerando a Resolução nº 5.142, de 22 de novembro de 2021, que aprovou o Manual de Gerenciamento de Frota, MAGEF, marque a alternativa INCORRETA a respeito das situações em que será instaurado o Procedimento Administrativo de Viatura (PAV).</t>
+  </si>
+  <si>
+    <t>Em caso de prejuízo ao erário decorrente de acidente de trânsito com viatura, com ou sem dano ao terceiro.</t>
+  </si>
+  <si>
+    <t>Para apurar responsabilidade disciplinar decorrente de multa de trânsito.</t>
+  </si>
+  <si>
+    <t>Quando verificado dano/extravio de viatura ou de equipamentos nela instalados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estelionato. </t>
+  </si>
+  <si>
+    <t>Em observância à Lei Federal nº 8.429, de 02/06/1992, que trata das sanções por atos de improbidade administrativa, analise as condutas a seguir. 
+I. Sgt Comandante de Destacamento utiliza o computador e o Instagram oficial da fração para divulgar ações rotineiras, inserindo sua imagem em destaque e frases como “Mais uma conquista do Sgt Fulano para a cidade”, com intenção de autopromoção para futura candidatura política ao cargo de vereador. 
+II. Policial militar revela informações sigilosas sobre operação contra facção criminosa ao líder da organização, comprometendo a segurança pública. 
+III. Comandante de Destacamento participa, fardado e durante o expediente, da inauguração de escola municipal, representando a PMMG. 
+Com base na Lei de Improbidade Administrativa, marque a alternativa CORRETA:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De acordo com o Plano Estratégico da PMMG para o quadriênio 2024-2027, aprovado pela Resolução nº 5.332, de 18/12/2023, a estratégia institucional está organizada em perspectivas, sendo elas: Sociedade; Pessoas, Aprendizagem e Crescimento; e Finanças. Na perspectiva Sociedade, foram estabelecidas 04 (quatro) diretrizes estratégicas, conforme se vê na 1ª coluna abaixo. Isto posto, ENUMERE a 2ª coluna, onde constam objetivos estratégicos, de acordo com as respectivas diretrizes estratégicas listadas na 1ª coluna e, ao final, responda o que se pede. 
+(-1-)  Aumentar a segurança e a sensação de segurança. 
+(-2-)  Proporcionar acesso a serviços de segurança pública de qualidade. 
+(-3-)  Combater as organizações criminosas. 
+(-4-)  Proteger e promover o uso sustentável dos ecossistemas. 
+(---) Otimizar as operações de inteligência policial militar; potencializar a capacidade de primeira resposta. 
+(---)  Manter a PMMG aprestada para atuação em Defesa Civil; expandir as iniciativas para preservação do meio ambiente e desenvolvimento sustentável. 
+(---)  Aumentar o custo do crime; enfrentar a violência contra a mulher; assegurar efetivo policial sustentável para atendimento à população. 
+(---)  Melhorar a agilidade e a qualidade do atendimento à população; totalizar a digitalização e a integração da rede de rádio; aprimorar o atendimento de minorias e pessoas em situação de vulnerabilidade. 
+Marque a alternativa que contém a sequência CORRETA de respostas, na ordem de cima para baixo: 
+</t>
+  </si>
+  <si>
+    <t>3,4,1,2</t>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+  </si>
+  <si>
+    <t>4,1,2,3</t>
+  </si>
+  <si>
+    <t>2,3,4,1</t>
+  </si>
+  <si>
+    <t>Em caso de acidente que ocasionar danos em patrimônio de terceiros.</t>
+  </si>
+  <si>
+    <t>EAP 3º SGT/2025</t>
+  </si>
+  <si>
+    <t>F, V, F, V, F.</t>
+  </si>
+  <si>
+    <t>V, F, V, F, F.</t>
+  </si>
+  <si>
+    <t>F, V, V, V, F.</t>
+  </si>
+  <si>
+    <t>V, F, V, F, V.</t>
+  </si>
+  <si>
+    <t>Conforme o Manual de Polícia Judiciária das Instituições Militares do Estado de Minas Gerais - Aprovado pela Resolução Conjunta nº 5.346, de 15/02/2024, marque a alternativa que corresponde à ordem CORRETA das oitivas no APF.</t>
+  </si>
+  <si>
+    <t>Ofendido, Condutor, Testemunhas, Conduzido.</t>
+  </si>
+  <si>
+    <t>Condutor, Ofendido, Testemunhas, Conduzido.</t>
+  </si>
+  <si>
+    <t>Condutor, Conduzido, Testemunhas, Ofendido.</t>
+  </si>
+  <si>
+    <t>De acordo com a Instrução Conjunta de Corregedorias nº 01, de 03 de fevereiro de 2014, ICCPM/BM nº 01/14, que estabelece padronização sobre as atividades administrativas e disciplinares no âmbito da PMMG e do CBMMG, marque a alternativa CORRETA que define situação que CONFIGURA bis in idem.</t>
+  </si>
+  <si>
+    <t>Destituição de cargo, função ou comissão, cumulada com sanção disciplinar.</t>
+  </si>
+  <si>
+    <t>Aplicar mais de uma sanção disciplinar pela prática simultânea ou conexão de duas ou mais transgressões, apuradas em um mesmo processo ou não.</t>
+  </si>
+  <si>
+    <t>Aplicar a sanção disciplinar e realizar a movimentação de unidade ou fração, por conveniência da disciplina ou interesse do serviço.</t>
+  </si>
+  <si>
+    <t>Realizar o cancelamento de matrícula e desligamento de curso, estágio ou exame, além de aplicar a sanção disciplinar.</t>
+  </si>
+  <si>
+    <t>Apenas as assertivas I e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Considerando o contido na Resolução Conjunta nº 4.220, de 28/06/2012, que criou o Manual de Processos e Procedimentos Administrativos das Instituições Militares do Estado de Minas Gerais (MAPPA), e no Ofício Circular nº 671.1.1/2023 - CPM, que trata da inviabilidade de consignação de perguntas em Termo de Interrogatório, após a invocação do direito ao silêncio pelo interrogado, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>O sindicado/acusado, devidamente notificado, que invocar o direito ao silêncio poderá deixar de comparecer ao ato pelo qual foi convocado para interrogatório.</t>
+  </si>
+  <si>
+    <t>O interrogatório é um ato processual dotado de natureza mista, por se tratar de meio de prova e concomitantemente de defesa, sendo personalíssimo, bifásico e protegido pelo direito ao silêncio.</t>
+  </si>
+  <si>
+    <t>Iniciado o ato de interrogatório, e invocado pelo interrogado o direito total ao silêncio, o encarregado do ato deverá encerrar imediatamente o termo, sem prosseguir com as perguntas, circunstanciando o ocorrido no próprio documento.</t>
+  </si>
+  <si>
+    <t>O direito ao silêncio assiste ao imputado nas perguntas em relação aos fatos, e pode ser exercido total ou parcialmente.</t>
+  </si>
+  <si>
+    <t>Com base na Resolução Conjunta nº 4.220, de 28/06/2012, que criou o Manual de Processos e Procedimentos Administrativos das Instituições Militares do Estado de Minas Gerais (MAPPA), é CORRETO afirmar.</t>
+  </si>
+  <si>
+    <t>O militar dispensado (dispensa saúde) de suas atividades rotineiras ficará, em regra, desobrigado a atender às citações e notificações em processos e procedimentos administrativos.</t>
+  </si>
+  <si>
+    <t>O Relatório de Investigação Preliminar é um processo administrativo que permite ao investigado a ampla defesa e o contraditório.</t>
+  </si>
+  <si>
+    <t>As testemunhas militares estaduais das IME estão obrigadas a depor em processos e procedimentos instaurados pela própria Instituição, por dever de ofício, sob pena, em tese, da prática de crime militar de desobediência e de transgressão disciplinar residual.</t>
+  </si>
+  <si>
+    <t>Com base no Manual de Polícia Judiciária das Instituições Militares do Estado de Minas Gerais - Aprovado pela Resolução Conjunta nº 5.346, de 15/02/2024, em relação às medidas preliminares a serem observadas durante o atendimento da ocorrência de crime militar, marque V (Verdadeiro) ou F (Falso).
+(---) Isolar, preservar, vigiar, controlar o acesso ao local de crime e seus vestígios, dando imediata ciência ao coordenador do policiamento/escalão superior ou equivalente no CBMMG. 
+(---) Socorrer a vítima, se houver, independente da segurança do local. 
+(---) Dar voz de prisão ao infrator, caso este ainda esteja em situação de flagrante. 
+(---) Relacionar e qualificar as testemunhas que presenciaram os fatos ou que detenham informações sobre os eventos e/ou presenciaram a atuação policial, não sendo necessário conduzi-las, em seguida, para o local onde será realizado o APF. 
+(---) Arrecadar, se necessário, os instrumentos da infração e/ou objetos que tenham relação com o fato e encaminhá-los às autoridades policiais competentes após a liberação do local de crime pela perícia técnica. 
+Marque a alternativa que corresponda, na ordem de cima para baixo, à sequência CORRETA:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ofendido, Condutor, Conduzido, Testemunhas. </t>
+  </si>
+  <si>
+    <t>Da solução do RIP poderá decorrer aplicação de sanção disciplinar, diretamente e sem necessidade de outro procedimento.</t>
+  </si>
+  <si>
+    <t>Analise as assertivas abaixo sobre a Lei Estadual nº 5.301/69, de 16/10/1969, que contém o Estatuto dos Militares do Estado de Minas Gerais, EMEMG, e marque V (Verdadeiro) ou F (Falso). 
+(---) A antiguidade de cada posto ou graduação será regulada pela data da promoção ou nomeação, pela prevalência dos graus hierárquicos anteriores, pela data de praça e pela data de nascimento. 
+(---) A precedência hierárquica é regulada pelo posto ou graduação e pela antiguidade no posto ou graduação salvo quando ocorrer precedência funcional, estabelecida em lei ou decreto. 
+(---) Serão organizados anualmente "almanaques" da Polícia Militar, contendo a relação nominal de oficiais, aspirantes a oficial e graduados da ativa, distribuídos pelos respectivos quadros, de acordo com a antiguidade dos postos e graduações. 
+(---) As escalas ordinárias de trabalho dos militares serão publicadas em ciclos de sete dias, com no mínimo dois dias de antecedência, e inseridas no sistema de dados da Instituição para acompanhamento e controle. 
+Assinale a alternativa que corresponda, na ordem de cima para baixo, à sequência CORRETA:</t>
+  </si>
+  <si>
+    <t>Considerando a Lei Estadual nº 14.310/02, de 19/06/2002, que contém o Código de Ética e Disciplina dos Militares do Estado de Minas Gerais, CEDM, analise as assertivas abaixo e, ao final, responda o que se pede. 
+I. As sanções disciplinares de militares, em regra, serão publicadas em boletim ostensivo, e o transgressor notificado pessoalmente, garantindo ampla divulgação como medida educativa para toda a coletividade, salvo os assuntos de caráter sigilosos assim definidos pelo CEDMU. 
+II. Poderão ser aplicadas, independentemente das demais sanções ou cumulativamente com elas, medidas como movimentação de unidade ou fração. 
+III. Quando se tratar de falta ou abandono ao serviço ou expediente, o militar perderá os vencimentos correspondentes aos dias em que se verificar a transgressão, desde que seja aplicada sanção disciplinar. 
+IV. A sanção disciplinar objetiva preservar a disciplina e tem caráter preventivo e educativo. 
+Marque a alternativa CORRETA:</t>
+  </si>
+  <si>
+    <t>Considerando a Lei Estadual nº 14.310, de 19/06/2002, que contém o Código de Ética e Disciplina dos Militares do Estado de Minas Gerais, CEDM, analise as assertivas abaixo e, ao final, responda o que se pede. 
+I. Participar, o militar da ativa, de firma comercial ou de empresa industrial de qualquer natureza, ou nelas exercer função ou emprego remunerado é transgressão disciplinar. 
+II. A palavra comandante é a denominação genérica dada ao militar investido de cargo ou função de direção, comando ou chefia.
+III. Os dias de suspensão serão remunerados. 
+IV. No julgamento da transgressão, obtido o somatório de cinco a dez pontos, será aplicada a sanção disciplinar de repreensão. 
+Marque a alternativa CORRETA:</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.03/2020-CG (MTP 03), Blitz Policial, marque a alternativa INCORRETA quanto aos Procedimentos Operacionais na Blitz Categoria 2.</t>
+  </si>
+  <si>
+    <t>O PM Selecionador, ao escolher o veículo a ser abordado, irá sinalizar para que todos os veículos na via diminuam a velocidade. Em seguida ordenará ao veículo selecionado que adentre ao Box.</t>
+  </si>
+  <si>
+    <t>Encerrada a fiscalização, o PM Vistoriador orientará o tráfego, fazendo o veículo retomar seu deslocamento tão logo as condições estejam seguras, olhando para a pista e sinalizando ao condutor para que siga em frente.</t>
+  </si>
+  <si>
+    <t>Após a parada, o PM Comandante deslocará para a retaguarda do veículo, ficando sobre a calçada e passará a atuar também como PM Segurança.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.03/2020-CG (MTP 03), Blitz Policial, marque a alternativa CORRETA quanto ao Preparo Mental, a Avaliação de Riscos e o Pensamento Tático na Blitz Policial.</t>
+  </si>
+  <si>
+    <t>No momento da abordagem, esteja no estado de atenção (amarelo) e considere as etapas da avaliação de riscos. Identifique quais as ações de respostas para o caso de uma ameaça e qual nível de força será necessário.</t>
+  </si>
+  <si>
+    <t>Durante as operações blitz, antes da abordagem, o policial militar integrante da equipe deve manterse no estado de atenção (amarelo). É importante estar precavido e considerar que a sua segurança deve ser priorizada, tanto em relação ao fluxo do trânsito, quanto a uma possível reação por parte do abordado ou de outras pessoas no veículo.</t>
+  </si>
+  <si>
+    <t>Mesmo que ocorram algumas situações durante a Blitz, como por exemplo, a ocorrência de uma perseguição policial, com ativação do plano de cerco, bloqueio e interceptação, a equipe policial não deve alterar o caráter da Blitz para repressivo, mantendo o preventivo.</t>
+  </si>
+  <si>
+    <t>Caso ocorra a parada de um veículo com número de ocupantes adultos superior ao de policiais e ainda estejam presentes outros fatores da análise de risco que indiquem falta de segurança para a guarnição seguir na intervenção, é recomendável reter os ocupantes dentro do veículo até que chegue apoio de outras guarnições, independentemente do tempo de espera. Não é recomendado liberar o veículo sem abordá-lo.</t>
+  </si>
+  <si>
+    <t>5, 4, 2, 3, 1.</t>
+  </si>
+  <si>
+    <t>2, 5, 4, 3, 1.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.02/2020-CG (MTP 02), Abordagem a Pessoas, marque a alternativa CORRETA quanto à abordagem a pessoas.</t>
+  </si>
+  <si>
+    <t>A supremacia de força na abordagem policial se limita ao número de policiais envolvidos na ação, sem considerar outros fatores como armamento e equipamentos disponíveis.</t>
+  </si>
+  <si>
+    <t>A abordagem policial a pessoas é um ato exclusivamente repressivo, devendo ocorrer apenas em situações onde haja fundada suspeita da prática de um crime.</t>
+  </si>
+  <si>
+    <t>A abordagem policial é o conjunto ordenado de ações policiais para aproximar-se de uma ou mais pessoas, veículos ou edificações. Tem por objetivo resolver demandas do policiamento ostensivo, como orientações, assistências, identificações, advertências de pessoas, verificações, realização de buscas e detenções.</t>
+  </si>
+  <si>
+    <t>A ação de abordar uma pessoa é um ato administrativo, arbitrário, autoexecutório e coercitivo.</t>
+  </si>
+  <si>
+    <t>A fundada suspeita para a busca pessoal pode ser caracterizada por estereótipos como classe social, raça ou forma de se vestir, desde que o policial militar avalie o contexto do ambiente.</t>
+  </si>
+  <si>
+    <t>A busca minuciosa na posição de contenção 2 (abordado em pé, com apoio) exige que o abordado coloque as mãos em uma superfície vertical, como uma parede, com pernas abertas e afastadas. Quanto mais distante da parede estiver os pés do abordado, será mais difícil sua possibilidade de reação.</t>
+  </si>
+  <si>
+    <t>Quando o abordado se opuser, mediante violência ou ameaça, à submissão da busca pessoal, estará incurso no crime de resistência. Neste caso, o policial militar usará a força adequada para vencer a resistência ou se defender. É importante não confundir relutâncias naturais por parte do abordado que se sente constrangido, com o crime de resistência.</t>
+  </si>
+  <si>
+    <t>Na busca completa, recomenda-se que o procedimento seja feito em local isolado do público e, sempre que possível, na presença de uma testemunha do mesmo sexo do abordado.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.02/2020-CG (MTP 02), Abordagem a Pessoas, marque a alternativa INCORRETA quanto às abordagens policiais a grupos vulneráveis.</t>
+  </si>
+  <si>
+    <t>Em relação à diversidade sexual, o BO/REDS deve ser redigido com o nome social (nome pelo qual a pessoa quer ser chamada), desprezando-se o nome de registro da pessoa.</t>
+  </si>
+  <si>
+    <t>As mulheres, quando capturadas, serão mantidas separadas dos homens capturados sempre quando houver condições logísticas e de segurança.</t>
+  </si>
+  <si>
+    <t>O adolescente, em caso de flagrância de ato infracional, será levado à Delegacia de Polícia Especializada. Na ausência desta, deverá ser encaminhado à Delegacia de Polícia local, onde deverá permanecer separado dos adultos, até que outra medida seja determinada.</t>
+  </si>
+  <si>
+    <t>A busca pessoal em mulheres suspeitas de portarem objetos ilícitos deverá ser realizada, preferencialmente, por outra mulher profissional de polícia ou encarregada de fazer cumprir a lei. Em momento algum poderão ser convocadas pessoas leigas ou civis, para realizar buscas em caso de suspeição, pois, isto colocará em risco a segurança e a integridade física destas pessoas.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.01/2020-CG (MTP 01), que regula a intervenção policial, o processo de comunicação e o uso da força no âmbito da Polícia Militar de Minas Gerais, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Com relação às etapas da intervenção policial, a etapa 4 é a avaliação. Nessa etapa, as condutas individuais e do grupo, os resultados alcançados e as falhas notadas em cada intervenção devem ser, posteriormente, discutidas e analisadas, e possíveis correções devem ser apresentadas, visando aperfeiçoar as competências profissionais.</t>
+  </si>
+  <si>
+    <t>Considera-se pensamento tático o processo de pré-visualizar os prováveis problemas a serem encontrados em cada tipo de intervenção policial-militar e ensaiar mentalmente as possibilidades de respostas.</t>
+  </si>
+  <si>
+    <t>Sobre os requisitos básicos para a intervenção policial-militar, o relacionamento compreende o caráter impessoal e imparcial da ação policial-militar, revela a natureza eminentemente profissional da atuação, em qualquer ocorrência, e requer que seja revestida de urbanidade, energia serena, brevidade compatível e, sobretudo, isenção.</t>
+  </si>
+  <si>
+    <t>O direcionamento do disparo e o estado emocional da pessoa atingida são variáveis parcialmente controladas pelo policial.</t>
+  </si>
+  <si>
+    <t>Nas situações em que o agressor estiver utilizando colete balístico, o policial deverá adotar a técnica de alteração de nível, buscando direcionar os disparos em áreas que não estejam protegidas, a exemplo da junção do peito com o pescoço.</t>
+  </si>
+  <si>
+    <t>O local do corpo do agressor em que se dará o impacto é uma variável não controlada pelo policial militar.</t>
+  </si>
+  <si>
+    <t>A letalidade (morte do agressor) apenas excepcionalmente será entendida como o objetivo finalístico do policial militar ao disparar sua arma de fogo em uma ação operacional. Afinal, o resultado “morte” poderá ser decorrente dos efeitos lesivos, próprios do instrumento utilizado (arma de fogo).</t>
+  </si>
+  <si>
+    <t>De acordo com o Manual Técnico-Profissional nº 3.04.01/2020-CG (MTP 01), que regula a intervenção policial, o processo de comunicação e o uso da força no âmbito da Polícia Militar de Minas Gerais, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>O policial militar que disparou sua arma de fogo deverá confeccionar o Boletim de Ocorrência (BO) e o respectivo Auto de Resistência (AR), detalhando todos os motivos de sua intervenção e suas consequências, assim como as medidas decorrentes adotadas e, por fim, após encerrados todos os procedimentos supracitados, comunicar o fato verbalmente aos seus superiores.</t>
+  </si>
+  <si>
+    <t>A abordagem a veículos tem como único objetivo a repressão imediata de delitos e prisão de suspeitos.</t>
+  </si>
+  <si>
+    <t>A busca veicular e a busca pessoal durante a abordagem dependem, em todos os casos, de mandado judicial.</t>
+  </si>
+  <si>
+    <t>A abordagem a veículos pode ser realizada com o objetivo de orientar, fiscalizar documentos, vistoriar sinais veiculares, realizar buscas, prestar assistência, dentre outros objetivos.</t>
+  </si>
+  <si>
+    <t>A abordagem a veículos só é permitida em vias urbanas com histórico de ocorrências criminais.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.04/2020-CG (MTP 04), Abordagem a veículos, marque a alternativa INCORRETA.</t>
+  </si>
+  <si>
+    <t>A abordagem a veículo nível 2 será empregada nas ações e operações de verificação preventiva (risco nível II) ou em fatos que indiquem ameaça à segurança pública. É o caso das abordagens baseadas em histórico de infrações ou situações em que a infração não foi consumada, mas há indício de preparação para o seu cometimento. Exemplo: veículo produto de furto ou roubo.</t>
+  </si>
+  <si>
+    <t>A abordagem a veículo nível 1 será empregada nas ações e operações policiais de caráter educativo e assistencial (risco nível I).</t>
+  </si>
+  <si>
+    <t>A abordagem a veículo nível 3 será empregada nas ações e operações repressivas, caracterizadas por situações onde há um elevado grau de perigo ou a certeza do cometimento de delito (risco nível III).</t>
+  </si>
+  <si>
+    <t>Independentemente da situação, os componentes da guarnição devem considerar que toda abordagem possui um risco em potencial, devendo observar todas as orientações técnicas e doutrinárias, mantendo um estado de prontidão coerente com cada situação.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.04/2020-CG (MTP 04), Abordagem a veículos, marque a alternativa CORRETA, a respeito dos procedimentos a serem adotados durante a realização de perseguição policial a veículo em fuga.</t>
+  </si>
+  <si>
+    <t>Acionar os sinais luminosos e a sirene para sinalizar a situação de emergência policial aos usuários da via e demonstrar a ordem de parada aos ocupantes do veículo em fuga.</t>
+  </si>
+  <si>
+    <t>A utilização do cinto de segurança pelos policiais é facultativa, tendo em vista que a abordagem é iminente.</t>
+  </si>
+  <si>
+    <t>Manter a distância mínima de segurança da viatura em relação ao veículo em fuga. Se os ocupantes efetuarem disparos de arma de fogo contra a viatura, a guarnição poderá ultrapassar ou emparelhar a viatura com o veículo em fuga. Nessas circunstâncias, os policiais militares deverão revidar a agressão.</t>
+  </si>
+  <si>
+    <t>A Resolução nº 5.383, de 29/08/2024, normatizou, na Polícia Militar de Minas Gerais, a Diretriz de Segurança para o Emprego Operacional. Esta Diretriz Estratégica estabeleceu os princípios e objetivos para a implementação de uma cultura de segurança pessoal e coletiva entre os membros da PMMG. De acordo com a mencionada norma, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>2 - 3 - 4 - 1.</t>
+  </si>
+  <si>
+    <t>1 - 4 - 3 - 2.</t>
+  </si>
+  <si>
+    <t>2 - 4 - 3 - 1.</t>
+  </si>
+  <si>
+    <t>Considerando o Procedimento Operacional Padrão previsto no Memorando nº 30.070.2 – EMPM, de 12/07/2024, marque a alternativa CORRETA, sobre os procedimentos específicos previstos.</t>
+  </si>
+  <si>
+    <t>No caso de porte de Cannabis sativa (maconha) para consumo pessoal (40 gramas ou até 6 plantas), mesmo após ser verificado que se trata de substância análoga à maconha, não se deve apreender o material.</t>
+  </si>
+  <si>
+    <t>O porte de Cannabis sativa (maconha) para consumo pessoal (40 gramas ou até 6 plantas), juntamente com outras drogas, deverá ser registrado por meio de Termo Circunstanciado de Ocorrência (TCO), independente da idade do indivíduo que figure como autor do fato.</t>
+  </si>
+  <si>
+    <t>O Termo Circunstanciado de Ocorrência relacionado ao porte de Cannabis sativa (maconha) para consumo pessoal envolvendo infrator adolescente deverá ser destinado à Delegacia Especializada de Proteção à Criança e ao Adolescente.</t>
+  </si>
+  <si>
+    <t>Nos casos de porte de Cannabis sativa (maconha) para consumo pessoal (40 gramas ou até 6 plantas) com infrator adolescente, lavrada a ocorrência, este deve ser liberado aos pais ou responsáveis legais. Quando os pais ou responsáveis legais não forem conhecidos ou localizados, o adolescente será entregue ao Conselho Tutelar local.</t>
+  </si>
+  <si>
+    <t>A Polícia Militar de Minas Gerais publicou o Procedimento Operacional Padrão decorrente da descriminalização do porte de Cannabis sativa (maconha) para consumo pessoal através do Memorando nº 30.070.2 – EMPM, de 12/07/2024. De acordo com a mencionada norma, marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.03/2020-CG (MTP 03), Blitz Policial, analise as assertivas a respeito da abordagem a motocicletas na Blitz Policial e ao final, responda o que se pede. 
+I. O PM Selecionador deverá proceder com cautela e avaliar o risco desta abordagem, considerando que a motocicleta tem sido o meio mais utilizado para a prática de delitos. 
+II. O PM Segurança realizará a abordagem pelo lado esquerdo dos ocupantes da motocicleta, enquanto o PM Revistador/Vistoriador ficará do lado direito. Neste momento os militares observarão os pressupostos da Tática de Aproximação Triangular (TAT), monitorando as mãos do motociclista e passageiro (se houver). 
+III. A busca pessoal, quando necessária, será realizada da seguinte maneira: ao motociclista será dada ordem para descer do veículo e retirar o capacete. Caso haja um passageiro, este será o último a desembarcar e ficará de pé ao lado do veículo, com as mãos sobre a cabeça. 
+IV. Após a busca pessoal e não sendo detectada situação ilícita, os procedimentos de fiscalização de documentos (motocicleta, motociclista e passageiro), bem como a vistoria da motocicleta (lacre da placa, debaixo do assento, compartimento, etc.) deverão ser realizados. 
+Marque a alternativa CORRETA.</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.02/2020-CG (MTP 02), Abordagem a Pessoas, considerando a classificação do local de crime e conceitos correlatos ao lugar do fato, ENUMERE a segunda coluna de acordo com a primeira. 
+(-1-) Local interno. 
+(-2-) Local externo.
+(-3-) Local imediato. 
+(-4-) Local mediato. 
+(-5-) Locais relacionados. 
+(---) São as áreas que podem apresentar conexão com o fato criminoso e, por isso, oferecer pontos comuns de contato (vestígios) a serem observados. 
+(---) São as adjacências; os pontos e áreas de acesso ao local do crime. Ex.: corredores, ambientes ao redor de cômodos, jardins, estradas, trilhas, dentre outros.
+(---) Área não restrita, e que não preserva os vestígios da ação dos fenômenos da natureza. Trata-se de áreas abertas, como ruas, rodovias, praças, estradas, matagal, beira de rios, dentre outros. 
+(---) É a área exata onde ocorreu o fato ou o crime. 
+(---) Área compreendida por ambiente fechado, que preserva os vestígios da ação dos fenômenos da natureza. Ex.: Interior de residências, interior de veículos, galpões, dentre outros. 
+Marque a alternativa que contém a sequência CORRETA, na ordem de cima para baixo:</t>
+  </si>
+  <si>
+    <t>Considerando o disposto no Manual Técnico-Profissional nº 3.04.01/2020-CG (MTP 01), que regula a intervenção policial, o processo de comunicação e o uso da força no âmbito da Polícia Militar de Minas Gerais, analise as assertivas abaixo e, ao final, responda o que se pede. 
+I. A ação do policial militar em levar a mão até a arma (arma localizada) enquanto verbaliza demonstra ao abordado um grau de força mais elevado do que se estivesse falando com as mãos livres. 
+II. Com base nos princípios do uso da força, sendo necessário utilizar imediatamente um nível de força mais elevado, o policial militar precisa percorrer os demais níveis. Assim, o policial militar pode utilizar a força potencialmente letal, para defender a sua vida ou de outra pessoa que se encontra em perigo iminente, provocado por um infrator, sempre que outros meios não tenham sido suficientes ou oportunos para impedir a agressão. 
+III. Os verbos atirar ou disparar arma de fogo devem ser entendidos como sinônimos e correspondem ao efetivo disparo feito pelo policial militar na direção da pessoa abordada. 
+IV. Todo policial militar deverá utilizar equipamentos de proteção individual (EPI) específicos para sua atuação, além de alternativas de armamentos e tecnologias, quando disponíveis e independentemente de ser habilitado para tal uso, para propiciar opções de uso progressivo de força. 
+Marque a alternativa CORRETA:</t>
+  </si>
+  <si>
+    <t>Com base no Manual Técnico-Profissional nº 3.04.04/2020-CG (MTP 04), Abordagem a veículos, analise as assertivas sobre a distribuição de funções em uma abordagem a veículos e, em seguida, responda o que se pede. 
+I. O PM Comandante é o responsável direto pela comunicação com os ocupantes do veículo abordado. 
+II. O PM Verbalizador tem a atribuição de vistoriar o veículo e fiscalizar os documentos do condutor. 
+III. O PM Revistador é o responsável pela realização da busca pessoal nos passageiros e busca no veículo abordado durante a intervenção. 
+IV. O PM Segurança é o responsável pela integridade e segurança dos componentes da equipe. 
+Marque a alternativa CORRETA:</t>
+  </si>
+  <si>
+    <t>De acordo com a Resolução nº 5.383, de 29/08/2024, que dispõe sobre a Diretriz de Segurança para o Emprego Operacional, ENUMERE a 2ª coluna de acordo com a 1ª e, ao final, responda o que se pede. 
+(-1-) Aculturamento. 
+(-2-) Treinamento. 
+(-3-) Comunicação.
+(-4-) Feedback. 
+(---) Por meio da Academia de Polícia Militar o tema “Segurança para o Emprego Operacional” será integrado aos cursos de formação e habilitação promovendo a conscientização dos policiais militares sobre a importância da prevenção de acidentes e a utilização correta dos equipamentos de proteção individual e coletiva, de sorte que estejam preparados para atuar de forma segura em suas atividades, internalizando a segurança como um valor intrínseco à profissão policial. 
+(---) Elemento crucial na construção de uma política de segurança para o trabalho operacional. Através da coleta e análise de dados dos policiais militares é possível identificar áreas de aprimoramento. 
+(---) Para efetivar o aculturamento da segurança para o emprego operacional todas as possibilidades de convencimento devem ser adotadas, incluindo produções audiovisuais de impacto, campanhas com pílulas de segurança, estímulos subliminares e treinamento contínuo. 
+(---) Visa transformar a segurança em um valor fundamental na cultura dos policiais militares e da própria PMMG, promovendo a adoção de procedimentos de segurança adequados, bem como o uso correto e a fiscalização dos equipamentos de proteção individual e coletiva, como um hábito natural e indissociável da atividade policial militar. 
+Marque a alternativa que contém a sequência CORRETA, na ordem de cima para baixo:</t>
+  </si>
+  <si>
+    <t>4 - 3 - 1 - 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procurar manter as armas em pronta-resposta, a fim de manterem-se em condições de revidar disparos de arma de fogo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ao verbalizar durante uma abordagem policial, o policial militar deve manter o equilíbrio e o autocontrole, salvo se o abordado não obedecer, se fizer comentários ofensivos, ignorar a sua presença ou atrair a atenção de pessoas em volta. A linguagem que deve prevalecer é a do policial militar e não a do abordado. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5, 3, 2, 4, 1. </t>
+  </si>
+  <si>
+    <t>Se houver necessidade de busca, será feita pelo PM Vistoriador, primeiramente no veículo e posteriormente em todos os ocupantes.</t>
   </si>
 </sst>
 </file>
@@ -1996,7 +4138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2005,6 +4147,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2339,11 +4483,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299ECF81-BBAD-4B94-AB20-5ECD9C9E2A6C}">
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M230"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" customWidth="1"/>
     <col min="8" max="8" width="17.140625" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="12" max="12" width="16.28515625" customWidth="1"/>
@@ -2391,6 +4535,9 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
@@ -2426,6 +4573,9 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
@@ -2461,6 +4611,9 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
       <c r="B4" t="s">
         <v>34</v>
       </c>
@@ -2488,7 +4641,7 @@
       <c r="J4" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" t="s">
         <v>481</v>
       </c>
       <c r="L4" t="s">
@@ -2499,6 +4652,9 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
       <c r="B5" t="s">
         <v>34</v>
       </c>
@@ -2526,7 +4682,7 @@
       <c r="J5" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" t="s">
         <v>482</v>
       </c>
       <c r="L5" t="s">
@@ -2537,6 +4693,9 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -2572,6 +4731,9 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
@@ -2607,6 +4769,9 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
@@ -2634,7 +4799,7 @@
       <c r="J8" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" t="s">
         <v>483</v>
       </c>
       <c r="L8" t="s">
@@ -2645,6 +4810,9 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -2672,7 +4840,7 @@
       <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" t="s">
         <v>484</v>
       </c>
       <c r="L9" t="s">
@@ -2683,6 +4851,9 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
       <c r="B10" t="s">
         <v>34</v>
       </c>
@@ -2710,7 +4881,7 @@
       <c r="J10" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" t="s">
         <v>485</v>
       </c>
       <c r="L10" t="s">
@@ -2721,6 +4892,9 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
       <c r="B11" t="s">
         <v>85</v>
       </c>
@@ -2756,6 +4930,9 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
       <c r="B12" t="s">
         <v>85</v>
       </c>
@@ -2791,6 +4968,9 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
@@ -2826,6 +5006,9 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
@@ -2853,7 +5036,7 @@
       <c r="J14" t="s">
         <v>57</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" t="s">
         <v>486</v>
       </c>
       <c r="L14" t="s">
@@ -2864,6 +5047,9 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
@@ -2899,6 +5085,9 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
@@ -2933,7 +5122,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
@@ -2968,7 +5160,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
@@ -3003,7 +5198,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
@@ -3038,7 +5236,10 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
@@ -3073,7 +5274,10 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
@@ -3108,7 +5312,10 @@
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
       <c r="B22" t="s">
         <v>12</v>
       </c>
@@ -3143,7 +5350,10 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
@@ -3178,7 +5388,10 @@
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
@@ -3213,7 +5426,10 @@
         <v>152</v>
       </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
@@ -3248,7 +5464,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
@@ -3283,7 +5502,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
@@ -3318,7 +5540,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
       <c r="B28" t="s">
         <v>12</v>
       </c>
@@ -3353,7 +5578,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
@@ -3388,7 +5616,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
@@ -3423,7 +5654,10 @@
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
@@ -3458,7 +5692,10 @@
         <v>199</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
       <c r="B32" t="s">
         <v>85</v>
       </c>
@@ -3493,7 +5730,10 @@
         <v>206</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
       <c r="B33" t="s">
         <v>85</v>
       </c>
@@ -3528,7 +5768,10 @@
         <v>214</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
       <c r="B34" t="s">
         <v>85</v>
       </c>
@@ -3563,7 +5806,10 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
       <c r="B35" t="s">
         <v>85</v>
       </c>
@@ -3591,7 +5837,7 @@
       <c r="J35" t="s">
         <v>33</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="K35" t="s">
         <v>505</v>
       </c>
       <c r="L35" t="s">
@@ -3601,7 +5847,10 @@
         <v>227</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
       <c r="B36" t="s">
         <v>85</v>
       </c>
@@ -3629,7 +5878,7 @@
       <c r="J36" t="s">
         <v>27</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="K36" t="s">
         <v>506</v>
       </c>
       <c r="L36" t="s">
@@ -3639,7 +5888,10 @@
         <v>228</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
       <c r="B37" t="s">
         <v>85</v>
       </c>
@@ -3667,7 +5919,7 @@
       <c r="J37" t="s">
         <v>57</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="K37" t="s">
         <v>507</v>
       </c>
       <c r="L37" t="s">
@@ -3677,7 +5929,10 @@
         <v>228</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
       <c r="B38" t="s">
         <v>85</v>
       </c>
@@ -3705,7 +5960,7 @@
       <c r="J38" t="s">
         <v>33</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="K38" t="s">
         <v>508</v>
       </c>
       <c r="L38" t="s">
@@ -3715,7 +5970,10 @@
         <v>267</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
       <c r="B39" t="s">
         <v>85</v>
       </c>
@@ -3743,7 +6001,7 @@
       <c r="J39" t="s">
         <v>33</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="K39" t="s">
         <v>509</v>
       </c>
       <c r="L39" t="s">
@@ -3753,7 +6011,10 @@
         <v>267</v>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
       <c r="B40" t="s">
         <v>85</v>
       </c>
@@ -3788,7 +6049,10 @@
         <v>268</v>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
       <c r="B41" t="s">
         <v>85</v>
       </c>
@@ -3823,7 +6087,10 @@
         <v>268</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
       <c r="B42" t="s">
         <v>85</v>
       </c>
@@ -3858,7 +6125,10 @@
         <v>269</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
       <c r="B43" t="s">
         <v>85</v>
       </c>
@@ -3893,7 +6163,10 @@
         <v>269</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
       <c r="B44" t="s">
         <v>34</v>
       </c>
@@ -3921,7 +6194,7 @@
       <c r="J44" t="s">
         <v>33</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="K44" t="s">
         <v>487</v>
       </c>
       <c r="L44" t="s">
@@ -3931,7 +6204,10 @@
         <v>313</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
       <c r="B45" t="s">
         <v>34</v>
       </c>
@@ -3959,7 +6235,7 @@
       <c r="J45" t="s">
         <v>33</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="K45" t="s">
         <v>488</v>
       </c>
       <c r="L45" t="s">
@@ -3969,7 +6245,10 @@
         <v>313</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
       <c r="B46" t="s">
         <v>34</v>
       </c>
@@ -3997,7 +6276,7 @@
       <c r="J46" t="s">
         <v>20</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="K46" t="s">
         <v>489</v>
       </c>
       <c r="L46" t="s">
@@ -4007,7 +6286,10 @@
         <v>314</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
       <c r="B47" t="s">
         <v>34</v>
       </c>
@@ -4035,7 +6317,7 @@
       <c r="J47" t="s">
         <v>57</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="K47" t="s">
         <v>490</v>
       </c>
       <c r="L47" t="s">
@@ -4045,7 +6327,10 @@
         <v>314</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
       <c r="B48" t="s">
         <v>34</v>
       </c>
@@ -4073,7 +6358,7 @@
       <c r="J48" t="s">
         <v>20</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="K48" t="s">
         <v>491</v>
       </c>
       <c r="L48" t="s">
@@ -4083,7 +6368,10 @@
         <v>315</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
       <c r="B49" t="s">
         <v>34</v>
       </c>
@@ -4111,7 +6399,7 @@
       <c r="J49" t="s">
         <v>33</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="K49" t="s">
         <v>492</v>
       </c>
       <c r="L49" t="s">
@@ -4121,7 +6409,10 @@
         <v>315</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
       <c r="B50" t="s">
         <v>34</v>
       </c>
@@ -4149,7 +6440,7 @@
       <c r="J50" t="s">
         <v>57</v>
       </c>
-      <c r="K50" s="3" t="s">
+      <c r="K50" t="s">
         <v>495</v>
       </c>
       <c r="L50" t="s">
@@ -4159,7 +6450,10 @@
         <v>316</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
       <c r="B51" t="s">
         <v>34</v>
       </c>
@@ -4187,7 +6481,7 @@
       <c r="J51" t="s">
         <v>57</v>
       </c>
-      <c r="K51" s="3" t="s">
+      <c r="K51" t="s">
         <v>496</v>
       </c>
       <c r="L51" t="s">
@@ -4197,7 +6491,10 @@
         <v>316</v>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
       <c r="B52" t="s">
         <v>34</v>
       </c>
@@ -4225,7 +6522,7 @@
       <c r="J52" t="s">
         <v>20</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="K52" t="s">
         <v>497</v>
       </c>
       <c r="L52" t="s">
@@ -4235,7 +6532,10 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
       <c r="B53" t="s">
         <v>34</v>
       </c>
@@ -4263,7 +6563,7 @@
       <c r="J53" t="s">
         <v>57</v>
       </c>
-      <c r="K53" s="3" t="s">
+      <c r="K53" t="s">
         <v>498</v>
       </c>
       <c r="L53" t="s">
@@ -4273,7 +6573,10 @@
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
       <c r="B54" t="s">
         <v>34</v>
       </c>
@@ -4301,7 +6604,7 @@
       <c r="J54" t="s">
         <v>33</v>
       </c>
-      <c r="K54" s="3" t="s">
+      <c r="K54" t="s">
         <v>493</v>
       </c>
       <c r="L54" t="s">
@@ -4311,7 +6614,10 @@
         <v>336</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
       <c r="B55" t="s">
         <v>34</v>
       </c>
@@ -4339,7 +6645,7 @@
       <c r="J55" t="s">
         <v>20</v>
       </c>
-      <c r="K55" s="3" t="s">
+      <c r="K55" t="s">
         <v>499</v>
       </c>
       <c r="L55" t="s">
@@ -4349,7 +6655,10 @@
         <v>344</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
       <c r="B56" t="s">
         <v>34</v>
       </c>
@@ -4377,7 +6686,7 @@
       <c r="J56" t="s">
         <v>57</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="K56" t="s">
         <v>494</v>
       </c>
       <c r="L56" t="s">
@@ -4387,7 +6696,10 @@
         <v>352</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
       <c r="B57" t="s">
         <v>34</v>
       </c>
@@ -4422,7 +6734,10 @@
         <v>313</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
       <c r="B58" t="s">
         <v>34</v>
       </c>
@@ -4450,7 +6765,7 @@
       <c r="J58" t="s">
         <v>57</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="K58" t="s">
         <v>500</v>
       </c>
       <c r="L58" t="s">
@@ -4460,7 +6775,10 @@
         <v>314</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
       <c r="B59" t="s">
         <v>34</v>
       </c>
@@ -4488,7 +6806,7 @@
       <c r="J59" t="s">
         <v>20</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="K59" t="s">
         <v>501</v>
       </c>
       <c r="L59" t="s">
@@ -4498,7 +6816,10 @@
         <v>315</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
       <c r="B60" t="s">
         <v>34</v>
       </c>
@@ -4526,7 +6847,7 @@
       <c r="J60" t="s">
         <v>33</v>
       </c>
-      <c r="K60" s="3" t="s">
+      <c r="K60" t="s">
         <v>502</v>
       </c>
       <c r="L60" t="s">
@@ -4536,7 +6857,10 @@
         <v>336</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
       <c r="B61" t="s">
         <v>34</v>
       </c>
@@ -4564,7 +6888,7 @@
       <c r="J61" t="s">
         <v>20</v>
       </c>
-      <c r="K61" s="3" t="s">
+      <c r="K61" t="s">
         <v>503</v>
       </c>
       <c r="L61" t="s">
@@ -4574,7 +6898,10 @@
         <v>383</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
       <c r="B62" t="s">
         <v>85</v>
       </c>
@@ -4609,7 +6936,10 @@
         <v>382</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
       <c r="B63" t="s">
         <v>85</v>
       </c>
@@ -4637,7 +6967,7 @@
       <c r="J63" t="s">
         <v>20</v>
       </c>
-      <c r="K63" s="3" t="s">
+      <c r="K63" t="s">
         <v>504</v>
       </c>
       <c r="L63" t="s">
@@ -4647,7 +6977,10 @@
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
       <c r="B64" t="s">
         <v>85</v>
       </c>
@@ -4682,7 +7015,10 @@
         <v>267</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
       <c r="B65" t="s">
         <v>85</v>
       </c>
@@ -4717,7 +7053,10 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
       <c r="B66" t="s">
         <v>85</v>
       </c>
@@ -4752,7 +7091,10 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
       <c r="B67" t="s">
         <v>85</v>
       </c>
@@ -4787,7 +7129,10 @@
         <v>269</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
       <c r="B68" t="s">
         <v>85</v>
       </c>
@@ -4822,7 +7167,10 @@
         <v>268</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
       <c r="B69" t="s">
         <v>85</v>
       </c>
@@ -4857,7 +7205,10 @@
         <v>228</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
       <c r="B70" t="s">
         <v>85</v>
       </c>
@@ -4892,7 +7243,10 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
       <c r="B71" t="s">
         <v>12</v>
       </c>
@@ -4927,7 +7281,10 @@
         <v>192</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
       <c r="B72" t="s">
         <v>12</v>
       </c>
@@ -4962,7 +7319,10 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
       <c r="B73" t="s">
         <v>12</v>
       </c>
@@ -4997,7 +7357,10 @@
         <v>461</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
       <c r="B74" t="s">
         <v>12</v>
       </c>
@@ -5032,7 +7395,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
@@ -5067,7 +7433,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
       <c r="B76" t="s">
         <v>12</v>
       </c>
@@ -5102,7 +7471,10 @@
         <v>462</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
       <c r="B77" t="s">
         <v>12</v>
       </c>
@@ -5137,7 +7509,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
@@ -5172,7 +7547,10 @@
         <v>123</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
@@ -5207,7 +7585,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
       <c r="B80" t="s">
         <v>12</v>
       </c>
@@ -5242,7 +7623,10 @@
         <v>154</v>
       </c>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
       <c r="B81" t="s">
         <v>12</v>
       </c>
@@ -5275,6 +7659,5700 @@
       </c>
       <c r="M81" t="s">
         <v>199</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82" t="s">
+        <v>351</v>
+      </c>
+      <c r="D82" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" t="s">
+        <v>510</v>
+      </c>
+      <c r="F82" t="s">
+        <v>511</v>
+      </c>
+      <c r="G82" t="s">
+        <v>512</v>
+      </c>
+      <c r="H82" t="s">
+        <v>513</v>
+      </c>
+      <c r="I82" t="s">
+        <v>514</v>
+      </c>
+      <c r="J82" t="s">
+        <v>57</v>
+      </c>
+      <c r="L82" t="s">
+        <v>515</v>
+      </c>
+      <c r="M82" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>34</v>
+      </c>
+      <c r="C83" t="s">
+        <v>317</v>
+      </c>
+      <c r="D83" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" t="s">
+        <v>516</v>
+      </c>
+      <c r="F83" t="s">
+        <v>517</v>
+      </c>
+      <c r="G83" t="s">
+        <v>518</v>
+      </c>
+      <c r="H83" t="s">
+        <v>519</v>
+      </c>
+      <c r="I83" t="s">
+        <v>520</v>
+      </c>
+      <c r="J83" t="s">
+        <v>27</v>
+      </c>
+      <c r="L83" t="s">
+        <v>515</v>
+      </c>
+      <c r="M83" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" t="s">
+        <v>317</v>
+      </c>
+      <c r="D84" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" t="s">
+        <v>521</v>
+      </c>
+      <c r="F84" t="s">
+        <v>522</v>
+      </c>
+      <c r="G84" t="s">
+        <v>523</v>
+      </c>
+      <c r="H84" t="s">
+        <v>524</v>
+      </c>
+      <c r="I84" t="s">
+        <v>525</v>
+      </c>
+      <c r="J84" t="s">
+        <v>20</v>
+      </c>
+      <c r="L84" t="s">
+        <v>515</v>
+      </c>
+      <c r="M84" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85" t="s">
+        <v>318</v>
+      </c>
+      <c r="D85" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" t="s">
+        <v>526</v>
+      </c>
+      <c r="F85" t="s">
+        <v>527</v>
+      </c>
+      <c r="G85" t="s">
+        <v>528</v>
+      </c>
+      <c r="H85" t="s">
+        <v>529</v>
+      </c>
+      <c r="I85" t="s">
+        <v>530</v>
+      </c>
+      <c r="J85" t="s">
+        <v>20</v>
+      </c>
+      <c r="L85" t="s">
+        <v>515</v>
+      </c>
+      <c r="M85" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>34</v>
+      </c>
+      <c r="C86" t="s">
+        <v>319</v>
+      </c>
+      <c r="D86" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" t="s">
+        <v>531</v>
+      </c>
+      <c r="F86" t="s">
+        <v>532</v>
+      </c>
+      <c r="G86" t="s">
+        <v>533</v>
+      </c>
+      <c r="H86" t="s">
+        <v>534</v>
+      </c>
+      <c r="I86" t="s">
+        <v>535</v>
+      </c>
+      <c r="J86" t="s">
+        <v>27</v>
+      </c>
+      <c r="L86" t="s">
+        <v>515</v>
+      </c>
+      <c r="M86" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>34</v>
+      </c>
+      <c r="C87" t="s">
+        <v>319</v>
+      </c>
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s">
+        <v>536</v>
+      </c>
+      <c r="F87" t="s">
+        <v>537</v>
+      </c>
+      <c r="G87" t="s">
+        <v>538</v>
+      </c>
+      <c r="H87" t="s">
+        <v>539</v>
+      </c>
+      <c r="I87" t="s">
+        <v>540</v>
+      </c>
+      <c r="J87" t="s">
+        <v>33</v>
+      </c>
+      <c r="L87" t="s">
+        <v>515</v>
+      </c>
+      <c r="M87" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>34</v>
+      </c>
+      <c r="C88" t="s">
+        <v>541</v>
+      </c>
+      <c r="D88" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" t="s">
+        <v>542</v>
+      </c>
+      <c r="F88" t="s">
+        <v>543</v>
+      </c>
+      <c r="G88" t="s">
+        <v>544</v>
+      </c>
+      <c r="H88" t="s">
+        <v>545</v>
+      </c>
+      <c r="I88" t="s">
+        <v>546</v>
+      </c>
+      <c r="J88" t="s">
+        <v>33</v>
+      </c>
+      <c r="L88" t="s">
+        <v>515</v>
+      </c>
+      <c r="M88" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>34</v>
+      </c>
+      <c r="C89" t="s">
+        <v>548</v>
+      </c>
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" t="s">
+        <v>549</v>
+      </c>
+      <c r="F89" t="s">
+        <v>550</v>
+      </c>
+      <c r="G89" t="s">
+        <v>551</v>
+      </c>
+      <c r="H89" t="s">
+        <v>552</v>
+      </c>
+      <c r="I89" t="s">
+        <v>553</v>
+      </c>
+      <c r="J89" t="s">
+        <v>20</v>
+      </c>
+      <c r="L89" t="s">
+        <v>515</v>
+      </c>
+      <c r="M89" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>34</v>
+      </c>
+      <c r="C90" t="s">
+        <v>337</v>
+      </c>
+      <c r="D90" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" t="s">
+        <v>555</v>
+      </c>
+      <c r="F90" t="s">
+        <v>556</v>
+      </c>
+      <c r="G90" t="s">
+        <v>557</v>
+      </c>
+      <c r="H90" t="s">
+        <v>558</v>
+      </c>
+      <c r="I90" t="s">
+        <v>559</v>
+      </c>
+      <c r="J90" t="s">
+        <v>27</v>
+      </c>
+      <c r="L90" t="s">
+        <v>515</v>
+      </c>
+      <c r="M90" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>34</v>
+      </c>
+      <c r="C91" t="s">
+        <v>376</v>
+      </c>
+      <c r="D91" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" t="s">
+        <v>561</v>
+      </c>
+      <c r="F91" t="s">
+        <v>562</v>
+      </c>
+      <c r="G91" t="s">
+        <v>563</v>
+      </c>
+      <c r="H91" t="s">
+        <v>564</v>
+      </c>
+      <c r="I91" t="s">
+        <v>565</v>
+      </c>
+      <c r="J91" t="s">
+        <v>27</v>
+      </c>
+      <c r="L91" t="s">
+        <v>515</v>
+      </c>
+      <c r="M91" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>34</v>
+      </c>
+      <c r="C92" t="s">
+        <v>345</v>
+      </c>
+      <c r="D92" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" t="s">
+        <v>566</v>
+      </c>
+      <c r="F92" t="s">
+        <v>574</v>
+      </c>
+      <c r="G92" t="s">
+        <v>575</v>
+      </c>
+      <c r="H92" t="s">
+        <v>576</v>
+      </c>
+      <c r="I92" t="s">
+        <v>577</v>
+      </c>
+      <c r="J92" t="s">
+        <v>27</v>
+      </c>
+      <c r="L92" t="s">
+        <v>515</v>
+      </c>
+      <c r="M92" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>85</v>
+      </c>
+      <c r="C93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D93" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" t="s">
+        <v>567</v>
+      </c>
+      <c r="F93" t="s">
+        <v>578</v>
+      </c>
+      <c r="G93" t="s">
+        <v>579</v>
+      </c>
+      <c r="H93" t="s">
+        <v>580</v>
+      </c>
+      <c r="I93" t="s">
+        <v>581</v>
+      </c>
+      <c r="J93" t="s">
+        <v>57</v>
+      </c>
+      <c r="L93" t="s">
+        <v>515</v>
+      </c>
+      <c r="M93" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>85</v>
+      </c>
+      <c r="C94" t="s">
+        <v>230</v>
+      </c>
+      <c r="D94" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s">
+        <v>568</v>
+      </c>
+      <c r="F94" t="s">
+        <v>582</v>
+      </c>
+      <c r="G94" t="s">
+        <v>583</v>
+      </c>
+      <c r="H94" t="s">
+        <v>584</v>
+      </c>
+      <c r="I94" t="s">
+        <v>585</v>
+      </c>
+      <c r="J94" t="s">
+        <v>33</v>
+      </c>
+      <c r="L94" t="s">
+        <v>515</v>
+      </c>
+      <c r="M94" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>85</v>
+      </c>
+      <c r="C95" t="s">
+        <v>270</v>
+      </c>
+      <c r="D95" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="F95" t="s">
+        <v>586</v>
+      </c>
+      <c r="G95" t="s">
+        <v>587</v>
+      </c>
+      <c r="H95" t="s">
+        <v>588</v>
+      </c>
+      <c r="I95" t="s">
+        <v>589</v>
+      </c>
+      <c r="J95" t="s">
+        <v>20</v>
+      </c>
+      <c r="L95" t="s">
+        <v>515</v>
+      </c>
+      <c r="M95" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>85</v>
+      </c>
+      <c r="C96" t="s">
+        <v>613</v>
+      </c>
+      <c r="D96" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" t="s">
+        <v>569</v>
+      </c>
+      <c r="F96" t="s">
+        <v>590</v>
+      </c>
+      <c r="G96" t="s">
+        <v>591</v>
+      </c>
+      <c r="H96" t="s">
+        <v>592</v>
+      </c>
+      <c r="I96" t="s">
+        <v>593</v>
+      </c>
+      <c r="J96" t="s">
+        <v>33</v>
+      </c>
+      <c r="L96" t="s">
+        <v>515</v>
+      </c>
+      <c r="M96" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>85</v>
+      </c>
+      <c r="C97" t="s">
+        <v>271</v>
+      </c>
+      <c r="D97" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" t="s">
+        <v>570</v>
+      </c>
+      <c r="F97" t="s">
+        <v>594</v>
+      </c>
+      <c r="G97" t="s">
+        <v>595</v>
+      </c>
+      <c r="H97" t="s">
+        <v>596</v>
+      </c>
+      <c r="I97" t="s">
+        <v>597</v>
+      </c>
+      <c r="J97" t="s">
+        <v>20</v>
+      </c>
+      <c r="L97" t="s">
+        <v>515</v>
+      </c>
+      <c r="M97" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>85</v>
+      </c>
+      <c r="C98" t="s">
+        <v>384</v>
+      </c>
+      <c r="D98" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" t="s">
+        <v>571</v>
+      </c>
+      <c r="F98" t="s">
+        <v>598</v>
+      </c>
+      <c r="G98" t="s">
+        <v>599</v>
+      </c>
+      <c r="H98" t="s">
+        <v>600</v>
+      </c>
+      <c r="I98" t="s">
+        <v>601</v>
+      </c>
+      <c r="J98" t="s">
+        <v>27</v>
+      </c>
+      <c r="L98" t="s">
+        <v>515</v>
+      </c>
+      <c r="M98" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>85</v>
+      </c>
+      <c r="C99" t="s">
+        <v>213</v>
+      </c>
+      <c r="D99" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" t="s">
+        <v>572</v>
+      </c>
+      <c r="F99" t="s">
+        <v>602</v>
+      </c>
+      <c r="G99" t="s">
+        <v>603</v>
+      </c>
+      <c r="H99" t="s">
+        <v>604</v>
+      </c>
+      <c r="I99" t="s">
+        <v>605</v>
+      </c>
+      <c r="J99" t="s">
+        <v>57</v>
+      </c>
+      <c r="L99" t="s">
+        <v>515</v>
+      </c>
+      <c r="M99" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>85</v>
+      </c>
+      <c r="C100" t="s">
+        <v>614</v>
+      </c>
+      <c r="D100" t="s">
+        <v>14</v>
+      </c>
+      <c r="E100" t="s">
+        <v>573</v>
+      </c>
+      <c r="F100" t="s">
+        <v>606</v>
+      </c>
+      <c r="G100" t="s">
+        <v>607</v>
+      </c>
+      <c r="H100" t="s">
+        <v>608</v>
+      </c>
+      <c r="I100" t="s">
+        <v>609</v>
+      </c>
+      <c r="J100" t="s">
+        <v>20</v>
+      </c>
+      <c r="L100" t="s">
+        <v>515</v>
+      </c>
+      <c r="M100" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>85</v>
+      </c>
+      <c r="C101" t="s">
+        <v>272</v>
+      </c>
+      <c r="D101" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" t="s">
+        <v>615</v>
+      </c>
+      <c r="F101" t="s">
+        <v>616</v>
+      </c>
+      <c r="G101" t="s">
+        <v>617</v>
+      </c>
+      <c r="H101" t="s">
+        <v>618</v>
+      </c>
+      <c r="I101" t="s">
+        <v>619</v>
+      </c>
+      <c r="J101" t="s">
+        <v>57</v>
+      </c>
+      <c r="L101" t="s">
+        <v>515</v>
+      </c>
+      <c r="M101" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>85</v>
+      </c>
+      <c r="C102" t="s">
+        <v>229</v>
+      </c>
+      <c r="D102" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="F102" t="s">
+        <v>620</v>
+      </c>
+      <c r="G102" t="s">
+        <v>621</v>
+      </c>
+      <c r="H102" t="s">
+        <v>622</v>
+      </c>
+      <c r="I102" t="s">
+        <v>623</v>
+      </c>
+      <c r="J102" t="s">
+        <v>27</v>
+      </c>
+      <c r="L102" t="s">
+        <v>515</v>
+      </c>
+      <c r="M102" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>85</v>
+      </c>
+      <c r="C103" t="s">
+        <v>229</v>
+      </c>
+      <c r="D103" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" t="s">
+        <v>624</v>
+      </c>
+      <c r="F103" t="s">
+        <v>625</v>
+      </c>
+      <c r="G103" t="s">
+        <v>626</v>
+      </c>
+      <c r="H103" t="s">
+        <v>627</v>
+      </c>
+      <c r="I103" t="s">
+        <v>628</v>
+      </c>
+      <c r="J103" t="s">
+        <v>57</v>
+      </c>
+      <c r="L103" t="s">
+        <v>515</v>
+      </c>
+      <c r="M103" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>85</v>
+      </c>
+      <c r="C104" t="s">
+        <v>207</v>
+      </c>
+      <c r="D104" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" t="s">
+        <v>629</v>
+      </c>
+      <c r="F104" t="s">
+        <v>630</v>
+      </c>
+      <c r="G104" t="s">
+        <v>631</v>
+      </c>
+      <c r="H104" t="s">
+        <v>632</v>
+      </c>
+      <c r="I104" t="s">
+        <v>633</v>
+      </c>
+      <c r="J104" t="s">
+        <v>33</v>
+      </c>
+      <c r="L104" t="s">
+        <v>515</v>
+      </c>
+      <c r="M104" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>85</v>
+      </c>
+      <c r="C105" t="s">
+        <v>207</v>
+      </c>
+      <c r="D105" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s">
+        <v>634</v>
+      </c>
+      <c r="F105" t="s">
+        <v>635</v>
+      </c>
+      <c r="G105" t="s">
+        <v>636</v>
+      </c>
+      <c r="H105" t="s">
+        <v>637</v>
+      </c>
+      <c r="I105" t="s">
+        <v>639</v>
+      </c>
+      <c r="J105" t="s">
+        <v>20</v>
+      </c>
+      <c r="L105" t="s">
+        <v>515</v>
+      </c>
+      <c r="M105" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106" t="s">
+        <v>200</v>
+      </c>
+      <c r="D106" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106" t="s">
+        <v>640</v>
+      </c>
+      <c r="F106" t="s">
+        <v>641</v>
+      </c>
+      <c r="G106" t="s">
+        <v>642</v>
+      </c>
+      <c r="H106" t="s">
+        <v>643</v>
+      </c>
+      <c r="I106" t="s">
+        <v>644</v>
+      </c>
+      <c r="J106" t="s">
+        <v>27</v>
+      </c>
+      <c r="L106" t="s">
+        <v>515</v>
+      </c>
+      <c r="M106" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" t="s">
+        <v>112</v>
+      </c>
+      <c r="D107" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" t="s">
+        <v>645</v>
+      </c>
+      <c r="F107" t="s">
+        <v>646</v>
+      </c>
+      <c r="G107" t="s">
+        <v>647</v>
+      </c>
+      <c r="H107" t="s">
+        <v>648</v>
+      </c>
+      <c r="I107" t="s">
+        <v>649</v>
+      </c>
+      <c r="J107" t="s">
+        <v>27</v>
+      </c>
+      <c r="L107" t="s">
+        <v>515</v>
+      </c>
+      <c r="M107" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" t="s">
+        <v>650</v>
+      </c>
+      <c r="F108" t="s">
+        <v>651</v>
+      </c>
+      <c r="G108" t="s">
+        <v>652</v>
+      </c>
+      <c r="H108" t="s">
+        <v>653</v>
+      </c>
+      <c r="I108" t="s">
+        <v>654</v>
+      </c>
+      <c r="J108" t="s">
+        <v>20</v>
+      </c>
+      <c r="L108" t="s">
+        <v>515</v>
+      </c>
+      <c r="M108" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" t="s">
+        <v>111</v>
+      </c>
+      <c r="D109" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s">
+        <v>655</v>
+      </c>
+      <c r="F109" t="s">
+        <v>656</v>
+      </c>
+      <c r="G109" t="s">
+        <v>657</v>
+      </c>
+      <c r="H109" t="s">
+        <v>658</v>
+      </c>
+      <c r="I109" t="s">
+        <v>659</v>
+      </c>
+      <c r="J109" t="s">
+        <v>27</v>
+      </c>
+      <c r="L109" t="s">
+        <v>515</v>
+      </c>
+      <c r="M109" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" t="s">
+        <v>476</v>
+      </c>
+      <c r="D110" t="s">
+        <v>14</v>
+      </c>
+      <c r="E110" t="s">
+        <v>660</v>
+      </c>
+      <c r="F110" t="s">
+        <v>661</v>
+      </c>
+      <c r="G110" t="s">
+        <v>662</v>
+      </c>
+      <c r="H110" t="s">
+        <v>663</v>
+      </c>
+      <c r="I110" t="s">
+        <v>664</v>
+      </c>
+      <c r="J110" t="s">
+        <v>33</v>
+      </c>
+      <c r="L110" t="s">
+        <v>515</v>
+      </c>
+      <c r="M110" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" t="s">
+        <v>708</v>
+      </c>
+      <c r="D111" t="s">
+        <v>14</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="F111" t="s">
+        <v>665</v>
+      </c>
+      <c r="G111" t="s">
+        <v>666</v>
+      </c>
+      <c r="H111" t="s">
+        <v>667</v>
+      </c>
+      <c r="I111" t="s">
+        <v>668</v>
+      </c>
+      <c r="J111" t="s">
+        <v>57</v>
+      </c>
+      <c r="L111" t="s">
+        <v>515</v>
+      </c>
+      <c r="M111" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" t="s">
+        <v>14</v>
+      </c>
+      <c r="E112" t="s">
+        <v>669</v>
+      </c>
+      <c r="F112" t="s">
+        <v>670</v>
+      </c>
+      <c r="G112" t="s">
+        <v>671</v>
+      </c>
+      <c r="H112" t="s">
+        <v>672</v>
+      </c>
+      <c r="I112" t="s">
+        <v>673</v>
+      </c>
+      <c r="J112" t="s">
+        <v>33</v>
+      </c>
+      <c r="L112" t="s">
+        <v>515</v>
+      </c>
+      <c r="M112" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" t="s">
+        <v>14</v>
+      </c>
+      <c r="E113" t="s">
+        <v>674</v>
+      </c>
+      <c r="F113" t="s">
+        <v>675</v>
+      </c>
+      <c r="G113" t="s">
+        <v>676</v>
+      </c>
+      <c r="H113" t="s">
+        <v>677</v>
+      </c>
+      <c r="I113" t="s">
+        <v>678</v>
+      </c>
+      <c r="J113" t="s">
+        <v>57</v>
+      </c>
+      <c r="L113" t="s">
+        <v>515</v>
+      </c>
+      <c r="M113" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" t="s">
+        <v>167</v>
+      </c>
+      <c r="D114" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="F114" t="s">
+        <v>679</v>
+      </c>
+      <c r="G114" t="s">
+        <v>680</v>
+      </c>
+      <c r="H114" t="s">
+        <v>681</v>
+      </c>
+      <c r="I114" t="s">
+        <v>666</v>
+      </c>
+      <c r="J114" t="s">
+        <v>20</v>
+      </c>
+      <c r="L114" t="s">
+        <v>515</v>
+      </c>
+      <c r="M114" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115" t="s">
+        <v>167</v>
+      </c>
+      <c r="D115" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" t="s">
+        <v>682</v>
+      </c>
+      <c r="F115" t="s">
+        <v>683</v>
+      </c>
+      <c r="G115" t="s">
+        <v>684</v>
+      </c>
+      <c r="H115" t="s">
+        <v>685</v>
+      </c>
+      <c r="I115" t="s">
+        <v>686</v>
+      </c>
+      <c r="J115" t="s">
+        <v>27</v>
+      </c>
+      <c r="L115" t="s">
+        <v>515</v>
+      </c>
+      <c r="M115" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" t="s">
+        <v>709</v>
+      </c>
+      <c r="D116" t="s">
+        <v>14</v>
+      </c>
+      <c r="E116" t="s">
+        <v>687</v>
+      </c>
+      <c r="F116" t="s">
+        <v>688</v>
+      </c>
+      <c r="G116" t="s">
+        <v>689</v>
+      </c>
+      <c r="H116" t="s">
+        <v>690</v>
+      </c>
+      <c r="I116" t="s">
+        <v>691</v>
+      </c>
+      <c r="J116" t="s">
+        <v>27</v>
+      </c>
+      <c r="L116" t="s">
+        <v>515</v>
+      </c>
+      <c r="M116" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>12</v>
+      </c>
+      <c r="C117" t="s">
+        <v>124</v>
+      </c>
+      <c r="D117" t="s">
+        <v>14</v>
+      </c>
+      <c r="E117" t="s">
+        <v>692</v>
+      </c>
+      <c r="F117" t="s">
+        <v>693</v>
+      </c>
+      <c r="G117" t="s">
+        <v>694</v>
+      </c>
+      <c r="H117" t="s">
+        <v>695</v>
+      </c>
+      <c r="I117" t="s">
+        <v>696</v>
+      </c>
+      <c r="J117" t="s">
+        <v>57</v>
+      </c>
+      <c r="L117" t="s">
+        <v>515</v>
+      </c>
+      <c r="M117" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" t="s">
+        <v>153</v>
+      </c>
+      <c r="D118" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="F118" t="s">
+        <v>666</v>
+      </c>
+      <c r="G118" t="s">
+        <v>697</v>
+      </c>
+      <c r="H118" t="s">
+        <v>698</v>
+      </c>
+      <c r="I118" t="s">
+        <v>699</v>
+      </c>
+      <c r="J118" t="s">
+        <v>33</v>
+      </c>
+      <c r="L118" t="s">
+        <v>515</v>
+      </c>
+      <c r="M118" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>141</v>
+      </c>
+      <c r="D119" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" t="s">
+        <v>700</v>
+      </c>
+      <c r="F119" t="s">
+        <v>701</v>
+      </c>
+      <c r="G119" t="s">
+        <v>702</v>
+      </c>
+      <c r="H119" t="s">
+        <v>703</v>
+      </c>
+      <c r="I119" t="s">
+        <v>707</v>
+      </c>
+      <c r="J119" t="s">
+        <v>27</v>
+      </c>
+      <c r="L119" t="s">
+        <v>515</v>
+      </c>
+      <c r="M119" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>722</v>
+      </c>
+      <c r="C120" t="s">
+        <v>722</v>
+      </c>
+      <c r="D120" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" t="s">
+        <v>713</v>
+      </c>
+      <c r="F120" t="s">
+        <v>714</v>
+      </c>
+      <c r="G120" t="s">
+        <v>715</v>
+      </c>
+      <c r="H120" t="s">
+        <v>716</v>
+      </c>
+      <c r="I120" t="s">
+        <v>717</v>
+      </c>
+      <c r="J120" t="s">
+        <v>20</v>
+      </c>
+      <c r="L120" t="s">
+        <v>723</v>
+      </c>
+      <c r="M120" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>722</v>
+      </c>
+      <c r="C121" t="s">
+        <v>722</v>
+      </c>
+      <c r="D121" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="F121" t="s">
+        <v>718</v>
+      </c>
+      <c r="G121" t="s">
+        <v>719</v>
+      </c>
+      <c r="H121" t="s">
+        <v>720</v>
+      </c>
+      <c r="I121" t="s">
+        <v>721</v>
+      </c>
+      <c r="J121" t="s">
+        <v>33</v>
+      </c>
+      <c r="L121" t="s">
+        <v>723</v>
+      </c>
+      <c r="M121" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>34</v>
+      </c>
+      <c r="C122" t="s">
+        <v>548</v>
+      </c>
+      <c r="D122" t="s">
+        <v>14</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="F122" t="s">
+        <v>726</v>
+      </c>
+      <c r="G122" t="s">
+        <v>727</v>
+      </c>
+      <c r="H122" t="s">
+        <v>356</v>
+      </c>
+      <c r="I122" t="s">
+        <v>728</v>
+      </c>
+      <c r="J122" t="s">
+        <v>57</v>
+      </c>
+      <c r="L122" t="s">
+        <v>723</v>
+      </c>
+      <c r="M122" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>34</v>
+      </c>
+      <c r="C123" t="s">
+        <v>317</v>
+      </c>
+      <c r="D123" t="s">
+        <v>14</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="F123" t="s">
+        <v>730</v>
+      </c>
+      <c r="G123" t="s">
+        <v>731</v>
+      </c>
+      <c r="H123" t="s">
+        <v>732</v>
+      </c>
+      <c r="I123" t="s">
+        <v>733</v>
+      </c>
+      <c r="J123" t="s">
+        <v>27</v>
+      </c>
+      <c r="L123" t="s">
+        <v>723</v>
+      </c>
+      <c r="M123" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" t="s">
+        <v>318</v>
+      </c>
+      <c r="D124" t="s">
+        <v>14</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="F124" t="s">
+        <v>734</v>
+      </c>
+      <c r="G124" t="s">
+        <v>735</v>
+      </c>
+      <c r="H124" t="s">
+        <v>736</v>
+      </c>
+      <c r="I124" t="s">
+        <v>737</v>
+      </c>
+      <c r="J124" t="s">
+        <v>33</v>
+      </c>
+      <c r="L124" t="s">
+        <v>723</v>
+      </c>
+      <c r="M124" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" t="s">
+        <v>319</v>
+      </c>
+      <c r="D125" t="s">
+        <v>14</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="F125" t="s">
+        <v>730</v>
+      </c>
+      <c r="G125" t="s">
+        <v>731</v>
+      </c>
+      <c r="H125" t="s">
+        <v>732</v>
+      </c>
+      <c r="I125" t="s">
+        <v>733</v>
+      </c>
+      <c r="J125" t="s">
+        <v>27</v>
+      </c>
+      <c r="L125" t="s">
+        <v>723</v>
+      </c>
+      <c r="M125" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>34</v>
+      </c>
+      <c r="C126" t="s">
+        <v>541</v>
+      </c>
+      <c r="D126" t="s">
+        <v>14</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="F126" t="s">
+        <v>738</v>
+      </c>
+      <c r="G126" t="s">
+        <v>739</v>
+      </c>
+      <c r="H126" t="s">
+        <v>740</v>
+      </c>
+      <c r="I126" t="s">
+        <v>733</v>
+      </c>
+      <c r="J126" t="s">
+        <v>57</v>
+      </c>
+      <c r="L126" t="s">
+        <v>723</v>
+      </c>
+      <c r="M126" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>34</v>
+      </c>
+      <c r="C127" t="s">
+        <v>541</v>
+      </c>
+      <c r="D127" t="s">
+        <v>14</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="F127" t="s">
+        <v>745</v>
+      </c>
+      <c r="G127" t="s">
+        <v>733</v>
+      </c>
+      <c r="H127" t="s">
+        <v>730</v>
+      </c>
+      <c r="I127" t="s">
+        <v>731</v>
+      </c>
+      <c r="J127" t="s">
+        <v>27</v>
+      </c>
+      <c r="L127" t="s">
+        <v>723</v>
+      </c>
+      <c r="M127" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>34</v>
+      </c>
+      <c r="C128" t="s">
+        <v>351</v>
+      </c>
+      <c r="D128" t="s">
+        <v>14</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="F128" t="s">
+        <v>732</v>
+      </c>
+      <c r="G128" t="s">
+        <v>730</v>
+      </c>
+      <c r="H128" t="s">
+        <v>731</v>
+      </c>
+      <c r="I128" t="s">
+        <v>745</v>
+      </c>
+      <c r="J128" t="s">
+        <v>57</v>
+      </c>
+      <c r="L128" t="s">
+        <v>723</v>
+      </c>
+      <c r="M128" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>85</v>
+      </c>
+      <c r="C129" t="s">
+        <v>207</v>
+      </c>
+      <c r="D129" t="s">
+        <v>14</v>
+      </c>
+      <c r="E129" t="s">
+        <v>748</v>
+      </c>
+      <c r="F129" t="s">
+        <v>749</v>
+      </c>
+      <c r="G129" t="s">
+        <v>750</v>
+      </c>
+      <c r="H129" t="s">
+        <v>751</v>
+      </c>
+      <c r="I129" t="s">
+        <v>752</v>
+      </c>
+      <c r="J129" t="s">
+        <v>57</v>
+      </c>
+      <c r="L129" t="s">
+        <v>723</v>
+      </c>
+      <c r="M129" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>85</v>
+      </c>
+      <c r="C130" t="s">
+        <v>271</v>
+      </c>
+      <c r="D130" t="s">
+        <v>14</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="F130" t="s">
+        <v>753</v>
+      </c>
+      <c r="G130" t="s">
+        <v>754</v>
+      </c>
+      <c r="H130" t="s">
+        <v>755</v>
+      </c>
+      <c r="I130" t="s">
+        <v>756</v>
+      </c>
+      <c r="J130" t="s">
+        <v>57</v>
+      </c>
+      <c r="L130" t="s">
+        <v>723</v>
+      </c>
+      <c r="M130" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>85</v>
+      </c>
+      <c r="C131" t="s">
+        <v>230</v>
+      </c>
+      <c r="D131" t="s">
+        <v>14</v>
+      </c>
+      <c r="E131" t="s">
+        <v>758</v>
+      </c>
+      <c r="F131" t="s">
+        <v>759</v>
+      </c>
+      <c r="G131" t="s">
+        <v>760</v>
+      </c>
+      <c r="H131" t="s">
+        <v>761</v>
+      </c>
+      <c r="I131" t="s">
+        <v>762</v>
+      </c>
+      <c r="J131" t="s">
+        <v>33</v>
+      </c>
+      <c r="L131" t="s">
+        <v>723</v>
+      </c>
+      <c r="M131" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>85</v>
+      </c>
+      <c r="C132" t="s">
+        <v>270</v>
+      </c>
+      <c r="D132" t="s">
+        <v>14</v>
+      </c>
+      <c r="E132" t="s">
+        <v>763</v>
+      </c>
+      <c r="F132" t="s">
+        <v>764</v>
+      </c>
+      <c r="G132" t="s">
+        <v>765</v>
+      </c>
+      <c r="H132" t="s">
+        <v>766</v>
+      </c>
+      <c r="I132" t="s">
+        <v>767</v>
+      </c>
+      <c r="J132" t="s">
+        <v>27</v>
+      </c>
+      <c r="L132" t="s">
+        <v>723</v>
+      </c>
+      <c r="M132" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>85</v>
+      </c>
+      <c r="C133" t="s">
+        <v>271</v>
+      </c>
+      <c r="D133" t="s">
+        <v>14</v>
+      </c>
+      <c r="E133" t="s">
+        <v>768</v>
+      </c>
+      <c r="F133" t="s">
+        <v>769</v>
+      </c>
+      <c r="G133" t="s">
+        <v>770</v>
+      </c>
+      <c r="H133" t="s">
+        <v>771</v>
+      </c>
+      <c r="I133" t="s">
+        <v>772</v>
+      </c>
+      <c r="J133" t="s">
+        <v>27</v>
+      </c>
+      <c r="L133" t="s">
+        <v>723</v>
+      </c>
+      <c r="M133" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>85</v>
+      </c>
+      <c r="C134" t="s">
+        <v>229</v>
+      </c>
+      <c r="D134" t="s">
+        <v>14</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="F134" t="s">
+        <v>732</v>
+      </c>
+      <c r="G134" t="s">
+        <v>733</v>
+      </c>
+      <c r="H134" t="s">
+        <v>730</v>
+      </c>
+      <c r="I134" t="s">
+        <v>731</v>
+      </c>
+      <c r="J134" t="s">
+        <v>33</v>
+      </c>
+      <c r="L134" t="s">
+        <v>723</v>
+      </c>
+      <c r="M134" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>85</v>
+      </c>
+      <c r="C135" t="s">
+        <v>207</v>
+      </c>
+      <c r="D135" t="s">
+        <v>14</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="F135" t="s">
+        <v>774</v>
+      </c>
+      <c r="G135" t="s">
+        <v>775</v>
+      </c>
+      <c r="H135" t="s">
+        <v>776</v>
+      </c>
+      <c r="I135" t="s">
+        <v>820</v>
+      </c>
+      <c r="J135" t="s">
+        <v>33</v>
+      </c>
+      <c r="L135" t="s">
+        <v>723</v>
+      </c>
+      <c r="M135" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>12</v>
+      </c>
+      <c r="C136" t="s">
+        <v>111</v>
+      </c>
+      <c r="D136" t="s">
+        <v>14</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="F136" t="s">
+        <v>777</v>
+      </c>
+      <c r="G136" t="s">
+        <v>778</v>
+      </c>
+      <c r="H136" t="s">
+        <v>779</v>
+      </c>
+      <c r="I136" t="s">
+        <v>745</v>
+      </c>
+      <c r="J136" t="s">
+        <v>57</v>
+      </c>
+      <c r="L136" t="s">
+        <v>723</v>
+      </c>
+      <c r="M136" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" t="s">
+        <v>476</v>
+      </c>
+      <c r="D137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="F137" t="s">
+        <v>778</v>
+      </c>
+      <c r="G137" t="s">
+        <v>779</v>
+      </c>
+      <c r="H137" t="s">
+        <v>777</v>
+      </c>
+      <c r="I137" t="s">
+        <v>733</v>
+      </c>
+      <c r="J137" t="s">
+        <v>27</v>
+      </c>
+      <c r="L137" t="s">
+        <v>723</v>
+      </c>
+      <c r="M137" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138" t="s">
+        <v>167</v>
+      </c>
+      <c r="D138" t="s">
+        <v>14</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="F138" t="s">
+        <v>780</v>
+      </c>
+      <c r="G138" t="s">
+        <v>781</v>
+      </c>
+      <c r="H138" t="s">
+        <v>782</v>
+      </c>
+      <c r="I138" t="s">
+        <v>783</v>
+      </c>
+      <c r="J138" t="s">
+        <v>57</v>
+      </c>
+      <c r="L138" t="s">
+        <v>723</v>
+      </c>
+      <c r="M138" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139" t="s">
+        <v>477</v>
+      </c>
+      <c r="D139" t="s">
+        <v>14</v>
+      </c>
+      <c r="E139" t="s">
+        <v>784</v>
+      </c>
+      <c r="F139" t="s">
+        <v>785</v>
+      </c>
+      <c r="G139" t="s">
+        <v>786</v>
+      </c>
+      <c r="H139" t="s">
+        <v>787</v>
+      </c>
+      <c r="I139" t="s">
+        <v>788</v>
+      </c>
+      <c r="J139" t="s">
+        <v>20</v>
+      </c>
+      <c r="L139" t="s">
+        <v>723</v>
+      </c>
+      <c r="M139" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>12</v>
+      </c>
+      <c r="C140" t="s">
+        <v>167</v>
+      </c>
+      <c r="D140" t="s">
+        <v>14</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="F140" t="s">
+        <v>733</v>
+      </c>
+      <c r="G140" t="s">
+        <v>777</v>
+      </c>
+      <c r="H140" t="s">
+        <v>778</v>
+      </c>
+      <c r="I140" t="s">
+        <v>779</v>
+      </c>
+      <c r="J140" t="s">
+        <v>57</v>
+      </c>
+      <c r="L140" t="s">
+        <v>723</v>
+      </c>
+      <c r="M140" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>12</v>
+      </c>
+      <c r="C141" t="s">
+        <v>112</v>
+      </c>
+      <c r="D141" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" t="s">
+        <v>789</v>
+      </c>
+      <c r="F141" t="s">
+        <v>790</v>
+      </c>
+      <c r="G141" t="s">
+        <v>791</v>
+      </c>
+      <c r="H141" t="s">
+        <v>792</v>
+      </c>
+      <c r="I141" t="s">
+        <v>793</v>
+      </c>
+      <c r="J141" t="s">
+        <v>33</v>
+      </c>
+      <c r="L141" t="s">
+        <v>723</v>
+      </c>
+      <c r="M141" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>12</v>
+      </c>
+      <c r="C142" t="s">
+        <v>829</v>
+      </c>
+      <c r="D142" t="s">
+        <v>14</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="F142" t="s">
+        <v>778</v>
+      </c>
+      <c r="G142" t="s">
+        <v>779</v>
+      </c>
+      <c r="H142" t="s">
+        <v>777</v>
+      </c>
+      <c r="I142" t="s">
+        <v>733</v>
+      </c>
+      <c r="J142" t="s">
+        <v>33</v>
+      </c>
+      <c r="L142" t="s">
+        <v>723</v>
+      </c>
+      <c r="M142" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>12</v>
+      </c>
+      <c r="C143" t="s">
+        <v>141</v>
+      </c>
+      <c r="D143" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="F143" t="s">
+        <v>794</v>
+      </c>
+      <c r="G143" t="s">
+        <v>795</v>
+      </c>
+      <c r="H143" t="s">
+        <v>796</v>
+      </c>
+      <c r="I143" t="s">
+        <v>797</v>
+      </c>
+      <c r="J143" t="s">
+        <v>33</v>
+      </c>
+      <c r="L143" t="s">
+        <v>723</v>
+      </c>
+      <c r="M143" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>12</v>
+      </c>
+      <c r="C144" t="s">
+        <v>153</v>
+      </c>
+      <c r="D144" t="s">
+        <v>14</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="F144" t="s">
+        <v>798</v>
+      </c>
+      <c r="G144" t="s">
+        <v>799</v>
+      </c>
+      <c r="H144" t="s">
+        <v>800</v>
+      </c>
+      <c r="I144" t="s">
+        <v>745</v>
+      </c>
+      <c r="J144" t="s">
+        <v>20</v>
+      </c>
+      <c r="L144" t="s">
+        <v>723</v>
+      </c>
+      <c r="M144" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>12</v>
+      </c>
+      <c r="C145" t="s">
+        <v>708</v>
+      </c>
+      <c r="D145" t="s">
+        <v>14</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="F145" t="s">
+        <v>801</v>
+      </c>
+      <c r="G145" t="s">
+        <v>802</v>
+      </c>
+      <c r="H145" t="s">
+        <v>803</v>
+      </c>
+      <c r="I145" t="s">
+        <v>804</v>
+      </c>
+      <c r="J145" t="s">
+        <v>20</v>
+      </c>
+      <c r="L145" t="s">
+        <v>723</v>
+      </c>
+      <c r="M145" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>12</v>
+      </c>
+      <c r="C146" t="s">
+        <v>200</v>
+      </c>
+      <c r="D146" t="s">
+        <v>14</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="F146" t="s">
+        <v>806</v>
+      </c>
+      <c r="G146" t="s">
+        <v>807</v>
+      </c>
+      <c r="H146" t="s">
+        <v>808</v>
+      </c>
+      <c r="I146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J146" t="s">
+        <v>27</v>
+      </c>
+      <c r="L146" t="s">
+        <v>723</v>
+      </c>
+      <c r="M146" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>12</v>
+      </c>
+      <c r="C147" t="s">
+        <v>13</v>
+      </c>
+      <c r="D147" t="s">
+        <v>14</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="F147" t="s">
+        <v>811</v>
+      </c>
+      <c r="G147" t="s">
+        <v>812</v>
+      </c>
+      <c r="H147" t="s">
+        <v>813</v>
+      </c>
+      <c r="I147" t="s">
+        <v>814</v>
+      </c>
+      <c r="J147" t="s">
+        <v>33</v>
+      </c>
+      <c r="L147" t="s">
+        <v>723</v>
+      </c>
+      <c r="M147" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>12</v>
+      </c>
+      <c r="C148" t="s">
+        <v>193</v>
+      </c>
+      <c r="D148" t="s">
+        <v>14</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="F148" t="s">
+        <v>816</v>
+      </c>
+      <c r="G148" t="s">
+        <v>817</v>
+      </c>
+      <c r="H148" t="s">
+        <v>818</v>
+      </c>
+      <c r="I148" t="s">
+        <v>830</v>
+      </c>
+      <c r="J148" t="s">
+        <v>20</v>
+      </c>
+      <c r="L148" t="s">
+        <v>723</v>
+      </c>
+      <c r="M148" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>12</v>
+      </c>
+      <c r="C149" t="s">
+        <v>200</v>
+      </c>
+      <c r="D149" t="s">
+        <v>14</v>
+      </c>
+      <c r="E149" t="s">
+        <v>831</v>
+      </c>
+      <c r="F149" t="s">
+        <v>832</v>
+      </c>
+      <c r="G149" t="s">
+        <v>833</v>
+      </c>
+      <c r="H149" t="s">
+        <v>834</v>
+      </c>
+      <c r="I149" t="s">
+        <v>835</v>
+      </c>
+      <c r="J149" t="s">
+        <v>27</v>
+      </c>
+      <c r="L149" t="s">
+        <v>893</v>
+      </c>
+      <c r="M149" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>12</v>
+      </c>
+      <c r="C150" t="s">
+        <v>200</v>
+      </c>
+      <c r="D150" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" t="s">
+        <v>836</v>
+      </c>
+      <c r="F150" t="s">
+        <v>837</v>
+      </c>
+      <c r="G150" t="s">
+        <v>838</v>
+      </c>
+      <c r="H150" t="s">
+        <v>839</v>
+      </c>
+      <c r="I150" t="s">
+        <v>840</v>
+      </c>
+      <c r="J150" t="s">
+        <v>20</v>
+      </c>
+      <c r="L150" t="s">
+        <v>893</v>
+      </c>
+      <c r="M150" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>12</v>
+      </c>
+      <c r="C151" t="s">
+        <v>13</v>
+      </c>
+      <c r="D151" t="s">
+        <v>14</v>
+      </c>
+      <c r="E151" t="s">
+        <v>841</v>
+      </c>
+      <c r="F151" t="s">
+        <v>842</v>
+      </c>
+      <c r="G151" t="s">
+        <v>843</v>
+      </c>
+      <c r="H151" t="s">
+        <v>844</v>
+      </c>
+      <c r="I151" t="s">
+        <v>929</v>
+      </c>
+      <c r="J151" t="s">
+        <v>57</v>
+      </c>
+      <c r="L151" t="s">
+        <v>893</v>
+      </c>
+      <c r="M151" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>12</v>
+      </c>
+      <c r="C152" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152" t="s">
+        <v>14</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="F152" t="s">
+        <v>445</v>
+      </c>
+      <c r="G152" t="s">
+        <v>236</v>
+      </c>
+      <c r="H152" t="s">
+        <v>238</v>
+      </c>
+      <c r="I152" t="s">
+        <v>235</v>
+      </c>
+      <c r="J152" t="s">
+        <v>57</v>
+      </c>
+      <c r="L152" t="s">
+        <v>893</v>
+      </c>
+      <c r="M152" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>12</v>
+      </c>
+      <c r="C153" t="s">
+        <v>829</v>
+      </c>
+      <c r="D153" t="s">
+        <v>14</v>
+      </c>
+      <c r="E153" t="s">
+        <v>845</v>
+      </c>
+      <c r="F153" t="s">
+        <v>846</v>
+      </c>
+      <c r="G153" t="s">
+        <v>188</v>
+      </c>
+      <c r="H153" t="s">
+        <v>190</v>
+      </c>
+      <c r="I153" t="s">
+        <v>847</v>
+      </c>
+      <c r="J153" t="s">
+        <v>33</v>
+      </c>
+      <c r="L153" t="s">
+        <v>893</v>
+      </c>
+      <c r="M153" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>12</v>
+      </c>
+      <c r="C154" t="s">
+        <v>829</v>
+      </c>
+      <c r="D154" t="s">
+        <v>14</v>
+      </c>
+      <c r="E154" t="s">
+        <v>848</v>
+      </c>
+      <c r="F154" t="s">
+        <v>849</v>
+      </c>
+      <c r="G154" t="s">
+        <v>850</v>
+      </c>
+      <c r="H154" t="s">
+        <v>851</v>
+      </c>
+      <c r="I154" t="s">
+        <v>852</v>
+      </c>
+      <c r="J154" t="s">
+        <v>27</v>
+      </c>
+      <c r="L154" t="s">
+        <v>893</v>
+      </c>
+      <c r="M154" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>12</v>
+      </c>
+      <c r="C155" t="s">
+        <v>112</v>
+      </c>
+      <c r="D155" t="s">
+        <v>14</v>
+      </c>
+      <c r="E155" t="s">
+        <v>853</v>
+      </c>
+      <c r="F155" t="s">
+        <v>854</v>
+      </c>
+      <c r="G155" t="s">
+        <v>855</v>
+      </c>
+      <c r="H155" t="s">
+        <v>856</v>
+      </c>
+      <c r="I155" t="s">
+        <v>928</v>
+      </c>
+      <c r="J155" t="s">
+        <v>57</v>
+      </c>
+      <c r="L155" t="s">
+        <v>893</v>
+      </c>
+      <c r="M155" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>12</v>
+      </c>
+      <c r="C156" t="s">
+        <v>112</v>
+      </c>
+      <c r="D156" t="s">
+        <v>14</v>
+      </c>
+      <c r="E156" t="s">
+        <v>857</v>
+      </c>
+      <c r="F156" t="s">
+        <v>858</v>
+      </c>
+      <c r="G156" t="s">
+        <v>859</v>
+      </c>
+      <c r="H156" t="s">
+        <v>860</v>
+      </c>
+      <c r="I156" t="s">
+        <v>861</v>
+      </c>
+      <c r="J156" t="s">
+        <v>20</v>
+      </c>
+      <c r="L156" t="s">
+        <v>893</v>
+      </c>
+      <c r="M156" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>12</v>
+      </c>
+      <c r="C157" t="s">
+        <v>112</v>
+      </c>
+      <c r="D157" t="s">
+        <v>14</v>
+      </c>
+      <c r="E157" t="s">
+        <v>862</v>
+      </c>
+      <c r="F157" t="s">
+        <v>863</v>
+      </c>
+      <c r="G157" t="s">
+        <v>864</v>
+      </c>
+      <c r="H157" t="s">
+        <v>450</v>
+      </c>
+      <c r="I157" t="s">
+        <v>865</v>
+      </c>
+      <c r="J157" t="s">
+        <v>57</v>
+      </c>
+      <c r="L157" t="s">
+        <v>893</v>
+      </c>
+      <c r="M157" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>12</v>
+      </c>
+      <c r="C158" t="s">
+        <v>829</v>
+      </c>
+      <c r="D158" t="s">
+        <v>14</v>
+      </c>
+      <c r="E158" t="s">
+        <v>866</v>
+      </c>
+      <c r="F158" t="s">
+        <v>867</v>
+      </c>
+      <c r="G158" t="s">
+        <v>868</v>
+      </c>
+      <c r="H158" t="s">
+        <v>869</v>
+      </c>
+      <c r="I158" t="s">
+        <v>927</v>
+      </c>
+      <c r="J158" t="s">
+        <v>57</v>
+      </c>
+      <c r="L158" t="s">
+        <v>893</v>
+      </c>
+      <c r="M158" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>12</v>
+      </c>
+      <c r="C159" t="s">
+        <v>112</v>
+      </c>
+      <c r="D159" t="s">
+        <v>14</v>
+      </c>
+      <c r="E159" t="s">
+        <v>870</v>
+      </c>
+      <c r="F159" t="s">
+        <v>451</v>
+      </c>
+      <c r="G159" t="s">
+        <v>450</v>
+      </c>
+      <c r="H159" t="s">
+        <v>449</v>
+      </c>
+      <c r="I159" t="s">
+        <v>871</v>
+      </c>
+      <c r="J159" t="s">
+        <v>27</v>
+      </c>
+      <c r="L159" t="s">
+        <v>893</v>
+      </c>
+      <c r="M159" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>12</v>
+      </c>
+      <c r="C160" t="s">
+        <v>167</v>
+      </c>
+      <c r="D160" t="s">
+        <v>14</v>
+      </c>
+      <c r="E160" t="s">
+        <v>872</v>
+      </c>
+      <c r="F160" t="s">
+        <v>873</v>
+      </c>
+      <c r="G160" t="s">
+        <v>874</v>
+      </c>
+      <c r="H160" t="s">
+        <v>875</v>
+      </c>
+      <c r="I160" t="s">
+        <v>876</v>
+      </c>
+      <c r="J160" t="s">
+        <v>27</v>
+      </c>
+      <c r="L160" t="s">
+        <v>893</v>
+      </c>
+      <c r="M160" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>12</v>
+      </c>
+      <c r="C161" t="s">
+        <v>167</v>
+      </c>
+      <c r="D161" t="s">
+        <v>14</v>
+      </c>
+      <c r="E161" t="s">
+        <v>877</v>
+      </c>
+      <c r="F161" t="s">
+        <v>878</v>
+      </c>
+      <c r="G161" t="s">
+        <v>879</v>
+      </c>
+      <c r="H161" t="s">
+        <v>880</v>
+      </c>
+      <c r="I161" t="s">
+        <v>926</v>
+      </c>
+      <c r="J161" t="s">
+        <v>33</v>
+      </c>
+      <c r="L161" t="s">
+        <v>893</v>
+      </c>
+      <c r="M161" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>12</v>
+      </c>
+      <c r="C162" t="s">
+        <v>141</v>
+      </c>
+      <c r="D162" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" t="s">
+        <v>881</v>
+      </c>
+      <c r="F162" t="s">
+        <v>701</v>
+      </c>
+      <c r="G162" t="s">
+        <v>882</v>
+      </c>
+      <c r="H162" t="s">
+        <v>883</v>
+      </c>
+      <c r="I162" t="s">
+        <v>925</v>
+      </c>
+      <c r="J162" t="s">
+        <v>57</v>
+      </c>
+      <c r="L162" t="s">
+        <v>893</v>
+      </c>
+      <c r="M162" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>85</v>
+      </c>
+      <c r="C163" t="s">
+        <v>207</v>
+      </c>
+      <c r="D163" t="s">
+        <v>14</v>
+      </c>
+      <c r="E163" t="s">
+        <v>884</v>
+      </c>
+      <c r="F163" t="s">
+        <v>885</v>
+      </c>
+      <c r="G163" t="s">
+        <v>886</v>
+      </c>
+      <c r="H163" t="s">
+        <v>887</v>
+      </c>
+      <c r="I163" t="s">
+        <v>888</v>
+      </c>
+      <c r="J163" t="s">
+        <v>20</v>
+      </c>
+      <c r="L163" t="s">
+        <v>893</v>
+      </c>
+      <c r="M163" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>85</v>
+      </c>
+      <c r="C164" t="s">
+        <v>207</v>
+      </c>
+      <c r="D164" t="s">
+        <v>14</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="F164" t="s">
+        <v>205</v>
+      </c>
+      <c r="G164" t="s">
+        <v>223</v>
+      </c>
+      <c r="H164" t="s">
+        <v>222</v>
+      </c>
+      <c r="I164" t="s">
+        <v>924</v>
+      </c>
+      <c r="J164" t="s">
+        <v>33</v>
+      </c>
+      <c r="L164" t="s">
+        <v>893</v>
+      </c>
+      <c r="M164" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>85</v>
+      </c>
+      <c r="C165" t="s">
+        <v>229</v>
+      </c>
+      <c r="D165" t="s">
+        <v>14</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="F165" t="s">
+        <v>889</v>
+      </c>
+      <c r="G165" t="s">
+        <v>890</v>
+      </c>
+      <c r="H165" t="s">
+        <v>891</v>
+      </c>
+      <c r="I165" t="s">
+        <v>892</v>
+      </c>
+      <c r="J165" t="s">
+        <v>27</v>
+      </c>
+      <c r="L165" t="s">
+        <v>893</v>
+      </c>
+      <c r="M165" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>85</v>
+      </c>
+      <c r="C166" t="s">
+        <v>229</v>
+      </c>
+      <c r="D166" t="s">
+        <v>14</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="F166" t="s">
+        <v>236</v>
+      </c>
+      <c r="G166" t="s">
+        <v>233</v>
+      </c>
+      <c r="H166" t="s">
+        <v>237</v>
+      </c>
+      <c r="I166" t="s">
+        <v>897</v>
+      </c>
+      <c r="J166" t="s">
+        <v>20</v>
+      </c>
+      <c r="L166" t="s">
+        <v>893</v>
+      </c>
+      <c r="M166" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>85</v>
+      </c>
+      <c r="C167" t="s">
+        <v>230</v>
+      </c>
+      <c r="D167" t="s">
+        <v>14</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I167" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="J167" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K167" s="4"/>
+      <c r="L167" t="s">
+        <v>893</v>
+      </c>
+      <c r="M167" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>85</v>
+      </c>
+      <c r="C168" t="s">
+        <v>230</v>
+      </c>
+      <c r="D168" t="s">
+        <v>14</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I168" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="J168" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K168" s="4"/>
+      <c r="L168" t="s">
+        <v>893</v>
+      </c>
+      <c r="M168" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>85</v>
+      </c>
+      <c r="C169" t="s">
+        <v>270</v>
+      </c>
+      <c r="D169" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="H169" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="I169" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J169" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K169" s="4"/>
+      <c r="L169" t="s">
+        <v>893</v>
+      </c>
+      <c r="M169" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>85</v>
+      </c>
+      <c r="C170" t="s">
+        <v>272</v>
+      </c>
+      <c r="D170" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G170" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="J170" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K170" s="4"/>
+      <c r="L170" t="s">
+        <v>893</v>
+      </c>
+      <c r="M170" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>85</v>
+      </c>
+      <c r="C171" t="s">
+        <v>271</v>
+      </c>
+      <c r="D171" t="s">
+        <v>14</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="I171" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="J171" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K171" s="4"/>
+      <c r="L171" t="s">
+        <v>893</v>
+      </c>
+      <c r="M171" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>85</v>
+      </c>
+      <c r="C172" t="s">
+        <v>271</v>
+      </c>
+      <c r="D172" t="s">
+        <v>14</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="J172" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K172" s="4"/>
+      <c r="L172" t="s">
+        <v>893</v>
+      </c>
+      <c r="M172" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>85</v>
+      </c>
+      <c r="C173" t="s">
+        <v>272</v>
+      </c>
+      <c r="D173" t="s">
+        <v>14</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="H173" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I173" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J173" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K173" s="4"/>
+      <c r="L173" t="s">
+        <v>893</v>
+      </c>
+      <c r="M173" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>85</v>
+      </c>
+      <c r="C174" t="s">
+        <v>213</v>
+      </c>
+      <c r="D174" t="s">
+        <v>14</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="J174" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K174" s="4"/>
+      <c r="L174" t="s">
+        <v>893</v>
+      </c>
+      <c r="M174" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>34</v>
+      </c>
+      <c r="C175" t="s">
+        <v>317</v>
+      </c>
+      <c r="D175" t="s">
+        <v>14</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="J175" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K175" s="4"/>
+      <c r="L175" t="s">
+        <v>893</v>
+      </c>
+      <c r="M175" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>34</v>
+      </c>
+      <c r="C176" t="s">
+        <v>317</v>
+      </c>
+      <c r="D176" t="s">
+        <v>14</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="H176" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I176" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="J176" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K176" s="4"/>
+      <c r="L176" t="s">
+        <v>893</v>
+      </c>
+      <c r="M176" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>34</v>
+      </c>
+      <c r="C177" t="s">
+        <v>317</v>
+      </c>
+      <c r="D177" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I177" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J177" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K177" s="4"/>
+      <c r="L177" t="s">
+        <v>893</v>
+      </c>
+      <c r="M177" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>34</v>
+      </c>
+      <c r="C178" t="s">
+        <v>317</v>
+      </c>
+      <c r="D178" t="s">
+        <v>14</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="J178" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K178" s="4"/>
+      <c r="L178" t="s">
+        <v>893</v>
+      </c>
+      <c r="M178" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>34</v>
+      </c>
+      <c r="C179" t="s">
+        <v>317</v>
+      </c>
+      <c r="D179" t="s">
+        <v>14</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="J179" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K179" s="4"/>
+      <c r="L179" t="s">
+        <v>893</v>
+      </c>
+      <c r="M179" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>34</v>
+      </c>
+      <c r="C180" t="s">
+        <v>318</v>
+      </c>
+      <c r="D180" t="s">
+        <v>14</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I180" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="J180" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K180" s="4"/>
+      <c r="L180" t="s">
+        <v>893</v>
+      </c>
+      <c r="M180" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>34</v>
+      </c>
+      <c r="C181" t="s">
+        <v>318</v>
+      </c>
+      <c r="D181" t="s">
+        <v>14</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="I181" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="J181" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K181" s="4"/>
+      <c r="L181" t="s">
+        <v>893</v>
+      </c>
+      <c r="M181" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>34</v>
+      </c>
+      <c r="C182" t="s">
+        <v>319</v>
+      </c>
+      <c r="D182" t="s">
+        <v>14</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="I182" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="J182" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K182" s="4"/>
+      <c r="L182" t="s">
+        <v>893</v>
+      </c>
+      <c r="M182" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>34</v>
+      </c>
+      <c r="C183" t="s">
+        <v>319</v>
+      </c>
+      <c r="D183" t="s">
+        <v>14</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="J183" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K183" s="4"/>
+      <c r="L183" t="s">
+        <v>893</v>
+      </c>
+      <c r="M183" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>34</v>
+      </c>
+      <c r="C184" t="s">
+        <v>319</v>
+      </c>
+      <c r="D184" t="s">
+        <v>14</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="J184" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K184" s="4"/>
+      <c r="L184" t="s">
+        <v>893</v>
+      </c>
+      <c r="M184" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>34</v>
+      </c>
+      <c r="C185" t="s">
+        <v>320</v>
+      </c>
+      <c r="D185" t="s">
+        <v>14</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I185" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J185" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K185" s="4"/>
+      <c r="L185" t="s">
+        <v>893</v>
+      </c>
+      <c r="M185" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>34</v>
+      </c>
+      <c r="C186" t="s">
+        <v>320</v>
+      </c>
+      <c r="D186" t="s">
+        <v>14</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="J186" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K186" s="4"/>
+      <c r="L186" t="s">
+        <v>893</v>
+      </c>
+      <c r="M186" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>34</v>
+      </c>
+      <c r="C187" t="s">
+        <v>35</v>
+      </c>
+      <c r="D187" t="s">
+        <v>14</v>
+      </c>
+      <c r="E187" t="s">
+        <v>972</v>
+      </c>
+      <c r="F187" t="s">
+        <v>973</v>
+      </c>
+      <c r="G187" t="s">
+        <v>974</v>
+      </c>
+      <c r="H187" t="s">
+        <v>975</v>
+      </c>
+      <c r="I187" t="s">
+        <v>976</v>
+      </c>
+      <c r="J187" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L187" t="s">
+        <v>893</v>
+      </c>
+      <c r="M187" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>34</v>
+      </c>
+      <c r="C188" t="s">
+        <v>35</v>
+      </c>
+      <c r="D188" t="s">
+        <v>14</v>
+      </c>
+      <c r="E188" t="s">
+        <v>977</v>
+      </c>
+      <c r="F188" t="s">
+        <v>325</v>
+      </c>
+      <c r="G188" t="s">
+        <v>323</v>
+      </c>
+      <c r="H188" t="s">
+        <v>324</v>
+      </c>
+      <c r="I188" t="s">
+        <v>983</v>
+      </c>
+      <c r="J188" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L188" t="s">
+        <v>893</v>
+      </c>
+      <c r="M188" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
+        <v>34</v>
+      </c>
+      <c r="C189" t="s">
+        <v>337</v>
+      </c>
+      <c r="D189" t="s">
+        <v>14</v>
+      </c>
+      <c r="E189" t="s">
+        <v>978</v>
+      </c>
+      <c r="F189" t="s">
+        <v>979</v>
+      </c>
+      <c r="G189" t="s">
+        <v>980</v>
+      </c>
+      <c r="H189" t="s">
+        <v>981</v>
+      </c>
+      <c r="I189" t="s">
+        <v>982</v>
+      </c>
+      <c r="J189" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L189" t="s">
+        <v>893</v>
+      </c>
+      <c r="M189" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>12</v>
+      </c>
+      <c r="C190" t="s">
+        <v>167</v>
+      </c>
+      <c r="D190" t="s">
+        <v>14</v>
+      </c>
+      <c r="E190" t="s">
+        <v>984</v>
+      </c>
+      <c r="F190" t="s">
+        <v>985</v>
+      </c>
+      <c r="G190" t="s">
+        <v>986</v>
+      </c>
+      <c r="H190" t="s">
+        <v>987</v>
+      </c>
+      <c r="I190" t="s">
+        <v>988</v>
+      </c>
+      <c r="J190" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L190" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M190" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>12</v>
+      </c>
+      <c r="C191" t="s">
+        <v>167</v>
+      </c>
+      <c r="D191" t="s">
+        <v>14</v>
+      </c>
+      <c r="E191" t="s">
+        <v>989</v>
+      </c>
+      <c r="F191" t="s">
+        <v>878</v>
+      </c>
+      <c r="G191" t="s">
+        <v>879</v>
+      </c>
+      <c r="H191" t="s">
+        <v>880</v>
+      </c>
+      <c r="I191" t="s">
+        <v>990</v>
+      </c>
+      <c r="J191" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L191" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M191" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>12</v>
+      </c>
+      <c r="C192" t="s">
+        <v>167</v>
+      </c>
+      <c r="D192" t="s">
+        <v>14</v>
+      </c>
+      <c r="E192" t="s">
+        <v>991</v>
+      </c>
+      <c r="F192" t="s">
+        <v>992</v>
+      </c>
+      <c r="G192" t="s">
+        <v>993</v>
+      </c>
+      <c r="H192" t="s">
+        <v>994</v>
+      </c>
+      <c r="I192" t="s">
+        <v>995</v>
+      </c>
+      <c r="J192" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L192" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M192" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>12</v>
+      </c>
+      <c r="C193" t="s">
+        <v>112</v>
+      </c>
+      <c r="D193" t="s">
+        <v>14</v>
+      </c>
+      <c r="E193" t="s">
+        <v>996</v>
+      </c>
+      <c r="F193" t="s">
+        <v>997</v>
+      </c>
+      <c r="G193" t="s">
+        <v>864</v>
+      </c>
+      <c r="H193" t="s">
+        <v>451</v>
+      </c>
+      <c r="I193" t="s">
+        <v>1027</v>
+      </c>
+      <c r="J193" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L193" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M193" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>12</v>
+      </c>
+      <c r="C194" t="s">
+        <v>112</v>
+      </c>
+      <c r="D194" t="s">
+        <v>14</v>
+      </c>
+      <c r="E194" t="s">
+        <v>998</v>
+      </c>
+      <c r="F194" t="s">
+        <v>871</v>
+      </c>
+      <c r="G194" t="s">
+        <v>451</v>
+      </c>
+      <c r="H194" t="s">
+        <v>449</v>
+      </c>
+      <c r="I194" t="s">
+        <v>450</v>
+      </c>
+      <c r="J194" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L194" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M194" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>12</v>
+      </c>
+      <c r="C195" t="s">
+        <v>112</v>
+      </c>
+      <c r="D195" t="s">
+        <v>14</v>
+      </c>
+      <c r="E195" t="s">
+        <v>999</v>
+      </c>
+      <c r="F195" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G195" t="s">
+        <v>880</v>
+      </c>
+      <c r="H195" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I195" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J195" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L195" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M195" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
+        <v>12</v>
+      </c>
+      <c r="C196" t="s">
+        <v>829</v>
+      </c>
+      <c r="D196" t="s">
+        <v>14</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G196" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H196" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I196" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J196" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L196" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M196" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>12</v>
+      </c>
+      <c r="C197" t="s">
+        <v>829</v>
+      </c>
+      <c r="D197" t="s">
+        <v>14</v>
+      </c>
+      <c r="E197" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G197" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H197" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I197" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J197" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L197" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M197" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
+        <v>12</v>
+      </c>
+      <c r="C198" t="s">
+        <v>141</v>
+      </c>
+      <c r="D198" t="s">
+        <v>14</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G198" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H198" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I198" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J198" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L198" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M198" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
+        <v>12</v>
+      </c>
+      <c r="C199" t="s">
+        <v>200</v>
+      </c>
+      <c r="D199" t="s">
+        <v>14</v>
+      </c>
+      <c r="E199" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F199" t="s">
+        <v>835</v>
+      </c>
+      <c r="G199" t="s">
+        <v>832</v>
+      </c>
+      <c r="H199" t="s">
+        <v>834</v>
+      </c>
+      <c r="I199" t="s">
+        <v>833</v>
+      </c>
+      <c r="J199" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L199" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M199" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
+        <v>12</v>
+      </c>
+      <c r="C200" t="s">
+        <v>13</v>
+      </c>
+      <c r="D200" t="s">
+        <v>14</v>
+      </c>
+      <c r="E200" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G200" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H200" t="s">
+        <v>178</v>
+      </c>
+      <c r="I200" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J200" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L200" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M200" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
+        <v>12</v>
+      </c>
+      <c r="C201" t="s">
+        <v>193</v>
+      </c>
+      <c r="D201" t="s">
+        <v>14</v>
+      </c>
+      <c r="E201" t="s">
+        <v>845</v>
+      </c>
+      <c r="F201" t="s">
+        <v>847</v>
+      </c>
+      <c r="G201" t="s">
+        <v>188</v>
+      </c>
+      <c r="H201" t="s">
+        <v>190</v>
+      </c>
+      <c r="I201" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J201" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L201" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M201" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
+        <v>85</v>
+      </c>
+      <c r="C202" t="s">
+        <v>207</v>
+      </c>
+      <c r="D202" t="s">
+        <v>14</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G202" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H202" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I202" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J202" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L202" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
+        <v>85</v>
+      </c>
+      <c r="C203" t="s">
+        <v>229</v>
+      </c>
+      <c r="D203" t="s">
+        <v>14</v>
+      </c>
+      <c r="E203" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G203" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H203" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I203" t="s">
+        <v>1034</v>
+      </c>
+      <c r="J203" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L203" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M203" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
+        <v>85</v>
+      </c>
+      <c r="C204" t="s">
+        <v>230</v>
+      </c>
+      <c r="D204" t="s">
+        <v>14</v>
+      </c>
+      <c r="E204" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J204" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L204" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M204" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
+        <v>85</v>
+      </c>
+      <c r="C205" t="s">
+        <v>272</v>
+      </c>
+      <c r="D205" t="s">
+        <v>14</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G205" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H205" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="J205" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L205" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M205" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="s">
+        <v>85</v>
+      </c>
+      <c r="C206" t="s">
+        <v>213</v>
+      </c>
+      <c r="D206" t="s">
+        <v>14</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G206" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H206" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I206" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="J206" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L206" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M206" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>85</v>
+      </c>
+      <c r="C207" t="s">
+        <v>230</v>
+      </c>
+      <c r="D207" t="s">
+        <v>14</v>
+      </c>
+      <c r="E207" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H207" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="I207" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="J207" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L207" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M207" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>85</v>
+      </c>
+      <c r="C208" t="s">
+        <v>270</v>
+      </c>
+      <c r="D208" t="s">
+        <v>14</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G208" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="H208" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I208" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J208" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L208" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M208" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>85</v>
+      </c>
+      <c r="C209" t="s">
+        <v>270</v>
+      </c>
+      <c r="D209" t="s">
+        <v>14</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G209" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="H209" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I209" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="J209" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L209" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M209" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>85</v>
+      </c>
+      <c r="C210" t="s">
+        <v>271</v>
+      </c>
+      <c r="D210" t="s">
+        <v>14</v>
+      </c>
+      <c r="E210" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G210" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H210" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I210" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J210" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L210" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M210" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>85</v>
+      </c>
+      <c r="C211" t="s">
+        <v>271</v>
+      </c>
+      <c r="D211" t="s">
+        <v>14</v>
+      </c>
+      <c r="E211" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G211" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H211" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="I211" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J211" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L211" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M211" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>34</v>
+      </c>
+      <c r="C212" t="s">
+        <v>319</v>
+      </c>
+      <c r="D212" t="s">
+        <v>14</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="I212" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J212" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L212" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M212" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>34</v>
+      </c>
+      <c r="C213" t="s">
+        <v>319</v>
+      </c>
+      <c r="D213" t="s">
+        <v>14</v>
+      </c>
+      <c r="E213" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G213" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I213" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="J213" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L213" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M213" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>34</v>
+      </c>
+      <c r="C214" t="s">
+        <v>319</v>
+      </c>
+      <c r="D214" t="s">
+        <v>14</v>
+      </c>
+      <c r="E214" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J214" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L214" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M214" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>34</v>
+      </c>
+      <c r="C215" t="s">
+        <v>318</v>
+      </c>
+      <c r="D215" t="s">
+        <v>14</v>
+      </c>
+      <c r="E215" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G215" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="H215" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I215" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="J215" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L215" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M215" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>34</v>
+      </c>
+      <c r="C216" t="s">
+        <v>318</v>
+      </c>
+      <c r="D216" t="s">
+        <v>14</v>
+      </c>
+      <c r="E216" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G216" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H216" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I216" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="J216" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L216" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M216" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>34</v>
+      </c>
+      <c r="C217" t="s">
+        <v>318</v>
+      </c>
+      <c r="D217" t="s">
+        <v>14</v>
+      </c>
+      <c r="E217" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G217" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H217" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I217" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J217" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L217" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M217" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>34</v>
+      </c>
+      <c r="C218" t="s">
+        <v>318</v>
+      </c>
+      <c r="D218" t="s">
+        <v>14</v>
+      </c>
+      <c r="E218" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G218" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H218" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="I218" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="J218" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L218" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M218" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>34</v>
+      </c>
+      <c r="C219" t="s">
+        <v>317</v>
+      </c>
+      <c r="D219" t="s">
+        <v>14</v>
+      </c>
+      <c r="E219" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G219" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H219" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I219" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J219" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K219" s="4"/>
+      <c r="L219" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M219" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>34</v>
+      </c>
+      <c r="C220" t="s">
+        <v>317</v>
+      </c>
+      <c r="D220" t="s">
+        <v>14</v>
+      </c>
+      <c r="E220" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H220" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I220" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="J220" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K220" s="4"/>
+      <c r="L220" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M220" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>34</v>
+      </c>
+      <c r="C221" t="s">
+        <v>317</v>
+      </c>
+      <c r="D221" t="s">
+        <v>14</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G221" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="H221" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I221" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="J221" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K221" s="4"/>
+      <c r="L221" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M221" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>34</v>
+      </c>
+      <c r="C222" t="s">
+        <v>317</v>
+      </c>
+      <c r="D222" t="s">
+        <v>14</v>
+      </c>
+      <c r="E222" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G222" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="H222" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="I222" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="J222" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K222" s="4"/>
+      <c r="L222" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M222" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>34</v>
+      </c>
+      <c r="C223" t="s">
+        <v>320</v>
+      </c>
+      <c r="D223" t="s">
+        <v>14</v>
+      </c>
+      <c r="E223" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G223" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H223" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I223" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J223" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K223" s="4"/>
+      <c r="L223" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M223" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>34</v>
+      </c>
+      <c r="C224" t="s">
+        <v>320</v>
+      </c>
+      <c r="D224" t="s">
+        <v>14</v>
+      </c>
+      <c r="E224" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H224" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="J224" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K224" s="4"/>
+      <c r="L224" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M224" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>34</v>
+      </c>
+      <c r="C225" t="s">
+        <v>320</v>
+      </c>
+      <c r="D225" t="s">
+        <v>14</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G225" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="H225" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="I225" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="J225" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K225" s="4"/>
+      <c r="L225" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M225" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>34</v>
+      </c>
+      <c r="C226" t="s">
+        <v>320</v>
+      </c>
+      <c r="D226" t="s">
+        <v>14</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H226" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I226" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="J226" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K226" s="4"/>
+      <c r="L226" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M226" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>34</v>
+      </c>
+      <c r="C227" t="s">
+        <v>35</v>
+      </c>
+      <c r="D227" t="s">
+        <v>14</v>
+      </c>
+      <c r="E227" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="G227" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="H227" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="I227" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="J227" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K227" s="4"/>
+      <c r="L227" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M227" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>34</v>
+      </c>
+      <c r="C228" t="s">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>14</v>
+      </c>
+      <c r="E228" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H228" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I228" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="J228" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K228" s="4"/>
+      <c r="L228" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M228" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>34</v>
+      </c>
+      <c r="C229" t="s">
+        <v>337</v>
+      </c>
+      <c r="D229" t="s">
+        <v>14</v>
+      </c>
+      <c r="E229" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G229" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H229" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I229" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="J229" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K229" s="4"/>
+      <c r="L229" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M229" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>34</v>
+      </c>
+      <c r="C230" t="s">
+        <v>337</v>
+      </c>
+      <c r="D230" t="s">
+        <v>14</v>
+      </c>
+      <c r="E230" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="G230" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H230" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="I230" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="J230" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K230" s="4"/>
+      <c r="L230" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M230" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/QUESTOES PROVA CRS.xlsx
+++ b/QUESTOES PROVA CRS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julião\Downloads\chobot-main (1)\chobot-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C719F259-84CD-450A-9264-967D7CC3A169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CB39E3-1CD5-4AE4-AA97-E2FFDC7D9EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="1133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1141">
   <si>
     <t>ID</t>
   </si>
@@ -4065,6 +4065,101 @@
   </si>
   <si>
     <t>Se houver necessidade de busca, será feita pelo PM Vistoriador, primeiramente no veículo e posteriormente em todos os ocupantes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicação Detalhada com base no MTP 04 (Abordagem a Veículos):
+• CORRETA: "A abordagem a veículos pode ser realizada com o objetivo de orientar, fiscalizar documentos, vistoriar sinais veiculares, realizar buscas, prestar assistência, dentre outros objetivos."
+    ◦ Fundamentação: Esta alternativa resume corretamente os diversos objetivos listados no item 2 (Considerações Iniciais) do manual. O texto prevê expressamente que a abordagem pode ter desde caráter educativo e assistencial (orientar, distribuir folders, prestar assistência) até fiscalizatório (verificar documentos, equipamentos obrigatórios, sinais veiculares) e repressivo (busca por ilícitos e prisão de infratores),.
+Análise das Incorreções:
+• INCORRETA: "A abordagem a veículos tem como único objetivo a repressão imediata de delitos e prisão de suspeitos."
+    ◦ Fundamentação: O manual classifica a abordagem em três níveis. O Nível 1, por exemplo, tem caráter puramente educativo ou assistencial (ex: Dicas PM, auxílio a veículo avariado), e o Nível 2 foca na verificação preventiva (fiscalização de trânsito). A repressão é foco principal apenas no Nível 3,,.
+• INCORRETA: "A busca veicular e a busca pessoal durante a abordagem dependem, em todos os casos, de mandado judicial."
+    ◦ Fundamentação: O item 2 esclarece que, conforme o art. 244 do CPP, a busca pessoal independe de mandado. Da mesma forma, nos veículos que não são utilizados como moradia, a busca veicular também independe de mandado judicial, exigindo-se apenas a fundada suspeita.
+• INCORRETA: "A abordagem a veículos só é permitida em vias urbanas com histórico de ocorrências criminais."
+    ◦ Fundamentação: A abordagem pode ocorrer em qualquer via pública (urbana ou rural). Além disso, o manual cita que abordagens de Nível 1 (educativas) ou Nível 2 (fiscalização) podem ocorrer independentemente de um histórico criminal específico do local, baseando-se no planejamento operacional ou na constatação de infrações de trânsito,.
+</t>
+  </si>
+  <si>
+    <t>Explicação Resumida:
+• O que está errado: A alternativa cita "veículo produto de furto ou roubo" como exemplo de abordagem nível 2.
+• O que é o certo: De acordo com o manual, veículo produto de furto ou roubo é classificado como abordagem nível 3 (repressiva/risco III), caracterizada por elevado grau de perigo ou certeza de delito.
+• Fundamentação (Item 2.1 do MTP 04):
+    ◦ Nível 2 (Item 2.1, 'b'): "Será empregada nas ações e operações de verificação preventiva... Exemplo: ações e operações de fiscalização de documentos...".
+    ◦ Nível 3 (Item 2.1, 'c'): "Será empregada nas ações e operações repressivas... Exemplos: veículo produto de furto ou roubo; veículo utilizado em sequestro..."</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base no MTP 04 (Item 2.3 - Distribuição de funções):
+• Assertiva I (FALSA): O responsável direto pela comunicação com os ocupantes não é, por definição, o PM Comandante, mas sim o PM Verbalizador.
+    ◦ Fundamentação: "b) PM Verbalizador: é o policial militar responsável pela comunicação com os ocupantes do veículo abordado;". O PM Comandante é responsável pela coordenação e controle da operação.
+• Assertiva II (FALSA): A atribuição de vistoriar o veículo e fiscalizar documentos é do PM Vistoriador, e não do Verbalizador.
+    ◦ Fundamentação: "c) PM Vistoriador: [...] É também o responsável pela verificação de documentos e vistoria do veículo;".
+• Assertiva III (VERDADEIRA): O PM Revistador é, de fato, quem realiza a busca pessoal e veicular.
+    ◦ Fundamentação: "d) PM Revistador: é o responsável pela realização da busca pessoal nos passageiros e busca no veículo abordado durante a intervenção;".
+• Assertiva IV (VERDADEIRA): A definição de PM Segurança está correta.
+    ◦ Fundamentação: "e) PM Segurança: é o responsável pela integridade e segurança dos componentes da equipe.".
+Portanto, apenas as assertivas III e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base no MTP 04 (Item 5.3 - Procedimentos para a realização da perseguição policial):
+• CORRETA (A): "Acionar os sinais luminosos e a sirene para sinalizar a situação de emergência policial aos usuários da via e demonstrar a ordem de parada aos ocupantes do veículo em fuga."
+    ◦ Fundamentação: Esta alternativa reproduz fielmente a alínea 'c' do item 5.3 do manual, que lista os procedimentos a serem adotados ao iniciar a perseguição.
+Análise das Incorreções:
+• INCORRETA: "A utilização do cinto de segurança pelos policiais é facultativa..."
+    ◦ Fundamentação: A alínea 'a' do item 5.3 determina expressamente: "deslocar-se utilizando o cinto de segurança". Não é facultativo.
+• INCORRETA: "...a guarnição poderá ultrapassar ou emparelhar a viatura... os policiais militares deverão revidar a agressão."
+    ◦ Fundamentação: O manual recomenda exatamente o oposto. Na alínea 'e' do item 5.3, orienta-se que, em caso de disparos, a distância deve ser aumentada e os policiais devem evitar revidar a agressão. Além disso, o texto destaca que não se deve executar a medida de ultrapassar ou emparelhar a viatura ("fechadas") ou disparar contra o veículo em fuga, devido ao risco a terceiros e reféns.
+• INCORRETA: "Procurar manter as armas em pronta-resposta..."
+    ◦ Fundamentação: A alínea 'd' do item 5.3 instrui: "procurar manter as armas no coldre e sacá-las somente no momento da parada do veículo em fuga". O manual explica que o deslocamento com a arma em pronta-resposta (posição 4) assusta a população e acarreta riscos de disparos acidentais.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base no MTP 01 (Intervenção Policial, Processo de Comunicação e Uso da Força):
+• CORRETA : "Com relação às etapas da intervenção policial, a etapa 4 é a avaliação. Nessa etapa, as condutas individuais e do grupo, os resultados alcançados e as falhas notadas em cada intervenção devem ser, posteriormente, discutidas e analisadas, e possíveis correções devem ser apresentadas, visando aperfeiçoar as competências profissionais."
+    ◦ Fundamentação: Esta alternativa é a transcrição literal da alínea 'd' do item 5.2 (Etapas da intervenção). O manual define quatro etapas: Diagnóstico, Plano de Ação, Execução e Avaliação.
+Análise das Incorreções:
+• (Incorreta): A definição apresentada refere-se ao Preparo Mental, e não ao Pensamento Tático.
+    ◦ Fundamentação: O item 2 (Preparo Mental) define: "Considera-se preparo mental o processo de pré-visualizar os prováveis problemas a serem encontrados em cada tipo de intervenção policial-militar e ensaiar mentalmente as possibilidades de respostas". Já o Pensamento Tático (item 4) é definido como o processo de análise do cenário (leitura do ambiente).
+•  (Incorreta): A definição apresentada refere-se ao requisito Comportamento na Ocorrência, e não ao Relacionamento.
+    ◦ Fundamentação: O item 5.4 (Requisitos básicos) diferencia os conceitos. A alínea 'e' define: "Comportamento na ocorrência: o caráter impessoal e imparcial da ação policial-militar revela a natureza eminentemente profissional da atuação...". Já o Relacionamento (alínea 'c') refere-se ao estabelecimento de contatos com a comunidade.
+•  (Incorreta): O policial deve manter o autocontrole mesmo se o abordado não obedecer, e não "salvo se".
+    ◦ Fundamentação: O item 6.1.1 estabelece: "O policial militar deve manter o equilíbrio e o autocontrole, mesmo se o abordado não obedecer, se fizer comentários ofensivos, ignorar a sua presença ou atrair a atenção de pessoas em volta". A exceção criada na alternativa ("salvo se") torna a afirmativa falsa, pois o autocontrole deve ser constante.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base no MTP 01 (Item 7.2.4.1 - Objetivo do disparo):
+• CORRETA : "Nas situações em que o agressor estiver utilizando colete balístico, o policial deverá adotar a técnica de alteração de nível, buscando direcionar os disparos em áreas que não estejam protegidas, a exemplo da junção do peito com o pescoço."
+    ◦ Fundamentação: A alternativa reproduz fielmente a orientação contida na página 74 do manual (final do item 7.2.4.1). O texto original afirma: "Para tanto, o policial deverá adotar a técnica de alteração de nível, buscando áreas que não estejam protegidas, tais como, junção do peito com o pescoço, fossa jugular, queixo, boca, nariz ou cabeça".
+Análise das Incorreções:
+• (Incorreta): O estado emocional é classificado como variável não controlada.
+    ◦ Fundamentação: O manual classifica as variáveis em:
+        ▪ Controladas: características balísticas, distância, quantidade e tipo de munição.
+        ▪ Parcialmente controladas: direcionamento do disparo.
+        ▪ Não controladas: compleição física, estado emocional e resistência orgânica da pessoa atingida.
+•  (Incorreta): O local do impacto é uma variável parcialmente controlada.
+    ◦ Fundamentação: O manual define: "b) variáveis parcialmente controladas pelo policial: direcionamento do disparo, ou seja, local do corpo do agressor em que se dará o impacto".
+•  (Incorreta): A letalidade nunca (e não excepcionalmente) será o objetivo finalístico.
+    ◦ Fundamentação: O texto é taxativo: "A letalidade (morte do agressor) nunca será entendida como o objetivo finalístico do policial militar ao disparar sua arma de fogo em uma ação operacional". O objetivo é interromper a agressão e preservar vidas, sendo a morte um resultado possível, mas não o fim pretendido.</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base no MTP 01 (3.04.01/2020):
+• Assertiva I (VERDADEIRA): "A ação do policial militar em levar a mão até a arma (arma localizada) enquanto verbaliza demonstra ao abordado um grau de força mais elevado do que se estivesse falando com as mãos livres."
+    ◦ Fundamentação: Transcrição fiel do Item 7.2.3 (Usar ou empregar arma de fogo), 5º parágrafo. O manual explica que essa postura, acompanhada de verbalização, sinaliza prontidão e tem efeito dissuasivo.
+• Assertiva II (FALSA): Afirma que o policial precisa percorrer os demais níveis antes de usar um mais elevado.
+    ◦ Fundamentação: O Item 7.1 (Princípio da Necessidade) estabelece exatamente o contrário: "Sendo necessário utilizar imediatamente um nível de força mais elevado, o policial militar não precisa percorrer os demais níveis". Se a ameaça for iminente e grave, o uso imediato de força letal (potencialmente letal) é legítimo sem passar por níveis inferiores.
+• Assertiva III (VERDADEIRA): "Os verbos atirar ou disparar arma de fogo devem ser entendidos como sinônimos e correspondem ao efetivo disparo feito pelo policial militar na direção da pessoa abordada."
+    ◦ Fundamentação: Transcrição fiel do Item 7.2.4 (Atirar ou disparar arma de fogo). O manual diferencia "usar/empregar" (apontar/empunhar) de "atirar/disparar" (efetuar o tiro).
+• Assertiva IV (FALSA): Afirma que o policial deve usar equipamentos "independentemente de ser habilitado para tal uso".
+    ◦ Fundamentação: O Item 7.1.2 (Uso diferenciado da força) e o Item 7.2.1 (Regras gerais de controle) condicionam o uso de qualquer armamento ou tecnologia à habilitação específica. O texto diz: "...se for habilitado para tal uso" e "...podendo utilizar cada tipo de arma de fogo somente após a respectiva habilitação"</t>
+  </si>
+  <si>
+    <t>Explicação Detalhada com base no MTP 01 (Manual Técnico-Profissional nº 3.04.01/2020):
+• CORRETA : "O disparo de advertência não é previsto como procedimento policial-militar."
+    ◦ Fundamentação: Esta afirmação está expressamente descrita no item 7.2.4.3 (Circunstâncias especiais para o disparo de arma de fogo). O manual é taxativo ao afirmar que: "O disparo de advertência não é previsto como procedimento policial-militar, pois quando o policial militar atira com sua arma, não o faz para advertir ou assustar, o faz para interromper, de imediato, uma agressão contra a sua vida ou a de terceiros.".
+Análise das Incorreções:
+•  (Incorreta): A alternativa afirma que a comunicação ao superior deve ocorrer após encerrados os procedimentos de confecção de BO e AR.
+    ◦ Fundamentação: O item 7.2.4.2 (alínea 'd') estabelece que a comunicação deve ser imediata: "O policial militar que disparou sua arma de fogo deverá comunicar o fato verbalmente e imediatamente aos seus superiores...".
+•  (Incorreta): A alternativa atribui a definição de "Disparos Táticos" aos disparos com munições de menor potencial ofensivo.
+    ◦ Fundamentação: Segundo o item 7.2.4.3 (alínea 'd'), os disparos realizados "para obter uma vantagem tática, para dar mais segurança ao reposicionamento da equipe" são definidos como Disparos Táticos (ex: cobertura, fogo e movimento), e não disparos de menor potencial ofensivo (elastômero), descritos na alínea 'c'.
+•  (Incorreta): A alternativa afirma que a intenção do policial será matar o agressor.
+    ◦ Fundamentação: O item 7.2.4.1 (Objetivo do disparo) esclarece que "A intenção do policial militar não é matar o agressor... O policial militar não busca o resultado morte",. O objetivo é interromper a agressão e preservar a vida, razão pela qual a doutrina utiliza o termo "força potencialmente letal" e não "força letal".</t>
   </si>
 </sst>
 </file>
@@ -12918,7 +13013,9 @@
       <c r="J219" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K219" s="4"/>
+      <c r="K219" s="5" t="s">
+        <v>1137</v>
+      </c>
       <c r="L219" t="s">
         <v>1035</v>
       </c>
@@ -12957,7 +13054,9 @@
       <c r="J220" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K220" s="4"/>
+      <c r="K220" s="5" t="s">
+        <v>1138</v>
+      </c>
       <c r="L220" t="s">
         <v>1035</v>
       </c>
@@ -12996,7 +13095,9 @@
       <c r="J221" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K221" s="4"/>
+      <c r="K221" s="5" t="s">
+        <v>1139</v>
+      </c>
       <c r="L221" t="s">
         <v>1035</v>
       </c>
@@ -13035,7 +13136,9 @@
       <c r="J222" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K222" s="4"/>
+      <c r="K222" s="5" t="s">
+        <v>1140</v>
+      </c>
       <c r="L222" t="s">
         <v>1035</v>
       </c>
@@ -13074,7 +13177,9 @@
       <c r="J223" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K223" s="4"/>
+      <c r="K223" s="5" t="s">
+        <v>1133</v>
+      </c>
       <c r="L223" t="s">
         <v>1035</v>
       </c>
@@ -13113,7 +13218,9 @@
       <c r="J224" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K224" s="4"/>
+      <c r="K224" s="5" t="s">
+        <v>1134</v>
+      </c>
       <c r="L224" t="s">
         <v>1035</v>
       </c>
@@ -13152,7 +13259,9 @@
       <c r="J225" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K225" s="4"/>
+      <c r="K225" s="5" t="s">
+        <v>1135</v>
+      </c>
       <c r="L225" t="s">
         <v>1035</v>
       </c>
@@ -13191,7 +13300,9 @@
       <c r="J226" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K226" s="4"/>
+      <c r="K226" s="5" t="s">
+        <v>1136</v>
+      </c>
       <c r="L226" t="s">
         <v>1035</v>
       </c>

--- a/QUESTOES PROVA CRS.xlsx
+++ b/QUESTOES PROVA CRS.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julião\Downloads\chobot-main (1)\chobot-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CB39E3-1CD5-4AE4-AA97-E2FFDC7D9EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189E6DBF-ED95-4D59-A36C-FFD348127F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$C$1:$C$230</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1139">
   <si>
     <t>ID</t>
   </si>
@@ -456,9 +459,6 @@
     <t>Decreto-Lei nº 3.689, de 03/10/1941, Código de Processo Penal</t>
   </si>
   <si>
-    <t>CODIGO PROCESSO PENAL</t>
-  </si>
-  <si>
     <t xml:space="preserve">Acerca do tema Cadeia de Custódia, previsto no Decreto-Lei nº 3.689, de 03/10/1941, Código de Processo Penal, ENUMERE a segunda coluna de acordo com a primeira. 
 1 - ACONDICIONAMENTO
 2 - PROCESSAMENTO
@@ -2553,9 +2553,6 @@
   </si>
   <si>
     <t>LEI DE ACESSO A INFORMAÇÃO</t>
-  </si>
-  <si>
-    <t>CODIGO PROCESSO PENAL MILITAR</t>
   </si>
   <si>
     <t>Lei nº 12.527, de 18 de novembro de 2011, que regula o acesso a informações</t>
@@ -4737,7 +4734,7 @@
         <v>33</v>
       </c>
       <c r="K4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L4" t="s">
         <v>21</v>
@@ -4778,7 +4775,7 @@
         <v>27</v>
       </c>
       <c r="K5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L5" t="s">
         <v>21</v>
@@ -4895,7 +4892,7 @@
         <v>27</v>
       </c>
       <c r="K8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L8" t="s">
         <v>51</v>
@@ -4936,7 +4933,7 @@
         <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L9" t="s">
         <v>51</v>
@@ -4977,7 +4974,7 @@
         <v>27</v>
       </c>
       <c r="K10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L10" t="s">
         <v>51</v>
@@ -5132,7 +5129,7 @@
         <v>57</v>
       </c>
       <c r="K14" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="L14" t="s">
         <v>51</v>
@@ -5301,25 +5298,25 @@
         <v>12</v>
       </c>
       <c r="C19" t="s">
+        <v>827</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s">
         <v>124</v>
       </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>125</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>126</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>127</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>128</v>
-      </c>
-      <c r="I19" t="s">
-        <v>129</v>
       </c>
       <c r="J19" t="s">
         <v>33</v>
@@ -5339,25 +5336,25 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>827</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
       </c>
       <c r="E20" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" t="s">
         <v>130</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>131</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>132</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>133</v>
-      </c>
-      <c r="I20" t="s">
-        <v>134</v>
       </c>
       <c r="J20" t="s">
         <v>33</v>
@@ -5377,25 +5374,25 @@
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F21" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" t="s">
         <v>137</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>138</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>139</v>
-      </c>
-      <c r="I21" t="s">
-        <v>140</v>
       </c>
       <c r="J21" t="s">
         <v>20</v>
@@ -5404,7 +5401,7 @@
         <v>103</v>
       </c>
       <c r="M21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -5415,25 +5412,25 @@
         <v>12</v>
       </c>
       <c r="C22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s">
         <v>141</v>
       </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>142</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>143</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>144</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>145</v>
-      </c>
-      <c r="I22" t="s">
-        <v>146</v>
       </c>
       <c r="J22" t="s">
         <v>33</v>
@@ -5442,7 +5439,7 @@
         <v>103</v>
       </c>
       <c r="M22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -5453,25 +5450,25 @@
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
       </c>
       <c r="E23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" t="s">
         <v>147</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>148</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>149</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>150</v>
-      </c>
-      <c r="I23" t="s">
-        <v>151</v>
       </c>
       <c r="J23" t="s">
         <v>57</v>
@@ -5480,7 +5477,7 @@
         <v>103</v>
       </c>
       <c r="M23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -5491,25 +5488,25 @@
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
       </c>
       <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24" t="s">
         <v>155</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>156</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>157</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>158</v>
-      </c>
-      <c r="I24" t="s">
-        <v>159</v>
       </c>
       <c r="J24" t="s">
         <v>27</v>
@@ -5518,7 +5515,7 @@
         <v>103</v>
       </c>
       <c r="M24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -5535,19 +5532,19 @@
         <v>14</v>
       </c>
       <c r="E25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" t="s">
         <v>160</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>161</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>162</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>163</v>
-      </c>
-      <c r="I25" t="s">
-        <v>164</v>
       </c>
       <c r="J25" t="s">
         <v>33</v>
@@ -5567,25 +5564,25 @@
         <v>12</v>
       </c>
       <c r="C26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26" t="s">
         <v>167</v>
       </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
-        <v>165</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>168</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
+        <v>170</v>
+      </c>
+      <c r="I26" t="s">
         <v>169</v>
-      </c>
-      <c r="H26" t="s">
-        <v>171</v>
-      </c>
-      <c r="I26" t="s">
-        <v>170</v>
       </c>
       <c r="J26" t="s">
         <v>20</v>
@@ -5594,7 +5591,7 @@
         <v>103</v>
       </c>
       <c r="M26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -5605,25 +5602,25 @@
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
       </c>
       <c r="E27" t="s">
+        <v>171</v>
+      </c>
+      <c r="F27" t="s">
         <v>172</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>173</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>174</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>175</v>
-      </c>
-      <c r="I27" t="s">
-        <v>176</v>
       </c>
       <c r="J27" t="s">
         <v>57</v>
@@ -5632,7 +5629,7 @@
         <v>103</v>
       </c>
       <c r="M27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -5649,19 +5646,19 @@
         <v>14</v>
       </c>
       <c r="E28" t="s">
+        <v>176</v>
+      </c>
+      <c r="F28" t="s">
         <v>177</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>178</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>179</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>180</v>
-      </c>
-      <c r="I28" t="s">
-        <v>181</v>
       </c>
       <c r="J28" t="s">
         <v>57</v>
@@ -5687,19 +5684,19 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F29" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" t="s">
         <v>182</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>183</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>184</v>
-      </c>
-      <c r="I29" t="s">
-        <v>185</v>
       </c>
       <c r="J29" t="s">
         <v>33</v>
@@ -5719,25 +5716,25 @@
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F30" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" t="s">
         <v>188</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>189</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>190</v>
-      </c>
-      <c r="I30" t="s">
-        <v>191</v>
       </c>
       <c r="J30" t="s">
         <v>27</v>
@@ -5746,7 +5743,7 @@
         <v>103</v>
       </c>
       <c r="M30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -5757,25 +5754,25 @@
         <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
       </c>
       <c r="E31" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" t="s">
         <v>194</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>195</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>196</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>197</v>
-      </c>
-      <c r="I31" t="s">
-        <v>198</v>
       </c>
       <c r="J31" t="s">
         <v>20</v>
@@ -5784,7 +5781,7 @@
         <v>103</v>
       </c>
       <c r="M31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -5795,25 +5792,25 @@
         <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
       </c>
       <c r="E32" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" t="s">
         <v>201</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>202</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>203</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>204</v>
-      </c>
-      <c r="I32" t="s">
-        <v>205</v>
       </c>
       <c r="J32" t="s">
         <v>27</v>
@@ -5822,7 +5819,7 @@
         <v>103</v>
       </c>
       <c r="M32" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -5833,25 +5830,25 @@
         <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
       </c>
       <c r="E33" t="s">
+        <v>207</v>
+      </c>
+      <c r="F33" t="s">
         <v>208</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>209</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>210</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>211</v>
-      </c>
-      <c r="I33" t="s">
-        <v>212</v>
       </c>
       <c r="J33" t="s">
         <v>57</v>
@@ -5860,7 +5857,7 @@
         <v>103</v>
       </c>
       <c r="M33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -5871,25 +5868,25 @@
         <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
       </c>
       <c r="E34" t="s">
+        <v>214</v>
+      </c>
+      <c r="F34" t="s">
         <v>215</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>216</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>217</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>218</v>
-      </c>
-      <c r="I34" t="s">
-        <v>219</v>
       </c>
       <c r="J34" t="s">
         <v>27</v>
@@ -5898,7 +5895,7 @@
         <v>103</v>
       </c>
       <c r="M34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -5909,37 +5906,37 @@
         <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F35" t="s">
+        <v>219</v>
+      </c>
+      <c r="G35" t="s">
         <v>220</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>221</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>222</v>
-      </c>
-      <c r="I35" t="s">
-        <v>223</v>
       </c>
       <c r="J35" t="s">
         <v>33</v>
       </c>
       <c r="K35" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L35" t="s">
         <v>103</v>
       </c>
       <c r="M35" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -5950,37 +5947,37 @@
         <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G36" t="s">
+        <v>223</v>
+      </c>
+      <c r="H36" t="s">
         <v>224</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>225</v>
-      </c>
-      <c r="I36" t="s">
-        <v>226</v>
       </c>
       <c r="J36" t="s">
         <v>27</v>
       </c>
       <c r="K36" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L36" t="s">
         <v>103</v>
       </c>
       <c r="M36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -5991,37 +5988,37 @@
         <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D37" t="s">
         <v>14</v>
       </c>
       <c r="E37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F37" t="s">
+        <v>232</v>
+      </c>
+      <c r="G37" t="s">
         <v>233</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>234</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>235</v>
-      </c>
-      <c r="I37" t="s">
-        <v>236</v>
       </c>
       <c r="J37" t="s">
         <v>57</v>
       </c>
       <c r="K37" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L37" t="s">
         <v>103</v>
       </c>
       <c r="M37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -6032,37 +6029,37 @@
         <v>85</v>
       </c>
       <c r="C38" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
       </c>
       <c r="E38" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F38" t="s">
+        <v>236</v>
+      </c>
+      <c r="G38" t="s">
         <v>237</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>238</v>
       </c>
-      <c r="H38" t="s">
-        <v>239</v>
-      </c>
       <c r="I38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J38" t="s">
         <v>33</v>
       </c>
       <c r="K38" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L38" t="s">
         <v>103</v>
       </c>
       <c r="M38" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -6073,37 +6070,37 @@
         <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
       </c>
       <c r="E39" t="s">
+        <v>239</v>
+      </c>
+      <c r="F39" t="s">
         <v>240</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>241</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>242</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>243</v>
-      </c>
-      <c r="I39" t="s">
-        <v>244</v>
       </c>
       <c r="J39" t="s">
         <v>33</v>
       </c>
       <c r="K39" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L39" t="s">
         <v>103</v>
       </c>
       <c r="M39" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -6114,25 +6111,25 @@
         <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
       </c>
       <c r="E40" t="s">
+        <v>244</v>
+      </c>
+      <c r="F40" t="s">
         <v>245</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>246</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>247</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>248</v>
-      </c>
-      <c r="I40" t="s">
-        <v>249</v>
       </c>
       <c r="J40" t="s">
         <v>20</v>
@@ -6141,7 +6138,7 @@
         <v>103</v>
       </c>
       <c r="M40" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -6152,25 +6149,25 @@
         <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D41" t="s">
         <v>14</v>
       </c>
       <c r="E41" t="s">
+        <v>249</v>
+      </c>
+      <c r="F41" t="s">
         <v>250</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>251</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>252</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>253</v>
-      </c>
-      <c r="I41" t="s">
-        <v>254</v>
       </c>
       <c r="J41" t="s">
         <v>27</v>
@@ -6179,7 +6176,7 @@
         <v>103</v>
       </c>
       <c r="M41" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -6190,25 +6187,25 @@
         <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D42" t="s">
         <v>14</v>
       </c>
       <c r="E42" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" t="s">
         <v>255</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>256</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>257</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>258</v>
-      </c>
-      <c r="I42" t="s">
-        <v>259</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
@@ -6217,7 +6214,7 @@
         <v>103</v>
       </c>
       <c r="M42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -6228,25 +6225,25 @@
         <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
       </c>
       <c r="E43" t="s">
+        <v>259</v>
+      </c>
+      <c r="F43" t="s">
         <v>260</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>261</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>262</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>263</v>
-      </c>
-      <c r="I43" t="s">
-        <v>264</v>
       </c>
       <c r="J43" t="s">
         <v>27</v>
@@ -6255,7 +6252,7 @@
         <v>103</v>
       </c>
       <c r="M43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -6266,37 +6263,37 @@
         <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
       </c>
       <c r="E44" t="s">
+        <v>272</v>
+      </c>
+      <c r="F44" t="s">
         <v>273</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>274</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>275</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
         <v>276</v>
-      </c>
-      <c r="I44" t="s">
-        <v>277</v>
       </c>
       <c r="J44" t="s">
         <v>33</v>
       </c>
       <c r="K44" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L44" t="s">
         <v>103</v>
       </c>
       <c r="M44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -6307,37 +6304,37 @@
         <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
       </c>
       <c r="E45" t="s">
+        <v>277</v>
+      </c>
+      <c r="F45" t="s">
         <v>278</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>279</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>280</v>
       </c>
-      <c r="H45" t="s">
+      <c r="I45" t="s">
         <v>281</v>
-      </c>
-      <c r="I45" t="s">
-        <v>282</v>
       </c>
       <c r="J45" t="s">
         <v>33</v>
       </c>
       <c r="K45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L45" t="s">
         <v>103</v>
       </c>
       <c r="M45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -6348,37 +6345,37 @@
         <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
       </c>
       <c r="E46" t="s">
+        <v>282</v>
+      </c>
+      <c r="F46" t="s">
         <v>283</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>284</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>285</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>286</v>
-      </c>
-      <c r="I46" t="s">
-        <v>287</v>
       </c>
       <c r="J46" t="s">
         <v>20</v>
       </c>
       <c r="K46" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L46" t="s">
         <v>103</v>
       </c>
       <c r="M46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -6389,37 +6386,37 @@
         <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
       </c>
       <c r="E47" t="s">
+        <v>287</v>
+      </c>
+      <c r="F47" t="s">
         <v>288</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>289</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>290</v>
       </c>
-      <c r="H47" t="s">
+      <c r="I47" t="s">
         <v>291</v>
-      </c>
-      <c r="I47" t="s">
-        <v>292</v>
       </c>
       <c r="J47" t="s">
         <v>57</v>
       </c>
       <c r="K47" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L47" t="s">
         <v>103</v>
       </c>
       <c r="M47" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -6430,37 +6427,37 @@
         <v>34</v>
       </c>
       <c r="C48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D48" t="s">
         <v>14</v>
       </c>
       <c r="E48" t="s">
+        <v>292</v>
+      </c>
+      <c r="F48" t="s">
         <v>293</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>294</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>295</v>
       </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
         <v>296</v>
-      </c>
-      <c r="I48" t="s">
-        <v>297</v>
       </c>
       <c r="J48" t="s">
         <v>20</v>
       </c>
       <c r="K48" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L48" t="s">
         <v>103</v>
       </c>
       <c r="M48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -6471,37 +6468,37 @@
         <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
       </c>
       <c r="E49" t="s">
+        <v>297</v>
+      </c>
+      <c r="F49" t="s">
         <v>298</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>299</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>300</v>
       </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
         <v>301</v>
-      </c>
-      <c r="I49" t="s">
-        <v>302</v>
       </c>
       <c r="J49" t="s">
         <v>33</v>
       </c>
       <c r="K49" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L49" t="s">
         <v>103</v>
       </c>
       <c r="M49" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
@@ -6512,37 +6509,37 @@
         <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D50" t="s">
         <v>14</v>
       </c>
       <c r="E50" t="s">
+        <v>302</v>
+      </c>
+      <c r="F50" t="s">
         <v>303</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>304</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>305</v>
       </c>
-      <c r="H50" t="s">
+      <c r="I50" t="s">
         <v>306</v>
-      </c>
-      <c r="I50" t="s">
-        <v>307</v>
       </c>
       <c r="J50" t="s">
         <v>57</v>
       </c>
       <c r="K50" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L50" t="s">
         <v>103</v>
       </c>
       <c r="M50" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -6553,37 +6550,37 @@
         <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D51" t="s">
         <v>14</v>
       </c>
       <c r="E51" t="s">
+        <v>307</v>
+      </c>
+      <c r="F51" t="s">
         <v>308</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>309</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>310</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>311</v>
-      </c>
-      <c r="I51" t="s">
-        <v>312</v>
       </c>
       <c r="J51" t="s">
         <v>57</v>
       </c>
       <c r="K51" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L51" t="s">
         <v>103</v>
       </c>
       <c r="M51" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -6600,25 +6597,25 @@
         <v>14</v>
       </c>
       <c r="E52" t="s">
+        <v>320</v>
+      </c>
+      <c r="F52" t="s">
         <v>321</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>322</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>323</v>
       </c>
-      <c r="H52" t="s">
+      <c r="I52" t="s">
         <v>324</v>
-      </c>
-      <c r="I52" t="s">
-        <v>325</v>
       </c>
       <c r="J52" t="s">
         <v>20</v>
       </c>
       <c r="K52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L52" t="s">
         <v>103</v>
@@ -6641,25 +6638,25 @@
         <v>14</v>
       </c>
       <c r="E53" t="s">
+        <v>325</v>
+      </c>
+      <c r="F53" t="s">
         <v>326</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>327</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>328</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>329</v>
-      </c>
-      <c r="I53" t="s">
-        <v>330</v>
       </c>
       <c r="J53" t="s">
         <v>57</v>
       </c>
       <c r="K53" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L53" t="s">
         <v>103</v>
@@ -6676,37 +6673,37 @@
         <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D54" t="s">
         <v>14</v>
       </c>
       <c r="E54" t="s">
+        <v>330</v>
+      </c>
+      <c r="F54" t="s">
         <v>331</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>332</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>333</v>
       </c>
-      <c r="H54" t="s">
+      <c r="I54" t="s">
         <v>334</v>
-      </c>
-      <c r="I54" t="s">
-        <v>335</v>
       </c>
       <c r="J54" t="s">
         <v>33</v>
       </c>
       <c r="K54" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="L54" t="s">
         <v>103</v>
       </c>
       <c r="M54" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -6717,37 +6714,37 @@
         <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D55" t="s">
         <v>14</v>
       </c>
       <c r="E55" t="s">
+        <v>337</v>
+      </c>
+      <c r="F55" t="s">
         <v>338</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>339</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>340</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55" t="s">
         <v>341</v>
-      </c>
-      <c r="I55" t="s">
-        <v>342</v>
       </c>
       <c r="J55" t="s">
         <v>20</v>
       </c>
       <c r="K55" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L55" t="s">
+        <v>342</v>
+      </c>
+      <c r="M55" t="s">
         <v>343</v>
-      </c>
-      <c r="M55" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -6758,37 +6755,37 @@
         <v>34</v>
       </c>
       <c r="C56" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D56" t="s">
         <v>14</v>
       </c>
       <c r="E56" t="s">
+        <v>345</v>
+      </c>
+      <c r="F56" t="s">
         <v>346</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>347</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>348</v>
       </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>349</v>
-      </c>
-      <c r="I56" t="s">
-        <v>350</v>
       </c>
       <c r="J56" t="s">
         <v>57</v>
       </c>
       <c r="K56" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L56" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M56" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -6799,34 +6796,34 @@
         <v>34</v>
       </c>
       <c r="C57" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D57" t="s">
         <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F57" t="s">
+        <v>352</v>
+      </c>
+      <c r="G57" t="s">
         <v>353</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>354</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>355</v>
-      </c>
-      <c r="I57" t="s">
-        <v>356</v>
       </c>
       <c r="J57" t="s">
         <v>33</v>
       </c>
       <c r="L57" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M57" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -6837,37 +6834,37 @@
         <v>34</v>
       </c>
       <c r="C58" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D58" t="s">
         <v>14</v>
       </c>
       <c r="E58" t="s">
+        <v>356</v>
+      </c>
+      <c r="F58" t="s">
         <v>357</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>358</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>359</v>
       </c>
-      <c r="H58" t="s">
-        <v>360</v>
-      </c>
       <c r="I58" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="J58" t="s">
         <v>57</v>
       </c>
       <c r="K58" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L58" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M58" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -6878,37 +6875,37 @@
         <v>34</v>
       </c>
       <c r="C59" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
       </c>
       <c r="E59" t="s">
+        <v>360</v>
+      </c>
+      <c r="F59" t="s">
         <v>361</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>362</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>363</v>
       </c>
-      <c r="H59" t="s">
-        <v>364</v>
-      </c>
       <c r="I59" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J59" t="s">
         <v>20</v>
       </c>
       <c r="K59" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L59" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -6919,37 +6916,37 @@
         <v>34</v>
       </c>
       <c r="C60" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D60" t="s">
         <v>14</v>
       </c>
       <c r="E60" t="s">
+        <v>364</v>
+      </c>
+      <c r="F60" t="s">
         <v>365</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>366</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>367</v>
       </c>
-      <c r="H60" t="s">
+      <c r="I60" t="s">
         <v>368</v>
-      </c>
-      <c r="I60" t="s">
-        <v>369</v>
       </c>
       <c r="J60" t="s">
         <v>33</v>
       </c>
       <c r="K60" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M60" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -6960,37 +6957,37 @@
         <v>34</v>
       </c>
       <c r="C61" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D61" t="s">
         <v>14</v>
       </c>
       <c r="E61" t="s">
+        <v>369</v>
+      </c>
+      <c r="F61" t="s">
         <v>370</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>371</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>372</v>
       </c>
-      <c r="H61" t="s">
+      <c r="I61" t="s">
         <v>373</v>
-      </c>
-      <c r="I61" t="s">
-        <v>374</v>
       </c>
       <c r="J61" t="s">
         <v>20</v>
       </c>
       <c r="K61" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L61" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M61" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -7001,34 +6998,34 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
       </c>
       <c r="E62" t="s">
+        <v>376</v>
+      </c>
+      <c r="F62" t="s">
         <v>377</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>378</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>379</v>
       </c>
-      <c r="H62" t="s">
+      <c r="I62" t="s">
         <v>380</v>
-      </c>
-      <c r="I62" t="s">
-        <v>381</v>
       </c>
       <c r="J62" t="s">
         <v>33</v>
       </c>
       <c r="L62" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M62" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -7039,37 +7036,37 @@
         <v>85</v>
       </c>
       <c r="C63" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D63" t="s">
         <v>14</v>
       </c>
       <c r="E63" t="s">
+        <v>384</v>
+      </c>
+      <c r="F63" t="s">
         <v>385</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>386</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>387</v>
       </c>
-      <c r="H63" t="s">
+      <c r="I63" t="s">
         <v>388</v>
-      </c>
-      <c r="I63" t="s">
-        <v>389</v>
       </c>
       <c r="J63" t="s">
         <v>20</v>
       </c>
       <c r="K63" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M63" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -7080,34 +7077,34 @@
         <v>85</v>
       </c>
       <c r="C64" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
       </c>
       <c r="E64" t="s">
+        <v>389</v>
+      </c>
+      <c r="F64" t="s">
         <v>390</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>391</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>392</v>
       </c>
-      <c r="H64" t="s">
+      <c r="I64" t="s">
         <v>393</v>
-      </c>
-      <c r="I64" t="s">
-        <v>394</v>
       </c>
       <c r="J64" t="s">
         <v>27</v>
       </c>
       <c r="L64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M64" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -7118,34 +7115,34 @@
         <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D65" t="s">
         <v>14</v>
       </c>
       <c r="E65" t="s">
+        <v>394</v>
+      </c>
+      <c r="F65" t="s">
         <v>395</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>396</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>397</v>
       </c>
-      <c r="H65" t="s">
+      <c r="I65" t="s">
         <v>398</v>
-      </c>
-      <c r="I65" t="s">
-        <v>399</v>
       </c>
       <c r="J65" t="s">
         <v>57</v>
       </c>
       <c r="L65" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
@@ -7156,34 +7153,34 @@
         <v>85</v>
       </c>
       <c r="C66" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
       </c>
       <c r="E66" t="s">
+        <v>399</v>
+      </c>
+      <c r="F66" t="s">
         <v>400</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>401</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>402</v>
       </c>
-      <c r="H66" t="s">
-        <v>403</v>
-      </c>
       <c r="I66" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J66" t="s">
         <v>33</v>
       </c>
       <c r="L66" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M66" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -7194,34 +7191,34 @@
         <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D67" t="s">
         <v>14</v>
       </c>
       <c r="E67" t="s">
+        <v>403</v>
+      </c>
+      <c r="F67" t="s">
         <v>404</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>405</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>406</v>
       </c>
-      <c r="H67" t="s">
+      <c r="I67" t="s">
         <v>407</v>
-      </c>
-      <c r="I67" t="s">
-        <v>408</v>
       </c>
       <c r="J67" t="s">
         <v>27</v>
       </c>
       <c r="L67" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M67" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -7232,34 +7229,34 @@
         <v>85</v>
       </c>
       <c r="C68" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
       </c>
       <c r="E68" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F68" t="s">
+        <v>477</v>
+      </c>
+      <c r="G68" t="s">
         <v>478</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>479</v>
       </c>
-      <c r="H68" t="s">
-        <v>480</v>
-      </c>
       <c r="I68" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J68" t="s">
         <v>20</v>
       </c>
       <c r="L68" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M68" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -7270,34 +7267,34 @@
         <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
       </c>
       <c r="E69" t="s">
+        <v>409</v>
+      </c>
+      <c r="F69" t="s">
         <v>410</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>411</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>412</v>
       </c>
-      <c r="H69" t="s">
+      <c r="I69" t="s">
         <v>413</v>
-      </c>
-      <c r="I69" t="s">
-        <v>414</v>
       </c>
       <c r="J69" t="s">
         <v>20</v>
       </c>
       <c r="L69" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -7308,34 +7305,34 @@
         <v>85</v>
       </c>
       <c r="C70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D70" t="s">
         <v>14</v>
       </c>
       <c r="E70" t="s">
+        <v>414</v>
+      </c>
+      <c r="F70" t="s">
         <v>415</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>416</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>417</v>
       </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>418</v>
-      </c>
-      <c r="I70" t="s">
-        <v>419</v>
       </c>
       <c r="J70" t="s">
         <v>57</v>
       </c>
       <c r="L70" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M70" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -7346,34 +7343,34 @@
         <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D71" t="s">
         <v>14</v>
       </c>
       <c r="E71" t="s">
+        <v>419</v>
+      </c>
+      <c r="F71" t="s">
         <v>420</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>421</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>422</v>
       </c>
-      <c r="H71" t="s">
+      <c r="I71" t="s">
         <v>423</v>
-      </c>
-      <c r="I71" t="s">
-        <v>424</v>
       </c>
       <c r="J71" t="s">
         <v>27</v>
       </c>
       <c r="L71" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M71" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -7384,34 +7381,34 @@
         <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D72" t="s">
         <v>14</v>
       </c>
       <c r="E72" t="s">
+        <v>424</v>
+      </c>
+      <c r="F72" t="s">
         <v>425</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>426</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>427</v>
       </c>
-      <c r="H72" t="s">
-        <v>428</v>
-      </c>
       <c r="I72" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J72" t="s">
         <v>20</v>
       </c>
       <c r="L72" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -7422,34 +7419,34 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D73" t="s">
         <v>14</v>
       </c>
       <c r="E73" t="s">
+        <v>428</v>
+      </c>
+      <c r="F73" t="s">
         <v>429</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>430</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>431</v>
       </c>
-      <c r="H73" t="s">
+      <c r="I73" t="s">
         <v>432</v>
-      </c>
-      <c r="I73" t="s">
-        <v>433</v>
       </c>
       <c r="J73" t="s">
         <v>27</v>
       </c>
       <c r="L73" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M73" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -7460,34 +7457,34 @@
         <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D74" t="s">
         <v>14</v>
       </c>
       <c r="E74" t="s">
+        <v>433</v>
+      </c>
+      <c r="F74" t="s">
         <v>434</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>435</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>436</v>
       </c>
-      <c r="H74" t="s">
+      <c r="I74" t="s">
         <v>437</v>
-      </c>
-      <c r="I74" t="s">
-        <v>438</v>
       </c>
       <c r="J74" t="s">
         <v>33</v>
       </c>
       <c r="L74" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M74" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -7498,34 +7495,34 @@
         <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D75" t="s">
         <v>14</v>
       </c>
       <c r="E75" t="s">
+        <v>438</v>
+      </c>
+      <c r="F75" t="s">
         <v>439</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>440</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>441</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>442</v>
-      </c>
-      <c r="I75" t="s">
-        <v>443</v>
       </c>
       <c r="J75" t="s">
         <v>27</v>
       </c>
       <c r="L75" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M75" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -7536,34 +7533,34 @@
         <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D76" t="s">
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F76" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G76" t="s">
+        <v>443</v>
+      </c>
+      <c r="H76" t="s">
         <v>444</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>445</v>
-      </c>
-      <c r="I76" t="s">
-        <v>446</v>
       </c>
       <c r="J76" t="s">
         <v>33</v>
       </c>
       <c r="L76" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M76" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -7580,25 +7577,25 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
+        <v>446</v>
+      </c>
+      <c r="F77" t="s">
         <v>447</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>448</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>449</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>450</v>
-      </c>
-      <c r="I77" t="s">
-        <v>451</v>
       </c>
       <c r="J77" t="s">
         <v>57</v>
       </c>
       <c r="L77" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M77" t="s">
         <v>110</v>
@@ -7612,31 +7609,31 @@
         <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>124</v>
+        <v>827</v>
       </c>
       <c r="D78" t="s">
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F78" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G78" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H78" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I78" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J78" t="s">
         <v>57</v>
       </c>
       <c r="L78" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M78" t="s">
         <v>123</v>
@@ -7656,25 +7653,25 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
+        <v>451</v>
+      </c>
+      <c r="F79" t="s">
         <v>452</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>453</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>454</v>
       </c>
-      <c r="H79" t="s">
-        <v>455</v>
-      </c>
       <c r="I79" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J79" t="s">
         <v>20</v>
       </c>
       <c r="L79" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M79" t="s">
         <v>104</v>
@@ -7688,34 +7685,34 @@
         <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D80" t="s">
         <v>14</v>
       </c>
       <c r="E80" t="s">
+        <v>455</v>
+      </c>
+      <c r="F80" t="s">
         <v>456</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>457</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>458</v>
       </c>
-      <c r="H80" t="s">
+      <c r="I80" t="s">
         <v>459</v>
-      </c>
-      <c r="I80" t="s">
-        <v>460</v>
       </c>
       <c r="J80" t="s">
         <v>33</v>
       </c>
       <c r="L80" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M80" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -7726,34 +7723,34 @@
         <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D81" t="s">
         <v>14</v>
       </c>
       <c r="E81" t="s">
+        <v>470</v>
+      </c>
+      <c r="F81" t="s">
         <v>471</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>472</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>473</v>
       </c>
-      <c r="H81" t="s">
+      <c r="I81" t="s">
         <v>474</v>
-      </c>
-      <c r="I81" t="s">
-        <v>475</v>
       </c>
       <c r="J81" t="s">
         <v>27</v>
       </c>
       <c r="L81" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
@@ -7764,34 +7761,34 @@
         <v>34</v>
       </c>
       <c r="C82" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D82" t="s">
         <v>14</v>
       </c>
       <c r="E82" t="s">
+        <v>509</v>
+      </c>
+      <c r="F82" t="s">
         <v>510</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>511</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>512</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>513</v>
-      </c>
-      <c r="I82" t="s">
-        <v>514</v>
       </c>
       <c r="J82" t="s">
         <v>57</v>
       </c>
       <c r="L82" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M82" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -7802,34 +7799,34 @@
         <v>34</v>
       </c>
       <c r="C83" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D83" t="s">
         <v>14</v>
       </c>
       <c r="E83" t="s">
+        <v>515</v>
+      </c>
+      <c r="F83" t="s">
         <v>516</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>517</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>518</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>519</v>
-      </c>
-      <c r="I83" t="s">
-        <v>520</v>
       </c>
       <c r="J83" t="s">
         <v>27</v>
       </c>
       <c r="L83" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M83" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -7840,34 +7837,34 @@
         <v>34</v>
       </c>
       <c r="C84" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D84" t="s">
         <v>14</v>
       </c>
       <c r="E84" t="s">
+        <v>520</v>
+      </c>
+      <c r="F84" t="s">
         <v>521</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>522</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>523</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>524</v>
-      </c>
-      <c r="I84" t="s">
-        <v>525</v>
       </c>
       <c r="J84" t="s">
         <v>20</v>
       </c>
       <c r="L84" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M84" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -7878,34 +7875,34 @@
         <v>34</v>
       </c>
       <c r="C85" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D85" t="s">
         <v>14</v>
       </c>
       <c r="E85" t="s">
+        <v>525</v>
+      </c>
+      <c r="F85" t="s">
         <v>526</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>527</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>528</v>
       </c>
-      <c r="H85" t="s">
+      <c r="I85" t="s">
         <v>529</v>
-      </c>
-      <c r="I85" t="s">
-        <v>530</v>
       </c>
       <c r="J85" t="s">
         <v>20</v>
       </c>
       <c r="L85" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M85" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -7916,34 +7913,34 @@
         <v>34</v>
       </c>
       <c r="C86" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D86" t="s">
         <v>14</v>
       </c>
       <c r="E86" t="s">
+        <v>530</v>
+      </c>
+      <c r="F86" t="s">
         <v>531</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>532</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>533</v>
       </c>
-      <c r="H86" t="s">
+      <c r="I86" t="s">
         <v>534</v>
-      </c>
-      <c r="I86" t="s">
-        <v>535</v>
       </c>
       <c r="J86" t="s">
         <v>27</v>
       </c>
       <c r="L86" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M86" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -7954,34 +7951,34 @@
         <v>34</v>
       </c>
       <c r="C87" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D87" t="s">
         <v>14</v>
       </c>
       <c r="E87" t="s">
+        <v>535</v>
+      </c>
+      <c r="F87" t="s">
         <v>536</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>537</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>538</v>
       </c>
-      <c r="H87" t="s">
+      <c r="I87" t="s">
         <v>539</v>
-      </c>
-      <c r="I87" t="s">
-        <v>540</v>
       </c>
       <c r="J87" t="s">
         <v>33</v>
       </c>
       <c r="L87" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M87" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -7992,34 +7989,34 @@
         <v>34</v>
       </c>
       <c r="C88" t="s">
+        <v>540</v>
+      </c>
+      <c r="D88" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" t="s">
         <v>541</v>
       </c>
-      <c r="D88" t="s">
-        <v>14</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>542</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>543</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>544</v>
       </c>
-      <c r="H88" t="s">
+      <c r="I88" t="s">
         <v>545</v>
-      </c>
-      <c r="I88" t="s">
-        <v>546</v>
       </c>
       <c r="J88" t="s">
         <v>33</v>
       </c>
       <c r="L88" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M88" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -8030,34 +8027,34 @@
         <v>34</v>
       </c>
       <c r="C89" t="s">
+        <v>547</v>
+      </c>
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" t="s">
         <v>548</v>
       </c>
-      <c r="D89" t="s">
-        <v>14</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>549</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>550</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>551</v>
       </c>
-      <c r="H89" t="s">
+      <c r="I89" t="s">
         <v>552</v>
-      </c>
-      <c r="I89" t="s">
-        <v>553</v>
       </c>
       <c r="J89" t="s">
         <v>20</v>
       </c>
       <c r="L89" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M89" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -8068,34 +8065,34 @@
         <v>34</v>
       </c>
       <c r="C90" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D90" t="s">
         <v>14</v>
       </c>
       <c r="E90" t="s">
+        <v>554</v>
+      </c>
+      <c r="F90" t="s">
         <v>555</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>556</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>557</v>
       </c>
-      <c r="H90" t="s">
+      <c r="I90" t="s">
         <v>558</v>
-      </c>
-      <c r="I90" t="s">
-        <v>559</v>
       </c>
       <c r="J90" t="s">
         <v>27</v>
       </c>
       <c r="L90" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M90" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -8106,34 +8103,34 @@
         <v>34</v>
       </c>
       <c r="C91" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D91" t="s">
         <v>14</v>
       </c>
       <c r="E91" t="s">
+        <v>560</v>
+      </c>
+      <c r="F91" t="s">
         <v>561</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>562</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>563</v>
       </c>
-      <c r="H91" t="s">
+      <c r="I91" t="s">
         <v>564</v>
-      </c>
-      <c r="I91" t="s">
-        <v>565</v>
       </c>
       <c r="J91" t="s">
         <v>27</v>
       </c>
       <c r="L91" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M91" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -8144,34 +8141,34 @@
         <v>34</v>
       </c>
       <c r="C92" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D92" t="s">
         <v>14</v>
       </c>
       <c r="E92" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F92" t="s">
+        <v>573</v>
+      </c>
+      <c r="G92" t="s">
         <v>574</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>575</v>
       </c>
-      <c r="H92" t="s">
+      <c r="I92" t="s">
         <v>576</v>
-      </c>
-      <c r="I92" t="s">
-        <v>577</v>
       </c>
       <c r="J92" t="s">
         <v>27</v>
       </c>
       <c r="L92" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M92" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -8182,34 +8179,34 @@
         <v>85</v>
       </c>
       <c r="C93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D93" t="s">
         <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F93" t="s">
+        <v>577</v>
+      </c>
+      <c r="G93" t="s">
         <v>578</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>579</v>
       </c>
-      <c r="H93" t="s">
+      <c r="I93" t="s">
         <v>580</v>
-      </c>
-      <c r="I93" t="s">
-        <v>581</v>
       </c>
       <c r="J93" t="s">
         <v>57</v>
       </c>
       <c r="L93" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M93" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -8220,34 +8217,34 @@
         <v>85</v>
       </c>
       <c r="C94" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D94" t="s">
         <v>14</v>
       </c>
       <c r="E94" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F94" t="s">
+        <v>581</v>
+      </c>
+      <c r="G94" t="s">
         <v>582</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>583</v>
       </c>
-      <c r="H94" t="s">
+      <c r="I94" t="s">
         <v>584</v>
-      </c>
-      <c r="I94" t="s">
-        <v>585</v>
       </c>
       <c r="J94" t="s">
         <v>33</v>
       </c>
       <c r="L94" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M94" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -8258,34 +8255,34 @@
         <v>85</v>
       </c>
       <c r="C95" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D95" t="s">
         <v>14</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F95" t="s">
+        <v>585</v>
+      </c>
+      <c r="G95" t="s">
         <v>586</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>587</v>
       </c>
-      <c r="H95" t="s">
+      <c r="I95" t="s">
         <v>588</v>
-      </c>
-      <c r="I95" t="s">
-        <v>589</v>
       </c>
       <c r="J95" t="s">
         <v>20</v>
       </c>
       <c r="L95" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M95" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -8296,34 +8293,34 @@
         <v>85</v>
       </c>
       <c r="C96" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D96" t="s">
         <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F96" t="s">
+        <v>589</v>
+      </c>
+      <c r="G96" t="s">
         <v>590</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
         <v>591</v>
       </c>
-      <c r="H96" t="s">
+      <c r="I96" t="s">
         <v>592</v>
-      </c>
-      <c r="I96" t="s">
-        <v>593</v>
       </c>
       <c r="J96" t="s">
         <v>33</v>
       </c>
       <c r="L96" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M96" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -8334,34 +8331,34 @@
         <v>85</v>
       </c>
       <c r="C97" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D97" t="s">
         <v>14</v>
       </c>
       <c r="E97" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F97" t="s">
+        <v>593</v>
+      </c>
+      <c r="G97" t="s">
         <v>594</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>595</v>
       </c>
-      <c r="H97" t="s">
+      <c r="I97" t="s">
         <v>596</v>
-      </c>
-      <c r="I97" t="s">
-        <v>597</v>
       </c>
       <c r="J97" t="s">
         <v>20</v>
       </c>
       <c r="L97" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M97" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
@@ -8372,34 +8369,34 @@
         <v>85</v>
       </c>
       <c r="C98" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D98" t="s">
         <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F98" t="s">
+        <v>597</v>
+      </c>
+      <c r="G98" t="s">
         <v>598</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>599</v>
       </c>
-      <c r="H98" t="s">
+      <c r="I98" t="s">
         <v>600</v>
-      </c>
-      <c r="I98" t="s">
-        <v>601</v>
       </c>
       <c r="J98" t="s">
         <v>27</v>
       </c>
       <c r="L98" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M98" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -8410,34 +8407,34 @@
         <v>85</v>
       </c>
       <c r="C99" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D99" t="s">
         <v>14</v>
       </c>
       <c r="E99" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F99" t="s">
+        <v>601</v>
+      </c>
+      <c r="G99" t="s">
         <v>602</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>603</v>
       </c>
-      <c r="H99" t="s">
+      <c r="I99" t="s">
         <v>604</v>
-      </c>
-      <c r="I99" t="s">
-        <v>605</v>
       </c>
       <c r="J99" t="s">
         <v>57</v>
       </c>
       <c r="L99" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M99" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
@@ -8448,34 +8445,34 @@
         <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F100" t="s">
+        <v>605</v>
+      </c>
+      <c r="G100" t="s">
         <v>606</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>607</v>
       </c>
-      <c r="H100" t="s">
+      <c r="I100" t="s">
         <v>608</v>
-      </c>
-      <c r="I100" t="s">
-        <v>609</v>
       </c>
       <c r="J100" t="s">
         <v>20</v>
       </c>
       <c r="L100" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M100" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
@@ -8486,34 +8483,34 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D101" t="s">
         <v>14</v>
       </c>
       <c r="E101" t="s">
+        <v>614</v>
+      </c>
+      <c r="F101" t="s">
         <v>615</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>616</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>617</v>
       </c>
-      <c r="H101" t="s">
+      <c r="I101" t="s">
         <v>618</v>
-      </c>
-      <c r="I101" t="s">
-        <v>619</v>
       </c>
       <c r="J101" t="s">
         <v>57</v>
       </c>
       <c r="L101" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M101" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
@@ -8524,34 +8521,34 @@
         <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D102" t="s">
         <v>14</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F102" t="s">
+        <v>619</v>
+      </c>
+      <c r="G102" t="s">
         <v>620</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>621</v>
       </c>
-      <c r="H102" t="s">
+      <c r="I102" t="s">
         <v>622</v>
-      </c>
-      <c r="I102" t="s">
-        <v>623</v>
       </c>
       <c r="J102" t="s">
         <v>27</v>
       </c>
       <c r="L102" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M102" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
@@ -8562,34 +8559,34 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D103" t="s">
         <v>14</v>
       </c>
       <c r="E103" t="s">
+        <v>623</v>
+      </c>
+      <c r="F103" t="s">
         <v>624</v>
       </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>625</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>626</v>
       </c>
-      <c r="H103" t="s">
+      <c r="I103" t="s">
         <v>627</v>
-      </c>
-      <c r="I103" t="s">
-        <v>628</v>
       </c>
       <c r="J103" t="s">
         <v>57</v>
       </c>
       <c r="L103" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M103" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -8600,34 +8597,34 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D104" t="s">
         <v>14</v>
       </c>
       <c r="E104" t="s">
+        <v>628</v>
+      </c>
+      <c r="F104" t="s">
         <v>629</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>630</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104" t="s">
         <v>631</v>
       </c>
-      <c r="H104" t="s">
+      <c r="I104" t="s">
         <v>632</v>
-      </c>
-      <c r="I104" t="s">
-        <v>633</v>
       </c>
       <c r="J104" t="s">
         <v>33</v>
       </c>
       <c r="L104" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M104" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
@@ -8638,34 +8635,34 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D105" t="s">
         <v>14</v>
       </c>
       <c r="E105" t="s">
+        <v>633</v>
+      </c>
+      <c r="F105" t="s">
         <v>634</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>635</v>
       </c>
-      <c r="G105" t="s">
+      <c r="H105" t="s">
         <v>636</v>
       </c>
-      <c r="H105" t="s">
-        <v>637</v>
-      </c>
       <c r="I105" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J105" t="s">
         <v>20</v>
       </c>
       <c r="L105" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M105" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
@@ -8676,34 +8673,34 @@
         <v>12</v>
       </c>
       <c r="C106" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D106" t="s">
         <v>14</v>
       </c>
       <c r="E106" t="s">
+        <v>639</v>
+      </c>
+      <c r="F106" t="s">
         <v>640</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>641</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>642</v>
       </c>
-      <c r="H106" t="s">
+      <c r="I106" t="s">
         <v>643</v>
-      </c>
-      <c r="I106" t="s">
-        <v>644</v>
       </c>
       <c r="J106" t="s">
         <v>27</v>
       </c>
       <c r="L106" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M106" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
@@ -8720,25 +8717,25 @@
         <v>14</v>
       </c>
       <c r="E107" t="s">
+        <v>644</v>
+      </c>
+      <c r="F107" t="s">
         <v>645</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>646</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>647</v>
       </c>
-      <c r="H107" t="s">
+      <c r="I107" t="s">
         <v>648</v>
-      </c>
-      <c r="I107" t="s">
-        <v>649</v>
       </c>
       <c r="J107" t="s">
         <v>27</v>
       </c>
       <c r="L107" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M107" t="s">
         <v>110</v>
@@ -8758,25 +8755,25 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
+        <v>649</v>
+      </c>
+      <c r="F108" t="s">
         <v>650</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>651</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
         <v>652</v>
       </c>
-      <c r="H108" t="s">
+      <c r="I108" t="s">
         <v>653</v>
-      </c>
-      <c r="I108" t="s">
-        <v>654</v>
       </c>
       <c r="J108" t="s">
         <v>20</v>
       </c>
       <c r="L108" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M108" t="s">
         <v>110</v>
@@ -8796,25 +8793,25 @@
         <v>14</v>
       </c>
       <c r="E109" t="s">
+        <v>654</v>
+      </c>
+      <c r="F109" t="s">
         <v>655</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>656</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>657</v>
       </c>
-      <c r="H109" t="s">
+      <c r="I109" t="s">
         <v>658</v>
-      </c>
-      <c r="I109" t="s">
-        <v>659</v>
       </c>
       <c r="J109" t="s">
         <v>27</v>
       </c>
       <c r="L109" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M109" t="s">
         <v>104</v>
@@ -8828,34 +8825,34 @@
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D110" t="s">
         <v>14</v>
       </c>
       <c r="E110" t="s">
+        <v>659</v>
+      </c>
+      <c r="F110" t="s">
         <v>660</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>661</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" t="s">
         <v>662</v>
       </c>
-      <c r="H110" t="s">
+      <c r="I110" t="s">
         <v>663</v>
-      </c>
-      <c r="I110" t="s">
-        <v>664</v>
       </c>
       <c r="J110" t="s">
         <v>33</v>
       </c>
       <c r="L110" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M110" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -8866,34 +8863,34 @@
         <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D111" t="s">
         <v>14</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F111" t="s">
+        <v>664</v>
+      </c>
+      <c r="G111" t="s">
         <v>665</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>666</v>
       </c>
-      <c r="H111" t="s">
+      <c r="I111" t="s">
         <v>667</v>
-      </c>
-      <c r="I111" t="s">
-        <v>668</v>
       </c>
       <c r="J111" t="s">
         <v>57</v>
       </c>
       <c r="L111" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M111" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
@@ -8910,25 +8907,25 @@
         <v>14</v>
       </c>
       <c r="E112" t="s">
+        <v>668</v>
+      </c>
+      <c r="F112" t="s">
         <v>669</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>670</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>671</v>
       </c>
-      <c r="H112" t="s">
+      <c r="I112" t="s">
         <v>672</v>
-      </c>
-      <c r="I112" t="s">
-        <v>673</v>
       </c>
       <c r="J112" t="s">
         <v>33</v>
       </c>
       <c r="L112" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M112" t="s">
         <v>45</v>
@@ -8948,25 +8945,25 @@
         <v>14</v>
       </c>
       <c r="E113" t="s">
+        <v>673</v>
+      </c>
+      <c r="F113" t="s">
         <v>674</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>675</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>676</v>
       </c>
-      <c r="H113" t="s">
+      <c r="I113" t="s">
         <v>677</v>
-      </c>
-      <c r="I113" t="s">
-        <v>678</v>
       </c>
       <c r="J113" t="s">
         <v>57</v>
       </c>
       <c r="L113" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M113" t="s">
         <v>45</v>
@@ -8980,34 +8977,34 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F114" t="s">
+        <v>678</v>
+      </c>
+      <c r="G114" t="s">
         <v>679</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>680</v>
       </c>
-      <c r="H114" t="s">
-        <v>681</v>
-      </c>
       <c r="I114" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="J114" t="s">
         <v>20</v>
       </c>
       <c r="L114" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M114" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
@@ -9018,34 +9015,34 @@
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D115" t="s">
         <v>14</v>
       </c>
       <c r="E115" t="s">
+        <v>681</v>
+      </c>
+      <c r="F115" t="s">
         <v>682</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>683</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>684</v>
       </c>
-      <c r="H115" t="s">
+      <c r="I115" t="s">
         <v>685</v>
-      </c>
-      <c r="I115" t="s">
-        <v>686</v>
       </c>
       <c r="J115" t="s">
         <v>27</v>
       </c>
       <c r="L115" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
@@ -9056,34 +9053,34 @@
         <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>709</v>
+        <v>476</v>
       </c>
       <c r="D116" t="s">
         <v>14</v>
       </c>
       <c r="E116" t="s">
+        <v>686</v>
+      </c>
+      <c r="F116" t="s">
         <v>687</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>688</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H116" t="s">
         <v>689</v>
       </c>
-      <c r="H116" t="s">
+      <c r="I116" t="s">
         <v>690</v>
-      </c>
-      <c r="I116" t="s">
-        <v>691</v>
       </c>
       <c r="J116" t="s">
         <v>27</v>
       </c>
       <c r="L116" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M116" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
@@ -9094,34 +9091,34 @@
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>124</v>
+        <v>827</v>
       </c>
       <c r="D117" t="s">
         <v>14</v>
       </c>
       <c r="E117" t="s">
+        <v>691</v>
+      </c>
+      <c r="F117" t="s">
         <v>692</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>693</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" t="s">
         <v>694</v>
       </c>
-      <c r="H117" t="s">
+      <c r="I117" t="s">
         <v>695</v>
-      </c>
-      <c r="I117" t="s">
-        <v>696</v>
       </c>
       <c r="J117" t="s">
         <v>57</v>
       </c>
       <c r="L117" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M117" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
@@ -9132,34 +9129,34 @@
         <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D118" t="s">
         <v>14</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F118" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G118" t="s">
+        <v>696</v>
+      </c>
+      <c r="H118" t="s">
         <v>697</v>
       </c>
-      <c r="H118" t="s">
+      <c r="I118" t="s">
         <v>698</v>
-      </c>
-      <c r="I118" t="s">
-        <v>699</v>
       </c>
       <c r="J118" t="s">
         <v>33</v>
       </c>
       <c r="L118" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M118" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
@@ -9170,34 +9167,34 @@
         <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D119" t="s">
         <v>14</v>
       </c>
       <c r="E119" t="s">
+        <v>699</v>
+      </c>
+      <c r="F119" t="s">
         <v>700</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>701</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>702</v>
       </c>
-      <c r="H119" t="s">
-        <v>703</v>
-      </c>
       <c r="I119" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J119" t="s">
         <v>27</v>
       </c>
       <c r="L119" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
@@ -9205,37 +9202,37 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C120" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D120" t="s">
         <v>14</v>
       </c>
       <c r="E120" t="s">
+        <v>711</v>
+      </c>
+      <c r="F120" t="s">
+        <v>712</v>
+      </c>
+      <c r="G120" t="s">
         <v>713</v>
       </c>
-      <c r="F120" t="s">
+      <c r="H120" t="s">
         <v>714</v>
       </c>
-      <c r="G120" t="s">
+      <c r="I120" t="s">
         <v>715</v>
-      </c>
-      <c r="H120" t="s">
-        <v>716</v>
-      </c>
-      <c r="I120" t="s">
-        <v>717</v>
       </c>
       <c r="J120" t="s">
         <v>20</v>
       </c>
       <c r="L120" t="s">
+        <v>721</v>
+      </c>
+      <c r="M120" t="s">
         <v>723</v>
-      </c>
-      <c r="M120" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
@@ -9243,37 +9240,37 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>720</v>
+      </c>
+      <c r="C121" t="s">
+        <v>720</v>
+      </c>
+      <c r="D121" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="C121" t="s">
-        <v>722</v>
-      </c>
-      <c r="D121" t="s">
-        <v>14</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>724</v>
-      </c>
       <c r="F121" t="s">
+        <v>716</v>
+      </c>
+      <c r="G121" t="s">
+        <v>717</v>
+      </c>
+      <c r="H121" t="s">
         <v>718</v>
       </c>
-      <c r="G121" t="s">
+      <c r="I121" t="s">
         <v>719</v>
-      </c>
-      <c r="H121" t="s">
-        <v>720</v>
-      </c>
-      <c r="I121" t="s">
-        <v>721</v>
       </c>
       <c r="J121" t="s">
         <v>33</v>
       </c>
       <c r="L121" t="s">
+        <v>721</v>
+      </c>
+      <c r="M121" t="s">
         <v>723</v>
-      </c>
-      <c r="M121" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
@@ -9284,34 +9281,34 @@
         <v>34</v>
       </c>
       <c r="C122" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D122" t="s">
         <v>14</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="F122" t="s">
+        <v>724</v>
+      </c>
+      <c r="G122" t="s">
+        <v>725</v>
+      </c>
+      <c r="H122" t="s">
+        <v>355</v>
+      </c>
+      <c r="I122" t="s">
         <v>726</v>
-      </c>
-      <c r="G122" t="s">
-        <v>727</v>
-      </c>
-      <c r="H122" t="s">
-        <v>356</v>
-      </c>
-      <c r="I122" t="s">
-        <v>728</v>
       </c>
       <c r="J122" t="s">
         <v>57</v>
       </c>
       <c r="L122" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M122" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -9322,34 +9319,34 @@
         <v>34</v>
       </c>
       <c r="C123" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D123" t="s">
         <v>14</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="F123" t="s">
+        <v>728</v>
+      </c>
+      <c r="G123" t="s">
+        <v>729</v>
+      </c>
+      <c r="H123" t="s">
         <v>730</v>
       </c>
-      <c r="G123" t="s">
+      <c r="I123" t="s">
         <v>731</v>
-      </c>
-      <c r="H123" t="s">
-        <v>732</v>
-      </c>
-      <c r="I123" t="s">
-        <v>733</v>
       </c>
       <c r="J123" t="s">
         <v>27</v>
       </c>
       <c r="L123" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M123" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
@@ -9360,34 +9357,34 @@
         <v>34</v>
       </c>
       <c r="C124" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D124" t="s">
         <v>14</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="F124" t="s">
+        <v>732</v>
+      </c>
+      <c r="G124" t="s">
+        <v>733</v>
+      </c>
+      <c r="H124" t="s">
         <v>734</v>
       </c>
-      <c r="G124" t="s">
+      <c r="I124" t="s">
         <v>735</v>
-      </c>
-      <c r="H124" t="s">
-        <v>736</v>
-      </c>
-      <c r="I124" t="s">
-        <v>737</v>
       </c>
       <c r="J124" t="s">
         <v>33</v>
       </c>
       <c r="L124" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M124" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -9398,34 +9395,34 @@
         <v>34</v>
       </c>
       <c r="C125" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D125" t="s">
         <v>14</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="F125" t="s">
+        <v>728</v>
+      </c>
+      <c r="G125" t="s">
+        <v>729</v>
+      </c>
+      <c r="H125" t="s">
         <v>730</v>
       </c>
-      <c r="G125" t="s">
+      <c r="I125" t="s">
         <v>731</v>
-      </c>
-      <c r="H125" t="s">
-        <v>732</v>
-      </c>
-      <c r="I125" t="s">
-        <v>733</v>
       </c>
       <c r="J125" t="s">
         <v>27</v>
       </c>
       <c r="L125" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M125" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -9436,34 +9433,34 @@
         <v>34</v>
       </c>
       <c r="C126" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D126" t="s">
         <v>14</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F126" t="s">
+        <v>736</v>
+      </c>
+      <c r="G126" t="s">
+        <v>737</v>
+      </c>
+      <c r="H126" t="s">
         <v>738</v>
       </c>
-      <c r="G126" t="s">
-        <v>739</v>
-      </c>
-      <c r="H126" t="s">
-        <v>740</v>
-      </c>
       <c r="I126" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="J126" t="s">
         <v>57</v>
       </c>
       <c r="L126" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M126" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -9474,34 +9471,34 @@
         <v>34</v>
       </c>
       <c r="C127" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D127" t="s">
         <v>14</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F127" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G127" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="H127" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="I127" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="J127" t="s">
         <v>27</v>
       </c>
       <c r="L127" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M127" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
@@ -9512,34 +9509,34 @@
         <v>34</v>
       </c>
       <c r="C128" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D128" t="s">
         <v>14</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F128" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G128" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="H128" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="I128" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="J128" t="s">
         <v>57</v>
       </c>
       <c r="L128" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M128" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -9550,34 +9547,34 @@
         <v>85</v>
       </c>
       <c r="C129" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D129" t="s">
         <v>14</v>
       </c>
       <c r="E129" t="s">
+        <v>746</v>
+      </c>
+      <c r="F129" t="s">
+        <v>747</v>
+      </c>
+      <c r="G129" t="s">
         <v>748</v>
       </c>
-      <c r="F129" t="s">
+      <c r="H129" t="s">
         <v>749</v>
       </c>
-      <c r="G129" t="s">
+      <c r="I129" t="s">
         <v>750</v>
-      </c>
-      <c r="H129" t="s">
-        <v>751</v>
-      </c>
-      <c r="I129" t="s">
-        <v>752</v>
       </c>
       <c r="J129" t="s">
         <v>57</v>
       </c>
       <c r="L129" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M129" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
@@ -9588,34 +9585,34 @@
         <v>85</v>
       </c>
       <c r="C130" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D130" t="s">
         <v>14</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="F130" t="s">
+        <v>751</v>
+      </c>
+      <c r="G130" t="s">
+        <v>752</v>
+      </c>
+      <c r="H130" t="s">
         <v>753</v>
       </c>
-      <c r="G130" t="s">
+      <c r="I130" t="s">
         <v>754</v>
-      </c>
-      <c r="H130" t="s">
-        <v>755</v>
-      </c>
-      <c r="I130" t="s">
-        <v>756</v>
       </c>
       <c r="J130" t="s">
         <v>57</v>
       </c>
       <c r="L130" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M130" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -9626,34 +9623,34 @@
         <v>85</v>
       </c>
       <c r="C131" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D131" t="s">
         <v>14</v>
       </c>
       <c r="E131" t="s">
+        <v>756</v>
+      </c>
+      <c r="F131" t="s">
+        <v>757</v>
+      </c>
+      <c r="G131" t="s">
         <v>758</v>
       </c>
-      <c r="F131" t="s">
+      <c r="H131" t="s">
         <v>759</v>
       </c>
-      <c r="G131" t="s">
+      <c r="I131" t="s">
         <v>760</v>
-      </c>
-      <c r="H131" t="s">
-        <v>761</v>
-      </c>
-      <c r="I131" t="s">
-        <v>762</v>
       </c>
       <c r="J131" t="s">
         <v>33</v>
       </c>
       <c r="L131" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M131" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -9664,34 +9661,34 @@
         <v>85</v>
       </c>
       <c r="C132" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D132" t="s">
         <v>14</v>
       </c>
       <c r="E132" t="s">
+        <v>761</v>
+      </c>
+      <c r="F132" t="s">
+        <v>762</v>
+      </c>
+      <c r="G132" t="s">
         <v>763</v>
       </c>
-      <c r="F132" t="s">
+      <c r="H132" t="s">
         <v>764</v>
       </c>
-      <c r="G132" t="s">
+      <c r="I132" t="s">
         <v>765</v>
-      </c>
-      <c r="H132" t="s">
-        <v>766</v>
-      </c>
-      <c r="I132" t="s">
-        <v>767</v>
       </c>
       <c r="J132" t="s">
         <v>27</v>
       </c>
       <c r="L132" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M132" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -9702,34 +9699,34 @@
         <v>85</v>
       </c>
       <c r="C133" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D133" t="s">
         <v>14</v>
       </c>
       <c r="E133" t="s">
+        <v>766</v>
+      </c>
+      <c r="F133" t="s">
+        <v>767</v>
+      </c>
+      <c r="G133" t="s">
         <v>768</v>
       </c>
-      <c r="F133" t="s">
+      <c r="H133" t="s">
         <v>769</v>
       </c>
-      <c r="G133" t="s">
+      <c r="I133" t="s">
         <v>770</v>
-      </c>
-      <c r="H133" t="s">
-        <v>771</v>
-      </c>
-      <c r="I133" t="s">
-        <v>772</v>
       </c>
       <c r="J133" t="s">
         <v>27</v>
       </c>
       <c r="L133" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M133" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
@@ -9740,34 +9737,34 @@
         <v>85</v>
       </c>
       <c r="C134" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D134" t="s">
         <v>14</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="F134" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G134" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="H134" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="I134" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="J134" t="s">
         <v>33</v>
       </c>
       <c r="L134" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M134" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
@@ -9778,34 +9775,34 @@
         <v>85</v>
       </c>
       <c r="C135" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D135" t="s">
         <v>14</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="F135" t="s">
+        <v>772</v>
+      </c>
+      <c r="G135" t="s">
+        <v>773</v>
+      </c>
+      <c r="H135" t="s">
         <v>774</v>
       </c>
-      <c r="G135" t="s">
-        <v>775</v>
-      </c>
-      <c r="H135" t="s">
-        <v>776</v>
-      </c>
       <c r="I135" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="J135" t="s">
         <v>33</v>
       </c>
       <c r="L135" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M135" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -9822,25 +9819,25 @@
         <v>14</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F136" t="s">
+        <v>775</v>
+      </c>
+      <c r="G136" t="s">
+        <v>776</v>
+      </c>
+      <c r="H136" t="s">
         <v>777</v>
       </c>
-      <c r="G136" t="s">
-        <v>778</v>
-      </c>
-      <c r="H136" t="s">
-        <v>779</v>
-      </c>
       <c r="I136" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="J136" t="s">
         <v>57</v>
       </c>
       <c r="L136" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M136" t="s">
         <v>104</v>
@@ -9854,34 +9851,34 @@
         <v>12</v>
       </c>
       <c r="C137" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D137" t="s">
         <v>14</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="F137" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G137" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="H137" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I137" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="J137" t="s">
         <v>27</v>
       </c>
       <c r="L137" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M137" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
@@ -9892,34 +9889,34 @@
         <v>12</v>
       </c>
       <c r="C138" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D138" t="s">
         <v>14</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F138" t="s">
+        <v>778</v>
+      </c>
+      <c r="G138" t="s">
+        <v>779</v>
+      </c>
+      <c r="H138" t="s">
         <v>780</v>
       </c>
-      <c r="G138" t="s">
+      <c r="I138" t="s">
         <v>781</v>
-      </c>
-      <c r="H138" t="s">
-        <v>782</v>
-      </c>
-      <c r="I138" t="s">
-        <v>783</v>
       </c>
       <c r="J138" t="s">
         <v>57</v>
       </c>
       <c r="L138" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M138" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
@@ -9930,34 +9927,34 @@
         <v>12</v>
       </c>
       <c r="C139" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D139" t="s">
         <v>14</v>
       </c>
       <c r="E139" t="s">
+        <v>782</v>
+      </c>
+      <c r="F139" t="s">
+        <v>783</v>
+      </c>
+      <c r="G139" t="s">
         <v>784</v>
       </c>
-      <c r="F139" t="s">
+      <c r="H139" t="s">
         <v>785</v>
       </c>
-      <c r="G139" t="s">
+      <c r="I139" t="s">
         <v>786</v>
-      </c>
-      <c r="H139" t="s">
-        <v>787</v>
-      </c>
-      <c r="I139" t="s">
-        <v>788</v>
       </c>
       <c r="J139" t="s">
         <v>20</v>
       </c>
       <c r="L139" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M139" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -9968,34 +9965,34 @@
         <v>12</v>
       </c>
       <c r="C140" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D140" t="s">
         <v>14</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F140" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G140" t="s">
+        <v>775</v>
+      </c>
+      <c r="H140" t="s">
+        <v>776</v>
+      </c>
+      <c r="I140" t="s">
         <v>777</v>
-      </c>
-      <c r="H140" t="s">
-        <v>778</v>
-      </c>
-      <c r="I140" t="s">
-        <v>779</v>
       </c>
       <c r="J140" t="s">
         <v>57</v>
       </c>
       <c r="L140" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M140" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -10012,25 +10009,25 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
+        <v>787</v>
+      </c>
+      <c r="F141" t="s">
+        <v>788</v>
+      </c>
+      <c r="G141" t="s">
         <v>789</v>
       </c>
-      <c r="F141" t="s">
+      <c r="H141" t="s">
         <v>790</v>
       </c>
-      <c r="G141" t="s">
+      <c r="I141" t="s">
         <v>791</v>
-      </c>
-      <c r="H141" t="s">
-        <v>792</v>
-      </c>
-      <c r="I141" t="s">
-        <v>793</v>
       </c>
       <c r="J141" t="s">
         <v>33</v>
       </c>
       <c r="L141" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M141" t="s">
         <v>110</v>
@@ -10044,34 +10041,34 @@
         <v>12</v>
       </c>
       <c r="C142" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D142" t="s">
         <v>14</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F142" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G142" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="H142" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I142" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="J142" t="s">
         <v>33</v>
       </c>
       <c r="L142" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M142" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
@@ -10082,34 +10079,34 @@
         <v>12</v>
       </c>
       <c r="C143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D143" t="s">
         <v>14</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F143" t="s">
+        <v>792</v>
+      </c>
+      <c r="G143" t="s">
+        <v>793</v>
+      </c>
+      <c r="H143" t="s">
         <v>794</v>
       </c>
-      <c r="G143" t="s">
+      <c r="I143" t="s">
         <v>795</v>
-      </c>
-      <c r="H143" t="s">
-        <v>796</v>
-      </c>
-      <c r="I143" t="s">
-        <v>797</v>
       </c>
       <c r="J143" t="s">
         <v>33</v>
       </c>
       <c r="L143" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M143" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -10120,34 +10117,34 @@
         <v>12</v>
       </c>
       <c r="C144" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D144" t="s">
         <v>14</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="F144" t="s">
+        <v>796</v>
+      </c>
+      <c r="G144" t="s">
+        <v>797</v>
+      </c>
+      <c r="H144" t="s">
         <v>798</v>
       </c>
-      <c r="G144" t="s">
-        <v>799</v>
-      </c>
-      <c r="H144" t="s">
-        <v>800</v>
-      </c>
       <c r="I144" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="J144" t="s">
         <v>20</v>
       </c>
       <c r="L144" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M144" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
@@ -10158,34 +10155,34 @@
         <v>12</v>
       </c>
       <c r="C145" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D145" t="s">
         <v>14</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="F145" t="s">
+        <v>799</v>
+      </c>
+      <c r="G145" t="s">
+        <v>800</v>
+      </c>
+      <c r="H145" t="s">
         <v>801</v>
       </c>
-      <c r="G145" t="s">
+      <c r="I145" t="s">
         <v>802</v>
-      </c>
-      <c r="H145" t="s">
-        <v>803</v>
-      </c>
-      <c r="I145" t="s">
-        <v>804</v>
       </c>
       <c r="J145" t="s">
         <v>20</v>
       </c>
       <c r="L145" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M145" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
@@ -10196,34 +10193,34 @@
         <v>12</v>
       </c>
       <c r="C146" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D146" t="s">
         <v>14</v>
       </c>
       <c r="E146" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="F146" t="s">
+        <v>804</v>
+      </c>
+      <c r="G146" t="s">
         <v>805</v>
       </c>
-      <c r="F146" t="s">
+      <c r="H146" t="s">
         <v>806</v>
       </c>
-      <c r="G146" t="s">
+      <c r="I146" t="s">
         <v>807</v>
-      </c>
-      <c r="H146" t="s">
-        <v>808</v>
-      </c>
-      <c r="I146" t="s">
-        <v>809</v>
       </c>
       <c r="J146" t="s">
         <v>27</v>
       </c>
       <c r="L146" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M146" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
@@ -10240,25 +10237,25 @@
         <v>14</v>
       </c>
       <c r="E147" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="F147" t="s">
+        <v>809</v>
+      </c>
+      <c r="G147" t="s">
         <v>810</v>
       </c>
-      <c r="F147" t="s">
+      <c r="H147" t="s">
         <v>811</v>
       </c>
-      <c r="G147" t="s">
+      <c r="I147" t="s">
         <v>812</v>
-      </c>
-      <c r="H147" t="s">
-        <v>813</v>
-      </c>
-      <c r="I147" t="s">
-        <v>814</v>
       </c>
       <c r="J147" t="s">
         <v>33</v>
       </c>
       <c r="L147" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M147" t="s">
         <v>45</v>
@@ -10272,34 +10269,34 @@
         <v>12</v>
       </c>
       <c r="C148" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D148" t="s">
         <v>14</v>
       </c>
       <c r="E148" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="F148" t="s">
+        <v>814</v>
+      </c>
+      <c r="G148" t="s">
         <v>815</v>
       </c>
-      <c r="F148" t="s">
+      <c r="H148" t="s">
         <v>816</v>
       </c>
-      <c r="G148" t="s">
-        <v>817</v>
-      </c>
-      <c r="H148" t="s">
-        <v>818</v>
-      </c>
       <c r="I148" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="J148" t="s">
         <v>20</v>
       </c>
       <c r="L148" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M148" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
@@ -10310,34 +10307,34 @@
         <v>12</v>
       </c>
       <c r="C149" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D149" t="s">
         <v>14</v>
       </c>
       <c r="E149" t="s">
+        <v>829</v>
+      </c>
+      <c r="F149" t="s">
+        <v>830</v>
+      </c>
+      <c r="G149" t="s">
         <v>831</v>
       </c>
-      <c r="F149" t="s">
+      <c r="H149" t="s">
         <v>832</v>
       </c>
-      <c r="G149" t="s">
+      <c r="I149" t="s">
         <v>833</v>
-      </c>
-      <c r="H149" t="s">
-        <v>834</v>
-      </c>
-      <c r="I149" t="s">
-        <v>835</v>
       </c>
       <c r="J149" t="s">
         <v>27</v>
       </c>
       <c r="L149" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M149" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
@@ -10348,34 +10345,34 @@
         <v>12</v>
       </c>
       <c r="C150" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D150" t="s">
         <v>14</v>
       </c>
       <c r="E150" t="s">
+        <v>834</v>
+      </c>
+      <c r="F150" t="s">
+        <v>835</v>
+      </c>
+      <c r="G150" t="s">
         <v>836</v>
       </c>
-      <c r="F150" t="s">
+      <c r="H150" t="s">
         <v>837</v>
       </c>
-      <c r="G150" t="s">
+      <c r="I150" t="s">
         <v>838</v>
-      </c>
-      <c r="H150" t="s">
-        <v>839</v>
-      </c>
-      <c r="I150" t="s">
-        <v>840</v>
       </c>
       <c r="J150" t="s">
         <v>20</v>
       </c>
       <c r="L150" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M150" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
@@ -10392,25 +10389,25 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
+        <v>839</v>
+      </c>
+      <c r="F151" t="s">
+        <v>840</v>
+      </c>
+      <c r="G151" t="s">
         <v>841</v>
       </c>
-      <c r="F151" t="s">
+      <c r="H151" t="s">
         <v>842</v>
       </c>
-      <c r="G151" t="s">
-        <v>843</v>
-      </c>
-      <c r="H151" t="s">
-        <v>844</v>
-      </c>
       <c r="I151" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="J151" t="s">
         <v>57</v>
       </c>
       <c r="L151" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M151" t="s">
         <v>45</v>
@@ -10430,25 +10427,25 @@
         <v>14</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="F152" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G152" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H152" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I152" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J152" t="s">
         <v>57</v>
       </c>
       <c r="L152" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M152" t="s">
         <v>45</v>
@@ -10462,34 +10459,34 @@
         <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D153" t="s">
         <v>14</v>
       </c>
       <c r="E153" t="s">
+        <v>843</v>
+      </c>
+      <c r="F153" t="s">
+        <v>844</v>
+      </c>
+      <c r="G153" t="s">
+        <v>187</v>
+      </c>
+      <c r="H153" t="s">
+        <v>189</v>
+      </c>
+      <c r="I153" t="s">
         <v>845</v>
-      </c>
-      <c r="F153" t="s">
-        <v>846</v>
-      </c>
-      <c r="G153" t="s">
-        <v>188</v>
-      </c>
-      <c r="H153" t="s">
-        <v>190</v>
-      </c>
-      <c r="I153" t="s">
-        <v>847</v>
       </c>
       <c r="J153" t="s">
         <v>33</v>
       </c>
       <c r="L153" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M153" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
@@ -10500,34 +10497,34 @@
         <v>12</v>
       </c>
       <c r="C154" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D154" t="s">
         <v>14</v>
       </c>
       <c r="E154" t="s">
+        <v>846</v>
+      </c>
+      <c r="F154" t="s">
+        <v>847</v>
+      </c>
+      <c r="G154" t="s">
         <v>848</v>
       </c>
-      <c r="F154" t="s">
+      <c r="H154" t="s">
         <v>849</v>
       </c>
-      <c r="G154" t="s">
+      <c r="I154" t="s">
         <v>850</v>
-      </c>
-      <c r="H154" t="s">
-        <v>851</v>
-      </c>
-      <c r="I154" t="s">
-        <v>852</v>
       </c>
       <c r="J154" t="s">
         <v>27</v>
       </c>
       <c r="L154" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M154" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
@@ -10544,25 +10541,25 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
+        <v>851</v>
+      </c>
+      <c r="F155" t="s">
+        <v>852</v>
+      </c>
+      <c r="G155" t="s">
         <v>853</v>
       </c>
-      <c r="F155" t="s">
+      <c r="H155" t="s">
         <v>854</v>
       </c>
-      <c r="G155" t="s">
-        <v>855</v>
-      </c>
-      <c r="H155" t="s">
-        <v>856</v>
-      </c>
       <c r="I155" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="J155" t="s">
         <v>57</v>
       </c>
       <c r="L155" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M155" t="s">
         <v>110</v>
@@ -10582,25 +10579,25 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
+        <v>855</v>
+      </c>
+      <c r="F156" t="s">
+        <v>856</v>
+      </c>
+      <c r="G156" t="s">
         <v>857</v>
       </c>
-      <c r="F156" t="s">
+      <c r="H156" t="s">
         <v>858</v>
       </c>
-      <c r="G156" t="s">
+      <c r="I156" t="s">
         <v>859</v>
-      </c>
-      <c r="H156" t="s">
-        <v>860</v>
-      </c>
-      <c r="I156" t="s">
-        <v>861</v>
       </c>
       <c r="J156" t="s">
         <v>20</v>
       </c>
       <c r="L156" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M156" t="s">
         <v>110</v>
@@ -10620,25 +10617,25 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
+        <v>860</v>
+      </c>
+      <c r="F157" t="s">
+        <v>861</v>
+      </c>
+      <c r="G157" t="s">
         <v>862</v>
       </c>
-      <c r="F157" t="s">
+      <c r="H157" t="s">
+        <v>449</v>
+      </c>
+      <c r="I157" t="s">
         <v>863</v>
-      </c>
-      <c r="G157" t="s">
-        <v>864</v>
-      </c>
-      <c r="H157" t="s">
-        <v>450</v>
-      </c>
-      <c r="I157" t="s">
-        <v>865</v>
       </c>
       <c r="J157" t="s">
         <v>57</v>
       </c>
       <c r="L157" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M157" t="s">
         <v>110</v>
@@ -10652,34 +10649,34 @@
         <v>12</v>
       </c>
       <c r="C158" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D158" t="s">
         <v>14</v>
       </c>
       <c r="E158" t="s">
+        <v>864</v>
+      </c>
+      <c r="F158" t="s">
+        <v>865</v>
+      </c>
+      <c r="G158" t="s">
         <v>866</v>
       </c>
-      <c r="F158" t="s">
+      <c r="H158" t="s">
         <v>867</v>
       </c>
-      <c r="G158" t="s">
-        <v>868</v>
-      </c>
-      <c r="H158" t="s">
-        <v>869</v>
-      </c>
       <c r="I158" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="J158" t="s">
         <v>57</v>
       </c>
       <c r="L158" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M158" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
@@ -10696,25 +10693,25 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="F159" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G159" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H159" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I159" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="J159" t="s">
         <v>27</v>
       </c>
       <c r="L159" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M159" t="s">
         <v>110</v>
@@ -10728,34 +10725,34 @@
         <v>12</v>
       </c>
       <c r="C160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D160" t="s">
         <v>14</v>
       </c>
       <c r="E160" t="s">
+        <v>870</v>
+      </c>
+      <c r="F160" t="s">
+        <v>871</v>
+      </c>
+      <c r="G160" t="s">
         <v>872</v>
       </c>
-      <c r="F160" t="s">
+      <c r="H160" t="s">
         <v>873</v>
       </c>
-      <c r="G160" t="s">
+      <c r="I160" t="s">
         <v>874</v>
-      </c>
-      <c r="H160" t="s">
-        <v>875</v>
-      </c>
-      <c r="I160" t="s">
-        <v>876</v>
       </c>
       <c r="J160" t="s">
         <v>27</v>
       </c>
       <c r="L160" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M160" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
@@ -10766,34 +10763,34 @@
         <v>12</v>
       </c>
       <c r="C161" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D161" t="s">
         <v>14</v>
       </c>
       <c r="E161" t="s">
+        <v>875</v>
+      </c>
+      <c r="F161" t="s">
+        <v>876</v>
+      </c>
+      <c r="G161" t="s">
         <v>877</v>
       </c>
-      <c r="F161" t="s">
+      <c r="H161" t="s">
         <v>878</v>
       </c>
-      <c r="G161" t="s">
-        <v>879</v>
-      </c>
-      <c r="H161" t="s">
-        <v>880</v>
-      </c>
       <c r="I161" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="J161" t="s">
         <v>33</v>
       </c>
       <c r="L161" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M161" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
@@ -10804,34 +10801,34 @@
         <v>12</v>
       </c>
       <c r="C162" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D162" t="s">
         <v>14</v>
       </c>
       <c r="E162" t="s">
+        <v>879</v>
+      </c>
+      <c r="F162" t="s">
+        <v>700</v>
+      </c>
+      <c r="G162" t="s">
+        <v>880</v>
+      </c>
+      <c r="H162" t="s">
         <v>881</v>
       </c>
-      <c r="F162" t="s">
-        <v>701</v>
-      </c>
-      <c r="G162" t="s">
-        <v>882</v>
-      </c>
-      <c r="H162" t="s">
-        <v>883</v>
-      </c>
       <c r="I162" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J162" t="s">
         <v>57</v>
       </c>
       <c r="L162" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M162" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
@@ -10842,34 +10839,34 @@
         <v>85</v>
       </c>
       <c r="C163" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D163" t="s">
         <v>14</v>
       </c>
       <c r="E163" t="s">
+        <v>882</v>
+      </c>
+      <c r="F163" t="s">
+        <v>883</v>
+      </c>
+      <c r="G163" t="s">
         <v>884</v>
       </c>
-      <c r="F163" t="s">
+      <c r="H163" t="s">
         <v>885</v>
       </c>
-      <c r="G163" t="s">
+      <c r="I163" t="s">
         <v>886</v>
-      </c>
-      <c r="H163" t="s">
-        <v>887</v>
-      </c>
-      <c r="I163" t="s">
-        <v>888</v>
       </c>
       <c r="J163" t="s">
         <v>20</v>
       </c>
       <c r="L163" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M163" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
@@ -10880,34 +10877,34 @@
         <v>85</v>
       </c>
       <c r="C164" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D164" t="s">
         <v>14</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="F164" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G164" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H164" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I164" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="J164" t="s">
         <v>33</v>
       </c>
       <c r="L164" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M164" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
@@ -10918,34 +10915,34 @@
         <v>85</v>
       </c>
       <c r="C165" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D165" t="s">
         <v>14</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="F165" t="s">
+        <v>887</v>
+      </c>
+      <c r="G165" t="s">
+        <v>888</v>
+      </c>
+      <c r="H165" t="s">
         <v>889</v>
       </c>
-      <c r="G165" t="s">
+      <c r="I165" t="s">
         <v>890</v>
-      </c>
-      <c r="H165" t="s">
-        <v>891</v>
-      </c>
-      <c r="I165" t="s">
-        <v>892</v>
       </c>
       <c r="J165" t="s">
         <v>27</v>
       </c>
       <c r="L165" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M165" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
@@ -10956,34 +10953,34 @@
         <v>85</v>
       </c>
       <c r="C166" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D166" t="s">
         <v>14</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F166" t="s">
+        <v>235</v>
+      </c>
+      <c r="G166" t="s">
+        <v>232</v>
+      </c>
+      <c r="H166" t="s">
         <v>236</v>
       </c>
-      <c r="G166" t="s">
-        <v>233</v>
-      </c>
-      <c r="H166" t="s">
-        <v>237</v>
-      </c>
       <c r="I166" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="J166" t="s">
         <v>20</v>
       </c>
       <c r="L166" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M166" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
@@ -10994,35 +10991,35 @@
         <v>85</v>
       </c>
       <c r="C167" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D167" t="s">
         <v>14</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H167" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="I167" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="I167" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K167" s="4"/>
       <c r="L167" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M167" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
@@ -11033,35 +11030,35 @@
         <v>85</v>
       </c>
       <c r="C168" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D168" t="s">
         <v>14</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G168" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I168" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="H168" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="I168" s="4" t="s">
-        <v>235</v>
       </c>
       <c r="J168" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K168" s="4"/>
       <c r="L168" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M168" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
@@ -11072,22 +11069,22 @@
         <v>85</v>
       </c>
       <c r="C169" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D169" t="s">
         <v>14</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="I169" s="4" t="s">
         <v>97</v>
@@ -11097,10 +11094,10 @@
       </c>
       <c r="K169" s="4"/>
       <c r="L169" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M169" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
@@ -11111,35 +11108,35 @@
         <v>85</v>
       </c>
       <c r="C170" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D170" t="s">
         <v>14</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G170" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="H170" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="H170" s="4" t="s">
+      <c r="I170" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="I170" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="J170" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K170" s="4"/>
       <c r="L170" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M170" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
@@ -11150,35 +11147,35 @@
         <v>85</v>
       </c>
       <c r="C171" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D171" t="s">
         <v>14</v>
       </c>
       <c r="E171" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="G171" s="4" t="s">
         <v>900</v>
       </c>
-      <c r="F171" s="4" t="s">
+      <c r="H171" s="4" t="s">
         <v>901</v>
       </c>
-      <c r="G171" s="4" t="s">
-        <v>902</v>
-      </c>
-      <c r="H171" s="4" t="s">
-        <v>903</v>
-      </c>
       <c r="I171" s="4" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="J171" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K171" s="4"/>
       <c r="L171" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M171" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
@@ -11189,35 +11186,35 @@
         <v>85</v>
       </c>
       <c r="C172" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D172" t="s">
         <v>14</v>
       </c>
       <c r="E172" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="G172" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="F172" s="4" t="s">
+      <c r="H172" s="4" t="s">
         <v>905</v>
       </c>
-      <c r="G172" s="4" t="s">
+      <c r="I172" s="4" t="s">
         <v>906</v>
-      </c>
-      <c r="H172" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="I172" s="4" t="s">
-        <v>908</v>
       </c>
       <c r="J172" s="4" t="s">
         <v>57</v>
       </c>
       <c r="K172" s="4"/>
       <c r="L172" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M172" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
@@ -11228,35 +11225,35 @@
         <v>85</v>
       </c>
       <c r="C173" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D173" t="s">
         <v>14</v>
       </c>
       <c r="E173" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G173" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="F173" s="4" t="s">
+      <c r="H173" s="4" t="s">
         <v>910</v>
       </c>
-      <c r="G173" s="4" t="s">
+      <c r="I173" s="4" t="s">
         <v>911</v>
-      </c>
-      <c r="H173" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="I173" s="4" t="s">
-        <v>913</v>
       </c>
       <c r="J173" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K173" s="4"/>
       <c r="L173" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M173" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
@@ -11267,35 +11264,35 @@
         <v>85</v>
       </c>
       <c r="C174" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D174" t="s">
         <v>14</v>
       </c>
       <c r="E174" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="G174" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="F174" s="4" t="s">
+      <c r="H174" s="4" t="s">
         <v>915</v>
       </c>
-      <c r="G174" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="H174" s="4" t="s">
-        <v>917</v>
-      </c>
       <c r="I174" s="4" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="J174" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K174" s="4"/>
       <c r="L174" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M174" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
@@ -11306,35 +11303,35 @@
         <v>34</v>
       </c>
       <c r="C175" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D175" t="s">
         <v>14</v>
       </c>
       <c r="E175" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="G175" s="4" t="s">
         <v>930</v>
       </c>
-      <c r="F175" s="4" t="s">
+      <c r="H175" s="4" t="s">
         <v>931</v>
       </c>
-      <c r="G175" s="4" t="s">
-        <v>932</v>
-      </c>
-      <c r="H175" s="4" t="s">
-        <v>933</v>
-      </c>
       <c r="I175" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="J175" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K175" s="4"/>
       <c r="L175" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M175" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
@@ -11345,35 +11342,35 @@
         <v>34</v>
       </c>
       <c r="C176" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D176" t="s">
         <v>14</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I176" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J176" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K176" s="4"/>
       <c r="L176" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M176" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
@@ -11384,22 +11381,22 @@
         <v>34</v>
       </c>
       <c r="C177" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D177" t="s">
         <v>14</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I177" s="4" t="s">
         <v>97</v>
@@ -11409,10 +11406,10 @@
       </c>
       <c r="K177" s="4"/>
       <c r="L177" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M177" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
@@ -11423,35 +11420,35 @@
         <v>34</v>
       </c>
       <c r="C178" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D178" t="s">
         <v>14</v>
       </c>
       <c r="E178" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="G178" s="4" t="s">
         <v>935</v>
       </c>
-      <c r="F178" s="4" t="s">
+      <c r="H178" s="4" t="s">
         <v>936</v>
       </c>
-      <c r="G178" s="4" t="s">
+      <c r="I178" s="4" t="s">
         <v>937</v>
-      </c>
-      <c r="H178" s="4" t="s">
-        <v>938</v>
-      </c>
-      <c r="I178" s="4" t="s">
-        <v>939</v>
       </c>
       <c r="J178" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K178" s="4"/>
       <c r="L178" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M178" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
@@ -11462,35 +11459,35 @@
         <v>34</v>
       </c>
       <c r="C179" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D179" t="s">
         <v>14</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F179" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="H179" s="4" t="s">
         <v>940</v>
       </c>
-      <c r="G179" s="4" t="s">
+      <c r="I179" s="4" t="s">
         <v>941</v>
-      </c>
-      <c r="H179" s="4" t="s">
-        <v>942</v>
-      </c>
-      <c r="I179" s="4" t="s">
-        <v>943</v>
       </c>
       <c r="J179" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K179" s="4"/>
       <c r="L179" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M179" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
@@ -11501,35 +11498,35 @@
         <v>34</v>
       </c>
       <c r="C180" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D180" t="s">
         <v>14</v>
       </c>
       <c r="E180" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="G180" s="4" t="s">
         <v>944</v>
       </c>
-      <c r="F180" s="4" t="s">
+      <c r="H180" s="4" t="s">
         <v>945</v>
       </c>
-      <c r="G180" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="H180" s="4" t="s">
-        <v>947</v>
-      </c>
       <c r="I180" s="4" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="J180" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K180" s="4"/>
       <c r="L180" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M180" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
@@ -11540,35 +11537,35 @@
         <v>34</v>
       </c>
       <c r="C181" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D181" t="s">
         <v>14</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F181" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="H181" s="4" t="s">
         <v>948</v>
       </c>
-      <c r="G181" s="4" t="s">
+      <c r="I181" s="4" t="s">
         <v>949</v>
-      </c>
-      <c r="H181" s="4" t="s">
-        <v>950</v>
-      </c>
-      <c r="I181" s="4" t="s">
-        <v>951</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K181" s="4"/>
       <c r="L181" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M181" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
@@ -11579,35 +11576,35 @@
         <v>34</v>
       </c>
       <c r="C182" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D182" t="s">
         <v>14</v>
       </c>
       <c r="E182" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="G182" s="4" t="s">
         <v>952</v>
       </c>
-      <c r="F182" s="4" t="s">
+      <c r="H182" s="4" t="s">
         <v>953</v>
       </c>
-      <c r="G182" s="4" t="s">
+      <c r="I182" s="4" t="s">
         <v>954</v>
-      </c>
-      <c r="H182" s="4" t="s">
-        <v>955</v>
-      </c>
-      <c r="I182" s="4" t="s">
-        <v>956</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K182" s="4"/>
       <c r="L182" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M182" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
@@ -11618,35 +11615,35 @@
         <v>34</v>
       </c>
       <c r="C183" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D183" t="s">
         <v>14</v>
       </c>
       <c r="E183" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G183" s="4" t="s">
         <v>957</v>
       </c>
-      <c r="F183" s="4" t="s">
+      <c r="H183" s="4" t="s">
         <v>958</v>
       </c>
-      <c r="G183" s="4" t="s">
-        <v>959</v>
-      </c>
-      <c r="H183" s="4" t="s">
-        <v>960</v>
-      </c>
       <c r="I183" s="4" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K183" s="4"/>
       <c r="L183" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M183" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
@@ -11657,35 +11654,35 @@
         <v>34</v>
       </c>
       <c r="C184" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D184" t="s">
         <v>14</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I184" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K184" s="4"/>
       <c r="L184" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M184" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
@@ -11696,22 +11693,22 @@
         <v>34</v>
       </c>
       <c r="C185" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D185" t="s">
         <v>14</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I185" s="4" t="s">
         <v>97</v>
@@ -11721,10 +11718,10 @@
       </c>
       <c r="K185" s="4"/>
       <c r="L185" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M185" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.25">
@@ -11735,35 +11732,35 @@
         <v>34</v>
       </c>
       <c r="C186" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D186" t="s">
         <v>14</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F186" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G186" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="G186" s="4" t="s">
+      <c r="H186" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="H186" s="4" t="s">
-        <v>311</v>
-      </c>
       <c r="I186" s="4" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>57</v>
       </c>
       <c r="K186" s="4"/>
       <c r="L186" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M186" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
@@ -11780,25 +11777,25 @@
         <v>14</v>
       </c>
       <c r="E187" t="s">
+        <v>970</v>
+      </c>
+      <c r="F187" t="s">
+        <v>971</v>
+      </c>
+      <c r="G187" t="s">
         <v>972</v>
       </c>
-      <c r="F187" t="s">
+      <c r="H187" t="s">
         <v>973</v>
       </c>
-      <c r="G187" t="s">
+      <c r="I187" t="s">
         <v>974</v>
-      </c>
-      <c r="H187" t="s">
-        <v>975</v>
-      </c>
-      <c r="I187" t="s">
-        <v>976</v>
       </c>
       <c r="J187" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L187" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M187" t="s">
         <v>44</v>
@@ -11818,25 +11815,25 @@
         <v>14</v>
       </c>
       <c r="E188" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="F188" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G188" t="s">
+        <v>322</v>
+      </c>
+      <c r="H188" t="s">
         <v>323</v>
       </c>
-      <c r="H188" t="s">
-        <v>324</v>
-      </c>
       <c r="I188" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L188" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M188" t="s">
         <v>44</v>
@@ -11850,34 +11847,34 @@
         <v>34</v>
       </c>
       <c r="C189" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D189" t="s">
         <v>14</v>
       </c>
       <c r="E189" t="s">
+        <v>976</v>
+      </c>
+      <c r="F189" t="s">
+        <v>977</v>
+      </c>
+      <c r="G189" t="s">
         <v>978</v>
       </c>
-      <c r="F189" t="s">
+      <c r="H189" t="s">
         <v>979</v>
       </c>
-      <c r="G189" t="s">
+      <c r="I189" t="s">
         <v>980</v>
-      </c>
-      <c r="H189" t="s">
-        <v>981</v>
-      </c>
-      <c r="I189" t="s">
-        <v>982</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>57</v>
       </c>
       <c r="L189" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M189" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
@@ -11888,34 +11885,34 @@
         <v>12</v>
       </c>
       <c r="C190" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D190" t="s">
         <v>14</v>
       </c>
       <c r="E190" t="s">
+        <v>982</v>
+      </c>
+      <c r="F190" t="s">
+        <v>983</v>
+      </c>
+      <c r="G190" t="s">
         <v>984</v>
       </c>
-      <c r="F190" t="s">
+      <c r="H190" t="s">
         <v>985</v>
       </c>
-      <c r="G190" t="s">
+      <c r="I190" t="s">
         <v>986</v>
-      </c>
-      <c r="H190" t="s">
-        <v>987</v>
-      </c>
-      <c r="I190" t="s">
-        <v>988</v>
       </c>
       <c r="J190" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L190" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M190" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
@@ -11926,34 +11923,34 @@
         <v>12</v>
       </c>
       <c r="C191" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D191" t="s">
         <v>14</v>
       </c>
       <c r="E191" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="F191" t="s">
+        <v>876</v>
+      </c>
+      <c r="G191" t="s">
+        <v>877</v>
+      </c>
+      <c r="H191" t="s">
         <v>878</v>
       </c>
-      <c r="G191" t="s">
-        <v>879</v>
-      </c>
-      <c r="H191" t="s">
-        <v>880</v>
-      </c>
       <c r="I191" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="J191" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L191" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M191" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
@@ -11964,34 +11961,34 @@
         <v>12</v>
       </c>
       <c r="C192" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D192" t="s">
         <v>14</v>
       </c>
       <c r="E192" t="s">
+        <v>989</v>
+      </c>
+      <c r="F192" t="s">
+        <v>990</v>
+      </c>
+      <c r="G192" t="s">
         <v>991</v>
       </c>
-      <c r="F192" t="s">
+      <c r="H192" t="s">
         <v>992</v>
       </c>
-      <c r="G192" t="s">
+      <c r="I192" t="s">
         <v>993</v>
-      </c>
-      <c r="H192" t="s">
-        <v>994</v>
-      </c>
-      <c r="I192" t="s">
-        <v>995</v>
       </c>
       <c r="J192" s="4" t="s">
         <v>57</v>
       </c>
       <c r="L192" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M192" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
@@ -12008,25 +12005,25 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="F193" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G193" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="H193" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I193" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L193" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M193" t="s">
         <v>110</v>
@@ -12046,25 +12043,25 @@
         <v>14</v>
       </c>
       <c r="E194" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="F194" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G194" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H194" t="s">
+        <v>448</v>
+      </c>
+      <c r="I194" t="s">
         <v>449</v>
-      </c>
-      <c r="I194" t="s">
-        <v>450</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L194" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M194" t="s">
         <v>110</v>
@@ -12084,25 +12081,25 @@
         <v>14</v>
       </c>
       <c r="E195" t="s">
+        <v>997</v>
+      </c>
+      <c r="F195" t="s">
+        <v>998</v>
+      </c>
+      <c r="G195" t="s">
+        <v>878</v>
+      </c>
+      <c r="H195" t="s">
         <v>999</v>
       </c>
-      <c r="F195" t="s">
+      <c r="I195" t="s">
         <v>1000</v>
-      </c>
-      <c r="G195" t="s">
-        <v>880</v>
-      </c>
-      <c r="H195" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I195" t="s">
-        <v>1002</v>
       </c>
       <c r="J195" s="4" t="s">
         <v>57</v>
       </c>
       <c r="L195" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M195" t="s">
         <v>110</v>
@@ -12116,34 +12113,34 @@
         <v>12</v>
       </c>
       <c r="C196" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D196" t="s">
         <v>14</v>
       </c>
       <c r="E196" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G196" t="s">
         <v>1003</v>
       </c>
-      <c r="F196" t="s">
+      <c r="H196" t="s">
         <v>1004</v>
       </c>
-      <c r="G196" t="s">
+      <c r="I196" t="s">
         <v>1005</v>
-      </c>
-      <c r="H196" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I196" t="s">
-        <v>1007</v>
       </c>
       <c r="J196" s="4" t="s">
         <v>57</v>
       </c>
       <c r="L196" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M196" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
@@ -12154,34 +12151,34 @@
         <v>12</v>
       </c>
       <c r="C197" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D197" t="s">
         <v>14</v>
       </c>
       <c r="E197" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G197" t="s">
         <v>1008</v>
       </c>
-      <c r="F197" t="s">
+      <c r="H197" t="s">
         <v>1009</v>
       </c>
-      <c r="G197" t="s">
+      <c r="I197" t="s">
         <v>1010</v>
-      </c>
-      <c r="H197" t="s">
-        <v>1011</v>
-      </c>
-      <c r="I197" t="s">
-        <v>1012</v>
       </c>
       <c r="J197" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L197" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M197" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
@@ -12192,34 +12189,34 @@
         <v>12</v>
       </c>
       <c r="C198" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D198" t="s">
         <v>14</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="F198" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G198" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H198" t="s">
         <v>1013</v>
       </c>
-      <c r="G198" t="s">
+      <c r="I198" t="s">
         <v>1014</v>
-      </c>
-      <c r="H198" t="s">
-        <v>1015</v>
-      </c>
-      <c r="I198" t="s">
-        <v>1016</v>
       </c>
       <c r="J198" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L198" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M198" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.25">
@@ -12230,34 +12227,34 @@
         <v>12</v>
       </c>
       <c r="C199" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D199" t="s">
         <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="F199" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G199" t="s">
+        <v>830</v>
+      </c>
+      <c r="H199" t="s">
         <v>832</v>
       </c>
-      <c r="H199" t="s">
-        <v>834</v>
-      </c>
       <c r="I199" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="J199" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L199" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M199" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.25">
@@ -12274,25 +12271,25 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G200" t="s">
         <v>1018</v>
       </c>
-      <c r="F200" t="s">
+      <c r="H200" t="s">
+        <v>177</v>
+      </c>
+      <c r="I200" t="s">
         <v>1019</v>
-      </c>
-      <c r="G200" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H200" t="s">
-        <v>178</v>
-      </c>
-      <c r="I200" t="s">
-        <v>1021</v>
       </c>
       <c r="J200" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L200" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M200" t="s">
         <v>45</v>
@@ -12306,34 +12303,34 @@
         <v>12</v>
       </c>
       <c r="C201" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D201" t="s">
         <v>14</v>
       </c>
       <c r="E201" t="s">
+        <v>843</v>
+      </c>
+      <c r="F201" t="s">
         <v>845</v>
       </c>
-      <c r="F201" t="s">
-        <v>847</v>
-      </c>
       <c r="G201" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H201" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I201" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J201" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L201" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.25">
@@ -12344,34 +12341,34 @@
         <v>85</v>
       </c>
       <c r="C202" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D202" t="s">
         <v>14</v>
       </c>
       <c r="E202" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G202" t="s">
         <v>1029</v>
       </c>
-      <c r="F202" t="s">
+      <c r="H202" t="s">
         <v>1030</v>
       </c>
-      <c r="G202" t="s">
+      <c r="I202" t="s">
         <v>1031</v>
-      </c>
-      <c r="H202" t="s">
-        <v>1032</v>
-      </c>
-      <c r="I202" t="s">
-        <v>1033</v>
       </c>
       <c r="J202" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L202" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M202" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.25">
@@ -12382,34 +12379,34 @@
         <v>85</v>
       </c>
       <c r="C203" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D203" t="s">
         <v>14</v>
       </c>
       <c r="E203" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G203" t="s">
         <v>1023</v>
       </c>
-      <c r="F203" t="s">
+      <c r="H203" t="s">
         <v>1024</v>
       </c>
-      <c r="G203" t="s">
-        <v>1025</v>
-      </c>
-      <c r="H203" t="s">
-        <v>1026</v>
-      </c>
       <c r="I203" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L203" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M203" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.25">
@@ -12420,34 +12417,34 @@
         <v>85</v>
       </c>
       <c r="C204" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D204" t="s">
         <v>14</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F204" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H204" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="G204" s="4" t="s">
+      <c r="I204" s="4" t="s">
         <v>1037</v>
-      </c>
-      <c r="H204" s="4" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I204" s="4" t="s">
-        <v>1039</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L204" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M204" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.25">
@@ -12458,34 +12455,34 @@
         <v>85</v>
       </c>
       <c r="C205" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D205" t="s">
         <v>14</v>
       </c>
       <c r="E205" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G205" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="F205" s="4" t="s">
+      <c r="H205" s="4" t="s">
         <v>1041</v>
       </c>
-      <c r="G205" s="4" t="s">
-        <v>1042</v>
-      </c>
-      <c r="H205" s="4" t="s">
-        <v>1043</v>
-      </c>
       <c r="I205" s="4" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="J205" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L205" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M205" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.25">
@@ -12496,34 +12493,34 @@
         <v>85</v>
       </c>
       <c r="C206" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D206" t="s">
         <v>14</v>
       </c>
       <c r="E206" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G206" s="4" t="s">
         <v>1044</v>
       </c>
-      <c r="F206" s="4" t="s">
+      <c r="H206" s="4" t="s">
         <v>1045</v>
       </c>
-      <c r="G206" s="4" t="s">
+      <c r="I206" s="4" t="s">
         <v>1046</v>
-      </c>
-      <c r="H206" s="4" t="s">
-        <v>1047</v>
-      </c>
-      <c r="I206" s="4" t="s">
-        <v>1048</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L206" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M206" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.25">
@@ -12534,34 +12531,34 @@
         <v>85</v>
       </c>
       <c r="C207" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D207" t="s">
         <v>14</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I207" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J207" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L207" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M207" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.25">
@@ -12572,22 +12569,22 @@
         <v>85</v>
       </c>
       <c r="C208" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D208" t="s">
         <v>14</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I208" s="4" t="s">
         <v>96</v>
@@ -12596,10 +12593,10 @@
         <v>57</v>
       </c>
       <c r="L208" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M208" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.25">
@@ -12610,34 +12607,34 @@
         <v>85</v>
       </c>
       <c r="C209" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D209" t="s">
         <v>14</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F209" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G209" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="H209" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="G209" s="4" t="s">
+      <c r="I209" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="H209" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="I209" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="J209" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L209" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M209" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.25">
@@ -12648,34 +12645,34 @@
         <v>85</v>
       </c>
       <c r="C210" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D210" t="s">
         <v>14</v>
       </c>
       <c r="E210" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G210" s="4" t="s">
         <v>1050</v>
       </c>
-      <c r="F210" s="4" t="s">
+      <c r="H210" s="4" t="s">
         <v>1051</v>
       </c>
-      <c r="G210" s="4" t="s">
+      <c r="I210" s="4" t="s">
         <v>1052</v>
-      </c>
-      <c r="H210" s="4" t="s">
-        <v>1053</v>
-      </c>
-      <c r="I210" s="4" t="s">
-        <v>1054</v>
       </c>
       <c r="J210" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L210" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M210" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.25">
@@ -12686,34 +12683,34 @@
         <v>85</v>
       </c>
       <c r="C211" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D211" t="s">
         <v>14</v>
       </c>
       <c r="E211" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G211" s="4" t="s">
         <v>1055</v>
       </c>
-      <c r="F211" s="4" t="s">
+      <c r="H211" s="4" t="s">
         <v>1056</v>
       </c>
-      <c r="G211" s="4" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H211" s="4" t="s">
-        <v>1058</v>
-      </c>
       <c r="I211" s="4" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="J211" s="4" t="s">
         <v>57</v>
       </c>
       <c r="L211" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M211" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.25">
@@ -12724,34 +12721,34 @@
         <v>34</v>
       </c>
       <c r="C212" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D212" t="s">
         <v>14</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="I212" s="4" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="J212" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L212" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M212" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.25">
@@ -12762,34 +12759,34 @@
         <v>34</v>
       </c>
       <c r="C213" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D213" t="s">
         <v>14</v>
       </c>
       <c r="E213" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G213" s="4" t="s">
         <v>1065</v>
       </c>
-      <c r="F213" s="4" t="s">
+      <c r="H213" s="4" t="s">
         <v>1066</v>
       </c>
-      <c r="G213" s="4" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H213" s="4" t="s">
-        <v>1068</v>
-      </c>
       <c r="I213" s="4" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="J213" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L213" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M213" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.25">
@@ -12800,34 +12797,34 @@
         <v>34</v>
       </c>
       <c r="C214" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D214" t="s">
         <v>14</v>
       </c>
       <c r="E214" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G214" s="4" t="s">
         <v>1069</v>
       </c>
-      <c r="F214" s="4" t="s">
+      <c r="H214" s="4" t="s">
         <v>1070</v>
       </c>
-      <c r="G214" s="4" t="s">
+      <c r="I214" s="4" t="s">
         <v>1071</v>
-      </c>
-      <c r="H214" s="4" t="s">
-        <v>1072</v>
-      </c>
-      <c r="I214" s="4" t="s">
-        <v>1073</v>
       </c>
       <c r="J214" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L214" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M214" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.25">
@@ -12838,34 +12835,34 @@
         <v>34</v>
       </c>
       <c r="C215" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D215" t="s">
         <v>14</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="I215" s="4" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="J215" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L215" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M215" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.25">
@@ -12876,34 +12873,34 @@
         <v>34</v>
       </c>
       <c r="C216" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D216" t="s">
         <v>14</v>
       </c>
       <c r="E216" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G216" s="4" t="s">
         <v>1076</v>
       </c>
-      <c r="F216" s="4" t="s">
+      <c r="H216" s="4" t="s">
         <v>1077</v>
       </c>
-      <c r="G216" s="4" t="s">
+      <c r="I216" s="4" t="s">
         <v>1078</v>
-      </c>
-      <c r="H216" s="4" t="s">
-        <v>1079</v>
-      </c>
-      <c r="I216" s="4" t="s">
-        <v>1080</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>57</v>
       </c>
       <c r="L216" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M216" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.25">
@@ -12914,34 +12911,34 @@
         <v>34</v>
       </c>
       <c r="C217" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D217" t="s">
         <v>14</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F217" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G217" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H217" s="4" t="s">
         <v>1081</v>
       </c>
-      <c r="G217" s="4" t="s">
+      <c r="I217" s="4" t="s">
         <v>1082</v>
-      </c>
-      <c r="H217" s="4" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I217" s="4" t="s">
-        <v>1084</v>
       </c>
       <c r="J217" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L217" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M217" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.25">
@@ -12952,34 +12949,34 @@
         <v>34</v>
       </c>
       <c r="C218" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D218" t="s">
         <v>14</v>
       </c>
       <c r="E218" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G218" s="4" t="s">
         <v>1085</v>
       </c>
-      <c r="F218" s="4" t="s">
+      <c r="H218" s="4" t="s">
         <v>1086</v>
       </c>
-      <c r="G218" s="4" t="s">
+      <c r="I218" s="4" t="s">
         <v>1087</v>
-      </c>
-      <c r="H218" s="4" t="s">
-        <v>1088</v>
-      </c>
-      <c r="I218" s="4" t="s">
-        <v>1089</v>
       </c>
       <c r="J218" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L218" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M218" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.25">
@@ -12990,37 +12987,37 @@
         <v>34</v>
       </c>
       <c r="C219" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D219" t="s">
         <v>14</v>
       </c>
       <c r="E219" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G219" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="F219" s="4" t="s">
+      <c r="H219" s="4" t="s">
         <v>1091</v>
       </c>
-      <c r="G219" s="4" t="s">
-        <v>1092</v>
-      </c>
-      <c r="H219" s="4" t="s">
-        <v>1093</v>
-      </c>
       <c r="I219" s="4" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="J219" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K219" s="5" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="L219" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M219" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.25">
@@ -13031,37 +13028,37 @@
         <v>34</v>
       </c>
       <c r="C220" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D220" t="s">
         <v>14</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="F220" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H220" s="4" t="s">
         <v>1094</v>
       </c>
-      <c r="G220" s="4" t="s">
+      <c r="I220" s="4" t="s">
         <v>1095</v>
-      </c>
-      <c r="H220" s="4" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I220" s="4" t="s">
-        <v>1097</v>
       </c>
       <c r="J220" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K220" s="5" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="L220" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M220" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.25">
@@ -13072,37 +13069,37 @@
         <v>34</v>
       </c>
       <c r="C221" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D221" t="s">
         <v>14</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H221" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I221" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="I221" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="J221" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K221" s="5" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="L221" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M221" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.25">
@@ -13113,37 +13110,37 @@
         <v>34</v>
       </c>
       <c r="C222" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D222" t="s">
         <v>14</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="I222" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="J222" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K222" s="5" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="L222" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M222" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.25">
@@ -13154,37 +13151,37 @@
         <v>34</v>
       </c>
       <c r="C223" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D223" t="s">
         <v>14</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F223" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G223" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H223" s="4" t="s">
         <v>1100</v>
       </c>
-      <c r="G223" s="4" t="s">
+      <c r="I223" s="4" t="s">
         <v>1101</v>
-      </c>
-      <c r="H223" s="4" t="s">
-        <v>1102</v>
-      </c>
-      <c r="I223" s="4" t="s">
-        <v>1103</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>57</v>
       </c>
       <c r="K223" s="5" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="L223" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M223" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.25">
@@ -13195,37 +13192,37 @@
         <v>34</v>
       </c>
       <c r="C224" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D224" t="s">
         <v>14</v>
       </c>
       <c r="E224" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G224" s="4" t="s">
         <v>1104</v>
       </c>
-      <c r="F224" s="4" t="s">
+      <c r="H224" s="4" t="s">
         <v>1105</v>
       </c>
-      <c r="G224" s="4" t="s">
+      <c r="I224" s="4" t="s">
         <v>1106</v>
-      </c>
-      <c r="H224" s="4" t="s">
-        <v>1107</v>
-      </c>
-      <c r="I224" s="4" t="s">
-        <v>1108</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K224" s="5" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="L224" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M224" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
@@ -13236,37 +13233,37 @@
         <v>34</v>
       </c>
       <c r="C225" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D225" t="s">
         <v>14</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="I225" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J225" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K225" s="5" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="L225" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M225" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
@@ -13277,37 +13274,37 @@
         <v>34</v>
       </c>
       <c r="C226" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D226" t="s">
         <v>14</v>
       </c>
       <c r="E226" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G226" s="4" t="s">
         <v>1109</v>
       </c>
-      <c r="F226" s="4" t="s">
+      <c r="H226" s="4" t="s">
         <v>1110</v>
       </c>
-      <c r="G226" s="4" t="s">
-        <v>1111</v>
-      </c>
-      <c r="H226" s="4" t="s">
-        <v>1112</v>
-      </c>
       <c r="I226" s="4" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K226" s="5" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="L226" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M226" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
@@ -13324,26 +13321,26 @@
         <v>14</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G227" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="H227" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="H227" s="4" t="s">
-        <v>324</v>
-      </c>
       <c r="I227" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J227" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K227" s="4"/>
       <c r="L227" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M227" t="s">
         <v>44</v>
@@ -13363,26 +13360,26 @@
         <v>14</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="F228" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H228" s="4" t="s">
         <v>1114</v>
       </c>
-      <c r="G228" s="4" t="s">
-        <v>1115</v>
-      </c>
-      <c r="H228" s="4" t="s">
-        <v>1116</v>
-      </c>
       <c r="I228" s="4" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="J228" s="4" t="s">
         <v>57</v>
       </c>
       <c r="K228" s="4"/>
       <c r="L228" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M228" t="s">
         <v>44</v>
@@ -13396,35 +13393,35 @@
         <v>34</v>
       </c>
       <c r="C229" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D229" t="s">
         <v>14</v>
       </c>
       <c r="E229" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G229" s="4" t="s">
         <v>1117</v>
       </c>
-      <c r="F229" s="4" t="s">
+      <c r="H229" s="4" t="s">
         <v>1118</v>
       </c>
-      <c r="G229" s="4" t="s">
+      <c r="I229" s="4" t="s">
         <v>1119</v>
-      </c>
-      <c r="H229" s="4" t="s">
-        <v>1120</v>
-      </c>
-      <c r="I229" s="4" t="s">
-        <v>1121</v>
       </c>
       <c r="J229" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K229" s="4"/>
       <c r="L229" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M229" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
@@ -13435,38 +13432,39 @@
         <v>34</v>
       </c>
       <c r="C230" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D230" t="s">
         <v>14</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G230" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="H230" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="I230" s="4" t="s">
         <v>980</v>
-      </c>
-      <c r="H230" s="4" t="s">
-        <v>979</v>
-      </c>
-      <c r="I230" s="4" t="s">
-        <v>982</v>
       </c>
       <c r="J230" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K230" s="4"/>
       <c r="L230" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="M230" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="C1:C230" xr:uid="{299ECF81-BBAD-4B94-AB20-5ECD9C9E2A6C}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/QUESTOES PROVA CRS.xlsx
+++ b/QUESTOES PROVA CRS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julião\Downloads\chobot-main (1)\chobot-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lizardo\Downloads\chobot-main\chobot-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189E6DBF-ED95-4D59-A36C-FFD348127F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD90F584-42C9-4F7B-B5E4-2BB0FE6BC7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1151">
   <si>
     <t>ID</t>
   </si>
@@ -4157,6 +4157,191 @@
     ◦ Fundamentação: Segundo o item 7.2.4.3 (alínea 'd'), os disparos realizados "para obter uma vantagem tática, para dar mais segurança ao reposicionamento da equipe" são definidos como Disparos Táticos (ex: cobertura, fogo e movimento), e não disparos de menor potencial ofensivo (elastômero), descritos na alínea 'c'.
 •  (Incorreta): A alternativa afirma que a intenção do policial será matar o agressor.
     ◦ Fundamentação: O item 7.2.4.1 (Objetivo do disparo) esclarece que "A intenção do policial militar não é matar o agressor... O policial militar não busca o resultado morte",. O objetivo é interromper a agressão e preservar a vida, razão pela qual a doutrina utiliza o termo "força potencialmente letal" e não "força letal".</t>
+  </si>
+  <si>
+    <t>Com base na Lei Federal nº 14.133/2021 (Nova Lei de Licitações), a alternativa que NÃO corresponde a uma modalidade de licitação é Registro de Preços.
+Abaixo, apresento a explicação detalhada com a fundamentação legal extraída diretamente do texto da norma fornecida:
+1. Quais são as Modalidades de Licitação?
+O Art. 28 da Lei nº 14.133/2021 define taxativamente quais são as modalidades de licitação admitidas. O Registro de Preços não consta neste rol.
+"Art. 28. São modalidades de licitação: I - pregão; II - concorrência; III - concurso; IV - leilão; V - diálogo competitivo."
+Portanto, Leilão, Pregão e Diálogo Competitivo (citados na sua questão) são modalidades oficiais.
+--------------------------------------------------------------------------------
+2. O que é o Registro de Preços?
+A Lei nº 14.133/2021 classifica o Sistema de Registro de Preços como um Procedimento Auxiliar, e não como uma modalidade de licitação.
+Isso está expressamente previsto no Art. 78:
+"Art. 78. São procedimentos auxiliares das licitações e das contratações regidas por esta Lei: I - credenciamento; II - pré-qualificação; III - procedimento de manifestação de interesse; IV - sistema de registro de preços; V - registro cadastral."
+Além disso, a definição legal no Art. 6º reforça que se trata de um conjunto de procedimentos para realizar contratações futuras, utilizando-se das modalidades pregão ou concorrência:
+"Art. 6º [...] XLV - sistema de registro de preços: conjunto de procedimentos para realização, mediante contratação direta ou licitação nas modalidades pregão ou concorrência, de registro formal de preços relativos a prestação de serviços, a obras e a aquisição e locação de bens para contratações futuras;"
+Conclusão
+Para responder à questão de prova:
+• Modalidades: Pregão, Concorrência, Concurso, Leilão, Diálogo Competitivo.
+• Procedimento Auxiliar: Registro de Preços (portanto, esta é a alternativa que NÃO é uma modalidade).</t>
+  </si>
+  <si>
+    <t>✅ Resposta Correta: Estudo Técnico Preliminar (ETP)
+O documento descrito no enunciado é, literalmente, a definição legal do ETP. Ele é a primeira etapa do planejamento e serve para identificar a necessidade e a melhor solução antes de se definir os detalhes da contratação.
+• Fundamentação Legal:
+    ◦ Art. 6º, XX: Define o ETP como documento constitutivo da primeira etapa do planejamento que caracteriza o interesse público envolvido e a sua melhor solução.
+    ◦ Art. 18, § 1º: Estabelece que o ETP deve evidenciar o problema a ser resolvido e a sua melhor solução, permitindo a avaliação da viabilidade técnica e econômica.
+    ◦ Art. 18, § 1º, V e VIII: Exige expressamente o levantamento de mercado com análise de alternativas e a justificativa para o parcelamento ou não da solução.
+--------------------------------------------------------------------------------
+❌ Correção das Alternativas Erradas
+A) Termo de Referência (TR)
+• Por que está errada: O TR é feito após o ETP. Enquanto o ETP define qual é a melhor solução, o TR define como essa solução será contratada e executada.
+• Fundamentação: Art. 6º, XXIII – O TR é o documento necessário para a contratação que contém a definição do objeto, fundamentação (baseada no ETP), modelo de execução e critérios de medição.
+C) Projeto Básico
+• Por que está errada: O Projeto Básico é um conjunto de elementos técnicos, geralmente focado em obras e serviços de engenharia, elaborado com base nas indicações do ETP. Ele visa definir e dimensionar a obra/serviço com precisão.
+• Fundamentação: Art. 6º, XXV – Define o projeto básico como o conjunto de elementos elaborado com base no ETP, assegurando a viabilidade técnica e o custo da obra.
+D) Edital de Licitação
+• Por que está errada: O Edital é o instrumento convocatório (a "regra do jogo" externa). Ele consolida todo o planejamento interno. O ETP, o TR ou o Projeto Básico são anexos ou subsídios para a elaboração do Edital, e não o edital em si.
+• Fundamentação: Art. 25 – O edital contém as regras de convocação, julgamento e habilitação, devendo ter como anexo o Termo de Referência ou Projeto Básico</t>
+  </si>
+  <si>
+    <t>De acordo com o Art. 6º da Lei nº 14.133/2021, a definição correta para cada modalidade apresentada nas alternativas é a seguinte:
+1. PREGÃO (Alternativa Correta):
+    ◦ Fundamentação: Art. 6º, inciso XLI.
+    ◦ Texto da Lei: "modalidade de licitação obrigatória para aquisição de bens e serviços comuns, cujo critério de julgamento poderá ser o de menor preço ou o de maior desconto".
+❌ Correção das Demais Alternativas
+As outras opções apresentadas na questão trocaram as definições das modalidades. Veja a correção:
+• Definição incorreta na questão: "O CONCURSO é a modalidade... para alienação de bens imóveis ou de bens móveis inservíveis..."
+    ◦ Correção: Essa definição refere-se ao LEILÃO (Art. 6º, inciso XL). O Concurso serve para escolha de trabalho técnico, científico ou artístico.
+• Definição incorreta na questão: "O DIÁLOGO COMPETITIVO é a modalidade... para escolha de trabalho técnico, científico ou artístico..."
+    ◦ Correção: Essa definição refere-se ao CONCURSO (Art. 6º, inciso XXXIX). O Diálogo Competitivo serve para inovações e soluções complexas.
+• Definição incorreta na questão: "O LEILÃO é uma modalidade... em que a Administração Pública realiza diálogos com licitantes previamente selecionados..."
+    ◦ Correção: Essa definição refere-se ao DIÁLOGO COMPETITIVO (Art. 6º, inciso XLII). O Leilão serve para alienação de bens.</t>
+  </si>
+  <si>
+    <t>A alternativa CORRETA é a que afirma:
+Não tiverem sua exequibilidade demonstrada, quando exigido pela Administração.
+📝 Explicação Detalhada e Fundamentação Legal
+De acordo com a Lei nº 14.133/2021 (Nova Lei de Licitações), a desclassificação das propostas é regida pelo Art. 59, que elenca taxativamente as hipóteses em que uma proposta deve ser retirada do certame.
+A alternativa correta é a reprodução literal do Inciso IV deste artigo:
+"Art. 59. Serão desclassificadas as propostas que: [...] IV - não tiverem sua exequibilidade demonstrada, quando exigido pela Administração;"
+Isso ocorre quando o preço ofertado é muito baixo (aparentemente inexequível) e a Administração solicita que o licitante prove que consegue executar o contrato por aquele valor. Se ele não conseguir provar, a proposta é desclassificada.
+--------------------------------------------------------------------------------
+❌ Correção das Alternativas Erradas
+Para facilitar seus estudos, veja por que as outras opções estão incorretas com base na lei:
+• Alternativa: "Obedecerem às especificações técnicas pormenorizadas no edital."
+    ◦ Correção: A desclassificação ocorre justamente pelo contrário. O Art. 59, II, determina que serão desclassificadas as propostas que NÃO obedecerem às especificações. Obedecer é um dever para a classificação.
+• Alternativa: "Apresentarem preços que permaneçam abaixo do orçamento estimado para a contratação."
+    ◦ Correção: Preços abaixo do orçamento são, via de regra, desejáveis (economicidade). A desclassificação ocorre se os preços permanecerem ACIMA do orçamento estimado (Art. 59, III) ou se forem inexequíveis.
+• Alternativa: "Apresentarem desconformidade com quaisquer outras exigências do edital, independentemente de serem insanáveis ou não."
+    ◦ Correção: O erro está na parte "independentemente de serem insanáveis". O Art. 59, V, afirma que a desclassificação por desconformidade ocorre "desde que insanável". Vícios sanáveis (formais) devem ser corrigidos, conforme o princípio do aproveitamento das propostas (Art. 12, III).</t>
+  </si>
+  <si>
+    <t>A alternativa CORRETA (a exceção) é a que afirma:
+Melhor relação custo-benefício.
+📝 Explicação Detalhada e Fundamentação Legal
+De acordo com a Lei Federal nº 14.133/2021, a modalidade concorrência possui critérios de julgamento taxativamente previstos no Art. 6º, inciso XXXVIII. A expressão "melhor relação custo-benefício" não figura no texto legal como uma nomenclatura de critério de julgamento autônomo para esta modalidade.
+Fundamentação no Texto da Lei:
+"Art. 6º [...] XXXVIII - concorrência: modalidade de licitação para contratação de bens e serviços especiais e de obras e serviços comuns e especiais de engenharia, cujo critério de julgamento poderá ser: a) menor preço; b) melhor técnica ou conteúdo artístico; c) técnica e preço; d) maior retorno econômico; e) maior desconto;",
+❌ Análise das Alternativas
+• Técnica e preço: É um critério expressamente previsto (alínea "c").
+• Melhor técnica ou conteúdo artístico: É um critério expressamente previsto (alínea "b").
+• Maior retorno econômico: É um critério expressamente previsto (alínea "d").
+• Melhor relação custo-benefício: NÃO consta no rol de critérios de julgamento do Art. 6º, XXXVIII, nem no rol geral do Art. 33 da Lei nº 14.133/2021. Embora o conceito de custo-benefício esteja intrínseco na análise de "técnica e preço", ele não é o nome legal do critério.</t>
+  </si>
+  <si>
+    <t>A alternativa CORRETA (a exceção à aplicação da lei) é a que afirma:
+Contratos que tenham por objeto operação de crédito, interno ou externo, e gestão de dívida pública.
+📝 Explicação Detalhada e Fundamentação Legal
+Para responder a esta questão, é necessário distinguir o Art. 2º (hipóteses de aplicação) do Art. 3º (exceções/não subordinação) da Lei nº 14.133/2021.
+Abaixo, apresento a correção e a fundamentação de cada alternativa:
+• Alternativa A (A Exceção - CORRETA):
+    ◦ Fundamentação: Art. 3º, inciso I.
+    ◦ Explicação: A norma é expressa ao determinar que NÃO se subordinam ao regime desta Lei os contratos de operação de crédito e gestão de dívida pública. Por isso, esta é a alternativa a ser marcada.
+• Alternativa B (Aplicação Correta da Lei):
+    ◦ Fundamentação: Art. 2º, incisos I, II e III.
+    ◦ Explicação: A lei aplica-se expressamente a alienação, concessão de direito real de uso, compra (inclusive por encomenda) e locação.
+• Alternativa C (Aplicação Correta da Lei):
+    ◦ Fundamentação: Art. 2º, incisos IV e V.
+    ◦ Explicação: A lei aplica-se expressamente a concessão e permissão de uso de bens públicos e à prestação de serviços (inclusive os técnicos especializados).
+• Alternativa D (Aplicação Correta da Lei):
+    ◦ Fundamentação: Art. 2º, incisos VI e VII.
+    ◦ Explicação: A lei aplica-se expressamente a obras e serviços de arquitetura e engenharia, bem como às contratações de tecnologia da informação e de comunicação (TIC).</t>
+  </si>
+  <si>
+    <t>A alternativa CORRETA é Superfaturamento.
+📝 Explicação Detalhada e Fundamentação Legal
+De acordo com a Lei nº 14.133/2021 (Nova Lei de Licitações), a definição apresentada no enunciado corresponde literalmente ao conceito de Superfaturamento, previsto no Art. 6º, inciso LVII.
+Fundamentação no Texto da Lei:
+"Art. 6º [...] LVII - superfaturamento: dano provocado ao patrimônio da Administração, caracterizado, entre outras situações, por: a) medição de quantidades superiores às efetivamente executadas ou fornecidas; b) deficiência na execução de obras e de serviços de engenharia que resulte em diminuição da sua qualidade, vida útil ou segurança; c) alterações no orçamento de obras e de serviços de engenharia que causem desequilíbrio econômico-financeiro do contrato em favor do contratado; d) outras alterações de cláusulas financeiras que gerem recebimentos contratuais antecipados, distorção do cronograma físico-financeiro, prorrogação injustificada do prazo contratual com custos adicionais para a Administração ou reajuste irregular de preços;"
+--------------------------------------------------------------------------------
+❌ Correção das Alternativas Incorretas
+Para garantir o entendimento completo, veja a definição legal dos outros termos citados nas alternativas, conforme o Art. 6º da mesma lei:
+• Sobrepreço: Refere-se ao preço orçado ou contratado acima do mercado, antes ou durante a contratação, mas não necessariamente envolve a execução de quantidades fraudulentas (medição falsa).
+• Reajustamento em sentido estrito: É um mecanismo de correção monetária, não um dano.
+• Repactuação: É um ajuste financeiro específico para contratos de mão de obra contínua.</t>
+  </si>
+  <si>
+    <t>A alternativa INCORRETA é a que afirma:
+A habilitação fiscal visa a demonstrar a aptidão econômica do licitante para cumprir as obrigações decorrentes do futuro contrato, devendo ser comprovada de forma objetiva, por coeficientes e índices econômicos previstos no edital, devidamente justificados no processo licitatório, e será restrita à apresentação, dentre outras, da certidão negativa de feitos sobre falência expedida pelo distribuidor da sede do licitante.
+📝 Explicação Detalhada e Fundamentação Legal
+Esta alternativa está incorreta porque ela atribui à Habilitação Fiscal a definição e os requisitos da Habilitação Econômico-Financeira.
+Veja a correção com base no texto da Lei nº 14.133/2021:
+• O Erro na Alternativa: O texto da questão descreve a "aptidão econômica" e exige "certidão negativa de falência". Isso é competência da habilitação econômico-financeira, não da fiscal.
+• Fundamentação Correta (Habilitação Econômico-Financeira): Conforme o Art. 69, "A habilitação econômico-financeira visa a demonstrar a aptidão econômica do licitante... e será restrita à apresentação... da certidão negativa de feitos sobre falência...".
+• Fundamentação da Habilitação Fiscal: A habilitação fiscal, social e trabalhista (prevista no Art. 68) foca na regularidade perante o Fisco (inscrição no CPF/CNPJ, regularidade com a Fazenda, Seguridade Social, FGTS e Justiça do Trabalho).
+--------------------------------------------------------------------------------
+✅ Análise das Demais Alternativas (Corretas)
+As outras opções reproduzem fielmente o texto da lei:
+• Sobre a Habilitação Jurídica: A alternativa reproduz literalmente o Art. 66: "A habilitação jurídica visa a demonstrar a capacidade de o licitante exercer direitos e assumir obrigações...".
+• Sobre as Fases da Habilitação: A alternativa está correta conforme o Art. 62: "A habilitação... dividindo-se em: I - jurídica; II - técnica; III - fiscal, social e trabalhista; IV - econômico-financeira.".
+• Sobre o Edital: A alternativa está correta conforme o Art. 65: "As condições de habilitação serão definidas no edital.".</t>
+  </si>
+  <si>
+    <t>A alternativa CORRETA (a que NÃO se refere a um procedimento auxiliar) é:
+Habilitação.
+📝 Explicação Detalhada e Fundamentação Legal
+Para responder a esta questão, é necessário diferenciar as Fases da Licitação dos Procedimentos Auxiliares.
+1. Por que Habilitação não é um procedimento auxiliar? De acordo com a Lei nº 14.133/2021, a Habilitação é uma fase do processo licitatório, e não um procedimento auxiliar.
+    ◦ Fundamentação: Art. 17, inciso V ("O processo de licitação observará as seguintes fases... V - de habilitação") e Art. 62 ("A habilitação é a fase da licitação em que se verifica o conjunto de informações e documentos...").,
+2. Quais são os Procedimentos Auxiliares? O Art. 78 da Lei nº 14.133/2021 define taxativamente quais são eles. Note que todas as outras alternativas da questão estão nesta lista:
+    ◦ I - Credenciamento;
+    ◦ II - Pré-qualificação;
+    ◦ III - Procedimento de manifestação de interesse;
+    ◦ IV - Sistema de registro de preços;
+    ◦ V - Registro cadastral.
+Portanto, Credenciamento, Sistema de registro de preços e Registro cadastral são procedimentos auxiliares, restando a Habilitação como a única opção que não se enquadra nesta categoria.</t>
+  </si>
+  <si>
+    <t>A alternativa CORRETA (a exceção) é a que afirma:
+Julgamento subjetivo.
+📝 Explicação Detalhada e Fundamentação Legal
+De acordo com a Lei nº 14.133/2021, o princípio que rege as licitações é exatamente o oposto: o Julgamento Objetivo. O julgamento subjetivo (baseado em critérios pessoais ou não mensuráveis do julgador) é vedado.
+O Art. 5º da referida lei elenca expressamente os princípios a serem observados. Veja a conferência de cada opção com o texto legal:
+• Interesse público: ✅ Previsto expressamente no Art. 5º.
+• Vinculação ao edital: ✅ Previsto expressamente no Art. 5º.
+• Segurança jurídica: ✅ Previsto expressamente no Art. 5º.
+• Julgamento subjetivo: ❌ NÃO existe. O texto legal determina o princípio do Julgamento Objetivo.
+Citação da Norma:
+"Art. 5º Na aplicação desta Lei, serão observados os princípios da legalidade, da impessoalidade, da moralidade, da publicidade, da eficiência, do interesse público, da probidade administrativa, da igualdade, do planejamento, da transparência, da eficácia, da segregação de funções, da motivação, da vinculação ao edital, do julgamento objetivo, da segurança jurídica [...]"</t>
+  </si>
+  <si>
+    <t>Apenas as assertivas I e III são verdadeiras.
+📝 Análise Detalhada e Fundamentação Legal
+I. VERDADEIRA O conceito apresentado é a reprodução exata da definição legal de pregão.
+Fundamentação: Art. 6º, inciso XLI da Lei nº 14.133/2021: "pregão: modalidade de licitação obrigatória para aquisição de bens e serviços comuns, cujo critério de julgamento poderá ser o de menor preço ou o de maior desconto;".
+II. FALSA O Sistema de Registro de Preços (SRP) NÃO é uma modalidade de licitação, mas sim um procedimento auxiliar. As modalidades são taxativas (pregão, concorrência, concurso, leilão e diálogo competitivo).
+Fundamentação: O Art. 28 lista as modalidades, enquanto o Art. 78, inciso IV, classifica o sistema de registro de preços expressamente como um procedimento auxiliar.
+III. VERDADEIRA A lei mantém a figura do pregoeiro especificamente para esta modalidade.
+Fundamentação: Art. 8º, § 5º da Lei nº 14.133/2021: "Em licitação na modalidade pregão, o agente responsável pela condução do certame será designado pregoeiro.".</t>
+  </si>
+  <si>
+    <t>A alternativa CORRETA (aquela que NÃO corresponde a um critério de julgamento) é:
+Diálogo competitivo.
+📝 Explicação Detalhada e Fundamentação Legal
+Para responder corretamente, é necessário distinguir Critérios de Julgamento (como a proposta vencedora é escolhida) de Modalidades de Licitação (o rito procedimental).
+1. Por que "Diálogo Competitivo" é a resposta? O Diálogo Competitivo é classificado pela Lei nº 14.133/2021 como uma Modalidade de Licitação, e não como um critério de julgamento.
+    ◦ Fundamentação: Art. 28, inciso V.
+2. Quais são os Critérios de Julgamento? O Art. 33 da Lei nº 14.133/2021 lista taxativamente os critérios. Note que todas as outras alternativas da questão estão nesta lista:
+    ◦ I - Menor preço;
+    ◦ II - Maior desconto;
+    ◦ III - Melhor técnica ou conteúdo artístico;
+    ◦ IV - Técnica e preço;
+    ◦ V - Maior lance (no caso de leilão);
+    ◦ VI - Maior retorno econômico.
+Portanto, Menor preço, Maior desconto e Técnica e preço são critérios de julgamento, enquanto Diálogo Competitivo é a modalidade.</t>
   </si>
 </sst>
 </file>
@@ -4230,7 +4415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4239,8 +4424,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4657,6 +4840,9 @@
       <c r="J2" t="s">
         <v>20</v>
       </c>
+      <c r="K2" s="3" t="s">
+        <v>1139</v>
+      </c>
       <c r="L2" t="s">
         <v>21</v>
       </c>
@@ -4695,6 +4881,9 @@
       <c r="J3" t="s">
         <v>27</v>
       </c>
+      <c r="K3" s="3" t="s">
+        <v>1140</v>
+      </c>
       <c r="L3" t="s">
         <v>21</v>
       </c>
@@ -4815,6 +5004,9 @@
       <c r="J6" t="s">
         <v>57</v>
       </c>
+      <c r="K6" s="3" t="s">
+        <v>1141</v>
+      </c>
       <c r="L6" t="s">
         <v>51</v>
       </c>
@@ -4853,6 +5045,9 @@
       <c r="J7" t="s">
         <v>20</v>
       </c>
+      <c r="K7" s="3" t="s">
+        <v>1142</v>
+      </c>
       <c r="L7" t="s">
         <v>51</v>
       </c>
@@ -5663,6 +5858,9 @@
       <c r="J28" t="s">
         <v>57</v>
       </c>
+      <c r="K28" s="3" t="s">
+        <v>1143</v>
+      </c>
       <c r="L28" t="s">
         <v>103</v>
       </c>
@@ -5701,6 +5899,9 @@
       <c r="J29" t="s">
         <v>33</v>
       </c>
+      <c r="K29" s="3" t="s">
+        <v>1144</v>
+      </c>
       <c r="L29" t="s">
         <v>103</v>
       </c>
@@ -8260,7 +8461,7 @@
       <c r="D95" t="s">
         <v>14</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" t="s">
         <v>609</v>
       </c>
       <c r="F95" t="s">
@@ -8526,7 +8727,7 @@
       <c r="D102" t="s">
         <v>14</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" t="s">
         <v>637</v>
       </c>
       <c r="F102" t="s">
@@ -8868,7 +9069,7 @@
       <c r="D111" t="s">
         <v>14</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E111" t="s">
         <v>703</v>
       </c>
       <c r="F111" t="s">
@@ -8924,6 +9125,9 @@
       <c r="J112" t="s">
         <v>33</v>
       </c>
+      <c r="K112" s="3" t="s">
+        <v>1145</v>
+      </c>
       <c r="L112" t="s">
         <v>514</v>
       </c>
@@ -8962,6 +9166,9 @@
       <c r="J113" t="s">
         <v>57</v>
       </c>
+      <c r="K113" s="3" t="s">
+        <v>1146</v>
+      </c>
       <c r="L113" t="s">
         <v>514</v>
       </c>
@@ -8982,7 +9189,7 @@
       <c r="D114" t="s">
         <v>14</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E114" t="s">
         <v>704</v>
       </c>
       <c r="F114" t="s">
@@ -9134,7 +9341,7 @@
       <c r="D118" t="s">
         <v>14</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="E118" t="s">
         <v>705</v>
       </c>
       <c r="F118" t="s">
@@ -9248,7 +9455,7 @@
       <c r="D121" t="s">
         <v>14</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E121" t="s">
         <v>722</v>
       </c>
       <c r="F121" t="s">
@@ -9286,7 +9493,7 @@
       <c r="D122" t="s">
         <v>14</v>
       </c>
-      <c r="E122" s="3" t="s">
+      <c r="E122" t="s">
         <v>727</v>
       </c>
       <c r="F122" t="s">
@@ -9324,7 +9531,7 @@
       <c r="D123" t="s">
         <v>14</v>
       </c>
-      <c r="E123" s="3" t="s">
+      <c r="E123" t="s">
         <v>739</v>
       </c>
       <c r="F123" t="s">
@@ -9362,7 +9569,7 @@
       <c r="D124" t="s">
         <v>14</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="E124" t="s">
         <v>740</v>
       </c>
       <c r="F124" t="s">
@@ -9400,7 +9607,7 @@
       <c r="D125" t="s">
         <v>14</v>
       </c>
-      <c r="E125" s="3" t="s">
+      <c r="E125" t="s">
         <v>741</v>
       </c>
       <c r="F125" t="s">
@@ -9438,7 +9645,7 @@
       <c r="D126" t="s">
         <v>14</v>
       </c>
-      <c r="E126" s="3" t="s">
+      <c r="E126" t="s">
         <v>742</v>
       </c>
       <c r="F126" t="s">
@@ -9476,7 +9683,7 @@
       <c r="D127" t="s">
         <v>14</v>
       </c>
-      <c r="E127" s="3" t="s">
+      <c r="E127" t="s">
         <v>744</v>
       </c>
       <c r="F127" t="s">
@@ -9514,7 +9721,7 @@
       <c r="D128" t="s">
         <v>14</v>
       </c>
-      <c r="E128" s="3" t="s">
+      <c r="E128" t="s">
         <v>745</v>
       </c>
       <c r="F128" t="s">
@@ -9590,7 +9797,7 @@
       <c r="D130" t="s">
         <v>14</v>
       </c>
-      <c r="E130" s="3" t="s">
+      <c r="E130" t="s">
         <v>755</v>
       </c>
       <c r="F130" t="s">
@@ -9742,7 +9949,7 @@
       <c r="D134" t="s">
         <v>14</v>
       </c>
-      <c r="E134" s="3" t="s">
+      <c r="E134" t="s">
         <v>771</v>
       </c>
       <c r="F134" t="s">
@@ -9780,7 +9987,7 @@
       <c r="D135" t="s">
         <v>14</v>
       </c>
-      <c r="E135" s="3" t="s">
+      <c r="E135" t="s">
         <v>817</v>
       </c>
       <c r="F135" t="s">
@@ -9818,7 +10025,7 @@
       <c r="D136" t="s">
         <v>14</v>
       </c>
-      <c r="E136" s="3" t="s">
+      <c r="E136" t="s">
         <v>819</v>
       </c>
       <c r="F136" t="s">
@@ -9856,7 +10063,7 @@
       <c r="D137" t="s">
         <v>14</v>
       </c>
-      <c r="E137" s="3" t="s">
+      <c r="E137" t="s">
         <v>820</v>
       </c>
       <c r="F137" t="s">
@@ -9894,7 +10101,7 @@
       <c r="D138" t="s">
         <v>14</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E138" t="s">
         <v>821</v>
       </c>
       <c r="F138" t="s">
@@ -9970,7 +10177,7 @@
       <c r="D140" t="s">
         <v>14</v>
       </c>
-      <c r="E140" s="3" t="s">
+      <c r="E140" t="s">
         <v>822</v>
       </c>
       <c r="F140" t="s">
@@ -10046,7 +10253,7 @@
       <c r="D142" t="s">
         <v>14</v>
       </c>
-      <c r="E142" s="3" t="s">
+      <c r="E142" t="s">
         <v>823</v>
       </c>
       <c r="F142" t="s">
@@ -10084,7 +10291,7 @@
       <c r="D143" t="s">
         <v>14</v>
       </c>
-      <c r="E143" s="3" t="s">
+      <c r="E143" t="s">
         <v>824</v>
       </c>
       <c r="F143" t="s">
@@ -10122,7 +10329,7 @@
       <c r="D144" t="s">
         <v>14</v>
       </c>
-      <c r="E144" s="3" t="s">
+      <c r="E144" t="s">
         <v>825</v>
       </c>
       <c r="F144" t="s">
@@ -10160,7 +10367,7 @@
       <c r="D145" t="s">
         <v>14</v>
       </c>
-      <c r="E145" s="3" t="s">
+      <c r="E145" t="s">
         <v>826</v>
       </c>
       <c r="F145" t="s">
@@ -10198,7 +10405,7 @@
       <c r="D146" t="s">
         <v>14</v>
       </c>
-      <c r="E146" s="3" t="s">
+      <c r="E146" t="s">
         <v>803</v>
       </c>
       <c r="F146" t="s">
@@ -10236,7 +10443,7 @@
       <c r="D147" t="s">
         <v>14</v>
       </c>
-      <c r="E147" s="3" t="s">
+      <c r="E147" t="s">
         <v>808</v>
       </c>
       <c r="F147" t="s">
@@ -10253,6 +10460,9 @@
       </c>
       <c r="J147" t="s">
         <v>33</v>
+      </c>
+      <c r="K147" s="3" t="s">
+        <v>1147</v>
       </c>
       <c r="L147" t="s">
         <v>721</v>
@@ -10274,7 +10484,7 @@
       <c r="D148" t="s">
         <v>14</v>
       </c>
-      <c r="E148" s="3" t="s">
+      <c r="E148" t="s">
         <v>813</v>
       </c>
       <c r="F148" t="s">
@@ -10406,6 +10616,9 @@
       <c r="J151" t="s">
         <v>57</v>
       </c>
+      <c r="K151" s="3" t="s">
+        <v>1148</v>
+      </c>
       <c r="L151" t="s">
         <v>891</v>
       </c>
@@ -10426,7 +10639,7 @@
       <c r="D152" t="s">
         <v>14</v>
       </c>
-      <c r="E152" s="3" t="s">
+      <c r="E152" t="s">
         <v>892</v>
       </c>
       <c r="F152" t="s">
@@ -10443,6 +10656,9 @@
       </c>
       <c r="J152" t="s">
         <v>57</v>
+      </c>
+      <c r="K152" s="3" t="s">
+        <v>1149</v>
       </c>
       <c r="L152" t="s">
         <v>891</v>
@@ -10882,7 +11098,7 @@
       <c r="D164" t="s">
         <v>14</v>
       </c>
-      <c r="E164" s="3" t="s">
+      <c r="E164" t="s">
         <v>893</v>
       </c>
       <c r="F164" t="s">
@@ -10920,7 +11136,7 @@
       <c r="D165" t="s">
         <v>14</v>
       </c>
-      <c r="E165" s="3" t="s">
+      <c r="E165" t="s">
         <v>896</v>
       </c>
       <c r="F165" t="s">
@@ -10958,7 +11174,7 @@
       <c r="D166" t="s">
         <v>14</v>
       </c>
-      <c r="E166" s="3" t="s">
+      <c r="E166" t="s">
         <v>894</v>
       </c>
       <c r="F166" t="s">
@@ -10996,25 +11212,24 @@
       <c r="D167" t="s">
         <v>14</v>
       </c>
-      <c r="E167" s="5" t="s">
+      <c r="E167" t="s">
         <v>916</v>
       </c>
-      <c r="F167" s="4" t="s">
+      <c r="F167" t="s">
         <v>225</v>
       </c>
-      <c r="G167" s="4" t="s">
+      <c r="G167" t="s">
         <v>223</v>
       </c>
-      <c r="H167" s="4" t="s">
+      <c r="H167" t="s">
         <v>221</v>
       </c>
-      <c r="I167" s="4" t="s">
+      <c r="I167" t="s">
         <v>222</v>
       </c>
-      <c r="J167" s="4" t="s">
+      <c r="J167" t="s">
         <v>33</v>
       </c>
-      <c r="K167" s="4"/>
       <c r="L167" t="s">
         <v>891</v>
       </c>
@@ -11035,25 +11250,24 @@
       <c r="D168" t="s">
         <v>14</v>
       </c>
-      <c r="E168" s="5" t="s">
+      <c r="E168" t="s">
         <v>917</v>
       </c>
-      <c r="F168" s="4" t="s">
+      <c r="F168" t="s">
         <v>235</v>
       </c>
-      <c r="G168" s="4" t="s">
+      <c r="G168" t="s">
         <v>233</v>
       </c>
-      <c r="H168" s="4" t="s">
+      <c r="H168" t="s">
         <v>238</v>
       </c>
-      <c r="I168" s="4" t="s">
+      <c r="I168" t="s">
         <v>234</v>
       </c>
-      <c r="J168" s="4" t="s">
+      <c r="J168" t="s">
         <v>20</v>
       </c>
-      <c r="K168" s="4"/>
       <c r="L168" t="s">
         <v>891</v>
       </c>
@@ -11074,25 +11288,24 @@
       <c r="D169" t="s">
         <v>14</v>
       </c>
-      <c r="E169" s="5" t="s">
+      <c r="E169" t="s">
         <v>918</v>
       </c>
-      <c r="F169" s="4" t="s">
+      <c r="F169" t="s">
         <v>234</v>
       </c>
-      <c r="G169" s="4" t="s">
+      <c r="G169" t="s">
         <v>444</v>
       </c>
-      <c r="H169" s="4" t="s">
+      <c r="H169" t="s">
         <v>897</v>
       </c>
-      <c r="I169" s="4" t="s">
+      <c r="I169" t="s">
         <v>97</v>
       </c>
-      <c r="J169" s="4" t="s">
+      <c r="J169" t="s">
         <v>33</v>
       </c>
-      <c r="K169" s="4"/>
       <c r="L169" t="s">
         <v>891</v>
       </c>
@@ -11113,25 +11326,24 @@
       <c r="D170" t="s">
         <v>14</v>
       </c>
-      <c r="E170" s="5" t="s">
+      <c r="E170" t="s">
         <v>919</v>
       </c>
-      <c r="F170" s="4" t="s">
+      <c r="F170" t="s">
         <v>237</v>
       </c>
-      <c r="G170" s="4" t="s">
+      <c r="G170" t="s">
         <v>233</v>
       </c>
-      <c r="H170" s="4" t="s">
+      <c r="H170" t="s">
         <v>234</v>
       </c>
-      <c r="I170" s="4" t="s">
+      <c r="I170" t="s">
         <v>235</v>
       </c>
-      <c r="J170" s="4" t="s">
+      <c r="J170" t="s">
         <v>27</v>
       </c>
-      <c r="K170" s="4"/>
       <c r="L170" t="s">
         <v>891</v>
       </c>
@@ -11152,25 +11364,24 @@
       <c r="D171" t="s">
         <v>14</v>
       </c>
-      <c r="E171" s="4" t="s">
+      <c r="E171" t="s">
         <v>898</v>
       </c>
-      <c r="F171" s="4" t="s">
+      <c r="F171" t="s">
         <v>899</v>
       </c>
-      <c r="G171" s="4" t="s">
+      <c r="G171" t="s">
         <v>900</v>
       </c>
-      <c r="H171" s="4" t="s">
+      <c r="H171" t="s">
         <v>901</v>
       </c>
-      <c r="I171" s="4" t="s">
+      <c r="I171" t="s">
         <v>920</v>
       </c>
-      <c r="J171" s="4" t="s">
+      <c r="J171" t="s">
         <v>33</v>
       </c>
-      <c r="K171" s="4"/>
       <c r="L171" t="s">
         <v>891</v>
       </c>
@@ -11191,25 +11402,24 @@
       <c r="D172" t="s">
         <v>14</v>
       </c>
-      <c r="E172" s="4" t="s">
+      <c r="E172" t="s">
         <v>902</v>
       </c>
-      <c r="F172" s="4" t="s">
+      <c r="F172" t="s">
         <v>903</v>
       </c>
-      <c r="G172" s="4" t="s">
+      <c r="G172" t="s">
         <v>904</v>
       </c>
-      <c r="H172" s="4" t="s">
+      <c r="H172" t="s">
         <v>905</v>
       </c>
-      <c r="I172" s="4" t="s">
+      <c r="I172" t="s">
         <v>906</v>
       </c>
-      <c r="J172" s="4" t="s">
+      <c r="J172" t="s">
         <v>57</v>
       </c>
-      <c r="K172" s="4"/>
       <c r="L172" t="s">
         <v>891</v>
       </c>
@@ -11230,25 +11440,24 @@
       <c r="D173" t="s">
         <v>14</v>
       </c>
-      <c r="E173" s="4" t="s">
+      <c r="E173" t="s">
         <v>907</v>
       </c>
-      <c r="F173" s="4" t="s">
+      <c r="F173" t="s">
         <v>908</v>
       </c>
-      <c r="G173" s="4" t="s">
+      <c r="G173" t="s">
         <v>909</v>
       </c>
-      <c r="H173" s="4" t="s">
+      <c r="H173" t="s">
         <v>910</v>
       </c>
-      <c r="I173" s="4" t="s">
+      <c r="I173" t="s">
         <v>911</v>
       </c>
-      <c r="J173" s="4" t="s">
+      <c r="J173" t="s">
         <v>27</v>
       </c>
-      <c r="K173" s="4"/>
       <c r="L173" t="s">
         <v>891</v>
       </c>
@@ -11269,25 +11478,24 @@
       <c r="D174" t="s">
         <v>14</v>
       </c>
-      <c r="E174" s="4" t="s">
+      <c r="E174" t="s">
         <v>912</v>
       </c>
-      <c r="F174" s="4" t="s">
+      <c r="F174" t="s">
         <v>913</v>
       </c>
-      <c r="G174" s="4" t="s">
+      <c r="G174" t="s">
         <v>914</v>
       </c>
-      <c r="H174" s="4" t="s">
+      <c r="H174" t="s">
         <v>915</v>
       </c>
-      <c r="I174" s="4" t="s">
+      <c r="I174" t="s">
         <v>921</v>
       </c>
-      <c r="J174" s="4" t="s">
+      <c r="J174" t="s">
         <v>33</v>
       </c>
-      <c r="K174" s="4"/>
       <c r="L174" t="s">
         <v>891</v>
       </c>
@@ -11308,25 +11516,24 @@
       <c r="D175" t="s">
         <v>14</v>
       </c>
-      <c r="E175" s="4" t="s">
+      <c r="E175" t="s">
         <v>928</v>
       </c>
-      <c r="F175" s="4" t="s">
+      <c r="F175" t="s">
         <v>929</v>
       </c>
-      <c r="G175" s="4" t="s">
+      <c r="G175" t="s">
         <v>930</v>
       </c>
-      <c r="H175" s="4" t="s">
+      <c r="H175" t="s">
         <v>931</v>
       </c>
-      <c r="I175" s="4" t="s">
+      <c r="I175" t="s">
         <v>963</v>
       </c>
-      <c r="J175" s="4" t="s">
+      <c r="J175" t="s">
         <v>20</v>
       </c>
-      <c r="K175" s="4"/>
       <c r="L175" t="s">
         <v>891</v>
       </c>
@@ -11347,25 +11554,24 @@
       <c r="D176" t="s">
         <v>14</v>
       </c>
-      <c r="E176" s="5" t="s">
+      <c r="E176" t="s">
         <v>966</v>
       </c>
-      <c r="F176" s="4" t="s">
+      <c r="F176" t="s">
         <v>932</v>
       </c>
-      <c r="G176" s="4" t="s">
+      <c r="G176" t="s">
         <v>221</v>
       </c>
-      <c r="H176" s="4" t="s">
+      <c r="H176" t="s">
         <v>202</v>
       </c>
-      <c r="I176" s="4" t="s">
+      <c r="I176" t="s">
         <v>201</v>
       </c>
-      <c r="J176" s="4" t="s">
+      <c r="J176" t="s">
         <v>27</v>
       </c>
-      <c r="K176" s="4"/>
       <c r="L176" t="s">
         <v>891</v>
       </c>
@@ -11386,25 +11592,24 @@
       <c r="D177" t="s">
         <v>14</v>
       </c>
-      <c r="E177" s="5" t="s">
+      <c r="E177" t="s">
         <v>967</v>
       </c>
-      <c r="F177" s="4" t="s">
+      <c r="F177" t="s">
         <v>238</v>
       </c>
-      <c r="G177" s="4" t="s">
+      <c r="G177" t="s">
         <v>237</v>
       </c>
-      <c r="H177" s="4" t="s">
+      <c r="H177" t="s">
         <v>234</v>
       </c>
-      <c r="I177" s="4" t="s">
+      <c r="I177" t="s">
         <v>97</v>
       </c>
-      <c r="J177" s="4" t="s">
+      <c r="J177" t="s">
         <v>57</v>
       </c>
-      <c r="K177" s="4"/>
       <c r="L177" t="s">
         <v>891</v>
       </c>
@@ -11425,25 +11630,24 @@
       <c r="D178" t="s">
         <v>14</v>
       </c>
-      <c r="E178" s="4" t="s">
+      <c r="E178" t="s">
         <v>933</v>
       </c>
-      <c r="F178" s="4" t="s">
+      <c r="F178" t="s">
         <v>934</v>
       </c>
-      <c r="G178" s="4" t="s">
+      <c r="G178" t="s">
         <v>935</v>
       </c>
-      <c r="H178" s="4" t="s">
+      <c r="H178" t="s">
         <v>936</v>
       </c>
-      <c r="I178" s="4" t="s">
+      <c r="I178" t="s">
         <v>937</v>
       </c>
-      <c r="J178" s="4" t="s">
+      <c r="J178" t="s">
         <v>20</v>
       </c>
-      <c r="K178" s="4"/>
       <c r="L178" t="s">
         <v>891</v>
       </c>
@@ -11464,25 +11668,24 @@
       <c r="D179" t="s">
         <v>14</v>
       </c>
-      <c r="E179" s="4" t="s">
+      <c r="E179" t="s">
         <v>287</v>
       </c>
-      <c r="F179" s="4" t="s">
+      <c r="F179" t="s">
         <v>938</v>
       </c>
-      <c r="G179" s="4" t="s">
+      <c r="G179" t="s">
         <v>939</v>
       </c>
-      <c r="H179" s="4" t="s">
+      <c r="H179" t="s">
         <v>940</v>
       </c>
-      <c r="I179" s="4" t="s">
+      <c r="I179" t="s">
         <v>941</v>
       </c>
-      <c r="J179" s="4" t="s">
+      <c r="J179" t="s">
         <v>33</v>
       </c>
-      <c r="K179" s="4"/>
       <c r="L179" t="s">
         <v>891</v>
       </c>
@@ -11503,25 +11706,24 @@
       <c r="D180" t="s">
         <v>14</v>
       </c>
-      <c r="E180" s="4" t="s">
+      <c r="E180" t="s">
         <v>942</v>
       </c>
-      <c r="F180" s="4" t="s">
+      <c r="F180" t="s">
         <v>943</v>
       </c>
-      <c r="G180" s="4" t="s">
+      <c r="G180" t="s">
         <v>944</v>
       </c>
-      <c r="H180" s="4" t="s">
+      <c r="H180" t="s">
         <v>945</v>
       </c>
-      <c r="I180" s="4" t="s">
+      <c r="I180" t="s">
         <v>964</v>
       </c>
-      <c r="J180" s="4" t="s">
+      <c r="J180" t="s">
         <v>33</v>
       </c>
-      <c r="K180" s="4"/>
       <c r="L180" t="s">
         <v>891</v>
       </c>
@@ -11542,25 +11744,24 @@
       <c r="D181" t="s">
         <v>14</v>
       </c>
-      <c r="E181" s="4" t="s">
+      <c r="E181" t="s">
         <v>282</v>
       </c>
-      <c r="F181" s="4" t="s">
+      <c r="F181" t="s">
         <v>946</v>
       </c>
-      <c r="G181" s="4" t="s">
+      <c r="G181" t="s">
         <v>947</v>
       </c>
-      <c r="H181" s="4" t="s">
+      <c r="H181" t="s">
         <v>948</v>
       </c>
-      <c r="I181" s="4" t="s">
+      <c r="I181" t="s">
         <v>949</v>
       </c>
-      <c r="J181" s="4" t="s">
+      <c r="J181" t="s">
         <v>20</v>
       </c>
-      <c r="K181" s="4"/>
       <c r="L181" t="s">
         <v>891</v>
       </c>
@@ -11581,25 +11782,24 @@
       <c r="D182" t="s">
         <v>14</v>
       </c>
-      <c r="E182" s="4" t="s">
+      <c r="E182" t="s">
         <v>950</v>
       </c>
-      <c r="F182" s="4" t="s">
+      <c r="F182" t="s">
         <v>951</v>
       </c>
-      <c r="G182" s="4" t="s">
+      <c r="G182" t="s">
         <v>952</v>
       </c>
-      <c r="H182" s="4" t="s">
+      <c r="H182" t="s">
         <v>953</v>
       </c>
-      <c r="I182" s="4" t="s">
+      <c r="I182" t="s">
         <v>954</v>
       </c>
-      <c r="J182" s="4" t="s">
+      <c r="J182" t="s">
         <v>27</v>
       </c>
-      <c r="K182" s="4"/>
       <c r="L182" t="s">
         <v>891</v>
       </c>
@@ -11620,25 +11820,24 @@
       <c r="D183" t="s">
         <v>14</v>
       </c>
-      <c r="E183" s="4" t="s">
+      <c r="E183" t="s">
         <v>955</v>
       </c>
-      <c r="F183" s="4" t="s">
+      <c r="F183" t="s">
         <v>956</v>
       </c>
-      <c r="G183" s="4" t="s">
+      <c r="G183" t="s">
         <v>957</v>
       </c>
-      <c r="H183" s="4" t="s">
+      <c r="H183" t="s">
         <v>958</v>
       </c>
-      <c r="I183" s="4" t="s">
+      <c r="I183" t="s">
         <v>965</v>
       </c>
-      <c r="J183" s="4" t="s">
+      <c r="J183" t="s">
         <v>33</v>
       </c>
-      <c r="K183" s="4"/>
       <c r="L183" t="s">
         <v>891</v>
       </c>
@@ -11659,25 +11858,24 @@
       <c r="D184" t="s">
         <v>14</v>
       </c>
-      <c r="E184" s="5" t="s">
+      <c r="E184" t="s">
         <v>968</v>
       </c>
-      <c r="F184" s="4" t="s">
+      <c r="F184" t="s">
         <v>959</v>
       </c>
-      <c r="G184" s="4" t="s">
+      <c r="G184" t="s">
         <v>444</v>
       </c>
-      <c r="H184" s="4" t="s">
+      <c r="H184" t="s">
         <v>233</v>
       </c>
-      <c r="I184" s="4" t="s">
+      <c r="I184" t="s">
         <v>232</v>
       </c>
-      <c r="J184" s="4" t="s">
+      <c r="J184" t="s">
         <v>27</v>
       </c>
-      <c r="K184" s="4"/>
       <c r="L184" t="s">
         <v>891</v>
       </c>
@@ -11698,25 +11896,24 @@
       <c r="D185" t="s">
         <v>14</v>
       </c>
-      <c r="E185" s="5" t="s">
+      <c r="E185" t="s">
         <v>969</v>
       </c>
-      <c r="F185" s="4" t="s">
+      <c r="F185" t="s">
         <v>960</v>
       </c>
-      <c r="G185" s="4" t="s">
+      <c r="G185" t="s">
         <v>232</v>
       </c>
-      <c r="H185" s="4" t="s">
+      <c r="H185" t="s">
         <v>444</v>
       </c>
-      <c r="I185" s="4" t="s">
+      <c r="I185" t="s">
         <v>97</v>
       </c>
-      <c r="J185" s="4" t="s">
+      <c r="J185" t="s">
         <v>57</v>
       </c>
-      <c r="K185" s="4"/>
       <c r="L185" t="s">
         <v>891</v>
       </c>
@@ -11737,25 +11934,24 @@
       <c r="D186" t="s">
         <v>14</v>
       </c>
-      <c r="E186" s="4" t="s">
+      <c r="E186" t="s">
         <v>961</v>
       </c>
-      <c r="F186" s="4" t="s">
+      <c r="F186" t="s">
         <v>308</v>
       </c>
-      <c r="G186" s="4" t="s">
+      <c r="G186" t="s">
         <v>309</v>
       </c>
-      <c r="H186" s="4" t="s">
+      <c r="H186" t="s">
         <v>310</v>
       </c>
-      <c r="I186" s="4" t="s">
+      <c r="I186" t="s">
         <v>962</v>
       </c>
-      <c r="J186" s="4" t="s">
+      <c r="J186" t="s">
         <v>57</v>
       </c>
-      <c r="K186" s="4"/>
       <c r="L186" t="s">
         <v>891</v>
       </c>
@@ -11791,7 +11987,7 @@
       <c r="I187" t="s">
         <v>974</v>
       </c>
-      <c r="J187" s="4" t="s">
+      <c r="J187" t="s">
         <v>27</v>
       </c>
       <c r="L187" t="s">
@@ -11829,7 +12025,7 @@
       <c r="I188" t="s">
         <v>981</v>
       </c>
-      <c r="J188" s="4" t="s">
+      <c r="J188" t="s">
         <v>33</v>
       </c>
       <c r="L188" t="s">
@@ -11867,7 +12063,7 @@
       <c r="I189" t="s">
         <v>980</v>
       </c>
-      <c r="J189" s="4" t="s">
+      <c r="J189" t="s">
         <v>57</v>
       </c>
       <c r="L189" t="s">
@@ -11905,7 +12101,7 @@
       <c r="I190" t="s">
         <v>986</v>
       </c>
-      <c r="J190" s="4" t="s">
+      <c r="J190" t="s">
         <v>33</v>
       </c>
       <c r="L190" t="s">
@@ -11943,7 +12139,7 @@
       <c r="I191" t="s">
         <v>988</v>
       </c>
-      <c r="J191" s="4" t="s">
+      <c r="J191" t="s">
         <v>33</v>
       </c>
       <c r="L191" t="s">
@@ -11981,7 +12177,7 @@
       <c r="I192" t="s">
         <v>993</v>
       </c>
-      <c r="J192" s="4" t="s">
+      <c r="J192" t="s">
         <v>57</v>
       </c>
       <c r="L192" t="s">
@@ -12019,7 +12215,7 @@
       <c r="I193" t="s">
         <v>1025</v>
       </c>
-      <c r="J193" s="4" t="s">
+      <c r="J193" t="s">
         <v>27</v>
       </c>
       <c r="L193" t="s">
@@ -12057,7 +12253,7 @@
       <c r="I194" t="s">
         <v>449</v>
       </c>
-      <c r="J194" s="4" t="s">
+      <c r="J194" t="s">
         <v>20</v>
       </c>
       <c r="L194" t="s">
@@ -12095,7 +12291,7 @@
       <c r="I195" t="s">
         <v>1000</v>
       </c>
-      <c r="J195" s="4" t="s">
+      <c r="J195" t="s">
         <v>57</v>
       </c>
       <c r="L195" t="s">
@@ -12133,7 +12329,7 @@
       <c r="I196" t="s">
         <v>1005</v>
       </c>
-      <c r="J196" s="4" t="s">
+      <c r="J196" t="s">
         <v>57</v>
       </c>
       <c r="L196" t="s">
@@ -12171,7 +12367,7 @@
       <c r="I197" t="s">
         <v>1010</v>
       </c>
-      <c r="J197" s="4" t="s">
+      <c r="J197" t="s">
         <v>20</v>
       </c>
       <c r="L197" t="s">
@@ -12194,7 +12390,7 @@
       <c r="D198" t="s">
         <v>14</v>
       </c>
-      <c r="E198" s="3" t="s">
+      <c r="E198" t="s">
         <v>1026</v>
       </c>
       <c r="F198" t="s">
@@ -12209,7 +12405,7 @@
       <c r="I198" t="s">
         <v>1014</v>
       </c>
-      <c r="J198" s="4" t="s">
+      <c r="J198" t="s">
         <v>27</v>
       </c>
       <c r="L198" t="s">
@@ -12247,7 +12443,7 @@
       <c r="I199" t="s">
         <v>831</v>
       </c>
-      <c r="J199" s="4" t="s">
+      <c r="J199" t="s">
         <v>20</v>
       </c>
       <c r="L199" t="s">
@@ -12285,8 +12481,11 @@
       <c r="I200" t="s">
         <v>1019</v>
       </c>
-      <c r="J200" s="4" t="s">
+      <c r="J200" t="s">
         <v>27</v>
+      </c>
+      <c r="K200" s="3" t="s">
+        <v>1150</v>
       </c>
       <c r="L200" t="s">
         <v>1033</v>
@@ -12323,7 +12522,7 @@
       <c r="I201" t="s">
         <v>1020</v>
       </c>
-      <c r="J201" s="4" t="s">
+      <c r="J201" t="s">
         <v>20</v>
       </c>
       <c r="L201" t="s">
@@ -12346,7 +12545,7 @@
       <c r="D202" t="s">
         <v>14</v>
       </c>
-      <c r="E202" s="3" t="s">
+      <c r="E202" t="s">
         <v>1027</v>
       </c>
       <c r="F202" t="s">
@@ -12361,7 +12560,7 @@
       <c r="I202" t="s">
         <v>1031</v>
       </c>
-      <c r="J202" s="4" t="s">
+      <c r="J202" t="s">
         <v>33</v>
       </c>
       <c r="L202" t="s">
@@ -12399,7 +12598,7 @@
       <c r="I203" t="s">
         <v>1032</v>
       </c>
-      <c r="J203" s="4" t="s">
+      <c r="J203" t="s">
         <v>27</v>
       </c>
       <c r="L203" t="s">
@@ -12422,22 +12621,22 @@
       <c r="D204" t="s">
         <v>14</v>
       </c>
-      <c r="E204" s="5" t="s">
+      <c r="E204" t="s">
         <v>1057</v>
       </c>
-      <c r="F204" s="4" t="s">
+      <c r="F204" t="s">
         <v>1034</v>
       </c>
-      <c r="G204" s="4" t="s">
+      <c r="G204" t="s">
         <v>1035</v>
       </c>
-      <c r="H204" s="4" t="s">
+      <c r="H204" t="s">
         <v>1036</v>
       </c>
-      <c r="I204" s="4" t="s">
+      <c r="I204" t="s">
         <v>1037</v>
       </c>
-      <c r="J204" s="4" t="s">
+      <c r="J204" t="s">
         <v>20</v>
       </c>
       <c r="L204" t="s">
@@ -12460,22 +12659,22 @@
       <c r="D205" t="s">
         <v>14</v>
       </c>
-      <c r="E205" s="4" t="s">
+      <c r="E205" t="s">
         <v>1038</v>
       </c>
-      <c r="F205" s="4" t="s">
+      <c r="F205" t="s">
         <v>1039</v>
       </c>
-      <c r="G205" s="4" t="s">
+      <c r="G205" t="s">
         <v>1040</v>
       </c>
-      <c r="H205" s="4" t="s">
+      <c r="H205" t="s">
         <v>1041</v>
       </c>
-      <c r="I205" s="4" t="s">
+      <c r="I205" t="s">
         <v>1058</v>
       </c>
-      <c r="J205" s="4" t="s">
+      <c r="J205" t="s">
         <v>27</v>
       </c>
       <c r="L205" t="s">
@@ -12498,22 +12697,22 @@
       <c r="D206" t="s">
         <v>14</v>
       </c>
-      <c r="E206" s="4" t="s">
+      <c r="E206" t="s">
         <v>1042</v>
       </c>
-      <c r="F206" s="4" t="s">
+      <c r="F206" t="s">
         <v>1043</v>
       </c>
-      <c r="G206" s="4" t="s">
+      <c r="G206" t="s">
         <v>1044</v>
       </c>
-      <c r="H206" s="4" t="s">
+      <c r="H206" t="s">
         <v>1045</v>
       </c>
-      <c r="I206" s="4" t="s">
+      <c r="I206" t="s">
         <v>1046</v>
       </c>
-      <c r="J206" s="4" t="s">
+      <c r="J206" t="s">
         <v>27</v>
       </c>
       <c r="L206" t="s">
@@ -12536,22 +12735,22 @@
       <c r="D207" t="s">
         <v>14</v>
       </c>
-      <c r="E207" s="5" t="s">
+      <c r="E207" t="s">
         <v>1060</v>
       </c>
-      <c r="F207" s="4" t="s">
+      <c r="F207" t="s">
         <v>202</v>
       </c>
-      <c r="G207" s="4" t="s">
+      <c r="G207" t="s">
         <v>225</v>
       </c>
-      <c r="H207" s="4" t="s">
+      <c r="H207" t="s">
         <v>224</v>
       </c>
-      <c r="I207" s="4" t="s">
+      <c r="I207" t="s">
         <v>223</v>
       </c>
-      <c r="J207" s="4" t="s">
+      <c r="J207" t="s">
         <v>20</v>
       </c>
       <c r="L207" t="s">
@@ -12574,22 +12773,22 @@
       <c r="D208" t="s">
         <v>14</v>
       </c>
-      <c r="E208" s="5" t="s">
+      <c r="E208" t="s">
         <v>1061</v>
       </c>
-      <c r="F208" s="4" t="s">
+      <c r="F208" t="s">
         <v>1047</v>
       </c>
-      <c r="G208" s="4" t="s">
+      <c r="G208" t="s">
         <v>237</v>
       </c>
-      <c r="H208" s="4" t="s">
+      <c r="H208" t="s">
         <v>236</v>
       </c>
-      <c r="I208" s="4" t="s">
+      <c r="I208" t="s">
         <v>96</v>
       </c>
-      <c r="J208" s="4" t="s">
+      <c r="J208" t="s">
         <v>57</v>
       </c>
       <c r="L208" t="s">
@@ -12612,22 +12811,22 @@
       <c r="D209" t="s">
         <v>14</v>
       </c>
-      <c r="E209" s="5" t="s">
+      <c r="E209" t="s">
         <v>1062</v>
       </c>
-      <c r="F209" s="4" t="s">
+      <c r="F209" t="s">
         <v>235</v>
       </c>
-      <c r="G209" s="4" t="s">
+      <c r="G209" t="s">
         <v>237</v>
       </c>
-      <c r="H209" s="4" t="s">
+      <c r="H209" t="s">
         <v>236</v>
       </c>
-      <c r="I209" s="4" t="s">
+      <c r="I209" t="s">
         <v>238</v>
       </c>
-      <c r="J209" s="4" t="s">
+      <c r="J209" t="s">
         <v>20</v>
       </c>
       <c r="L209" t="s">
@@ -12650,22 +12849,22 @@
       <c r="D210" t="s">
         <v>14</v>
       </c>
-      <c r="E210" s="4" t="s">
+      <c r="E210" t="s">
         <v>1048</v>
       </c>
-      <c r="F210" s="4" t="s">
+      <c r="F210" t="s">
         <v>1049</v>
       </c>
-      <c r="G210" s="4" t="s">
+      <c r="G210" t="s">
         <v>1050</v>
       </c>
-      <c r="H210" s="4" t="s">
+      <c r="H210" t="s">
         <v>1051</v>
       </c>
-      <c r="I210" s="4" t="s">
+      <c r="I210" t="s">
         <v>1052</v>
       </c>
-      <c r="J210" s="4" t="s">
+      <c r="J210" t="s">
         <v>33</v>
       </c>
       <c r="L210" t="s">
@@ -12688,22 +12887,22 @@
       <c r="D211" t="s">
         <v>14</v>
       </c>
-      <c r="E211" s="4" t="s">
+      <c r="E211" t="s">
         <v>1053</v>
       </c>
-      <c r="F211" s="4" t="s">
+      <c r="F211" t="s">
         <v>1054</v>
       </c>
-      <c r="G211" s="4" t="s">
+      <c r="G211" t="s">
         <v>1055</v>
       </c>
-      <c r="H211" s="4" t="s">
+      <c r="H211" t="s">
         <v>1056</v>
       </c>
-      <c r="I211" s="4" t="s">
+      <c r="I211" t="s">
         <v>1059</v>
       </c>
-      <c r="J211" s="4" t="s">
+      <c r="J211" t="s">
         <v>57</v>
       </c>
       <c r="L211" t="s">
@@ -12726,22 +12925,22 @@
       <c r="D212" t="s">
         <v>14</v>
       </c>
-      <c r="E212" s="5" t="s">
+      <c r="E212" t="s">
         <v>1121</v>
       </c>
-      <c r="F212" s="4" t="s">
+      <c r="F212" t="s">
         <v>235</v>
       </c>
-      <c r="G212" s="4" t="s">
+      <c r="G212" t="s">
         <v>232</v>
       </c>
-      <c r="H212" s="4" t="s">
+      <c r="H212" t="s">
         <v>959</v>
       </c>
-      <c r="I212" s="4" t="s">
+      <c r="I212" t="s">
         <v>1047</v>
       </c>
-      <c r="J212" s="4" t="s">
+      <c r="J212" t="s">
         <v>20</v>
       </c>
       <c r="L212" t="s">
@@ -12764,22 +12963,22 @@
       <c r="D213" t="s">
         <v>14</v>
       </c>
-      <c r="E213" s="4" t="s">
+      <c r="E213" t="s">
         <v>1063</v>
       </c>
-      <c r="F213" s="4" t="s">
+      <c r="F213" t="s">
         <v>1064</v>
       </c>
-      <c r="G213" s="4" t="s">
+      <c r="G213" t="s">
         <v>1065</v>
       </c>
-      <c r="H213" s="4" t="s">
+      <c r="H213" t="s">
         <v>1066</v>
       </c>
-      <c r="I213" s="4" t="s">
+      <c r="I213" t="s">
         <v>1130</v>
       </c>
-      <c r="J213" s="4" t="s">
+      <c r="J213" t="s">
         <v>20</v>
       </c>
       <c r="L213" t="s">
@@ -12802,22 +13001,22 @@
       <c r="D214" t="s">
         <v>14</v>
       </c>
-      <c r="E214" s="4" t="s">
+      <c r="E214" t="s">
         <v>1067</v>
       </c>
-      <c r="F214" s="4" t="s">
+      <c r="F214" t="s">
         <v>1068</v>
       </c>
-      <c r="G214" s="4" t="s">
+      <c r="G214" t="s">
         <v>1069</v>
       </c>
-      <c r="H214" s="4" t="s">
+      <c r="H214" t="s">
         <v>1070</v>
       </c>
-      <c r="I214" s="4" t="s">
+      <c r="I214" t="s">
         <v>1071</v>
       </c>
-      <c r="J214" s="4" t="s">
+      <c r="J214" t="s">
         <v>27</v>
       </c>
       <c r="L214" t="s">
@@ -12840,22 +13039,22 @@
       <c r="D215" t="s">
         <v>14</v>
       </c>
-      <c r="E215" s="5" t="s">
+      <c r="E215" t="s">
         <v>1122</v>
       </c>
-      <c r="F215" s="4" t="s">
+      <c r="F215" t="s">
         <v>1072</v>
       </c>
-      <c r="G215" s="4" t="s">
+      <c r="G215" t="s">
         <v>355</v>
       </c>
-      <c r="H215" s="4" t="s">
+      <c r="H215" t="s">
         <v>1073</v>
       </c>
-      <c r="I215" s="4" t="s">
+      <c r="I215" t="s">
         <v>1129</v>
       </c>
-      <c r="J215" s="4" t="s">
+      <c r="J215" t="s">
         <v>33</v>
       </c>
       <c r="L215" t="s">
@@ -12878,22 +13077,22 @@
       <c r="D216" t="s">
         <v>14</v>
       </c>
-      <c r="E216" s="4" t="s">
+      <c r="E216" t="s">
         <v>1074</v>
       </c>
-      <c r="F216" s="4" t="s">
+      <c r="F216" t="s">
         <v>1075</v>
       </c>
-      <c r="G216" s="4" t="s">
+      <c r="G216" t="s">
         <v>1076</v>
       </c>
-      <c r="H216" s="4" t="s">
+      <c r="H216" t="s">
         <v>1077</v>
       </c>
-      <c r="I216" s="4" t="s">
+      <c r="I216" t="s">
         <v>1078</v>
       </c>
-      <c r="J216" s="4" t="s">
+      <c r="J216" t="s">
         <v>57</v>
       </c>
       <c r="L216" t="s">
@@ -12916,22 +13115,22 @@
       <c r="D217" t="s">
         <v>14</v>
       </c>
-      <c r="E217" s="4" t="s">
+      <c r="E217" t="s">
         <v>287</v>
       </c>
-      <c r="F217" s="4" t="s">
+      <c r="F217" t="s">
         <v>1079</v>
       </c>
-      <c r="G217" s="4" t="s">
+      <c r="G217" t="s">
         <v>1080</v>
       </c>
-      <c r="H217" s="4" t="s">
+      <c r="H217" t="s">
         <v>1081</v>
       </c>
-      <c r="I217" s="4" t="s">
+      <c r="I217" t="s">
         <v>1082</v>
       </c>
-      <c r="J217" s="4" t="s">
+      <c r="J217" t="s">
         <v>33</v>
       </c>
       <c r="L217" t="s">
@@ -12954,22 +13153,22 @@
       <c r="D218" t="s">
         <v>14</v>
       </c>
-      <c r="E218" s="4" t="s">
+      <c r="E218" t="s">
         <v>1083</v>
       </c>
-      <c r="F218" s="4" t="s">
+      <c r="F218" t="s">
         <v>1084</v>
       </c>
-      <c r="G218" s="4" t="s">
+      <c r="G218" t="s">
         <v>1085</v>
       </c>
-      <c r="H218" s="4" t="s">
+      <c r="H218" t="s">
         <v>1086</v>
       </c>
-      <c r="I218" s="4" t="s">
+      <c r="I218" t="s">
         <v>1087</v>
       </c>
-      <c r="J218" s="4" t="s">
+      <c r="J218" t="s">
         <v>33</v>
       </c>
       <c r="L218" t="s">
@@ -12992,25 +13191,25 @@
       <c r="D219" t="s">
         <v>14</v>
       </c>
-      <c r="E219" s="4" t="s">
+      <c r="E219" t="s">
         <v>1088</v>
       </c>
-      <c r="F219" s="4" t="s">
+      <c r="F219" t="s">
         <v>1089</v>
       </c>
-      <c r="G219" s="4" t="s">
+      <c r="G219" t="s">
         <v>1090</v>
       </c>
-      <c r="H219" s="4" t="s">
+      <c r="H219" t="s">
         <v>1091</v>
       </c>
-      <c r="I219" s="4" t="s">
+      <c r="I219" t="s">
         <v>1128</v>
       </c>
-      <c r="J219" s="4" t="s">
+      <c r="J219" t="s">
         <v>33</v>
       </c>
-      <c r="K219" s="5" t="s">
+      <c r="K219" t="s">
         <v>1135</v>
       </c>
       <c r="L219" t="s">
@@ -13033,25 +13232,25 @@
       <c r="D220" t="s">
         <v>14</v>
       </c>
-      <c r="E220" s="4" t="s">
+      <c r="E220" t="s">
         <v>1088</v>
       </c>
-      <c r="F220" s="4" t="s">
+      <c r="F220" t="s">
         <v>1092</v>
       </c>
-      <c r="G220" s="4" t="s">
+      <c r="G220" t="s">
         <v>1093</v>
       </c>
-      <c r="H220" s="4" t="s">
+      <c r="H220" t="s">
         <v>1094</v>
       </c>
-      <c r="I220" s="4" t="s">
+      <c r="I220" t="s">
         <v>1095</v>
       </c>
-      <c r="J220" s="4" t="s">
+      <c r="J220" t="s">
         <v>27</v>
       </c>
-      <c r="K220" s="5" t="s">
+      <c r="K220" t="s">
         <v>1136</v>
       </c>
       <c r="L220" t="s">
@@ -13074,25 +13273,25 @@
       <c r="D221" t="s">
         <v>14</v>
       </c>
-      <c r="E221" s="5" t="s">
+      <c r="E221" t="s">
         <v>1123</v>
       </c>
-      <c r="F221" s="4" t="s">
+      <c r="F221" t="s">
         <v>238</v>
       </c>
-      <c r="G221" s="4" t="s">
+      <c r="G221" t="s">
         <v>237</v>
       </c>
-      <c r="H221" s="4" t="s">
+      <c r="H221" t="s">
         <v>234</v>
       </c>
-      <c r="I221" s="4" t="s">
+      <c r="I221" t="s">
         <v>235</v>
       </c>
-      <c r="J221" s="4" t="s">
+      <c r="J221" t="s">
         <v>27</v>
       </c>
-      <c r="K221" s="5" t="s">
+      <c r="K221" t="s">
         <v>1137</v>
       </c>
       <c r="L221" t="s">
@@ -13115,25 +13314,25 @@
       <c r="D222" t="s">
         <v>14</v>
       </c>
-      <c r="E222" s="4" t="s">
+      <c r="E222" t="s">
         <v>1096</v>
       </c>
-      <c r="F222" s="4" t="s">
+      <c r="F222" t="s">
         <v>1097</v>
       </c>
-      <c r="G222" s="4" t="s">
+      <c r="G222" t="s">
         <v>930</v>
       </c>
-      <c r="H222" s="4" t="s">
+      <c r="H222" t="s">
         <v>931</v>
       </c>
-      <c r="I222" s="4" t="s">
+      <c r="I222" t="s">
         <v>963</v>
       </c>
-      <c r="J222" s="4" t="s">
+      <c r="J222" t="s">
         <v>20</v>
       </c>
-      <c r="K222" s="5" t="s">
+      <c r="K222" t="s">
         <v>1138</v>
       </c>
       <c r="L222" t="s">
@@ -13156,25 +13355,25 @@
       <c r="D223" t="s">
         <v>14</v>
       </c>
-      <c r="E223" s="4" t="s">
+      <c r="E223" t="s">
         <v>302</v>
       </c>
-      <c r="F223" s="4" t="s">
+      <c r="F223" t="s">
         <v>1098</v>
       </c>
-      <c r="G223" s="4" t="s">
+      <c r="G223" t="s">
         <v>1099</v>
       </c>
-      <c r="H223" s="4" t="s">
+      <c r="H223" t="s">
         <v>1100</v>
       </c>
-      <c r="I223" s="4" t="s">
+      <c r="I223" t="s">
         <v>1101</v>
       </c>
-      <c r="J223" s="4" t="s">
+      <c r="J223" t="s">
         <v>57</v>
       </c>
-      <c r="K223" s="5" t="s">
+      <c r="K223" t="s">
         <v>1131</v>
       </c>
       <c r="L223" t="s">
@@ -13197,25 +13396,25 @@
       <c r="D224" t="s">
         <v>14</v>
       </c>
-      <c r="E224" s="4" t="s">
+      <c r="E224" t="s">
         <v>1102</v>
       </c>
-      <c r="F224" s="4" t="s">
+      <c r="F224" t="s">
         <v>1103</v>
       </c>
-      <c r="G224" s="4" t="s">
+      <c r="G224" t="s">
         <v>1104</v>
       </c>
-      <c r="H224" s="4" t="s">
+      <c r="H224" t="s">
         <v>1105</v>
       </c>
-      <c r="I224" s="4" t="s">
+      <c r="I224" t="s">
         <v>1106</v>
       </c>
-      <c r="J224" s="4" t="s">
+      <c r="J224" t="s">
         <v>33</v>
       </c>
-      <c r="K224" s="5" t="s">
+      <c r="K224" t="s">
         <v>1132</v>
       </c>
       <c r="L224" t="s">
@@ -13238,25 +13437,25 @@
       <c r="D225" t="s">
         <v>14</v>
       </c>
-      <c r="E225" s="5" t="s">
+      <c r="E225" t="s">
         <v>1124</v>
       </c>
-      <c r="F225" s="4" t="s">
+      <c r="F225" t="s">
         <v>235</v>
       </c>
-      <c r="G225" s="4" t="s">
+      <c r="G225" t="s">
         <v>232</v>
       </c>
-      <c r="H225" s="4" t="s">
+      <c r="H225" t="s">
         <v>959</v>
       </c>
-      <c r="I225" s="4" t="s">
+      <c r="I225" t="s">
         <v>445</v>
       </c>
-      <c r="J225" s="4" t="s">
+      <c r="J225" t="s">
         <v>20</v>
       </c>
-      <c r="K225" s="5" t="s">
+      <c r="K225" t="s">
         <v>1133</v>
       </c>
       <c r="L225" t="s">
@@ -13279,25 +13478,25 @@
       <c r="D226" t="s">
         <v>14</v>
       </c>
-      <c r="E226" s="4" t="s">
+      <c r="E226" t="s">
         <v>1107</v>
       </c>
-      <c r="F226" s="4" t="s">
+      <c r="F226" t="s">
         <v>1108</v>
       </c>
-      <c r="G226" s="4" t="s">
+      <c r="G226" t="s">
         <v>1109</v>
       </c>
-      <c r="H226" s="4" t="s">
+      <c r="H226" t="s">
         <v>1110</v>
       </c>
-      <c r="I226" s="4" t="s">
+      <c r="I226" t="s">
         <v>1127</v>
       </c>
-      <c r="J226" s="4" t="s">
+      <c r="J226" t="s">
         <v>33</v>
       </c>
-      <c r="K226" s="5" t="s">
+      <c r="K226" t="s">
         <v>1134</v>
       </c>
       <c r="L226" t="s">
@@ -13320,25 +13519,24 @@
       <c r="D227" t="s">
         <v>14</v>
       </c>
-      <c r="E227" s="4" t="s">
+      <c r="E227" t="s">
         <v>1111</v>
       </c>
-      <c r="F227" s="4" t="s">
+      <c r="F227" t="s">
         <v>324</v>
       </c>
-      <c r="G227" s="4" t="s">
+      <c r="G227" t="s">
         <v>322</v>
       </c>
-      <c r="H227" s="4" t="s">
+      <c r="H227" t="s">
         <v>323</v>
       </c>
-      <c r="I227" s="4" t="s">
+      <c r="I227" t="s">
         <v>321</v>
       </c>
-      <c r="J227" s="4" t="s">
+      <c r="J227" t="s">
         <v>33</v>
       </c>
-      <c r="K227" s="4"/>
       <c r="L227" t="s">
         <v>1033</v>
       </c>
@@ -13359,25 +13557,24 @@
       <c r="D228" t="s">
         <v>14</v>
       </c>
-      <c r="E228" s="5" t="s">
+      <c r="E228" t="s">
         <v>1125</v>
       </c>
-      <c r="F228" s="4" t="s">
+      <c r="F228" t="s">
         <v>1112</v>
       </c>
-      <c r="G228" s="4" t="s">
+      <c r="G228" t="s">
         <v>1113</v>
       </c>
-      <c r="H228" s="4" t="s">
+      <c r="H228" t="s">
         <v>1114</v>
       </c>
-      <c r="I228" s="4" t="s">
+      <c r="I228" t="s">
         <v>1126</v>
       </c>
-      <c r="J228" s="4" t="s">
+      <c r="J228" t="s">
         <v>57</v>
       </c>
-      <c r="K228" s="4"/>
       <c r="L228" t="s">
         <v>1033</v>
       </c>
@@ -13398,25 +13595,24 @@
       <c r="D229" t="s">
         <v>14</v>
       </c>
-      <c r="E229" s="4" t="s">
+      <c r="E229" t="s">
         <v>1115</v>
       </c>
-      <c r="F229" s="4" t="s">
+      <c r="F229" t="s">
         <v>1116</v>
       </c>
-      <c r="G229" s="4" t="s">
+      <c r="G229" t="s">
         <v>1117</v>
       </c>
-      <c r="H229" s="4" t="s">
+      <c r="H229" t="s">
         <v>1118</v>
       </c>
-      <c r="I229" s="4" t="s">
+      <c r="I229" t="s">
         <v>1119</v>
       </c>
-      <c r="J229" s="4" t="s">
+      <c r="J229" t="s">
         <v>20</v>
       </c>
-      <c r="K229" s="4"/>
       <c r="L229" t="s">
         <v>1033</v>
       </c>
@@ -13437,25 +13633,24 @@
       <c r="D230" t="s">
         <v>14</v>
       </c>
-      <c r="E230" s="4" t="s">
+      <c r="E230" t="s">
         <v>1120</v>
       </c>
-      <c r="F230" s="4" t="s">
+      <c r="F230" t="s">
         <v>979</v>
       </c>
-      <c r="G230" s="4" t="s">
+      <c r="G230" t="s">
         <v>978</v>
       </c>
-      <c r="H230" s="4" t="s">
+      <c r="H230" t="s">
         <v>977</v>
       </c>
-      <c r="I230" s="4" t="s">
+      <c r="I230" t="s">
         <v>980</v>
       </c>
-      <c r="J230" s="4" t="s">
+      <c r="J230" t="s">
         <v>33</v>
       </c>
-      <c r="K230" s="4"/>
       <c r="L230" t="s">
         <v>1033</v>
       </c>

--- a/QUESTOES PROVA CRS.xlsx
+++ b/QUESTOES PROVA CRS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julião\Downloads\chobot-main (2)\chobot-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5F6ABF-3176-400C-B04D-B4CF69FAFBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AB010F-B940-4B4C-B2DA-040C932C2A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
   </bookViews>
@@ -2406,9 +2406,6 @@
   </si>
   <si>
     <t>Em relação ao Decreto-Lei nº 1.001, de 21 de outubro de 1969, Código Penal Militar, marque a alternativa CORRETA.</t>
-  </si>
-  <si>
-    <t>O crime de_desacato a superior classifica-se como propriamente militar e terá sua pena agravada se o superior for Oficial.</t>
   </si>
   <si>
     <t>O crime de desacato a militar exige que o militar desacatado esteja no exercício da função de natureza militar ou em razão dela.</t>
@@ -5402,6 +5399,9 @@
 Assertiva II - INCORRETA: O erro está em afirmar que os princípios apurados em face de dados objetivos são a "publicidade e a legalidade". Na verdade, o § 1º do Art. 13 determina expressamente que são "A moralidade e a razoabilidade dos atos do Poder Público serão apuradas, para efeito de controle e invalidação, em face dos dados objetivos de cada caso".
 Assertiva III - INCORRETA: A motivação dos atos não fica ao encargo da discricionariedade do agente. O § 2º do Art. 13 impõe um dever objetivo e obrigatório: "O agente público motivará o ato administrativo que praticar, explicitando-lhe o fundamento legal, o fático e a finalidade". Não há margem legal na Constituição para que o agente escolha quando deve ou não fundamentar sua decisão.
 Assertiva IV - INCORRETA: O erro está na parte final da afirmação, ao dizer que a extinção pode ser procedida mediante Resolução do Tribunal de Contas. Conforme o Art. 14, § 4º, inciso I, tanto a instituição quanto a extinção exigem o mesmo rigor formal: "Depende de lei específica: I - a instituição e a extinção de autarquia, fundação pública e órgão autônomo".</t>
+  </si>
+  <si>
+    <t>O crime de desacato a superior classifica-se como propriamente militar e terá sua pena agravada se o superior for Oficial.</t>
   </si>
 </sst>
 </file>
@@ -5524,7 +5524,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5532,7 +5532,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -5543,7 +5542,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5961,7 +5959,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="L2" t="s">
         <v>21</v>
@@ -6002,7 +6000,7 @@
         <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="L3" t="s">
         <v>21</v>
@@ -6125,7 +6123,7 @@
         <v>57</v>
       </c>
       <c r="K6" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="L6" t="s">
         <v>51</v>
@@ -6166,7 +6164,7 @@
         <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="L7" t="s">
         <v>51</v>
@@ -6560,8 +6558,8 @@
       <c r="J17" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>1185</v>
+      <c r="K17" t="s">
+        <v>1184</v>
       </c>
       <c r="L17" t="s">
         <v>103</v>
@@ -6601,8 +6599,8 @@
       <c r="J18" t="s">
         <v>57</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>1186</v>
+      <c r="K18" t="s">
+        <v>1185</v>
       </c>
       <c r="L18" t="s">
         <v>103</v>
@@ -6619,7 +6617,7 @@
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -6657,7 +6655,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -6718,8 +6716,8 @@
       <c r="J21" t="s">
         <v>20</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>1162</v>
+      <c r="K21" t="s">
+        <v>1161</v>
       </c>
       <c r="L21" t="s">
         <v>103</v>
@@ -6759,8 +6757,8 @@
       <c r="J22" t="s">
         <v>33</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>1163</v>
+      <c r="K22" t="s">
+        <v>1162</v>
       </c>
       <c r="L22" t="s">
         <v>103</v>
@@ -6914,8 +6912,8 @@
       <c r="J26" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>1168</v>
+      <c r="K26" t="s">
+        <v>1167</v>
       </c>
       <c r="L26" t="s">
         <v>103</v>
@@ -6955,8 +6953,8 @@
       <c r="J27" t="s">
         <v>57</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>1169</v>
+      <c r="K27" t="s">
+        <v>1168</v>
       </c>
       <c r="L27" t="s">
         <v>103</v>
@@ -6997,7 +6995,7 @@
         <v>57</v>
       </c>
       <c r="K28" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="L28" t="s">
         <v>103</v>
@@ -7038,7 +7036,7 @@
         <v>33</v>
       </c>
       <c r="K29" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L29" t="s">
         <v>103</v>
@@ -7111,13 +7109,13 @@
         <v>196</v>
       </c>
       <c r="I31" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="J31" t="s">
         <v>20</v>
       </c>
-      <c r="K31" s="8" t="s">
-        <v>1155</v>
+      <c r="K31" s="3" t="s">
+        <v>1154</v>
       </c>
       <c r="L31" t="s">
         <v>103</v>
@@ -7157,8 +7155,8 @@
       <c r="J32" t="s">
         <v>27</v>
       </c>
-      <c r="K32" s="4" t="s">
-        <v>1146</v>
+      <c r="K32" s="3" t="s">
+        <v>1145</v>
       </c>
       <c r="L32" t="s">
         <v>103</v>
@@ -7199,7 +7197,7 @@
         <v>57</v>
       </c>
       <c r="K33" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="L33" t="s">
         <v>103</v>
@@ -7239,8 +7237,8 @@
       <c r="J34" t="s">
         <v>27</v>
       </c>
-      <c r="K34" s="4" t="s">
-        <v>1148</v>
+      <c r="K34" s="3" t="s">
+        <v>1147</v>
       </c>
       <c r="L34" t="s">
         <v>103</v>
@@ -7280,7 +7278,7 @@
       <c r="J35" t="s">
         <v>33</v>
       </c>
-      <c r="K35" s="5"/>
+      <c r="K35" s="4"/>
       <c r="L35" t="s">
         <v>103</v>
       </c>
@@ -7319,8 +7317,8 @@
       <c r="J36" t="s">
         <v>27</v>
       </c>
-      <c r="K36" s="6" t="s">
-        <v>1149</v>
+      <c r="K36" s="5" t="s">
+        <v>1148</v>
       </c>
       <c r="L36" t="s">
         <v>103</v>
@@ -7360,8 +7358,8 @@
       <c r="J37" t="s">
         <v>57</v>
       </c>
-      <c r="K37" s="7" t="s">
-        <v>1150</v>
+      <c r="K37" s="6" t="s">
+        <v>1149</v>
       </c>
       <c r="L37" t="s">
         <v>103</v>
@@ -7401,8 +7399,8 @@
       <c r="J38" t="s">
         <v>33</v>
       </c>
-      <c r="K38" s="6" t="s">
-        <v>1151</v>
+      <c r="K38" s="5" t="s">
+        <v>1150</v>
       </c>
       <c r="L38" t="s">
         <v>103</v>
@@ -7442,8 +7440,8 @@
       <c r="J39" t="s">
         <v>33</v>
       </c>
-      <c r="K39" s="7" t="s">
-        <v>1152</v>
+      <c r="K39" s="6" t="s">
+        <v>1151</v>
       </c>
       <c r="L39" t="s">
         <v>103</v>
@@ -7483,8 +7481,8 @@
       <c r="J40" t="s">
         <v>20</v>
       </c>
-      <c r="K40" s="6" t="s">
-        <v>1153</v>
+      <c r="K40" s="5" t="s">
+        <v>1152</v>
       </c>
       <c r="L40" t="s">
         <v>103</v>
@@ -7524,8 +7522,8 @@
       <c r="J41" t="s">
         <v>27</v>
       </c>
-      <c r="K41" s="7" t="s">
-        <v>1154</v>
+      <c r="K41" s="6" t="s">
+        <v>1153</v>
       </c>
       <c r="L41" t="s">
         <v>103</v>
@@ -8759,8 +8757,8 @@
       <c r="J72" t="s">
         <v>20</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>1164</v>
+      <c r="K72" t="s">
+        <v>1163</v>
       </c>
       <c r="L72" t="s">
         <v>341</v>
@@ -8800,8 +8798,8 @@
       <c r="J73" t="s">
         <v>27</v>
       </c>
-      <c r="K73" s="3" t="s">
-        <v>1198</v>
+      <c r="K73" t="s">
+        <v>1197</v>
       </c>
       <c r="L73" t="s">
         <v>341</v>
@@ -8841,8 +8839,8 @@
       <c r="J74" t="s">
         <v>33</v>
       </c>
-      <c r="K74" s="3" t="s">
-        <v>1170</v>
+      <c r="K74" t="s">
+        <v>1169</v>
       </c>
       <c r="L74" t="s">
         <v>341</v>
@@ -8882,8 +8880,8 @@
       <c r="J75" t="s">
         <v>27</v>
       </c>
-      <c r="K75" s="3" t="s">
-        <v>1171</v>
+      <c r="K75" t="s">
+        <v>1170</v>
       </c>
       <c r="L75" t="s">
         <v>341</v>
@@ -8961,8 +8959,8 @@
       <c r="J77" t="s">
         <v>57</v>
       </c>
-      <c r="K77" s="3" t="s">
-        <v>1187</v>
+      <c r="K77" t="s">
+        <v>1186</v>
       </c>
       <c r="L77" t="s">
         <v>341</v>
@@ -8979,7 +8977,7 @@
         <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D78" t="s">
         <v>14</v>
@@ -9116,8 +9114,8 @@
       <c r="J81" t="s">
         <v>27</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>1156</v>
+      <c r="K81" t="s">
+        <v>1155</v>
       </c>
       <c r="L81" t="s">
         <v>341</v>
@@ -10069,8 +10067,8 @@
       <c r="J106" t="s">
         <v>27</v>
       </c>
-      <c r="K106" s="3" t="s">
-        <v>1157</v>
+      <c r="K106" t="s">
+        <v>1156</v>
       </c>
       <c r="L106" t="s">
         <v>508</v>
@@ -10110,8 +10108,8 @@
       <c r="J107" t="s">
         <v>27</v>
       </c>
-      <c r="K107" s="3" t="s">
-        <v>1188</v>
+      <c r="K107" t="s">
+        <v>1187</v>
       </c>
       <c r="L107" t="s">
         <v>508</v>
@@ -10151,8 +10149,8 @@
       <c r="J108" t="s">
         <v>20</v>
       </c>
-      <c r="K108" s="3" t="s">
-        <v>1189</v>
+      <c r="K108" t="s">
+        <v>1188</v>
       </c>
       <c r="L108" t="s">
         <v>508</v>
@@ -10230,8 +10228,8 @@
       <c r="J110" t="s">
         <v>33</v>
       </c>
-      <c r="K110" s="3" t="s">
-        <v>1199</v>
+      <c r="K110" t="s">
+        <v>1198</v>
       </c>
       <c r="L110" t="s">
         <v>508</v>
@@ -10248,13 +10246,13 @@
         <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D111" t="s">
         <v>14</v>
       </c>
       <c r="E111" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F111" t="s">
         <v>658</v>
@@ -10275,7 +10273,7 @@
         <v>508</v>
       </c>
       <c r="M111" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -10310,7 +10308,7 @@
         <v>33</v>
       </c>
       <c r="K112" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L112" t="s">
         <v>508</v>
@@ -10351,7 +10349,7 @@
         <v>57</v>
       </c>
       <c r="K113" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="L113" t="s">
         <v>508</v>
@@ -10374,7 +10372,7 @@
         <v>14</v>
       </c>
       <c r="E114" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F114" t="s">
         <v>672</v>
@@ -10391,8 +10389,8 @@
       <c r="J114" t="s">
         <v>20</v>
       </c>
-      <c r="K114" s="4" t="s">
-        <v>1172</v>
+      <c r="K114" s="3" t="s">
+        <v>1171</v>
       </c>
       <c r="L114" t="s">
         <v>508</v>
@@ -10418,22 +10416,22 @@
         <v>675</v>
       </c>
       <c r="F115" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G115" t="s">
         <v>676</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>677</v>
       </c>
-      <c r="H115" t="s">
+      <c r="I115" t="s">
         <v>678</v>
-      </c>
-      <c r="I115" t="s">
-        <v>679</v>
       </c>
       <c r="J115" t="s">
         <v>27</v>
       </c>
-      <c r="K115" s="8" t="s">
-        <v>1177</v>
+      <c r="K115" s="3" t="s">
+        <v>1176</v>
       </c>
       <c r="L115" t="s">
         <v>508</v>
@@ -10456,29 +10454,29 @@
         <v>14</v>
       </c>
       <c r="E116" t="s">
+        <v>679</v>
+      </c>
+      <c r="F116" t="s">
         <v>680</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>681</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H116" t="s">
         <v>682</v>
       </c>
-      <c r="H116" t="s">
+      <c r="I116" t="s">
         <v>683</v>
-      </c>
-      <c r="I116" t="s">
-        <v>684</v>
       </c>
       <c r="J116" t="s">
         <v>27</v>
       </c>
-      <c r="K116" s="5"/>
+      <c r="K116" s="4"/>
       <c r="L116" t="s">
         <v>508</v>
       </c>
       <c r="M116" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -10489,37 +10487,37 @@
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D117" t="s">
         <v>14</v>
       </c>
       <c r="E117" t="s">
+        <v>684</v>
+      </c>
+      <c r="F117" t="s">
         <v>685</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>686</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" t="s">
         <v>687</v>
       </c>
-      <c r="H117" t="s">
+      <c r="I117" t="s">
         <v>688</v>
-      </c>
-      <c r="I117" t="s">
-        <v>689</v>
       </c>
       <c r="J117" t="s">
         <v>57</v>
       </c>
-      <c r="K117" s="6" t="s">
-        <v>1173</v>
+      <c r="K117" s="5" t="s">
+        <v>1172</v>
       </c>
       <c r="L117" t="s">
         <v>508</v>
       </c>
       <c r="M117" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -10536,25 +10534,25 @@
         <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F118" t="s">
         <v>659</v>
       </c>
       <c r="G118" t="s">
+        <v>689</v>
+      </c>
+      <c r="H118" t="s">
         <v>690</v>
       </c>
-      <c r="H118" t="s">
+      <c r="I118" t="s">
         <v>691</v>
-      </c>
-      <c r="I118" t="s">
-        <v>692</v>
       </c>
       <c r="J118" t="s">
         <v>33</v>
       </c>
-      <c r="K118" s="6" t="s">
-        <v>1174</v>
+      <c r="K118" s="5" t="s">
+        <v>1173</v>
       </c>
       <c r="L118" t="s">
         <v>508</v>
@@ -10577,25 +10575,25 @@
         <v>14</v>
       </c>
       <c r="E119" t="s">
+        <v>692</v>
+      </c>
+      <c r="F119" t="s">
         <v>693</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>694</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>695</v>
       </c>
-      <c r="H119" t="s">
-        <v>696</v>
-      </c>
       <c r="I119" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J119" t="s">
         <v>27</v>
       </c>
-      <c r="K119" s="6" t="s">
-        <v>1175</v>
+      <c r="K119" s="5" t="s">
+        <v>1174</v>
       </c>
       <c r="L119" t="s">
         <v>508</v>
@@ -10609,40 +10607,40 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C120" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D120" t="s">
         <v>14</v>
       </c>
       <c r="E120" t="s">
+        <v>704</v>
+      </c>
+      <c r="F120" t="s">
         <v>705</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>706</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>707</v>
       </c>
-      <c r="H120" t="s">
+      <c r="I120" t="s">
         <v>708</v>
-      </c>
-      <c r="I120" t="s">
-        <v>709</v>
       </c>
       <c r="J120" t="s">
         <v>20</v>
       </c>
-      <c r="K120" s="6" t="s">
-        <v>1176</v>
+      <c r="K120" s="5" t="s">
+        <v>1175</v>
       </c>
       <c r="L120" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M120" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -10650,37 +10648,37 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C121" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D121" t="s">
         <v>14</v>
       </c>
       <c r="E121" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F121" t="s">
+        <v>709</v>
+      </c>
+      <c r="G121" t="s">
         <v>710</v>
       </c>
-      <c r="G121" t="s">
+      <c r="H121" t="s">
         <v>711</v>
       </c>
-      <c r="H121" t="s">
+      <c r="I121" t="s">
         <v>712</v>
-      </c>
-      <c r="I121" t="s">
-        <v>713</v>
       </c>
       <c r="J121" t="s">
         <v>33</v>
       </c>
       <c r="L121" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M121" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -10697,25 +10695,25 @@
         <v>14</v>
       </c>
       <c r="E122" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F122" t="s">
+        <v>717</v>
+      </c>
+      <c r="G122" t="s">
         <v>718</v>
-      </c>
-      <c r="G122" t="s">
-        <v>719</v>
       </c>
       <c r="H122" t="s">
         <v>354</v>
       </c>
       <c r="I122" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J122" t="s">
         <v>57</v>
       </c>
       <c r="L122" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M122" t="s">
         <v>547</v>
@@ -10735,25 +10733,25 @@
         <v>14</v>
       </c>
       <c r="E123" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F123" t="s">
+        <v>721</v>
+      </c>
+      <c r="G123" t="s">
         <v>722</v>
       </c>
-      <c r="G123" t="s">
+      <c r="H123" t="s">
         <v>723</v>
       </c>
-      <c r="H123" t="s">
+      <c r="I123" t="s">
         <v>724</v>
-      </c>
-      <c r="I123" t="s">
-        <v>725</v>
       </c>
       <c r="J123" t="s">
         <v>27</v>
       </c>
       <c r="L123" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M123" t="s">
         <v>311</v>
@@ -10773,25 +10771,25 @@
         <v>14</v>
       </c>
       <c r="E124" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F124" t="s">
+        <v>725</v>
+      </c>
+      <c r="G124" t="s">
         <v>726</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>727</v>
       </c>
-      <c r="H124" t="s">
+      <c r="I124" t="s">
         <v>728</v>
-      </c>
-      <c r="I124" t="s">
-        <v>729</v>
       </c>
       <c r="J124" t="s">
         <v>33</v>
       </c>
       <c r="L124" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M124" t="s">
         <v>312</v>
@@ -10811,25 +10809,25 @@
         <v>14</v>
       </c>
       <c r="E125" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F125" t="s">
+        <v>721</v>
+      </c>
+      <c r="G125" t="s">
         <v>722</v>
       </c>
-      <c r="G125" t="s">
+      <c r="H125" t="s">
         <v>723</v>
       </c>
-      <c r="H125" t="s">
+      <c r="I125" t="s">
         <v>724</v>
-      </c>
-      <c r="I125" t="s">
-        <v>725</v>
       </c>
       <c r="J125" t="s">
         <v>27</v>
       </c>
       <c r="L125" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M125" t="s">
         <v>313</v>
@@ -10849,25 +10847,25 @@
         <v>14</v>
       </c>
       <c r="E126" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F126" t="s">
+        <v>729</v>
+      </c>
+      <c r="G126" t="s">
         <v>730</v>
       </c>
-      <c r="G126" t="s">
+      <c r="H126" t="s">
         <v>731</v>
       </c>
-      <c r="H126" t="s">
-        <v>732</v>
-      </c>
       <c r="I126" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="J126" t="s">
         <v>57</v>
       </c>
       <c r="L126" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M126" t="s">
         <v>540</v>
@@ -10887,25 +10885,25 @@
         <v>14</v>
       </c>
       <c r="E127" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F127" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G127" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H127" t="s">
+        <v>721</v>
+      </c>
+      <c r="I127" t="s">
         <v>722</v>
-      </c>
-      <c r="I127" t="s">
-        <v>723</v>
       </c>
       <c r="J127" t="s">
         <v>27</v>
       </c>
       <c r="L127" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M127" t="s">
         <v>540</v>
@@ -10925,25 +10923,25 @@
         <v>14</v>
       </c>
       <c r="E128" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F128" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G128" t="s">
+        <v>721</v>
+      </c>
+      <c r="H128" t="s">
         <v>722</v>
       </c>
-      <c r="H128" t="s">
-        <v>723</v>
-      </c>
       <c r="I128" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J128" t="s">
         <v>57</v>
       </c>
       <c r="L128" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M128" t="s">
         <v>350</v>
@@ -10963,25 +10961,25 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
+        <v>739</v>
+      </c>
+      <c r="F129" t="s">
         <v>740</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>741</v>
       </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>742</v>
       </c>
-      <c r="H129" t="s">
+      <c r="I129" t="s">
         <v>743</v>
-      </c>
-      <c r="I129" t="s">
-        <v>744</v>
       </c>
       <c r="J129" t="s">
         <v>57</v>
       </c>
       <c r="L129" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M129" t="s">
         <v>204</v>
@@ -11001,25 +10999,25 @@
         <v>14</v>
       </c>
       <c r="E130" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F130" t="s">
+        <v>744</v>
+      </c>
+      <c r="G130" t="s">
         <v>745</v>
       </c>
-      <c r="G130" t="s">
+      <c r="H130" t="s">
         <v>746</v>
       </c>
-      <c r="H130" t="s">
+      <c r="I130" t="s">
         <v>747</v>
-      </c>
-      <c r="I130" t="s">
-        <v>748</v>
       </c>
       <c r="J130" t="s">
         <v>57</v>
       </c>
       <c r="L130" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M130" t="s">
         <v>266</v>
@@ -11039,25 +11037,25 @@
         <v>14</v>
       </c>
       <c r="E131" t="s">
+        <v>749</v>
+      </c>
+      <c r="F131" t="s">
         <v>750</v>
       </c>
-      <c r="F131" t="s">
+      <c r="G131" t="s">
         <v>751</v>
       </c>
-      <c r="G131" t="s">
+      <c r="H131" t="s">
         <v>752</v>
       </c>
-      <c r="H131" t="s">
+      <c r="I131" t="s">
         <v>753</v>
-      </c>
-      <c r="I131" t="s">
-        <v>754</v>
       </c>
       <c r="J131" t="s">
         <v>33</v>
       </c>
       <c r="L131" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M131" t="s">
         <v>226</v>
@@ -11077,25 +11075,25 @@
         <v>14</v>
       </c>
       <c r="E132" t="s">
+        <v>754</v>
+      </c>
+      <c r="F132" t="s">
         <v>755</v>
       </c>
-      <c r="F132" t="s">
+      <c r="G132" t="s">
         <v>756</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H132" t="s">
         <v>757</v>
       </c>
-      <c r="H132" t="s">
+      <c r="I132" t="s">
         <v>758</v>
-      </c>
-      <c r="I132" t="s">
-        <v>759</v>
       </c>
       <c r="J132" t="s">
         <v>27</v>
       </c>
       <c r="L132" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M132" t="s">
         <v>265</v>
@@ -11115,25 +11113,25 @@
         <v>14</v>
       </c>
       <c r="E133" t="s">
+        <v>759</v>
+      </c>
+      <c r="F133" t="s">
         <v>760</v>
       </c>
-      <c r="F133" t="s">
+      <c r="G133" t="s">
         <v>761</v>
       </c>
-      <c r="G133" t="s">
+      <c r="H133" t="s">
         <v>762</v>
       </c>
-      <c r="H133" t="s">
+      <c r="I133" t="s">
         <v>763</v>
-      </c>
-      <c r="I133" t="s">
-        <v>764</v>
       </c>
       <c r="J133" t="s">
         <v>27</v>
       </c>
       <c r="L133" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M133" t="s">
         <v>266</v>
@@ -11153,25 +11151,25 @@
         <v>14</v>
       </c>
       <c r="E134" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F134" t="s">
+        <v>723</v>
+      </c>
+      <c r="G134" t="s">
         <v>724</v>
       </c>
-      <c r="G134" t="s">
-        <v>725</v>
-      </c>
       <c r="H134" t="s">
+        <v>721</v>
+      </c>
+      <c r="I134" t="s">
         <v>722</v>
-      </c>
-      <c r="I134" t="s">
-        <v>723</v>
       </c>
       <c r="J134" t="s">
         <v>33</v>
       </c>
       <c r="L134" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M134" t="s">
         <v>225</v>
@@ -11191,25 +11189,25 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
+        <v>810</v>
+      </c>
+      <c r="F135" t="s">
+        <v>765</v>
+      </c>
+      <c r="G135" t="s">
+        <v>766</v>
+      </c>
+      <c r="H135" t="s">
+        <v>767</v>
+      </c>
+      <c r="I135" t="s">
         <v>811</v>
-      </c>
-      <c r="F135" t="s">
-        <v>766</v>
-      </c>
-      <c r="G135" t="s">
-        <v>767</v>
-      </c>
-      <c r="H135" t="s">
-        <v>768</v>
-      </c>
-      <c r="I135" t="s">
-        <v>812</v>
       </c>
       <c r="J135" t="s">
         <v>33</v>
       </c>
       <c r="L135" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M135" t="s">
         <v>204</v>
@@ -11229,25 +11227,25 @@
         <v>14</v>
       </c>
       <c r="E136" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F136" t="s">
+        <v>768</v>
+      </c>
+      <c r="G136" t="s">
         <v>769</v>
       </c>
-      <c r="G136" t="s">
+      <c r="H136" t="s">
         <v>770</v>
       </c>
-      <c r="H136" t="s">
-        <v>771</v>
-      </c>
       <c r="I136" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J136" t="s">
         <v>57</v>
       </c>
       <c r="L136" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M136" t="s">
         <v>104</v>
@@ -11267,28 +11265,28 @@
         <v>14</v>
       </c>
       <c r="E137" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F137" t="s">
+        <v>769</v>
+      </c>
+      <c r="G137" t="s">
         <v>770</v>
       </c>
-      <c r="G137" t="s">
-        <v>771</v>
-      </c>
       <c r="H137" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="I137" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="J137" t="s">
         <v>27</v>
       </c>
-      <c r="K137" s="3" t="s">
-        <v>1200</v>
+      <c r="K137" t="s">
+        <v>1199</v>
       </c>
       <c r="L137" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M137" t="s">
         <v>459</v>
@@ -11308,28 +11306,28 @@
         <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F138" t="s">
+        <v>771</v>
+      </c>
+      <c r="G138" t="s">
         <v>772</v>
       </c>
-      <c r="G138" t="s">
+      <c r="H138" t="s">
         <v>773</v>
       </c>
-      <c r="H138" t="s">
+      <c r="I138" t="s">
         <v>774</v>
-      </c>
-      <c r="I138" t="s">
-        <v>775</v>
       </c>
       <c r="J138" t="s">
         <v>57</v>
       </c>
-      <c r="K138" s="3" t="s">
-        <v>1178</v>
+      <c r="K138" t="s">
+        <v>1177</v>
       </c>
       <c r="L138" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M138" t="s">
         <v>165</v>
@@ -11349,28 +11347,28 @@
         <v>14</v>
       </c>
       <c r="E139" t="s">
+        <v>775</v>
+      </c>
+      <c r="F139" t="s">
         <v>776</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
         <v>777</v>
       </c>
-      <c r="G139" t="s">
+      <c r="H139" t="s">
         <v>778</v>
       </c>
-      <c r="H139" t="s">
+      <c r="I139" t="s">
         <v>779</v>
-      </c>
-      <c r="I139" t="s">
-        <v>780</v>
       </c>
       <c r="J139" t="s">
         <v>20</v>
       </c>
       <c r="L139" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M139" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -11387,28 +11385,28 @@
         <v>14</v>
       </c>
       <c r="E140" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F140" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G140" t="s">
+        <v>768</v>
+      </c>
+      <c r="H140" t="s">
         <v>769</v>
       </c>
-      <c r="H140" t="s">
+      <c r="I140" t="s">
         <v>770</v>
-      </c>
-      <c r="I140" t="s">
-        <v>771</v>
       </c>
       <c r="J140" t="s">
         <v>57</v>
       </c>
-      <c r="K140" s="3" t="s">
-        <v>1179</v>
+      <c r="K140" t="s">
+        <v>1178</v>
       </c>
       <c r="L140" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M140" t="s">
         <v>165</v>
@@ -11428,28 +11426,28 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
+        <v>780</v>
+      </c>
+      <c r="F141" t="s">
         <v>781</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>782</v>
       </c>
-      <c r="G141" t="s">
+      <c r="H141" t="s">
         <v>783</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I141" t="s">
         <v>784</v>
-      </c>
-      <c r="I141" t="s">
-        <v>785</v>
       </c>
       <c r="J141" t="s">
         <v>33</v>
       </c>
-      <c r="K141" s="3" t="s">
-        <v>1190</v>
+      <c r="K141" t="s">
+        <v>1189</v>
       </c>
       <c r="L141" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M141" t="s">
         <v>110</v>
@@ -11463,34 +11461,34 @@
         <v>12</v>
       </c>
       <c r="C142" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D142" t="s">
         <v>14</v>
       </c>
       <c r="E142" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F142" t="s">
+        <v>769</v>
+      </c>
+      <c r="G142" t="s">
         <v>770</v>
       </c>
-      <c r="G142" t="s">
-        <v>771</v>
-      </c>
       <c r="H142" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="I142" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="J142" t="s">
         <v>33</v>
       </c>
       <c r="L142" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M142" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -11507,28 +11505,28 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F143" t="s">
+        <v>785</v>
+      </c>
+      <c r="G143" t="s">
         <v>786</v>
       </c>
-      <c r="G143" t="s">
+      <c r="H143" t="s">
         <v>787</v>
       </c>
-      <c r="H143" t="s">
+      <c r="I143" t="s">
         <v>788</v>
-      </c>
-      <c r="I143" t="s">
-        <v>789</v>
       </c>
       <c r="J143" t="s">
         <v>33</v>
       </c>
-      <c r="K143" s="3" t="s">
-        <v>1165</v>
+      <c r="K143" t="s">
+        <v>1164</v>
       </c>
       <c r="L143" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M143" t="s">
         <v>135</v>
@@ -11548,25 +11546,25 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F144" t="s">
+        <v>789</v>
+      </c>
+      <c r="G144" t="s">
         <v>790</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" t="s">
         <v>791</v>
       </c>
-      <c r="H144" t="s">
-        <v>792</v>
-      </c>
       <c r="I144" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J144" t="s">
         <v>20</v>
       </c>
       <c r="L144" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M144" t="s">
         <v>153</v>
@@ -11580,34 +11578,34 @@
         <v>12</v>
       </c>
       <c r="C145" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D145" t="s">
         <v>14</v>
       </c>
       <c r="E145" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F145" t="s">
+        <v>792</v>
+      </c>
+      <c r="G145" t="s">
         <v>793</v>
       </c>
-      <c r="G145" t="s">
+      <c r="H145" t="s">
         <v>794</v>
       </c>
-      <c r="H145" t="s">
+      <c r="I145" t="s">
         <v>795</v>
-      </c>
-      <c r="I145" t="s">
-        <v>796</v>
       </c>
       <c r="J145" t="s">
         <v>20</v>
       </c>
       <c r="L145" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M145" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -11624,28 +11622,28 @@
         <v>14</v>
       </c>
       <c r="E146" t="s">
+        <v>796</v>
+      </c>
+      <c r="F146" t="s">
         <v>797</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>798</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>799</v>
       </c>
-      <c r="H146" t="s">
+      <c r="I146" t="s">
         <v>800</v>
-      </c>
-      <c r="I146" t="s">
-        <v>801</v>
       </c>
       <c r="J146" t="s">
         <v>27</v>
       </c>
-      <c r="K146" s="3" t="s">
-        <v>1158</v>
+      <c r="K146" t="s">
+        <v>1157</v>
       </c>
       <c r="L146" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M146" t="s">
         <v>197</v>
@@ -11665,28 +11663,28 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
+        <v>801</v>
+      </c>
+      <c r="F147" t="s">
         <v>802</v>
       </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
         <v>803</v>
       </c>
-      <c r="G147" t="s">
+      <c r="H147" t="s">
         <v>804</v>
       </c>
-      <c r="H147" t="s">
+      <c r="I147" t="s">
         <v>805</v>
-      </c>
-      <c r="I147" t="s">
-        <v>806</v>
       </c>
       <c r="J147" t="s">
         <v>33</v>
       </c>
       <c r="K147" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="L147" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M147" t="s">
         <v>45</v>
@@ -11706,25 +11704,25 @@
         <v>14</v>
       </c>
       <c r="E148" t="s">
+        <v>806</v>
+      </c>
+      <c r="F148" t="s">
         <v>807</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>808</v>
       </c>
-      <c r="G148" t="s">
+      <c r="H148" t="s">
         <v>809</v>
       </c>
-      <c r="H148" t="s">
-        <v>810</v>
-      </c>
       <c r="I148" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J148" t="s">
         <v>20</v>
       </c>
       <c r="L148" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M148" t="s">
         <v>191</v>
@@ -11744,28 +11742,28 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
+        <v>822</v>
+      </c>
+      <c r="F149" t="s">
         <v>823</v>
       </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
         <v>824</v>
       </c>
-      <c r="G149" t="s">
+      <c r="H149" t="s">
         <v>825</v>
       </c>
-      <c r="H149" t="s">
+      <c r="I149" t="s">
         <v>826</v>
-      </c>
-      <c r="I149" t="s">
-        <v>827</v>
       </c>
       <c r="J149" t="s">
         <v>27</v>
       </c>
-      <c r="K149" s="3" t="s">
-        <v>1159</v>
+      <c r="K149" t="s">
+        <v>1158</v>
       </c>
       <c r="L149" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M149" t="s">
         <v>197</v>
@@ -11785,28 +11783,28 @@
         <v>14</v>
       </c>
       <c r="E150" t="s">
+        <v>827</v>
+      </c>
+      <c r="F150" t="s">
         <v>828</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>829</v>
       </c>
-      <c r="G150" t="s">
+      <c r="H150" t="s">
         <v>830</v>
       </c>
-      <c r="H150" t="s">
+      <c r="I150" t="s">
         <v>831</v>
-      </c>
-      <c r="I150" t="s">
-        <v>832</v>
       </c>
       <c r="J150" t="s">
         <v>20</v>
       </c>
-      <c r="K150" s="3" t="s">
-        <v>1160</v>
+      <c r="K150" t="s">
+        <v>1159</v>
       </c>
       <c r="L150" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M150" t="s">
         <v>197</v>
@@ -11826,28 +11824,28 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
+        <v>832</v>
+      </c>
+      <c r="F151" t="s">
         <v>833</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
         <v>834</v>
       </c>
-      <c r="G151" t="s">
+      <c r="H151" t="s">
         <v>835</v>
       </c>
-      <c r="H151" t="s">
-        <v>836</v>
-      </c>
       <c r="I151" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J151" t="s">
         <v>57</v>
       </c>
       <c r="K151" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="L151" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M151" t="s">
         <v>45</v>
@@ -11867,7 +11865,7 @@
         <v>14</v>
       </c>
       <c r="E152" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F152" t="s">
         <v>443</v>
@@ -11885,10 +11883,10 @@
         <v>57</v>
       </c>
       <c r="K152" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="L152" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M152" t="s">
         <v>45</v>
@@ -11902,16 +11900,16 @@
         <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D153" t="s">
         <v>14</v>
       </c>
       <c r="E153" t="s">
+        <v>836</v>
+      </c>
+      <c r="F153" t="s">
         <v>837</v>
-      </c>
-      <c r="F153" t="s">
-        <v>838</v>
       </c>
       <c r="G153" t="s">
         <v>187</v>
@@ -11920,16 +11918,16 @@
         <v>189</v>
       </c>
       <c r="I153" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="J153" t="s">
         <v>33</v>
       </c>
       <c r="L153" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M153" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -11940,34 +11938,34 @@
         <v>12</v>
       </c>
       <c r="C154" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D154" t="s">
         <v>14</v>
       </c>
       <c r="E154" t="s">
+        <v>839</v>
+      </c>
+      <c r="F154" t="s">
         <v>840</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>841</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H154" t="s">
         <v>842</v>
       </c>
-      <c r="H154" t="s">
+      <c r="I154" t="s">
         <v>843</v>
-      </c>
-      <c r="I154" t="s">
-        <v>844</v>
       </c>
       <c r="J154" t="s">
         <v>27</v>
       </c>
       <c r="L154" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M154" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -11984,28 +11982,28 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
+        <v>844</v>
+      </c>
+      <c r="F155" t="s">
         <v>845</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>846</v>
       </c>
-      <c r="G155" t="s">
+      <c r="H155" t="s">
         <v>847</v>
       </c>
-      <c r="H155" t="s">
-        <v>848</v>
-      </c>
       <c r="I155" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="J155" t="s">
         <v>57</v>
       </c>
-      <c r="K155" s="3" t="s">
-        <v>1191</v>
+      <c r="K155" t="s">
+        <v>1190</v>
       </c>
       <c r="L155" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M155" t="s">
         <v>110</v>
@@ -12025,28 +12023,28 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
+        <v>848</v>
+      </c>
+      <c r="F156" t="s">
         <v>849</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>850</v>
       </c>
-      <c r="G156" t="s">
+      <c r="H156" t="s">
         <v>851</v>
       </c>
-      <c r="H156" t="s">
+      <c r="I156" t="s">
         <v>852</v>
-      </c>
-      <c r="I156" t="s">
-        <v>853</v>
       </c>
       <c r="J156" t="s">
         <v>20</v>
       </c>
-      <c r="K156" s="3" t="s">
-        <v>1192</v>
+      <c r="K156" t="s">
+        <v>1191</v>
       </c>
       <c r="L156" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M156" t="s">
         <v>110</v>
@@ -12066,28 +12064,28 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
+        <v>853</v>
+      </c>
+      <c r="F157" t="s">
         <v>854</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
         <v>855</v>
-      </c>
-      <c r="G157" t="s">
-        <v>856</v>
       </c>
       <c r="H157" t="s">
         <v>448</v>
       </c>
       <c r="I157" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="J157" t="s">
         <v>57</v>
       </c>
-      <c r="K157" s="3" t="s">
-        <v>1193</v>
+      <c r="K157" t="s">
+        <v>1192</v>
       </c>
       <c r="L157" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M157" t="s">
         <v>110</v>
@@ -12101,34 +12099,34 @@
         <v>12</v>
       </c>
       <c r="C158" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D158" t="s">
         <v>14</v>
       </c>
       <c r="E158" t="s">
+        <v>857</v>
+      </c>
+      <c r="F158" t="s">
         <v>858</v>
       </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
         <v>859</v>
       </c>
-      <c r="G158" t="s">
+      <c r="H158" t="s">
         <v>860</v>
       </c>
-      <c r="H158" t="s">
-        <v>861</v>
-      </c>
       <c r="I158" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="J158" t="s">
         <v>57</v>
       </c>
       <c r="L158" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M158" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -12145,7 +12143,7 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F159" t="s">
         <v>449</v>
@@ -12157,16 +12155,16 @@
         <v>447</v>
       </c>
       <c r="I159" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J159" t="s">
         <v>27</v>
       </c>
-      <c r="K159" s="3" t="s">
-        <v>1194</v>
+      <c r="K159" t="s">
+        <v>1193</v>
       </c>
       <c r="L159" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M159" t="s">
         <v>110</v>
@@ -12186,28 +12184,28 @@
         <v>14</v>
       </c>
       <c r="E160" t="s">
+        <v>863</v>
+      </c>
+      <c r="F160" t="s">
         <v>864</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>865</v>
       </c>
-      <c r="G160" t="s">
+      <c r="H160" t="s">
         <v>866</v>
       </c>
-      <c r="H160" t="s">
+      <c r="I160" t="s">
         <v>867</v>
-      </c>
-      <c r="I160" t="s">
-        <v>868</v>
       </c>
       <c r="J160" t="s">
         <v>27</v>
       </c>
-      <c r="K160" s="3" t="s">
-        <v>1180</v>
+      <c r="K160" t="s">
+        <v>1179</v>
       </c>
       <c r="L160" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M160" t="s">
         <v>165</v>
@@ -12227,28 +12225,28 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
+        <v>868</v>
+      </c>
+      <c r="F161" t="s">
         <v>869</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
         <v>870</v>
       </c>
-      <c r="G161" t="s">
+      <c r="H161" t="s">
         <v>871</v>
       </c>
-      <c r="H161" t="s">
-        <v>872</v>
-      </c>
       <c r="I161" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J161" t="s">
         <v>33</v>
       </c>
-      <c r="K161" s="3" t="s">
-        <v>1181</v>
+      <c r="K161" t="s">
+        <v>1180</v>
       </c>
       <c r="L161" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M161" t="s">
         <v>165</v>
@@ -12268,28 +12266,28 @@
         <v>14</v>
       </c>
       <c r="E162" t="s">
+        <v>872</v>
+      </c>
+      <c r="F162" t="s">
+        <v>693</v>
+      </c>
+      <c r="G162" t="s">
         <v>873</v>
       </c>
-      <c r="F162" t="s">
-        <v>694</v>
-      </c>
-      <c r="G162" t="s">
+      <c r="H162" t="s">
         <v>874</v>
       </c>
-      <c r="H162" t="s">
-        <v>875</v>
-      </c>
       <c r="I162" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J162" t="s">
         <v>57</v>
       </c>
-      <c r="K162" s="3" t="s">
-        <v>1166</v>
+      <c r="K162" t="s">
+        <v>1165</v>
       </c>
       <c r="L162" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M162" t="s">
         <v>135</v>
@@ -12309,25 +12307,25 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
+        <v>875</v>
+      </c>
+      <c r="F163" t="s">
         <v>876</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>877</v>
       </c>
-      <c r="G163" t="s">
+      <c r="H163" t="s">
         <v>878</v>
       </c>
-      <c r="H163" t="s">
+      <c r="I163" t="s">
         <v>879</v>
-      </c>
-      <c r="I163" t="s">
-        <v>880</v>
       </c>
       <c r="J163" t="s">
         <v>20</v>
       </c>
       <c r="L163" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M163" t="s">
         <v>204</v>
@@ -12347,7 +12345,7 @@
         <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F164" t="s">
         <v>203</v>
@@ -12359,13 +12357,13 @@
         <v>220</v>
       </c>
       <c r="I164" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="J164" t="s">
         <v>33</v>
       </c>
       <c r="L164" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M164" t="s">
         <v>204</v>
@@ -12385,25 +12383,25 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F165" t="s">
+        <v>880</v>
+      </c>
+      <c r="G165" t="s">
         <v>881</v>
       </c>
-      <c r="G165" t="s">
+      <c r="H165" t="s">
         <v>882</v>
       </c>
-      <c r="H165" t="s">
+      <c r="I165" t="s">
         <v>883</v>
-      </c>
-      <c r="I165" t="s">
-        <v>884</v>
       </c>
       <c r="J165" t="s">
         <v>27</v>
       </c>
       <c r="L165" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M165" t="s">
         <v>225</v>
@@ -12423,7 +12421,7 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F166" t="s">
         <v>234</v>
@@ -12435,13 +12433,13 @@
         <v>235</v>
       </c>
       <c r="I166" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J166" t="s">
         <v>20</v>
       </c>
       <c r="L166" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M166" t="s">
         <v>225</v>
@@ -12461,7 +12459,7 @@
         <v>14</v>
       </c>
       <c r="E167" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F167" t="s">
         <v>224</v>
@@ -12479,7 +12477,7 @@
         <v>33</v>
       </c>
       <c r="L167" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M167" t="s">
         <v>226</v>
@@ -12499,7 +12497,7 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F168" t="s">
         <v>234</v>
@@ -12517,7 +12515,7 @@
         <v>20</v>
       </c>
       <c r="L168" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M168" t="s">
         <v>226</v>
@@ -12537,7 +12535,7 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F169" t="s">
         <v>233</v>
@@ -12546,7 +12544,7 @@
         <v>443</v>
       </c>
       <c r="H169" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I169" t="s">
         <v>97</v>
@@ -12555,7 +12553,7 @@
         <v>33</v>
       </c>
       <c r="L169" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M169" t="s">
         <v>265</v>
@@ -12575,7 +12573,7 @@
         <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F170" t="s">
         <v>236</v>
@@ -12593,7 +12591,7 @@
         <v>27</v>
       </c>
       <c r="L170" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M170" t="s">
         <v>267</v>
@@ -12613,25 +12611,25 @@
         <v>14</v>
       </c>
       <c r="E171" t="s">
+        <v>891</v>
+      </c>
+      <c r="F171" t="s">
         <v>892</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>893</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>894</v>
       </c>
-      <c r="H171" t="s">
-        <v>895</v>
-      </c>
       <c r="I171" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="J171" t="s">
         <v>33</v>
       </c>
       <c r="L171" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M171" t="s">
         <v>266</v>
@@ -12651,25 +12649,25 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
+        <v>895</v>
+      </c>
+      <c r="F172" t="s">
         <v>896</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>897</v>
       </c>
-      <c r="G172" t="s">
+      <c r="H172" t="s">
         <v>898</v>
       </c>
-      <c r="H172" t="s">
+      <c r="I172" t="s">
         <v>899</v>
-      </c>
-      <c r="I172" t="s">
-        <v>900</v>
       </c>
       <c r="J172" t="s">
         <v>57</v>
       </c>
       <c r="L172" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M172" t="s">
         <v>266</v>
@@ -12689,25 +12687,25 @@
         <v>14</v>
       </c>
       <c r="E173" t="s">
+        <v>900</v>
+      </c>
+      <c r="F173" t="s">
         <v>901</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G173" t="s">
         <v>902</v>
       </c>
-      <c r="G173" t="s">
+      <c r="H173" t="s">
         <v>903</v>
       </c>
-      <c r="H173" t="s">
+      <c r="I173" t="s">
         <v>904</v>
-      </c>
-      <c r="I173" t="s">
-        <v>905</v>
       </c>
       <c r="J173" t="s">
         <v>27</v>
       </c>
       <c r="L173" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M173" t="s">
         <v>267</v>
@@ -12727,25 +12725,25 @@
         <v>14</v>
       </c>
       <c r="E174" t="s">
+        <v>905</v>
+      </c>
+      <c r="F174" t="s">
         <v>906</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>907</v>
       </c>
-      <c r="G174" t="s">
+      <c r="H174" t="s">
         <v>908</v>
       </c>
-      <c r="H174" t="s">
-        <v>909</v>
-      </c>
       <c r="I174" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="J174" t="s">
         <v>33</v>
       </c>
       <c r="L174" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M174" t="s">
         <v>212</v>
@@ -12765,25 +12763,25 @@
         <v>14</v>
       </c>
       <c r="E175" t="s">
+        <v>921</v>
+      </c>
+      <c r="F175" t="s">
         <v>922</v>
       </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
         <v>923</v>
       </c>
-      <c r="G175" t="s">
+      <c r="H175" t="s">
         <v>924</v>
       </c>
-      <c r="H175" t="s">
-        <v>925</v>
-      </c>
       <c r="I175" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="J175" t="s">
         <v>20</v>
       </c>
       <c r="L175" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M175" t="s">
         <v>311</v>
@@ -12803,10 +12801,10 @@
         <v>14</v>
       </c>
       <c r="E176" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F176" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G176" t="s">
         <v>220</v>
@@ -12821,7 +12819,7 @@
         <v>27</v>
       </c>
       <c r="L176" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M176" t="s">
         <v>311</v>
@@ -12841,7 +12839,7 @@
         <v>14</v>
       </c>
       <c r="E177" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F177" t="s">
         <v>237</v>
@@ -12859,7 +12857,7 @@
         <v>57</v>
       </c>
       <c r="L177" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M177" t="s">
         <v>311</v>
@@ -12879,25 +12877,25 @@
         <v>14</v>
       </c>
       <c r="E178" t="s">
+        <v>926</v>
+      </c>
+      <c r="F178" t="s">
         <v>927</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
         <v>928</v>
       </c>
-      <c r="G178" t="s">
+      <c r="H178" t="s">
         <v>929</v>
       </c>
-      <c r="H178" t="s">
+      <c r="I178" t="s">
         <v>930</v>
-      </c>
-      <c r="I178" t="s">
-        <v>931</v>
       </c>
       <c r="J178" t="s">
         <v>20</v>
       </c>
       <c r="L178" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M178" t="s">
         <v>311</v>
@@ -12920,22 +12918,22 @@
         <v>286</v>
       </c>
       <c r="F179" t="s">
+        <v>931</v>
+      </c>
+      <c r="G179" t="s">
         <v>932</v>
       </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
         <v>933</v>
       </c>
-      <c r="H179" t="s">
+      <c r="I179" t="s">
         <v>934</v>
-      </c>
-      <c r="I179" t="s">
-        <v>935</v>
       </c>
       <c r="J179" t="s">
         <v>33</v>
       </c>
       <c r="L179" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M179" t="s">
         <v>311</v>
@@ -12955,25 +12953,25 @@
         <v>14</v>
       </c>
       <c r="E180" t="s">
+        <v>935</v>
+      </c>
+      <c r="F180" t="s">
         <v>936</v>
       </c>
-      <c r="F180" t="s">
+      <c r="G180" t="s">
         <v>937</v>
       </c>
-      <c r="G180" t="s">
+      <c r="H180" t="s">
         <v>938</v>
       </c>
-      <c r="H180" t="s">
-        <v>939</v>
-      </c>
       <c r="I180" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="J180" t="s">
         <v>33</v>
       </c>
       <c r="L180" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M180" t="s">
         <v>312</v>
@@ -12996,22 +12994,22 @@
         <v>281</v>
       </c>
       <c r="F181" t="s">
+        <v>939</v>
+      </c>
+      <c r="G181" t="s">
         <v>940</v>
       </c>
-      <c r="G181" t="s">
+      <c r="H181" t="s">
         <v>941</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>942</v>
-      </c>
-      <c r="I181" t="s">
-        <v>943</v>
       </c>
       <c r="J181" t="s">
         <v>20</v>
       </c>
       <c r="L181" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M181" t="s">
         <v>312</v>
@@ -13031,25 +13029,25 @@
         <v>14</v>
       </c>
       <c r="E182" t="s">
+        <v>943</v>
+      </c>
+      <c r="F182" t="s">
         <v>944</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>945</v>
       </c>
-      <c r="G182" t="s">
+      <c r="H182" t="s">
         <v>946</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>947</v>
-      </c>
-      <c r="I182" t="s">
-        <v>948</v>
       </c>
       <c r="J182" t="s">
         <v>27</v>
       </c>
       <c r="L182" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M182" t="s">
         <v>313</v>
@@ -13069,25 +13067,25 @@
         <v>14</v>
       </c>
       <c r="E183" t="s">
+        <v>948</v>
+      </c>
+      <c r="F183" t="s">
         <v>949</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>950</v>
       </c>
-      <c r="G183" t="s">
+      <c r="H183" t="s">
         <v>951</v>
       </c>
-      <c r="H183" t="s">
-        <v>952</v>
-      </c>
       <c r="I183" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="J183" t="s">
         <v>33</v>
       </c>
       <c r="L183" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M183" t="s">
         <v>313</v>
@@ -13107,10 +13105,10 @@
         <v>14</v>
       </c>
       <c r="E184" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F184" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G184" t="s">
         <v>443</v>
@@ -13125,7 +13123,7 @@
         <v>27</v>
       </c>
       <c r="L184" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M184" t="s">
         <v>313</v>
@@ -13145,10 +13143,10 @@
         <v>14</v>
       </c>
       <c r="E185" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F185" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G185" t="s">
         <v>231</v>
@@ -13163,7 +13161,7 @@
         <v>57</v>
       </c>
       <c r="L185" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M185" t="s">
         <v>314</v>
@@ -13183,7 +13181,7 @@
         <v>14</v>
       </c>
       <c r="E186" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F186" t="s">
         <v>307</v>
@@ -13195,13 +13193,13 @@
         <v>309</v>
       </c>
       <c r="I186" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="J186" t="s">
         <v>57</v>
       </c>
       <c r="L186" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M186" t="s">
         <v>314</v>
@@ -13221,25 +13219,25 @@
         <v>14</v>
       </c>
       <c r="E187" t="s">
+        <v>963</v>
+      </c>
+      <c r="F187" t="s">
         <v>964</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>965</v>
       </c>
-      <c r="G187" t="s">
+      <c r="H187" t="s">
         <v>966</v>
       </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>967</v>
-      </c>
-      <c r="I187" t="s">
-        <v>968</v>
       </c>
       <c r="J187" t="s">
         <v>27</v>
       </c>
       <c r="L187" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M187" t="s">
         <v>44</v>
@@ -13259,7 +13257,7 @@
         <v>14</v>
       </c>
       <c r="E188" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F188" t="s">
         <v>323</v>
@@ -13271,13 +13269,13 @@
         <v>322</v>
       </c>
       <c r="I188" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J188" t="s">
         <v>33</v>
       </c>
       <c r="L188" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M188" t="s">
         <v>44</v>
@@ -13297,25 +13295,25 @@
         <v>14</v>
       </c>
       <c r="E189" t="s">
+        <v>969</v>
+      </c>
+      <c r="F189" t="s">
         <v>970</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>971</v>
       </c>
-      <c r="G189" t="s">
+      <c r="H189" t="s">
         <v>972</v>
       </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>973</v>
-      </c>
-      <c r="I189" t="s">
-        <v>974</v>
       </c>
       <c r="J189" t="s">
         <v>57</v>
       </c>
       <c r="L189" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M189" t="s">
         <v>553</v>
@@ -13335,28 +13333,28 @@
         <v>14</v>
       </c>
       <c r="E190" t="s">
+        <v>975</v>
+      </c>
+      <c r="F190" t="s">
         <v>976</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>977</v>
       </c>
-      <c r="G190" t="s">
+      <c r="H190" t="s">
         <v>978</v>
       </c>
-      <c r="H190" t="s">
+      <c r="I190" t="s">
         <v>979</v>
-      </c>
-      <c r="I190" t="s">
-        <v>980</v>
       </c>
       <c r="J190" t="s">
         <v>33</v>
       </c>
-      <c r="K190" s="3" t="s">
-        <v>1182</v>
+      <c r="K190" t="s">
+        <v>1181</v>
       </c>
       <c r="L190" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M190" t="s">
         <v>165</v>
@@ -13376,28 +13374,28 @@
         <v>14</v>
       </c>
       <c r="E191" t="s">
+        <v>980</v>
+      </c>
+      <c r="F191" t="s">
+        <v>869</v>
+      </c>
+      <c r="G191" t="s">
+        <v>870</v>
+      </c>
+      <c r="H191" t="s">
+        <v>871</v>
+      </c>
+      <c r="I191" t="s">
         <v>981</v>
-      </c>
-      <c r="F191" t="s">
-        <v>870</v>
-      </c>
-      <c r="G191" t="s">
-        <v>871</v>
-      </c>
-      <c r="H191" t="s">
-        <v>872</v>
-      </c>
-      <c r="I191" t="s">
-        <v>982</v>
       </c>
       <c r="J191" t="s">
         <v>33</v>
       </c>
-      <c r="K191" s="3" t="s">
-        <v>1183</v>
+      <c r="K191" t="s">
+        <v>1182</v>
       </c>
       <c r="L191" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M191" t="s">
         <v>165</v>
@@ -13417,28 +13415,28 @@
         <v>14</v>
       </c>
       <c r="E192" t="s">
+        <v>982</v>
+      </c>
+      <c r="F192" t="s">
         <v>983</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>984</v>
       </c>
-      <c r="G192" t="s">
+      <c r="H192" t="s">
         <v>985</v>
       </c>
-      <c r="H192" t="s">
+      <c r="I192" t="s">
         <v>986</v>
-      </c>
-      <c r="I192" t="s">
-        <v>987</v>
       </c>
       <c r="J192" t="s">
         <v>57</v>
       </c>
-      <c r="K192" s="3" t="s">
-        <v>1184</v>
+      <c r="K192" t="s">
+        <v>1183</v>
       </c>
       <c r="L192" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M192" t="s">
         <v>165</v>
@@ -13458,28 +13456,28 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
+        <v>987</v>
+      </c>
+      <c r="F193" t="s">
         <v>988</v>
       </c>
-      <c r="F193" t="s">
-        <v>989</v>
-      </c>
       <c r="G193" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H193" t="s">
         <v>449</v>
       </c>
       <c r="I193" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="J193" t="s">
         <v>27</v>
       </c>
-      <c r="K193" s="3" t="s">
-        <v>1195</v>
+      <c r="K193" t="s">
+        <v>1194</v>
       </c>
       <c r="L193" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M193" t="s">
         <v>110</v>
@@ -13499,10 +13497,10 @@
         <v>14</v>
       </c>
       <c r="E194" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F194" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G194" t="s">
         <v>449</v>
@@ -13516,11 +13514,11 @@
       <c r="J194" t="s">
         <v>20</v>
       </c>
-      <c r="K194" s="3" t="s">
-        <v>1196</v>
+      <c r="K194" t="s">
+        <v>1195</v>
       </c>
       <c r="L194" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M194" t="s">
         <v>110</v>
@@ -13540,28 +13538,28 @@
         <v>14</v>
       </c>
       <c r="E195" t="s">
+        <v>990</v>
+      </c>
+      <c r="F195" t="s">
         <v>991</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
+        <v>871</v>
+      </c>
+      <c r="H195" t="s">
         <v>992</v>
       </c>
-      <c r="G195" t="s">
-        <v>872</v>
-      </c>
-      <c r="H195" t="s">
+      <c r="I195" t="s">
         <v>993</v>
-      </c>
-      <c r="I195" t="s">
-        <v>994</v>
       </c>
       <c r="J195" t="s">
         <v>57</v>
       </c>
-      <c r="K195" s="3" t="s">
-        <v>1197</v>
+      <c r="K195" t="s">
+        <v>1196</v>
       </c>
       <c r="L195" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M195" t="s">
         <v>110</v>
@@ -13575,34 +13573,34 @@
         <v>12</v>
       </c>
       <c r="C196" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D196" t="s">
         <v>14</v>
       </c>
       <c r="E196" t="s">
+        <v>994</v>
+      </c>
+      <c r="F196" t="s">
         <v>995</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>996</v>
       </c>
-      <c r="G196" t="s">
+      <c r="H196" t="s">
         <v>997</v>
       </c>
-      <c r="H196" t="s">
+      <c r="I196" t="s">
         <v>998</v>
-      </c>
-      <c r="I196" t="s">
-        <v>999</v>
       </c>
       <c r="J196" t="s">
         <v>57</v>
       </c>
       <c r="L196" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M196" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -13613,34 +13611,34 @@
         <v>12</v>
       </c>
       <c r="C197" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D197" t="s">
         <v>14</v>
       </c>
       <c r="E197" t="s">
+        <v>999</v>
+      </c>
+      <c r="F197" t="s">
         <v>1000</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>1001</v>
       </c>
-      <c r="G197" t="s">
+      <c r="H197" t="s">
         <v>1002</v>
       </c>
-      <c r="H197" t="s">
+      <c r="I197" t="s">
         <v>1003</v>
-      </c>
-      <c r="I197" t="s">
-        <v>1004</v>
       </c>
       <c r="J197" t="s">
         <v>20</v>
       </c>
       <c r="L197" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M197" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="198" spans="1:13">
@@ -13657,28 +13655,28 @@
         <v>14</v>
       </c>
       <c r="E198" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F198" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G198" t="s">
         <v>1005</v>
       </c>
-      <c r="G198" t="s">
+      <c r="H198" t="s">
         <v>1006</v>
       </c>
-      <c r="H198" t="s">
+      <c r="I198" t="s">
         <v>1007</v>
-      </c>
-      <c r="I198" t="s">
-        <v>1008</v>
       </c>
       <c r="J198" t="s">
         <v>27</v>
       </c>
-      <c r="K198" s="3" t="s">
-        <v>1167</v>
+      <c r="K198" t="s">
+        <v>1166</v>
       </c>
       <c r="L198" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M198" t="s">
         <v>135</v>
@@ -13698,28 +13696,28 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F199" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G199" t="s">
+        <v>823</v>
+      </c>
+      <c r="H199" t="s">
+        <v>825</v>
+      </c>
+      <c r="I199" t="s">
         <v>824</v>
-      </c>
-      <c r="H199" t="s">
-        <v>826</v>
-      </c>
-      <c r="I199" t="s">
-        <v>825</v>
       </c>
       <c r="J199" t="s">
         <v>20</v>
       </c>
-      <c r="K199" s="3" t="s">
-        <v>1161</v>
+      <c r="K199" t="s">
+        <v>1160</v>
       </c>
       <c r="L199" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M199" t="s">
         <v>197</v>
@@ -13739,28 +13737,28 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F200" t="s">
         <v>1010</v>
       </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
         <v>1011</v>
-      </c>
-      <c r="G200" t="s">
-        <v>1012</v>
       </c>
       <c r="H200" t="s">
         <v>177</v>
       </c>
       <c r="I200" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="J200" t="s">
         <v>27</v>
       </c>
       <c r="K200" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="L200" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M200" t="s">
         <v>45</v>
@@ -13780,10 +13778,10 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F201" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G201" t="s">
         <v>187</v>
@@ -13792,13 +13790,13 @@
         <v>189</v>
       </c>
       <c r="I201" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="J201" t="s">
         <v>20</v>
       </c>
       <c r="L201" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M201" t="s">
         <v>191</v>
@@ -13818,25 +13816,25 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F202" t="s">
         <v>1021</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>1022</v>
       </c>
-      <c r="G202" t="s">
+      <c r="H202" t="s">
         <v>1023</v>
       </c>
-      <c r="H202" t="s">
+      <c r="I202" t="s">
         <v>1024</v>
-      </c>
-      <c r="I202" t="s">
-        <v>1025</v>
       </c>
       <c r="J202" t="s">
         <v>33</v>
       </c>
       <c r="L202" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M202" t="s">
         <v>204</v>
@@ -13856,25 +13854,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F203" t="s">
         <v>1015</v>
       </c>
-      <c r="F203" t="s">
+      <c r="G203" t="s">
         <v>1016</v>
       </c>
-      <c r="G203" t="s">
+      <c r="H203" t="s">
         <v>1017</v>
       </c>
-      <c r="H203" t="s">
-        <v>1018</v>
-      </c>
       <c r="I203" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="J203" t="s">
         <v>27</v>
       </c>
       <c r="L203" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M203" t="s">
         <v>225</v>
@@ -13894,25 +13892,25 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F204" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G204" t="s">
         <v>1028</v>
       </c>
-      <c r="G204" t="s">
+      <c r="H204" t="s">
         <v>1029</v>
       </c>
-      <c r="H204" t="s">
+      <c r="I204" t="s">
         <v>1030</v>
-      </c>
-      <c r="I204" t="s">
-        <v>1031</v>
       </c>
       <c r="J204" t="s">
         <v>20</v>
       </c>
       <c r="L204" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M204" t="s">
         <v>226</v>
@@ -13932,25 +13930,25 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F205" t="s">
         <v>1032</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>1033</v>
       </c>
-      <c r="G205" t="s">
+      <c r="H205" t="s">
         <v>1034</v>
       </c>
-      <c r="H205" t="s">
-        <v>1035</v>
-      </c>
       <c r="I205" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="J205" t="s">
         <v>27</v>
       </c>
       <c r="L205" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M205" t="s">
         <v>267</v>
@@ -13970,25 +13968,25 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F206" t="s">
         <v>1036</v>
       </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
         <v>1037</v>
       </c>
-      <c r="G206" t="s">
+      <c r="H206" t="s">
         <v>1038</v>
       </c>
-      <c r="H206" t="s">
+      <c r="I206" t="s">
         <v>1039</v>
-      </c>
-      <c r="I206" t="s">
-        <v>1040</v>
       </c>
       <c r="J206" t="s">
         <v>27</v>
       </c>
       <c r="L206" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M206" t="s">
         <v>212</v>
@@ -14008,7 +14006,7 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F207" t="s">
         <v>201</v>
@@ -14026,7 +14024,7 @@
         <v>20</v>
       </c>
       <c r="L207" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M207" t="s">
         <v>226</v>
@@ -14046,10 +14044,10 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F208" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G208" t="s">
         <v>236</v>
@@ -14064,7 +14062,7 @@
         <v>57</v>
       </c>
       <c r="L208" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M208" t="s">
         <v>265</v>
@@ -14084,7 +14082,7 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F209" t="s">
         <v>234</v>
@@ -14102,7 +14100,7 @@
         <v>20</v>
       </c>
       <c r="L209" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M209" t="s">
         <v>265</v>
@@ -14122,25 +14120,25 @@
         <v>14</v>
       </c>
       <c r="E210" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F210" t="s">
         <v>1042</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>1043</v>
       </c>
-      <c r="G210" t="s">
+      <c r="H210" t="s">
         <v>1044</v>
       </c>
-      <c r="H210" t="s">
+      <c r="I210" t="s">
         <v>1045</v>
-      </c>
-      <c r="I210" t="s">
-        <v>1046</v>
       </c>
       <c r="J210" t="s">
         <v>33</v>
       </c>
       <c r="L210" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M210" t="s">
         <v>266</v>
@@ -14160,25 +14158,25 @@
         <v>14</v>
       </c>
       <c r="E211" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F211" t="s">
         <v>1047</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>1048</v>
       </c>
-      <c r="G211" t="s">
+      <c r="H211" t="s">
         <v>1049</v>
       </c>
-      <c r="H211" t="s">
-        <v>1050</v>
-      </c>
       <c r="I211" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="J211" t="s">
         <v>57</v>
       </c>
       <c r="L211" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M211" t="s">
         <v>266</v>
@@ -14198,7 +14196,7 @@
         <v>14</v>
       </c>
       <c r="E212" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F212" t="s">
         <v>234</v>
@@ -14207,16 +14205,16 @@
         <v>231</v>
       </c>
       <c r="H212" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="I212" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="J212" t="s">
         <v>20</v>
       </c>
       <c r="L212" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M212" t="s">
         <v>313</v>
@@ -14236,25 +14234,25 @@
         <v>14</v>
       </c>
       <c r="E213" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F213" t="s">
         <v>1057</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>1058</v>
       </c>
-      <c r="G213" t="s">
+      <c r="H213" t="s">
         <v>1059</v>
       </c>
-      <c r="H213" t="s">
-        <v>1060</v>
-      </c>
       <c r="I213" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="J213" t="s">
         <v>20</v>
       </c>
       <c r="L213" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M213" t="s">
         <v>313</v>
@@ -14274,25 +14272,25 @@
         <v>14</v>
       </c>
       <c r="E214" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F214" t="s">
         <v>1061</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>1062</v>
       </c>
-      <c r="G214" t="s">
+      <c r="H214" t="s">
         <v>1063</v>
       </c>
-      <c r="H214" t="s">
+      <c r="I214" t="s">
         <v>1064</v>
-      </c>
-      <c r="I214" t="s">
-        <v>1065</v>
       </c>
       <c r="J214" t="s">
         <v>27</v>
       </c>
       <c r="L214" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M214" t="s">
         <v>313</v>
@@ -14312,25 +14310,25 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F215" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G215" t="s">
         <v>354</v>
       </c>
       <c r="H215" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="I215" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="J215" t="s">
         <v>33</v>
       </c>
       <c r="L215" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M215" t="s">
         <v>312</v>
@@ -14350,25 +14348,25 @@
         <v>14</v>
       </c>
       <c r="E216" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F216" t="s">
         <v>1068</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>1069</v>
       </c>
-      <c r="G216" t="s">
+      <c r="H216" t="s">
         <v>1070</v>
       </c>
-      <c r="H216" t="s">
+      <c r="I216" t="s">
         <v>1071</v>
-      </c>
-      <c r="I216" t="s">
-        <v>1072</v>
       </c>
       <c r="J216" t="s">
         <v>57</v>
       </c>
       <c r="L216" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M216" t="s">
         <v>312</v>
@@ -14391,22 +14389,22 @@
         <v>286</v>
       </c>
       <c r="F217" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G217" t="s">
         <v>1073</v>
       </c>
-      <c r="G217" t="s">
+      <c r="H217" t="s">
         <v>1074</v>
       </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>1075</v>
-      </c>
-      <c r="I217" t="s">
-        <v>1076</v>
       </c>
       <c r="J217" t="s">
         <v>33</v>
       </c>
       <c r="L217" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M217" t="s">
         <v>312</v>
@@ -14426,25 +14424,25 @@
         <v>14</v>
       </c>
       <c r="E218" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F218" t="s">
         <v>1077</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>1078</v>
       </c>
-      <c r="G218" t="s">
+      <c r="H218" t="s">
         <v>1079</v>
       </c>
-      <c r="H218" t="s">
+      <c r="I218" t="s">
         <v>1080</v>
-      </c>
-      <c r="I218" t="s">
-        <v>1081</v>
       </c>
       <c r="J218" t="s">
         <v>33</v>
       </c>
       <c r="L218" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M218" t="s">
         <v>312</v>
@@ -14464,28 +14462,28 @@
         <v>14</v>
       </c>
       <c r="E219" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F219" t="s">
         <v>1082</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>1083</v>
       </c>
-      <c r="G219" t="s">
+      <c r="H219" t="s">
         <v>1084</v>
       </c>
-      <c r="H219" t="s">
-        <v>1085</v>
-      </c>
       <c r="I219" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="J219" t="s">
         <v>33</v>
       </c>
       <c r="K219" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="L219" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M219" t="s">
         <v>311</v>
@@ -14505,28 +14503,28 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F220" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G220" t="s">
         <v>1086</v>
       </c>
-      <c r="G220" t="s">
+      <c r="H220" t="s">
         <v>1087</v>
       </c>
-      <c r="H220" t="s">
+      <c r="I220" t="s">
         <v>1088</v>
-      </c>
-      <c r="I220" t="s">
-        <v>1089</v>
       </c>
       <c r="J220" t="s">
         <v>27</v>
       </c>
       <c r="K220" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="L220" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M220" t="s">
         <v>311</v>
@@ -14546,7 +14544,7 @@
         <v>14</v>
       </c>
       <c r="E221" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="F221" t="s">
         <v>237</v>
@@ -14564,10 +14562,10 @@
         <v>27</v>
       </c>
       <c r="K221" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L221" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M221" t="s">
         <v>311</v>
@@ -14587,28 +14585,28 @@
         <v>14</v>
       </c>
       <c r="E222" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F222" t="s">
         <v>1090</v>
       </c>
-      <c r="F222" t="s">
-        <v>1091</v>
-      </c>
       <c r="G222" t="s">
+        <v>923</v>
+      </c>
+      <c r="H222" t="s">
         <v>924</v>
       </c>
-      <c r="H222" t="s">
-        <v>925</v>
-      </c>
       <c r="I222" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="J222" t="s">
         <v>20</v>
       </c>
       <c r="K222" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="L222" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M222" t="s">
         <v>311</v>
@@ -14631,25 +14629,25 @@
         <v>301</v>
       </c>
       <c r="F223" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G223" t="s">
         <v>1092</v>
       </c>
-      <c r="G223" t="s">
+      <c r="H223" t="s">
         <v>1093</v>
       </c>
-      <c r="H223" t="s">
+      <c r="I223" t="s">
         <v>1094</v>
-      </c>
-      <c r="I223" t="s">
-        <v>1095</v>
       </c>
       <c r="J223" t="s">
         <v>57</v>
       </c>
       <c r="K223" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="L223" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M223" t="s">
         <v>314</v>
@@ -14669,28 +14667,28 @@
         <v>14</v>
       </c>
       <c r="E224" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F224" t="s">
         <v>1096</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>1097</v>
       </c>
-      <c r="G224" t="s">
+      <c r="H224" t="s">
         <v>1098</v>
       </c>
-      <c r="H224" t="s">
+      <c r="I224" t="s">
         <v>1099</v>
-      </c>
-      <c r="I224" t="s">
-        <v>1100</v>
       </c>
       <c r="J224" t="s">
         <v>33</v>
       </c>
       <c r="K224" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L224" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M224" t="s">
         <v>314</v>
@@ -14710,7 +14708,7 @@
         <v>14</v>
       </c>
       <c r="E225" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="F225" t="s">
         <v>234</v>
@@ -14719,7 +14717,7 @@
         <v>231</v>
       </c>
       <c r="H225" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="I225" t="s">
         <v>444</v>
@@ -14728,10 +14726,10 @@
         <v>20</v>
       </c>
       <c r="K225" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L225" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M225" t="s">
         <v>314</v>
@@ -14751,28 +14749,28 @@
         <v>14</v>
       </c>
       <c r="E226" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F226" t="s">
         <v>1101</v>
       </c>
-      <c r="F226" t="s">
+      <c r="G226" t="s">
         <v>1102</v>
       </c>
-      <c r="G226" t="s">
+      <c r="H226" t="s">
         <v>1103</v>
       </c>
-      <c r="H226" t="s">
-        <v>1104</v>
-      </c>
       <c r="I226" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J226" t="s">
         <v>33</v>
       </c>
       <c r="K226" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="L226" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M226" t="s">
         <v>314</v>
@@ -14792,7 +14790,7 @@
         <v>14</v>
       </c>
       <c r="E227" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F227" t="s">
         <v>323</v>
@@ -14810,7 +14808,7 @@
         <v>33</v>
       </c>
       <c r="L227" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M227" t="s">
         <v>44</v>
@@ -14830,25 +14828,25 @@
         <v>14</v>
       </c>
       <c r="E228" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F228" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G228" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H228" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I228" t="s">
         <v>1119</v>
-      </c>
-      <c r="F228" t="s">
-        <v>1106</v>
-      </c>
-      <c r="G228" t="s">
-        <v>1107</v>
-      </c>
-      <c r="H228" t="s">
-        <v>1108</v>
-      </c>
-      <c r="I228" t="s">
-        <v>1120</v>
       </c>
       <c r="J228" t="s">
         <v>57</v>
       </c>
       <c r="L228" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M228" t="s">
         <v>44</v>
@@ -14868,25 +14866,25 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F229" t="s">
         <v>1109</v>
       </c>
-      <c r="F229" t="s">
+      <c r="G229" t="s">
         <v>1110</v>
       </c>
-      <c r="G229" t="s">
+      <c r="H229" t="s">
         <v>1111</v>
       </c>
-      <c r="H229" t="s">
+      <c r="I229" t="s">
         <v>1112</v>
-      </c>
-      <c r="I229" t="s">
-        <v>1113</v>
       </c>
       <c r="J229" t="s">
         <v>20</v>
       </c>
       <c r="L229" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M229" t="s">
         <v>334</v>
@@ -14906,25 +14904,25 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F230" t="s">
+        <v>972</v>
+      </c>
+      <c r="G230" t="s">
+        <v>971</v>
+      </c>
+      <c r="H230" t="s">
+        <v>970</v>
+      </c>
+      <c r="I230" t="s">
         <v>973</v>
-      </c>
-      <c r="G230" t="s">
-        <v>972</v>
-      </c>
-      <c r="H230" t="s">
-        <v>971</v>
-      </c>
-      <c r="I230" t="s">
-        <v>974</v>
       </c>
       <c r="J230" t="s">
         <v>33</v>
       </c>
       <c r="L230" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M230" t="s">
         <v>334</v>

--- a/QUESTOES PROVA CRS.xlsx
+++ b/QUESTOES PROVA CRS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julião\Downloads\chobot-main (2)\chobot-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AB010F-B940-4B4C-B2DA-040C932C2A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C09BF2-B8B2-4134-8E2F-FBD189908FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21ECCF9C-427C-4719-9746-16AD4683314D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2631" uniqueCount="1201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2665" uniqueCount="1209">
   <si>
     <t>ID</t>
   </si>
@@ -4288,243 +4288,6 @@
   </si>
   <si>
     <t xml:space="preserve">Os crimes previstos na Lei de Abuso de Autoridade são de ação penal pública condicionada à representação. </t>
-  </si>
-  <si>
-    <r>
-      <t>📖 Fundamentação Legal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> O erro está na palavra "condicionada". Os crimes de abuso de autoridade não dependem de representação da vítima para que o Ministério Público ofereça a denúncia. Conforme a redação promulgada do </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Art. 3º</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Os crimes previstos nesta Lei são de ação penal pública </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>incondicionada</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>."</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">-------------------------------------------------------------------------------- </t>
-  </si>
-  <si>
-    <t>❌ ANÁLISE DAS DEMAIS ALTERNATIVAS (Estão corretas perante a lei, portanto, não são a resposta da questão):</t>
-  </si>
-  <si>
-    <t>Sobre a obrigação de indenizar:</t>
-  </si>
-  <si>
-    <r>
-      <t>Onde está na norma:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> A afirmação é verdadeira. O </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>Art. 4º, I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve">, elenca como um dos efeitos da condenação: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>"tornar certa a obrigação de indenizar o dano causado pelo crime, devendo o juiz, a requerimento do ofendido, fixar na sentença o valor mínimo para reparação dos danos..."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Sobre a finalidade específica do agente (Dolo Específico):</t>
-  </si>
-  <si>
-    <r>
-      <t>Onde está na norma:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> A afirmação é verdadeira e é uma das principais "pegadinhas" de prova. Não existe abuso de autoridade culposo ou sem intenção específica. O </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>Art. 1º, § 1º</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve">, prevê: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve">"As condutas descritas nesta Lei constituem crime de abuso de autoridade quando praticadas pelo agente com a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>finalidade específica de prejudicar outrem ou beneficiar a si mesmo ou a terceiro, ou, ainda, por mero capricho ou satisfação pessoal</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Sobre quem pode ser o sujeito ativo do crime:</t>
-  </si>
-  <si>
-    <r>
-      <t>Onde está na norma:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> A afirmação é verdadeira. A lei adotou um conceito amplíssimo de agente público. O </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>Art. 2º, caput</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve">, estabelece: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>"É sujeito ativo do crime de abuso de autoridade qualquer agente público, servidor ou não, da administração direta, indireta ou fundacional de qualquer dos Poderes da União, dos Estados, do Distrito Federal, dos Municípios e de Território..."</t>
-    </r>
   </si>
   <si>
     <t>✅ ALTERNATIVA CORRETA (A QUE DEVE SER MARCADA POR ESTAR INCORRETA): A afirmativa que diz: "Os crimes previstos na Lei de Abuso de Autoridade são de ação penal pública condicionada à representação."
@@ -4905,104 +4668,6 @@
         <rFont val="Google Sans Text"/>
       </rPr>
       <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Item III - VERDADEIRO:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>(Informação externa à fonte)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> A assertiva define o crime de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>Conspiração</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve">, tipificado no </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>Art. 152</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> do CPM: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>"Concertarem-se militares ou assemelhados para a prática do crime de motim ou revolta"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve">. Como o Motim (Art. 149, I) inclui a conduta de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>"agindo contra a ordem recebida de superior"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF303030"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>, o concerto (acordo/planejamento) para realizar essa ação é perfeitamente classificado como conspiração.</t>
     </r>
   </si>
   <si>
@@ -5403,12 +5068,78 @@
   <si>
     <t>O crime de desacato a superior classifica-se como propriamente militar e terá sua pena agravada se o superior for Oficial.</t>
   </si>
+  <si>
+    <t>Considerando o que dispõe a Diretriz n. 3.01.01/2019 – CG, a qual Regula o Emprego Operacional da Polícia Militar de Minas Gerais, analise as assertivas abaixo e, em seguida responda o que se pede: 
+I. Detentora exclusiva da execução do policiamento ostensivo a PMMG norteia seu emprego operacional com base em parâmetros de qualidade, produtividade e sistematicidade. 
+II. O policiamento orientado para o problema utiliza-se do método IARA, o qual possui quatro fases: Identificação, Análise, Resposta e Avaliação. A resposta é a chave para o referido método, pois é nesta fase que ocorre o desenvolvimento das ações adequadas para enfrentamento do problema que foi claramente identificado e detalhadamente analisado. 
+III. A gestão pública dos novos tempos impõe alguns desafios, que somente serão vencidos a partir da adoção de um planejamento prospectivo que contemple: a capacidade de conquistar e fidelizar clientes, a necessidade de diferenciar produtos e serviços e a necessidade de fixar objetivos e atingir resultados. 
+IV. No emprego do Esforço Suplementar, considerando as características específicas da Academia de Polícia Militar e do Batalhão Metrópole, no que se refere ao efetivo disponível da atividade-meio empregado na atividade-fim, estes poderão ser empregados nos diversos esforços de escalonamento da Malha Protetora, conforme o conceito de operação atribuído, em caráter ordinário ou extraordinário, preferencialmente, nas subáreas das Cias Operacionais da RMBH onde os índices criminais demonstrem esta necessidade, como força de reação do Comando-Geral, a critério do Chefe do Estado-Maior da Polícia Militar. 
+Assinale a opção CORRETA:</t>
+  </si>
+  <si>
+    <t>penas as assertivas II e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>As assertivas I, III e IV são verdadeiras.</t>
+  </si>
+  <si>
+    <t>CHO/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Com base na Lei Federal n. 8.429/1992 – Lei de Improbidade Administrativa, considere a seguinte situação hipotética e, ao final, responda o que se pede:  
+“Um policial militar da ativa da PMMG, dolosamente, revela um fato de que tinha ciência em razão de suas atribuições e que deveria permanecer em segredo, propiciando, também dolosamente, o beneficiamento de determinada pessoa pela posse de informação privilegiada.” 
+Assinale a alternativa que contém a resposta CORRETA: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O caso hipotético se encaixa em modalidade de improbidade administrativa punida com perda dos bens acrescidos ilicitamente e suspensão dos direitos políticos de até 12 anos. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O caso hipotético se encaixa em modalidade de improbidade administrativa punida com multa civil de até 24 vezes a remuneração do agente e proibição de contratar com o Poder Público ou receber benefícios pelo prazo não superior a 4 (quatro) anos. </t>
+  </si>
+  <si>
+    <t>O caso hipotético não se encaixa em quaisquer das hipóteses previstas como atos de improbidade administrativa.</t>
+  </si>
+  <si>
+    <t>O caso hipotético se encaixa em modalidade de improbidade administrativa punida com perda dos bens acrescidos ilicitamente e suspensão dos direitos políticos por até 14 anos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De acordo com o estabelecido na Constituição do Estado de Minas Gerais, de 1989, examine os itens abaixo e responda, ao final, o que se pede: 
+I. A Justiça Militar é constituída, em primeiro grau, pelos Juízes de Direito e, em segundo grau, pelos Conselhos de Justiça e pelo Tribunal de Justiça Militar. 
+II. Os Conselhos de Justiça, com sede na Capital e jurisdição em todo o território do Estado, compõem se de juízes Oficiais da ativa, do mais alto posto da Polícia Militar ou do Corpo de Bombeiros Militar, e de juízes civis, em número ímpar, fixado na Lei de Organização e Divisão Judiciárias, excedendo o número de juízes Oficiais ao de juízes civis em uma unidade. 
+III. A Polícia Militar e o Corpo de Bombeiros Militar, forças públicas estaduais, são órgãos permanentes, organizados com base na hierarquia e na disciplina militares e comandados, preferencialmente, por oficial da ativa do último posto, competindo ao Corpo de Bombeiros Militar, dentre outras competências, as perícias de incêndio. 
+IV. A Seção VI, sob o título “Dos Militares do Estado”, trata apenas dos Policiais Militares do Estado de Minas Gerais. 
+Assinale a alternativa que contém a resposta CORRETA: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">As assertivas I, II, III e IV são falsas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somente as assertivas I e III são verdadeiras. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somente a assertiva IV é verdadeira. </t>
+  </si>
+  <si>
+    <t>Considerando o que dispõe o Decreto-Lei n. 1.001/1969 – Código Penal Militar, especialmente quanto à definição de crime militar, assinale a alternativa INCORRETA:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Consideram-se crimes militares, em tempo de paz, os crimes previstos no Código Penal Militar e os previstos na legislação penal, quando praticados por militar em situação de atividade ou assemelhado, em lugar sujeito à administração militar, contra militar da reserva, ou reformado, ou assemelhado, ou civil. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Consideram-se crimes militares, em tempo de paz, os crimes previstos no Código Penal Militar e os previstos na legislação penal, quando praticados por militar em serviço ou atuando em razão da função, em comissão de natureza militar, ou em formatura, ainda que fora do lugar sujeito à administração militar, contra militar da reserva, ou reformado, ou civil. </t>
+  </si>
+  <si>
+    <t>Consideram-se crimes militares, em tempo de paz, os crimes previstos no Código Penal Militar e os previstos na legislação penal, quando praticados por militar durante o período de manobras ou exercício, contra militar da reserva, ou reformado, ou assemelhado, ou civil.</t>
+  </si>
+  <si>
+    <t>Consideram-se crimes militares, em tempo de paz, os crimes previstos no Código Penal Militar e os previstos na legislação penal, quando praticados por militar da reserva contra a ordem administrativa expedida pelo juízo da circunscrição militar.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5437,23 +5168,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF303030"/>
       <name val="Google Sans Text"/>
@@ -5465,13 +5179,6 @@
       <name val="Google Sans Text"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF303030"/>
-      <name val="Google Sans Text"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="11"/>
       <color rgb="FF303030"/>
@@ -5524,7 +5231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5536,12 +5243,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5876,7 +5584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299ECF81-BBAD-4B94-AB20-5ECD9C9E2A6C}">
-  <dimension ref="A1:M230"/>
+  <dimension ref="A1:M234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22.85546875" customWidth="1"/>
@@ -6559,7 +6267,7 @@
         <v>20</v>
       </c>
       <c r="K17" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
       <c r="L17" t="s">
         <v>103</v>
@@ -6600,7 +6308,7 @@
         <v>57</v>
       </c>
       <c r="K18" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="L18" t="s">
         <v>103</v>
@@ -6717,7 +6425,7 @@
         <v>20</v>
       </c>
       <c r="K21" t="s">
-        <v>1161</v>
+        <v>1152</v>
       </c>
       <c r="L21" t="s">
         <v>103</v>
@@ -6758,7 +6466,7 @@
         <v>33</v>
       </c>
       <c r="K22" t="s">
-        <v>1162</v>
+        <v>1153</v>
       </c>
       <c r="L22" t="s">
         <v>103</v>
@@ -6913,7 +6621,7 @@
         <v>20</v>
       </c>
       <c r="K26" t="s">
-        <v>1167</v>
+        <v>1158</v>
       </c>
       <c r="L26" t="s">
         <v>103</v>
@@ -6954,7 +6662,7 @@
         <v>57</v>
       </c>
       <c r="K27" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="L27" t="s">
         <v>103</v>
@@ -7115,7 +6823,7 @@
         <v>20</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>1154</v>
+        <v>1145</v>
       </c>
       <c r="L31" t="s">
         <v>103</v>
@@ -7155,9 +6863,7 @@
       <c r="J32" t="s">
         <v>27</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>1145</v>
-      </c>
+      <c r="K32" s="3"/>
       <c r="L32" t="s">
         <v>103</v>
       </c>
@@ -7196,9 +6902,6 @@
       <c r="J33" t="s">
         <v>57</v>
       </c>
-      <c r="K33" t="s">
-        <v>1146</v>
-      </c>
       <c r="L33" t="s">
         <v>103</v>
       </c>
@@ -7237,9 +6940,7 @@
       <c r="J34" t="s">
         <v>27</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>1147</v>
-      </c>
+      <c r="K34" s="3"/>
       <c r="L34" t="s">
         <v>103</v>
       </c>
@@ -7317,9 +7018,7 @@
       <c r="J36" t="s">
         <v>27</v>
       </c>
-      <c r="K36" s="5" t="s">
-        <v>1148</v>
-      </c>
+      <c r="K36" s="5"/>
       <c r="L36" t="s">
         <v>103</v>
       </c>
@@ -7358,9 +7057,7 @@
       <c r="J37" t="s">
         <v>57</v>
       </c>
-      <c r="K37" s="6" t="s">
-        <v>1149</v>
-      </c>
+      <c r="K37" s="6"/>
       <c r="L37" t="s">
         <v>103</v>
       </c>
@@ -7399,9 +7096,7 @@
       <c r="J38" t="s">
         <v>33</v>
       </c>
-      <c r="K38" s="5" t="s">
-        <v>1150</v>
-      </c>
+      <c r="K38" s="5"/>
       <c r="L38" t="s">
         <v>103</v>
       </c>
@@ -7440,9 +7135,7 @@
       <c r="J39" t="s">
         <v>33</v>
       </c>
-      <c r="K39" s="6" t="s">
-        <v>1151</v>
-      </c>
+      <c r="K39" s="6"/>
       <c r="L39" t="s">
         <v>103</v>
       </c>
@@ -7481,9 +7174,7 @@
       <c r="J40" t="s">
         <v>20</v>
       </c>
-      <c r="K40" s="5" t="s">
-        <v>1152</v>
-      </c>
+      <c r="K40" s="5"/>
       <c r="L40" t="s">
         <v>103</v>
       </c>
@@ -7522,9 +7213,7 @@
       <c r="J41" t="s">
         <v>27</v>
       </c>
-      <c r="K41" s="6" t="s">
-        <v>1153</v>
-      </c>
+      <c r="K41" s="6"/>
       <c r="L41" t="s">
         <v>103</v>
       </c>
@@ -8758,7 +8447,7 @@
         <v>20</v>
       </c>
       <c r="K72" t="s">
-        <v>1163</v>
+        <v>1154</v>
       </c>
       <c r="L72" t="s">
         <v>341</v>
@@ -8799,7 +8488,7 @@
         <v>27</v>
       </c>
       <c r="K73" t="s">
-        <v>1197</v>
+        <v>1187</v>
       </c>
       <c r="L73" t="s">
         <v>341</v>
@@ -8840,7 +8529,7 @@
         <v>33</v>
       </c>
       <c r="K74" t="s">
-        <v>1169</v>
+        <v>1160</v>
       </c>
       <c r="L74" t="s">
         <v>341</v>
@@ -8881,7 +8570,7 @@
         <v>27</v>
       </c>
       <c r="K75" t="s">
-        <v>1170</v>
+        <v>1161</v>
       </c>
       <c r="L75" t="s">
         <v>341</v>
@@ -8960,7 +8649,7 @@
         <v>57</v>
       </c>
       <c r="K77" t="s">
-        <v>1186</v>
+        <v>1176</v>
       </c>
       <c r="L77" t="s">
         <v>341</v>
@@ -9115,7 +8804,7 @@
         <v>27</v>
       </c>
       <c r="K81" t="s">
-        <v>1155</v>
+        <v>1146</v>
       </c>
       <c r="L81" t="s">
         <v>341</v>
@@ -10068,7 +9757,7 @@
         <v>27</v>
       </c>
       <c r="K106" t="s">
-        <v>1156</v>
+        <v>1147</v>
       </c>
       <c r="L106" t="s">
         <v>508</v>
@@ -10109,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="K107" t="s">
-        <v>1187</v>
+        <v>1177</v>
       </c>
       <c r="L107" t="s">
         <v>508</v>
@@ -10150,7 +9839,7 @@
         <v>20</v>
       </c>
       <c r="K108" t="s">
-        <v>1188</v>
+        <v>1178</v>
       </c>
       <c r="L108" t="s">
         <v>508</v>
@@ -10229,7 +9918,7 @@
         <v>33</v>
       </c>
       <c r="K110" t="s">
-        <v>1198</v>
+        <v>1188</v>
       </c>
       <c r="L110" t="s">
         <v>508</v>
@@ -10390,7 +10079,7 @@
         <v>20</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>1171</v>
+        <v>1162</v>
       </c>
       <c r="L114" t="s">
         <v>508</v>
@@ -10416,7 +10105,7 @@
         <v>675</v>
       </c>
       <c r="F115" t="s">
-        <v>1200</v>
+        <v>1190</v>
       </c>
       <c r="G115" t="s">
         <v>676</v>
@@ -10431,7 +10120,7 @@
         <v>27</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>1176</v>
+        <v>1166</v>
       </c>
       <c r="L115" t="s">
         <v>508</v>
@@ -10511,7 +10200,7 @@
         <v>57</v>
       </c>
       <c r="K117" s="5" t="s">
-        <v>1172</v>
+        <v>1163</v>
       </c>
       <c r="L117" t="s">
         <v>508</v>
@@ -10552,7 +10241,7 @@
         <v>33</v>
       </c>
       <c r="K118" s="5" t="s">
-        <v>1173</v>
+        <v>1164</v>
       </c>
       <c r="L118" t="s">
         <v>508</v>
@@ -10592,9 +10281,7 @@
       <c r="J119" t="s">
         <v>27</v>
       </c>
-      <c r="K119" s="5" t="s">
-        <v>1174</v>
-      </c>
+      <c r="K119" s="5"/>
       <c r="L119" t="s">
         <v>508</v>
       </c>
@@ -10634,7 +10321,7 @@
         <v>20</v>
       </c>
       <c r="K120" s="5" t="s">
-        <v>1175</v>
+        <v>1165</v>
       </c>
       <c r="L120" t="s">
         <v>714</v>
@@ -11283,7 +10970,7 @@
         <v>27</v>
       </c>
       <c r="K137" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
       <c r="L137" t="s">
         <v>714</v>
@@ -11324,7 +11011,7 @@
         <v>57</v>
       </c>
       <c r="K138" t="s">
-        <v>1177</v>
+        <v>1167</v>
       </c>
       <c r="L138" t="s">
         <v>714</v>
@@ -11403,7 +11090,7 @@
         <v>57</v>
       </c>
       <c r="K140" t="s">
-        <v>1178</v>
+        <v>1168</v>
       </c>
       <c r="L140" t="s">
         <v>714</v>
@@ -11444,7 +11131,7 @@
         <v>33</v>
       </c>
       <c r="K141" t="s">
-        <v>1189</v>
+        <v>1179</v>
       </c>
       <c r="L141" t="s">
         <v>714</v>
@@ -11523,7 +11210,7 @@
         <v>33</v>
       </c>
       <c r="K143" t="s">
-        <v>1164</v>
+        <v>1155</v>
       </c>
       <c r="L143" t="s">
         <v>714</v>
@@ -11640,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="K146" t="s">
-        <v>1157</v>
+        <v>1148</v>
       </c>
       <c r="L146" t="s">
         <v>714</v>
@@ -11760,7 +11447,7 @@
         <v>27</v>
       </c>
       <c r="K149" t="s">
-        <v>1158</v>
+        <v>1149</v>
       </c>
       <c r="L149" t="s">
         <v>884</v>
@@ -11801,7 +11488,7 @@
         <v>20</v>
       </c>
       <c r="K150" t="s">
-        <v>1159</v>
+        <v>1150</v>
       </c>
       <c r="L150" t="s">
         <v>884</v>
@@ -12000,7 +11687,7 @@
         <v>57</v>
       </c>
       <c r="K155" t="s">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="L155" t="s">
         <v>884</v>
@@ -12041,7 +11728,7 @@
         <v>20</v>
       </c>
       <c r="K156" t="s">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="L156" t="s">
         <v>884</v>
@@ -12082,7 +11769,7 @@
         <v>57</v>
       </c>
       <c r="K157" t="s">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="L157" t="s">
         <v>884</v>
@@ -12161,7 +11848,7 @@
         <v>27</v>
       </c>
       <c r="K159" t="s">
-        <v>1193</v>
+        <v>1183</v>
       </c>
       <c r="L159" t="s">
         <v>884</v>
@@ -12202,7 +11889,7 @@
         <v>27</v>
       </c>
       <c r="K160" t="s">
-        <v>1179</v>
+        <v>1169</v>
       </c>
       <c r="L160" t="s">
         <v>884</v>
@@ -12243,7 +11930,7 @@
         <v>33</v>
       </c>
       <c r="K161" t="s">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="L161" t="s">
         <v>884</v>
@@ -12284,7 +11971,7 @@
         <v>57</v>
       </c>
       <c r="K162" t="s">
-        <v>1165</v>
+        <v>1156</v>
       </c>
       <c r="L162" t="s">
         <v>884</v>
@@ -13351,7 +13038,7 @@
         <v>33</v>
       </c>
       <c r="K190" t="s">
-        <v>1181</v>
+        <v>1171</v>
       </c>
       <c r="L190" t="s">
         <v>1026</v>
@@ -13392,7 +13079,7 @@
         <v>33</v>
       </c>
       <c r="K191" t="s">
-        <v>1182</v>
+        <v>1172</v>
       </c>
       <c r="L191" t="s">
         <v>1026</v>
@@ -13433,7 +13120,7 @@
         <v>57</v>
       </c>
       <c r="K192" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="L192" t="s">
         <v>1026</v>
@@ -13474,7 +13161,7 @@
         <v>27</v>
       </c>
       <c r="K193" t="s">
-        <v>1194</v>
+        <v>1184</v>
       </c>
       <c r="L193" t="s">
         <v>1026</v>
@@ -13515,7 +13202,7 @@
         <v>20</v>
       </c>
       <c r="K194" t="s">
-        <v>1195</v>
+        <v>1185</v>
       </c>
       <c r="L194" t="s">
         <v>1026</v>
@@ -13556,7 +13243,7 @@
         <v>57</v>
       </c>
       <c r="K195" t="s">
-        <v>1196</v>
+        <v>1186</v>
       </c>
       <c r="L195" t="s">
         <v>1026</v>
@@ -13673,7 +13360,7 @@
         <v>27</v>
       </c>
       <c r="K198" t="s">
-        <v>1166</v>
+        <v>1157</v>
       </c>
       <c r="L198" t="s">
         <v>1026</v>
@@ -13714,7 +13401,7 @@
         <v>20</v>
       </c>
       <c r="K199" t="s">
-        <v>1160</v>
+        <v>1151</v>
       </c>
       <c r="L199" t="s">
         <v>1026</v>
@@ -14926,6 +14613,158 @@
       </c>
       <c r="M230" t="s">
         <v>334</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>34</v>
+      </c>
+      <c r="C231" t="s">
+        <v>343</v>
+      </c>
+      <c r="D231" t="s">
+        <v>14</v>
+      </c>
+      <c r="E231" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F231" t="s">
+        <v>443</v>
+      </c>
+      <c r="G231" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H231" t="s">
+        <v>1193</v>
+      </c>
+      <c r="I231" t="s">
+        <v>890</v>
+      </c>
+      <c r="J231" t="s">
+        <v>20</v>
+      </c>
+      <c r="L231" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M231" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>12</v>
+      </c>
+      <c r="C232" t="s">
+        <v>140</v>
+      </c>
+      <c r="D232" t="s">
+        <v>14</v>
+      </c>
+      <c r="E232" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F232" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G232" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H232" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I232" t="s">
+        <v>1199</v>
+      </c>
+      <c r="J232" t="s">
+        <v>27</v>
+      </c>
+      <c r="L232" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M232" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>12</v>
+      </c>
+      <c r="C233" t="s">
+        <v>474</v>
+      </c>
+      <c r="D233" t="s">
+        <v>14</v>
+      </c>
+      <c r="E233" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F233" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G233" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H233" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I233" t="s">
+        <v>660</v>
+      </c>
+      <c r="J233" t="s">
+        <v>20</v>
+      </c>
+      <c r="L233" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M233" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>12</v>
+      </c>
+      <c r="C234" t="s">
+        <v>166</v>
+      </c>
+      <c r="D234" t="s">
+        <v>14</v>
+      </c>
+      <c r="E234" s="7" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F234" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G234" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H234" t="s">
+        <v>1207</v>
+      </c>
+      <c r="I234" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J234" t="s">
+        <v>20</v>
+      </c>
+      <c r="L234" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M234" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
